--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7E948D-7DFA-4528-97CA-EDC39DCA5337}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C954B433-7768-45D8-AEBB-3FE786854C1E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="765">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="767">
   <si>
     <t>1С</t>
   </si>
@@ -2329,6 +2329,12 @@
   </si>
   <si>
     <t>7382  САЛЯМИ МЕЛКОЗЕРНЕНАЯ с/к в/у1/120 8шт.  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>БАЛЫК с/к с/н в/у 1/100 10шт. (7288)</t>
+  </si>
+  <si>
+    <t>БАЛЫК с/к с/н в/у 1/100 10шт.</t>
   </si>
 </sst>
 </file>
@@ -2685,7 +2691,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F488"/>
+  <dimension ref="A1:F489"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" style="2" customWidth="1"/>
@@ -8086,6 +8092,17 @@
         <v>760</v>
       </c>
     </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A489" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B489" s="3">
+        <v>1001223907288</v>
+      </c>
+      <c r="C489" t="s">
+        <v>766</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C488" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C954B433-7768-45D8-AEBB-3FE786854C1E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68EADA45-1575-4F7F-9DB7-D417A3A9BB3C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$488</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$490</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="984" uniqueCount="767">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="768">
   <si>
     <t>1С</t>
   </si>
@@ -2335,6 +2335,9 @@
   </si>
   <si>
     <t>БАЛЫК с/к с/н в/у 1/100 10шт.</t>
+  </si>
+  <si>
+    <t>7288 БАЛЫК с/к с/н в/у 1/100 10шт ОСТАНКИНО</t>
   </si>
 </sst>
 </file>
@@ -2691,7 +2694,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F489"/>
+  <dimension ref="A1:F490"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" style="2" customWidth="1"/>
@@ -8103,8 +8106,19 @@
         <v>766</v>
       </c>
     </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A490" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="B490" s="3">
+        <v>1001223907288</v>
+      </c>
+      <c r="C490" t="s">
+        <v>766</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C488" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
+  <autoFilter ref="A1:C490" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\moduls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68EADA45-1575-4F7F-9DB7-D417A3A9BB3C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0757F952-716C-451D-8A80-2E30D351CA8E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$490</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$498</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="768">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="780">
   <si>
     <t>1С</t>
   </si>
@@ -1107,9 +1107,6 @@
     <t>СЕРВЕЛАТ ПРЕМИУМ в/к в/у</t>
   </si>
   <si>
-    <t>БАЛЫКОВАЯ в/к в/у 0.33кг 8шт.</t>
-  </si>
-  <si>
     <t>БАЛЫКОВАЯ в/к в/у</t>
   </si>
   <si>
@@ -1545,9 +1542,6 @@
     <t>6324 ДОКТОРСКАЯ ГОСТ вар п/о 0.4кг 8шт.  ОСТАНКИНО</t>
   </si>
   <si>
-    <t>ДОКТОРСКАЯ ГОСТ вар п/о 0.4кг 8шт.</t>
-  </si>
-  <si>
     <t>6909 ДЛЯ ДЕТЕЙ сос п/о мгс 0.33кг 8шт.  ОСТАНКИНО</t>
   </si>
   <si>
@@ -1956,9 +1950,6 @@
     <t>7131 БАЛЫКОВАЯ в/к в/у 0.84кг</t>
   </si>
   <si>
-    <t>БАЛЫКОВАЯ в/к в/у 0.84кг</t>
-  </si>
-  <si>
     <t>7146 МРАМОРНАЯ ПРЕМИУМ в/к в/у</t>
   </si>
   <si>
@@ -2292,9 +2283,6 @@
     <t>АРОМАТНАЯ с/к в/у 1/250 8шт.</t>
   </si>
   <si>
-    <t>ротация 04,11,25</t>
-  </si>
-  <si>
     <t>СЕЙЧАС СЕЗОН ПМ вар п/о 0.4кг</t>
   </si>
   <si>
@@ -2322,9 +2310,6 @@
     <t>7255 МЯСНЫЕ С ГОВЯД.ПМ сос п/о мгс 0.4кг 6шт.  ОСТАНКИНО</t>
   </si>
   <si>
-    <t>ротация 01,12,25</t>
-  </si>
-  <si>
     <t>САЛЯМИ МЕЛКОЗЕРНЕНАЯ с/к в/у 1/120 8шт.</t>
   </si>
   <si>
@@ -2338,6 +2323,57 @@
   </si>
   <si>
     <t>7288 БАЛЫК с/к с/н в/у 1/100 10шт ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>6797 С ИНДЕЙКОЙ Папа может вар п/о 0,4кг 8шт. ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>С ИНДЕЙКОЙ Папа может вар п/о 0.4кг 8шт.</t>
+  </si>
+  <si>
+    <t>6925 ВЕТЧ.КЛАССИЧЕСКАЯ в/у 0,6кг 8шт. ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>ВЕТЧ.КЛАССИЧЕСКАЯ в/у 0.6кг 8шт.</t>
+  </si>
+  <si>
+    <t>7059 ШПИКАЧКИ СОЧНЫЕ С БЕК. п/о мгс 0,3кг 60с ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>ШПИКАЧКИ СОЧНЫЕ С БЕК. п/о мгс 0.3кг_60с</t>
+  </si>
+  <si>
+    <t>7461 ДЛЯ ДЕТЕЙ Папа Может сос п/о мгс 0,33кг ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>ДЛЯ ДЕТЕЙ Папа может сос п/о мгс 0.33кг</t>
+  </si>
+  <si>
+    <t>7564 Балыковая в/к в/у Останкино Вес  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>БАЛЫКОВАЯ Останкино в/к в/у</t>
+  </si>
+  <si>
+    <t>БАЛЫКОВАЯ Останкино в/к в/у 0.33кг 8шт.</t>
+  </si>
+  <si>
+    <t>ДОКТОРСКАЯ ГОСТ Останкино вар п/о 0.35кг</t>
+  </si>
+  <si>
+    <t>7371 БРЕСТСКИЕ сос п/о в/у 0,3кг 8шт. ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>БРЕСТСКИЕ сос п/о в/у 0.3кг 8шт.</t>
+  </si>
+  <si>
+    <t>7523 ГОВЯЖЬЯ Папа Может вар п/о 0,4кг 6шт. ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>ГОВЯЖЬЯ Папа может вар п/о 0.4кг 6шт.</t>
+  </si>
+  <si>
+    <t>7539 ДОКТОРСКАЯ ГОСТ вар п/о 0,35кг ОСТАНКИНО</t>
   </si>
 </sst>
 </file>
@@ -2694,7 +2730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F490"/>
+  <dimension ref="A1:F498"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" style="2" customWidth="1"/>
@@ -2790,62 +2826,62 @@
         <v>1001095716865</v>
       </c>
       <c r="C8" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B9" s="3">
         <v>1001095716866</v>
       </c>
       <c r="C9" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B10" s="3">
         <v>1001095716866</v>
       </c>
       <c r="C10" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B11" s="3">
         <v>1001095716866</v>
       </c>
       <c r="C11" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="B12" s="3">
         <v>1001095716866</v>
       </c>
       <c r="C12" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B13" s="3">
         <v>1001095716866</v>
       </c>
       <c r="C13" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -2856,7 +2892,7 @@
         <v>1001095716865</v>
       </c>
       <c r="C14" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -2881,7 +2917,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>18</v>
       </c>
@@ -2892,7 +2928,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
@@ -2903,7 +2939,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>22</v>
       </c>
@@ -2914,7 +2950,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>24</v>
       </c>
@@ -2922,32 +2958,32 @@
         <v>1001015646861</v>
       </c>
       <c r="C20" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B21" s="3">
         <v>1001015706862</v>
       </c>
       <c r="C21" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B22" s="3">
         <v>1001015706862</v>
       </c>
       <c r="C22" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>26</v>
       </c>
@@ -2955,32 +2991,32 @@
         <v>1001015706862</v>
       </c>
       <c r="C23" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B24" s="3">
         <v>1001303987166</v>
       </c>
       <c r="C24" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B25" s="3">
         <v>1001303987166</v>
       </c>
       <c r="C25" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>28</v>
       </c>
@@ -2991,7 +3027,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>30</v>
       </c>
@@ -3002,7 +3038,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>32</v>
       </c>
@@ -3010,35 +3046,32 @@
         <v>1001203117382</v>
       </c>
       <c r="C28" t="s">
-        <v>763</v>
-      </c>
-      <c r="E28" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="B29" s="3">
         <v>1001203117382</v>
       </c>
       <c r="C29" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="B30" s="3">
         <v>1001061973986</v>
       </c>
       <c r="C30" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>33</v>
       </c>
@@ -3046,13 +3079,10 @@
         <v>1001061973986</v>
       </c>
       <c r="C31" t="s">
-        <v>751</v>
-      </c>
-      <c r="E31" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>34</v>
       </c>
@@ -3093,7 +3123,7 @@
         <v>1001060755931</v>
       </c>
       <c r="C35" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3104,7 +3134,7 @@
         <v>1001060755931</v>
       </c>
       <c r="C36" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3137,18 +3167,18 @@
         <v>1001024976829</v>
       </c>
       <c r="C39" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B40" s="3">
         <v>1001084216206</v>
       </c>
       <c r="C40" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -3159,40 +3189,40 @@
         <v>1001084216206</v>
       </c>
       <c r="C41" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="B42" s="3">
         <v>1001022557257</v>
       </c>
       <c r="C42" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B43" s="3">
         <v>1001022557257</v>
       </c>
       <c r="C43" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B44" s="3">
         <v>1001022557257</v>
       </c>
       <c r="C44" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -3203,7 +3233,7 @@
         <v>1001022556069</v>
       </c>
       <c r="C45" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F45" s="3"/>
     </row>
@@ -3248,7 +3278,7 @@
         <v>1001304507236</v>
       </c>
       <c r="C49" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
@@ -3259,18 +3289,18 @@
         <v>1001304507236</v>
       </c>
       <c r="C50" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B51" s="3">
         <v>1001304507236</v>
       </c>
       <c r="C51" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -3286,24 +3316,24 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="B53" s="3">
         <v>1001303637149</v>
       </c>
       <c r="C53" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B54" s="3">
         <v>1001303637149</v>
       </c>
       <c r="C54" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -3314,7 +3344,7 @@
         <v>1001013956426</v>
       </c>
       <c r="C55" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -3594,46 +3624,46 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="B81" s="3">
         <v>1001300387154</v>
       </c>
       <c r="C81" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B82" s="3">
         <v>1001300387154</v>
       </c>
       <c r="C82" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B83" s="3">
         <v>1001303987169</v>
       </c>
       <c r="C83" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B84" s="3">
         <v>1001303987169</v>
       </c>
       <c r="C84" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -3682,7 +3712,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B89" s="3">
         <v>1001303106773</v>
@@ -3693,7 +3723,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B90" s="3">
         <v>1001303106773</v>
@@ -3704,7 +3734,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B91" s="3">
         <v>1001303106773</v>
@@ -3726,7 +3756,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B93" s="3">
         <v>1001012566392</v>
@@ -3748,29 +3778,29 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B95" s="3">
         <v>1001302277173</v>
       </c>
       <c r="C95" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B96" s="3">
         <v>1001302277173</v>
       </c>
       <c r="C96" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B97" s="3">
         <v>1001012426268</v>
@@ -3946,24 +3976,24 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="B113" s="3">
         <v>1001022376955</v>
       </c>
       <c r="C113" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B114" s="3">
         <v>1001022376955</v>
       </c>
       <c r="C114" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -3974,7 +4004,7 @@
         <v>1001022376955</v>
       </c>
       <c r="C115" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -4249,29 +4279,29 @@
         <v>1001012816341</v>
       </c>
       <c r="C140" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B141" s="3">
         <v>1001012816341</v>
       </c>
       <c r="C141" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B142" s="3">
         <v>1001012816341</v>
       </c>
       <c r="C142" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -4282,7 +4312,7 @@
         <v>1001012816341</v>
       </c>
       <c r="C143" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -4320,35 +4350,35 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="B147" s="3">
         <v>1001022656854</v>
       </c>
       <c r="C147" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B148" s="3">
         <v>1001022656854</v>
       </c>
       <c r="C148" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B149" s="3">
         <v>1001022656854</v>
       </c>
       <c r="C149" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -4359,7 +4389,7 @@
         <v>1001022656854</v>
       </c>
       <c r="C150" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -4474,13 +4504,13 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="B161" s="3">
         <v>1001014486159</v>
       </c>
       <c r="C161" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
@@ -4507,7 +4537,7 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B164" s="3">
         <v>1001012426220</v>
@@ -4689,7 +4719,7 @@
         <v>1001035026308</v>
       </c>
       <c r="C180" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
@@ -4749,29 +4779,29 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="B186" s="3">
         <v>1001033856608</v>
       </c>
       <c r="C186" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B187" s="3">
         <v>1001033856608</v>
       </c>
       <c r="C187" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B188" s="3">
         <v>1001033856609</v>
@@ -4799,7 +4829,7 @@
         <v>1001093345495</v>
       </c>
       <c r="C190" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -4837,13 +4867,13 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B194" s="3">
         <v>1001063926780</v>
       </c>
       <c r="C194" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
@@ -5000,7 +5030,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>265</v>
       </c>
@@ -5011,7 +5041,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>268</v>
       </c>
@@ -5022,7 +5052,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>270</v>
       </c>
@@ -5033,7 +5063,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>271</v>
       </c>
@@ -5044,7 +5074,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>272</v>
       </c>
@@ -5055,7 +5085,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>274</v>
       </c>
@@ -5066,7 +5096,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>276</v>
       </c>
@@ -5077,7 +5107,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>279</v>
       </c>
@@ -5088,9 +5118,9 @@
         <v>280</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B217" s="3">
         <v>1001215576586</v>
@@ -5099,7 +5129,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>281</v>
       </c>
@@ -5110,7 +5140,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>283</v>
       </c>
@@ -5121,7 +5151,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>290</v>
       </c>
@@ -5132,7 +5162,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>300</v>
       </c>
@@ -5140,27 +5170,21 @@
         <v>1001016747343</v>
       </c>
       <c r="C221" t="s">
-        <v>753</v>
-      </c>
-      <c r="E221" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B222" s="3">
         <v>1001016747343</v>
       </c>
       <c r="C222" t="s">
-        <v>753</v>
-      </c>
-      <c r="E222" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>291</v>
       </c>
@@ -5168,21 +5192,18 @@
         <v>1001016747343</v>
       </c>
       <c r="C223" t="s">
-        <v>753</v>
-      </c>
-      <c r="E223" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B224" s="3">
         <v>1001016747343</v>
       </c>
       <c r="C224" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
@@ -5248,7 +5269,7 @@
         <v>1001025546822</v>
       </c>
       <c r="C230" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
@@ -5264,7 +5285,7 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="B232" s="3">
         <v>1001024976616</v>
@@ -5297,13 +5318,13 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B235" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C235" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
@@ -5314,7 +5335,7 @@
         <v>1001223296919</v>
       </c>
       <c r="C236" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -5325,29 +5346,29 @@
         <v>1001223296919</v>
       </c>
       <c r="C237" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B238" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C238" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B239" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C239" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -5358,7 +5379,7 @@
         <v>1001223296919</v>
       </c>
       <c r="C240" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
@@ -5506,7 +5527,7 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B254" s="3">
         <v>1001304096792</v>
@@ -5531,32 +5552,32 @@
         <v>346</v>
       </c>
       <c r="B256" s="3">
-        <v>1001303636793</v>
+        <v>1001303637603</v>
       </c>
       <c r="C256" t="s">
-        <v>357</v>
+        <v>773</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B257" s="3">
         <v>1001303636794</v>
       </c>
       <c r="C257" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B258" s="3">
         <v>1001303636794</v>
       </c>
       <c r="C258" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
@@ -5567,7 +5588,7 @@
         <v>1001303636794</v>
       </c>
       <c r="C259" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
@@ -5578,7 +5599,7 @@
         <v>1001302596795</v>
       </c>
       <c r="C260" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
@@ -5589,7 +5610,7 @@
         <v>1001302596796</v>
       </c>
       <c r="C261" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
@@ -5600,18 +5621,18 @@
         <v>1001300456804</v>
       </c>
       <c r="C262" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B263" s="3">
         <v>1001300366806</v>
       </c>
       <c r="C263" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
@@ -5622,7 +5643,7 @@
         <v>1001300366806</v>
       </c>
       <c r="C264" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
@@ -5633,7 +5654,7 @@
         <v>1001300516803</v>
       </c>
       <c r="C265" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
@@ -5644,188 +5665,188 @@
         <v>1001300366807</v>
       </c>
       <c r="C266" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B267" s="3">
         <v>1001300366807</v>
       </c>
       <c r="C267" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B268" s="3">
         <v>1001300516785</v>
       </c>
       <c r="C268" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B269" s="3">
         <v>1001300456787</v>
       </c>
       <c r="C269" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="B270" s="3">
         <v>1001300456787</v>
       </c>
       <c r="C270" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B271" s="3">
         <v>1001300456787</v>
       </c>
       <c r="C271" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B272" s="3">
-        <v>1001303636793</v>
+        <v>1001303637603</v>
       </c>
       <c r="C272" t="s">
-        <v>357</v>
+        <v>773</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B273" s="3">
         <v>1001302596795</v>
       </c>
       <c r="C273" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B274" s="3">
         <v>1001012486332</v>
       </c>
       <c r="C274" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B275" s="3">
         <v>1001012566345</v>
       </c>
       <c r="C275" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B276" s="3">
         <v>1001031076528</v>
       </c>
       <c r="C276" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B277" s="3">
         <v>1001020836761</v>
       </c>
       <c r="C277" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B278" s="3">
         <v>1001020836761</v>
       </c>
       <c r="C278" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B279" s="3">
         <v>1001020836761</v>
       </c>
       <c r="C279" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B280" s="3">
         <v>1001020846764</v>
       </c>
       <c r="C280" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B281" s="3">
         <v>1001020846764</v>
       </c>
       <c r="C281" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B282" s="3">
         <v>1001020846764</v>
       </c>
       <c r="C282" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B283" s="3">
         <v>1001300366790</v>
@@ -5836,7 +5857,7 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B284" s="3">
         <v>1001300366790</v>
@@ -5858,7 +5879,7 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B286" s="3">
         <v>1001304096791</v>
@@ -5869,7 +5890,7 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B287" s="3">
         <v>1001304096791</v>
@@ -5880,161 +5901,161 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B288" s="3">
-        <v>1001303636793</v>
+        <v>1001303637603</v>
       </c>
       <c r="C288" t="s">
-        <v>357</v>
+        <v>773</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B289" s="3">
         <v>1001302596795</v>
       </c>
       <c r="C289" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B290" s="3">
         <v>1001300516803</v>
       </c>
       <c r="C290" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B291" s="3">
         <v>1001300456804</v>
       </c>
       <c r="C291" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B292" s="3">
         <v>1001300366807</v>
       </c>
       <c r="C292" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B293" s="3">
         <v>1001302596796</v>
       </c>
       <c r="C293" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B294" s="3">
         <v>1001023696765</v>
       </c>
       <c r="C294" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B295" s="3">
         <v>1001023696765</v>
       </c>
       <c r="C295" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B296" s="3">
         <v>1001023696765</v>
       </c>
       <c r="C296" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B297" s="3">
         <v>1001023696767</v>
       </c>
       <c r="C297" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B298" s="3">
         <v>1001023696767</v>
       </c>
       <c r="C298" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B299" s="3">
         <v>1001023696767</v>
       </c>
       <c r="C299" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B300" s="3">
         <v>1001024976829</v>
       </c>
       <c r="C300" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B301" s="3">
         <v>1001024976829</v>
       </c>
       <c r="C301" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B302" s="3">
         <v>1001022376722</v>
@@ -6045,35 +6066,35 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B303" s="3">
         <v>1001020846762</v>
       </c>
       <c r="C303" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B304" s="3">
         <v>1001020846762</v>
       </c>
       <c r="C304" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B305" s="3">
         <v>1001020846762</v>
       </c>
       <c r="C305" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -6084,150 +6105,150 @@
         <v>1001022656853</v>
       </c>
       <c r="C306" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B307" s="3">
         <v>1001022656853</v>
       </c>
       <c r="C307" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B308" s="3">
         <v>1001022656948</v>
       </c>
       <c r="C308" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B309" s="3">
         <v>1001022656948</v>
       </c>
       <c r="C309" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B310" s="3">
         <v>1001022656948</v>
       </c>
       <c r="C310" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B311" s="3">
         <v>1001022656852</v>
       </c>
       <c r="C311" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B312" s="3">
         <v>1001020836759</v>
       </c>
       <c r="C312" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B313" s="3">
         <v>1001020836759</v>
       </c>
       <c r="C313" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B314" s="3">
         <v>1001020836759</v>
       </c>
       <c r="C314" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B315" s="3">
         <v>1001023856870</v>
       </c>
       <c r="C315" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B316" s="3">
         <v>1001013956426</v>
       </c>
       <c r="C316" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B317" s="3">
         <v>1001093345495</v>
       </c>
       <c r="C317" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B318" s="3">
         <v>1001022656868</v>
       </c>
       <c r="C318" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B319" s="3">
         <v>1001022656868</v>
       </c>
       <c r="C319" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
@@ -6238,7 +6259,7 @@
         <v>1001034065698</v>
       </c>
       <c r="C320" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
@@ -6249,128 +6270,128 @@
         <v>1001034065698</v>
       </c>
       <c r="C321" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B322" s="3">
         <v>1001034065698</v>
       </c>
       <c r="C322" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B323" s="3">
         <v>1001034065698</v>
       </c>
       <c r="C323" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B324" s="3">
         <v>1001084216206</v>
       </c>
       <c r="C324" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B325" s="3">
         <v>1001015646861</v>
       </c>
       <c r="C325" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B326" s="3">
         <v>1001015646861</v>
       </c>
       <c r="C326" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B327" s="3">
         <v>1001025176768</v>
       </c>
       <c r="C327" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B328" s="3">
         <v>1001025176768</v>
       </c>
       <c r="C328" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B329" s="3">
         <v>1001025176768</v>
       </c>
       <c r="C329" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B330" s="3">
         <v>1001025486770</v>
       </c>
       <c r="C330" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B331" s="3">
         <v>1001025486770</v>
       </c>
       <c r="C331" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B332" s="3">
         <v>1001025486770</v>
       </c>
       <c r="C332" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
@@ -6381,29 +6402,29 @@
         <v>1001012816340</v>
       </c>
       <c r="C333" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B334" s="3">
         <v>1001012816340</v>
       </c>
       <c r="C334" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B335" s="3">
         <v>1001012816340</v>
       </c>
       <c r="C335" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
@@ -6414,1327 +6435,1321 @@
         <v>1001203146834</v>
       </c>
       <c r="C336" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B337" s="3">
         <v>1001203146834</v>
       </c>
       <c r="C337" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B338" s="3">
         <v>1001203146834</v>
       </c>
       <c r="C338" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B339" s="3">
         <v>1001203146834</v>
       </c>
       <c r="C339" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B340" s="3">
         <v>1001300456788</v>
       </c>
       <c r="C340" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B341" s="3">
         <v>1001300516786</v>
       </c>
       <c r="C341" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="B342" s="3">
         <v>1001092436495</v>
       </c>
       <c r="C342" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B343" s="3">
         <v>1001092436495</v>
       </c>
       <c r="C343" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B344" s="3">
         <v>1001092436495</v>
       </c>
       <c r="C344" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B345" s="3">
         <v>1001025526901</v>
       </c>
       <c r="C345" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B346" s="3">
         <v>1001025546931</v>
       </c>
       <c r="C346" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B347" s="3">
-        <v>1001010016324</v>
+        <v>1001010017539</v>
       </c>
       <c r="C347" t="s">
-        <v>503</v>
+        <v>774</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="B348" s="3">
-        <v>1001010016324</v>
+        <v>1001010017539</v>
       </c>
       <c r="C348" t="s">
-        <v>503</v>
+        <v>774</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B349" s="3">
-        <v>1001010016324</v>
+        <v>1001010017539</v>
       </c>
       <c r="C349" t="s">
-        <v>503</v>
+        <v>774</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>506</v>
+        <v>779</v>
       </c>
       <c r="B350" s="3">
-        <v>1001025766909</v>
+        <v>1001010017539</v>
       </c>
       <c r="C350" t="s">
-        <v>505</v>
+        <v>774</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>540</v>
+        <v>504</v>
       </c>
       <c r="B351" s="3">
         <v>1001025766909</v>
       </c>
       <c r="C351" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>504</v>
+        <v>538</v>
       </c>
       <c r="B352" s="3">
         <v>1001025766909</v>
       </c>
       <c r="C352" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>538</v>
+        <v>502</v>
       </c>
       <c r="B353" s="3">
-        <v>1001010014558</v>
+        <v>1001025766909</v>
       </c>
       <c r="C353" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>507</v>
+        <v>536</v>
       </c>
       <c r="B354" s="3">
         <v>1001010014558</v>
       </c>
       <c r="C354" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>533</v>
+        <v>505</v>
       </c>
       <c r="B355" s="3">
-        <v>1001012596802</v>
+        <v>1001010014558</v>
       </c>
       <c r="C355" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>542</v>
+        <v>531</v>
       </c>
       <c r="B356" s="3">
         <v>1001012596802</v>
       </c>
       <c r="C356" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>510</v>
+        <v>540</v>
       </c>
       <c r="B357" s="3">
         <v>1001012596802</v>
       </c>
       <c r="C357" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>528</v>
+        <v>508</v>
       </c>
       <c r="B358" s="3">
-        <v>1001012596801</v>
+        <v>1001012596802</v>
       </c>
       <c r="C358" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
-        <v>541</v>
+        <v>526</v>
       </c>
       <c r="B359" s="3">
         <v>1001012596801</v>
       </c>
       <c r="C359" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="B360" s="3">
         <v>1001012596801</v>
       </c>
       <c r="C360" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="B361" s="3">
-        <v>1001062353684</v>
+        <v>1001012596801</v>
       </c>
       <c r="C361" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B362" s="3">
-        <v>1001010014555</v>
+        <v>1001062353684</v>
       </c>
       <c r="C362" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="B363" s="3">
-        <v>1001083424691</v>
+        <v>1001010014555</v>
       </c>
       <c r="C363" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B364" s="3">
-        <v>1001190765679</v>
+        <v>1001083424691</v>
       </c>
       <c r="C364" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="B365" s="3">
-        <v>1001085636200</v>
+        <v>1001190765679</v>
       </c>
       <c r="C365" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="B366" s="3">
-        <v>1001020836253</v>
+        <v>1001085636200</v>
       </c>
       <c r="C366" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="B367" s="3">
-        <v>1001084226492</v>
+        <v>1001020836253</v>
       </c>
       <c r="C367" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B368" s="3">
-        <v>1001223296921</v>
+        <v>1001084226492</v>
       </c>
       <c r="C368" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B369" s="3">
-        <v>1001053944786</v>
+        <v>1001223296921</v>
       </c>
       <c r="C369" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="B370" s="3">
-        <v>1001010016839</v>
+        <v>1001053944786</v>
       </c>
       <c r="C370" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="B371" s="3">
-        <v>1001023857038</v>
+        <v>1001010016839</v>
       </c>
       <c r="C371" t="s">
-        <v>584</v>
+        <v>535</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="B372" s="3">
-        <v>1001040434903</v>
+        <v>1001023857038</v>
       </c>
       <c r="C372" t="s">
-        <v>545</v>
+        <v>582</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="B373" s="3">
-        <v>1001080216842</v>
+        <v>1001040434903</v>
       </c>
       <c r="C373" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>560</v>
+        <v>545</v>
       </c>
       <c r="B374" s="3">
-        <v>1001022466951</v>
+        <v>1001080216842</v>
       </c>
       <c r="C374" t="s">
-        <v>561</v>
+        <v>546</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="B375" s="3">
         <v>1001022466951</v>
       </c>
       <c r="C375" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="B376" s="3">
-        <v>1001035276653</v>
+        <v>1001022466951</v>
       </c>
       <c r="C376" t="s">
-        <v>569</v>
+        <v>559</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="B377" s="3">
-        <v>1001062353680</v>
+        <v>1001035276653</v>
       </c>
       <c r="C377" t="s">
-        <v>574</v>
+        <v>567</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B378" s="3">
-        <v>1001061971146</v>
+        <v>1001062353680</v>
       </c>
       <c r="C378" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="B379" s="3">
-        <v>1001225636201</v>
+        <v>1001061971146</v>
       </c>
       <c r="C379" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="B380" s="3">
-        <v>1001095227035</v>
+        <v>1001225636201</v>
       </c>
       <c r="C380" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B381" s="3">
-        <v>1001023857038</v>
+        <v>1001095227035</v>
       </c>
       <c r="C381" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="B382" s="3">
-        <v>1001025027040</v>
+        <v>1001023857038</v>
       </c>
       <c r="C382" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="B383" s="3">
-        <v>1001223297103</v>
+        <v>1001025027040</v>
       </c>
       <c r="C383" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B384" s="3">
         <v>1001223297103</v>
       </c>
       <c r="C384" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B385" s="3">
         <v>1001223297103</v>
       </c>
       <c r="C385" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>609</v>
+        <v>586</v>
       </c>
       <c r="B386" s="3">
-        <v>1001010032675</v>
+        <v>1001223297103</v>
       </c>
       <c r="C386" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>590</v>
+        <v>607</v>
       </c>
       <c r="B387" s="3">
         <v>1001010032675</v>
       </c>
       <c r="C387" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>614</v>
+        <v>588</v>
       </c>
       <c r="B388" s="3">
-        <v>1001035937001</v>
+        <v>1001010032675</v>
       </c>
       <c r="C388" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>592</v>
+        <v>612</v>
       </c>
       <c r="B389" s="3">
         <v>1001035937001</v>
       </c>
       <c r="C389" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
-        <v>615</v>
+        <v>590</v>
       </c>
       <c r="B390" s="3">
-        <v>1001084217090</v>
+        <v>1001035937001</v>
       </c>
       <c r="C390" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
-        <v>594</v>
+        <v>613</v>
       </c>
       <c r="B391" s="3">
         <v>1001084217090</v>
       </c>
       <c r="C391" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
-        <v>616</v>
+        <v>592</v>
       </c>
       <c r="B392" s="3">
-        <v>1001022377066</v>
+        <v>1001084217090</v>
       </c>
       <c r="C392" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
-        <v>596</v>
+        <v>614</v>
       </c>
       <c r="B393" s="3">
         <v>1001022377066</v>
       </c>
       <c r="C393" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
-        <v>617</v>
+        <v>594</v>
       </c>
       <c r="B394" s="3">
-        <v>1001022467080</v>
+        <v>1001022377066</v>
       </c>
       <c r="C394" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
-        <v>598</v>
+        <v>615</v>
       </c>
       <c r="B395" s="3">
         <v>1001022467080</v>
       </c>
       <c r="C395" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
-        <v>618</v>
+        <v>596</v>
       </c>
       <c r="B396" s="3">
-        <v>1001025507255</v>
+        <v>1001022467080</v>
       </c>
       <c r="C396" t="s">
-        <v>754</v>
-      </c>
-      <c r="E396" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
-        <v>600</v>
+        <v>616</v>
       </c>
       <c r="B397" s="3">
         <v>1001025507255</v>
       </c>
       <c r="C397" t="s">
-        <v>754</v>
-      </c>
-      <c r="E397" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
-        <v>761</v>
+        <v>598</v>
       </c>
       <c r="B398" s="3">
         <v>1001025507255</v>
       </c>
       <c r="C398" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
-        <v>621</v>
+        <v>757</v>
       </c>
       <c r="B399" s="3">
-        <v>1001022657075</v>
+        <v>1001025507255</v>
       </c>
       <c r="C399" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
-        <v>601</v>
+        <v>619</v>
       </c>
       <c r="B400" s="3">
         <v>1001022657075</v>
       </c>
       <c r="C400" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
-        <v>619</v>
+        <v>599</v>
       </c>
       <c r="B401" s="3">
-        <v>1001022467082</v>
+        <v>1001022657075</v>
       </c>
       <c r="C401" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
-        <v>603</v>
+        <v>617</v>
       </c>
       <c r="B402" s="3">
         <v>1001022467082</v>
       </c>
       <c r="C402" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
-        <v>620</v>
+        <v>601</v>
       </c>
       <c r="B403" s="3">
-        <v>1001022377070</v>
+        <v>1001022467082</v>
       </c>
       <c r="C403" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
-        <v>605</v>
+        <v>618</v>
       </c>
       <c r="B404" s="3">
         <v>1001022377070</v>
       </c>
       <c r="C404" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
-        <v>622</v>
+        <v>603</v>
       </c>
       <c r="B405" s="3">
-        <v>1001022657073</v>
+        <v>1001022377070</v>
       </c>
       <c r="C405" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
-        <v>607</v>
+        <v>620</v>
       </c>
       <c r="B406" s="3">
         <v>1001022657073</v>
       </c>
       <c r="C406" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
-        <v>633</v>
+        <v>605</v>
       </c>
       <c r="B407" s="3">
-        <v>1001010027126</v>
+        <v>1001022657073</v>
       </c>
       <c r="C407" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
-        <v>610</v>
+        <v>631</v>
       </c>
       <c r="B408" s="3">
         <v>1001010027126</v>
       </c>
       <c r="C408" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="B409" s="3">
-        <v>1001010027125</v>
+        <v>1001010027126</v>
       </c>
       <c r="C409" t="s">
-        <v>613</v>
+        <v>609</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
-        <v>634</v>
+        <v>610</v>
       </c>
       <c r="B410" s="3">
         <v>1001010027125</v>
       </c>
       <c r="C410" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
-        <v>657</v>
+        <v>632</v>
       </c>
       <c r="B411" s="3">
-        <v>1001016366888</v>
+        <v>1001010027125</v>
       </c>
       <c r="C411" t="s">
-        <v>636</v>
+        <v>611</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
-        <v>635</v>
+        <v>654</v>
       </c>
       <c r="B412" s="3">
         <v>1001016366888</v>
       </c>
       <c r="C412" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>658</v>
+        <v>633</v>
       </c>
       <c r="B413" s="3">
-        <v>1001300367133</v>
+        <v>1001016366888</v>
       </c>
       <c r="C413" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
-        <v>637</v>
+        <v>655</v>
       </c>
       <c r="B414" s="3">
         <v>1001300367133</v>
       </c>
       <c r="C414" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>656</v>
+        <v>635</v>
       </c>
       <c r="B415" s="3">
-        <v>1001303637131</v>
+        <v>1001300367133</v>
       </c>
       <c r="C415" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
-        <v>639</v>
+        <v>653</v>
       </c>
       <c r="B416" s="3">
-        <v>1001303637131</v>
+        <v>1001303637564</v>
       </c>
       <c r="C416" t="s">
-        <v>640</v>
+        <v>772</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
-        <v>659</v>
+        <v>637</v>
       </c>
       <c r="B417" s="3">
-        <v>1001304527146</v>
+        <v>1001303637564</v>
       </c>
       <c r="C417" t="s">
-        <v>642</v>
+        <v>772</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
-        <v>641</v>
+        <v>656</v>
       </c>
       <c r="B418" s="3">
         <v>1001304527146</v>
       </c>
       <c r="C418" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
-        <v>654</v>
+        <v>638</v>
       </c>
       <c r="B419" s="3">
-        <v>1001300517134</v>
+        <v>1001304527146</v>
       </c>
       <c r="C419" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
-        <v>643</v>
+        <v>651</v>
       </c>
       <c r="B420" s="3">
         <v>1001300517134</v>
       </c>
       <c r="C420" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>645</v>
+        <v>640</v>
       </c>
       <c r="B421" s="3">
-        <v>1001300457135</v>
+        <v>1001300517134</v>
       </c>
       <c r="C421" t="s">
-        <v>646</v>
+        <v>641</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="B422" s="3">
-        <v>1001304527144</v>
+        <v>1001300457135</v>
       </c>
       <c r="C422" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
       <c r="B423" s="3">
         <v>1001304527144</v>
       </c>
       <c r="C423" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
-        <v>679</v>
+        <v>652</v>
       </c>
       <c r="B424" s="3">
-        <v>1001081596620</v>
+        <v>1001304527144</v>
       </c>
       <c r="C424" t="s">
-        <v>661</v>
+        <v>645</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>662</v>
+        <v>676</v>
       </c>
       <c r="B425" s="3">
         <v>1001081596620</v>
       </c>
       <c r="C425" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
-        <v>684</v>
+        <v>659</v>
       </c>
       <c r="B426" s="3">
-        <v>1001085637187</v>
+        <v>1001081596620</v>
       </c>
       <c r="C426" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>664</v>
+        <v>681</v>
       </c>
       <c r="B427" s="3">
         <v>1001085637187</v>
       </c>
       <c r="C427" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>683</v>
+        <v>661</v>
       </c>
       <c r="B428" s="3">
-        <v>1001015676877</v>
+        <v>1001085637187</v>
       </c>
       <c r="C428" t="s">
-        <v>665</v>
+        <v>660</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>666</v>
+        <v>680</v>
       </c>
       <c r="B429" s="3">
         <v>1001015676877</v>
       </c>
       <c r="C429" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>686</v>
+        <v>663</v>
       </c>
       <c r="B430" s="3">
-        <v>1001015686878</v>
+        <v>1001015676877</v>
       </c>
       <c r="C430" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
-        <v>668</v>
+        <v>683</v>
       </c>
       <c r="B431" s="3">
         <v>1001015686878</v>
       </c>
       <c r="C431" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="B432" s="3">
-        <v>1001302277232</v>
+        <v>1001015686878</v>
       </c>
       <c r="C432" t="s">
-        <v>672</v>
+        <v>664</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="B433" s="3">
-        <v>1001304497237</v>
+        <v>1001302277232</v>
       </c>
       <c r="C433" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B434" s="3">
-        <v>1001303107241</v>
+        <v>1001304497237</v>
       </c>
       <c r="C434" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
-        <v>677</v>
+        <v>668</v>
       </c>
       <c r="B435" s="3">
-        <v>1002162216872</v>
+        <v>1001303107241</v>
       </c>
       <c r="C435" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
-        <v>685</v>
+        <v>674</v>
       </c>
       <c r="B436" s="3">
         <v>1002162216872</v>
       </c>
       <c r="C436" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
-        <v>700</v>
+        <v>682</v>
       </c>
       <c r="B437" s="3">
-        <v>1001063237147</v>
+        <v>1002162216872</v>
       </c>
       <c r="C437" t="s">
-        <v>692</v>
+        <v>675</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
-        <v>687</v>
+        <v>697</v>
       </c>
       <c r="B438" s="3">
         <v>1001063237147</v>
       </c>
       <c r="C438" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
-        <v>699</v>
+        <v>684</v>
       </c>
       <c r="B439" s="3">
-        <v>1001063097227</v>
+        <v>1001063237147</v>
       </c>
       <c r="C439" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="B440" s="3">
         <v>1001063097227</v>
       </c>
       <c r="C440" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
-        <v>697</v>
+        <v>685</v>
       </c>
       <c r="B441" s="3">
-        <v>1001066537225</v>
+        <v>1001063097227</v>
       </c>
       <c r="C441" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="B442" s="3">
         <v>1001066537225</v>
       </c>
       <c r="C442" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
       <c r="B443" s="3">
-        <v>1001066527226</v>
+        <v>1001066537225</v>
       </c>
       <c r="C443" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
-        <v>690</v>
+        <v>695</v>
       </c>
       <c r="B444" s="3">
         <v>1001066527226</v>
       </c>
       <c r="C444" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="B445" s="3">
-        <v>1001066547228</v>
+        <v>1001066527226</v>
       </c>
       <c r="C445" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
-        <v>707</v>
+        <v>688</v>
       </c>
       <c r="B446" s="3">
-        <v>1001063237229</v>
+        <v>1001066547228</v>
       </c>
       <c r="C446" t="s">
-        <v>704</v>
+        <v>693</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="B447" s="3">
         <v>1001063237229</v>
       </c>
       <c r="C447" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="B448" s="3">
-        <v>1001063237150</v>
+        <v>1001063237229</v>
       </c>
       <c r="C448" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="B449" s="3">
         <v>1001063237150</v>
       </c>
       <c r="C449" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="B450" s="3">
-        <v>1001022467276</v>
+        <v>1001063237150</v>
       </c>
       <c r="C450" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
-        <v>708</v>
+        <v>700</v>
       </c>
       <c r="B451" s="3">
         <v>1001022467276</v>
       </c>
       <c r="C451" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
-        <v>484</v>
+        <v>705</v>
       </c>
       <c r="B452" s="3">
-        <v>1001022556837</v>
+        <v>1001022467276</v>
       </c>
       <c r="C452" t="s">
-        <v>485</v>
+        <v>703</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>730</v>
+        <v>483</v>
       </c>
       <c r="B453" s="3">
         <v>1001022556837</v>
       </c>
       <c r="C453" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="B454" s="5">
+        <v>727</v>
+      </c>
+      <c r="B454" s="3">
         <v>1001022556837</v>
       </c>
-      <c r="C454" s="6" t="s">
-        <v>485</v>
+      <c r="C454" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="B455" s="3">
-        <v>1001205376221</v>
-      </c>
-      <c r="C455" t="s">
-        <v>179</v>
+        <v>708</v>
+      </c>
+      <c r="B455" s="5">
+        <v>1001022556837</v>
+      </c>
+      <c r="C455" s="6" t="s">
+        <v>484</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
-        <v>728</v>
+        <v>181</v>
       </c>
       <c r="B456" s="3">
         <v>1001205376221</v>
@@ -7745,95 +7760,95 @@
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="B457" s="5">
+        <v>725</v>
+      </c>
+      <c r="B457" s="3">
         <v>1001205376221</v>
       </c>
-      <c r="C457" s="6" t="s">
+      <c r="C457" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="B458" s="3">
-        <v>1001214196459</v>
-      </c>
-      <c r="C458" t="s">
-        <v>494</v>
+        <v>709</v>
+      </c>
+      <c r="B458" s="5">
+        <v>1001205376221</v>
+      </c>
+      <c r="C458" s="6" t="s">
+        <v>179</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
-        <v>725</v>
+        <v>492</v>
       </c>
       <c r="B459" s="3">
         <v>1001214196459</v>
       </c>
       <c r="C459" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="B460" s="5">
+        <v>722</v>
+      </c>
+      <c r="B460" s="3">
         <v>1001214196459</v>
       </c>
-      <c r="C460" s="6" t="s">
-        <v>494</v>
+      <c r="C460" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="B461" s="5">
-        <v>1001010106325</v>
+        <v>1001214196459</v>
       </c>
       <c r="C461" s="6" t="s">
-        <v>51</v>
+        <v>493</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>726</v>
+        <v>712</v>
       </c>
       <c r="B462" s="5">
-        <v>1001013957231</v>
+        <v>1001010106325</v>
       </c>
       <c r="C462" s="6" t="s">
-        <v>722</v>
+        <v>51</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="B463" s="5">
         <v>1001013957231</v>
       </c>
       <c r="C463" s="6" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B464" s="3">
-        <v>1001220286279</v>
-      </c>
-      <c r="C464" t="s">
-        <v>47</v>
+        <v>713</v>
+      </c>
+      <c r="B464" s="5">
+        <v>1001013957231</v>
+      </c>
+      <c r="C464" s="6" t="s">
+        <v>719</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
-        <v>732</v>
+        <v>46</v>
       </c>
       <c r="B465" s="3">
         <v>1001220286279</v>
@@ -7844,281 +7859,369 @@
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
-        <v>717</v>
-      </c>
-      <c r="B466" s="5">
+        <v>729</v>
+      </c>
+      <c r="B466" s="3">
         <v>1001220286279</v>
       </c>
-      <c r="C466" s="6" t="s">
+      <c r="C466" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
-        <v>727</v>
+        <v>714</v>
       </c>
       <c r="B467" s="5">
-        <v>1001223297092</v>
+        <v>1001220286279</v>
       </c>
       <c r="C467" s="6" t="s">
-        <v>723</v>
+        <v>47</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
-        <v>718</v>
+        <v>724</v>
       </c>
       <c r="B468" s="5">
         <v>1001223297092</v>
       </c>
       <c r="C468" s="6" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="B469" s="3">
-        <v>1001020836724</v>
-      </c>
-      <c r="C469" t="s">
-        <v>580</v>
+        <v>715</v>
+      </c>
+      <c r="B469" s="5">
+        <v>1001223297092</v>
+      </c>
+      <c r="C469" s="6" t="s">
+        <v>720</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
-        <v>729</v>
+        <v>577</v>
       </c>
       <c r="B470" s="3">
         <v>1001020836724</v>
       </c>
       <c r="C470" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
-        <v>719</v>
-      </c>
-      <c r="B471" s="5">
+        <v>726</v>
+      </c>
+      <c r="B471" s="3">
         <v>1001020836724</v>
       </c>
-      <c r="C471" s="6" t="s">
-        <v>580</v>
+      <c r="C471" t="s">
+        <v>578</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
-        <v>731</v>
+        <v>716</v>
       </c>
       <c r="B472" s="5">
-        <v>1001062475707</v>
+        <v>1001020836724</v>
       </c>
       <c r="C472" s="6" t="s">
-        <v>724</v>
+        <v>578</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="B473" s="5">
         <v>1001062475707</v>
       </c>
       <c r="C473" s="6" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B474" s="5">
+        <v>1001062475707</v>
+      </c>
+      <c r="C474" s="6" t="s">
         <v>721</v>
-      </c>
-      <c r="B474" s="5">
-        <v>1001033856609</v>
-      </c>
-      <c r="C474" s="6" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="B475" s="3">
+        <v>718</v>
+      </c>
+      <c r="B475" s="5">
+        <v>1001033856609</v>
+      </c>
+      <c r="C475" s="6" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A476" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="B476" s="3">
         <v>1001025767284</v>
       </c>
-      <c r="C475" s="6" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="476" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A476" s="7" t="s">
-        <v>735</v>
-      </c>
-      <c r="B476" s="5">
-        <v>1001301777332</v>
-      </c>
       <c r="C476" s="6" t="s">
-        <v>741</v>
+        <v>731</v>
       </c>
     </row>
     <row r="477" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A477" s="7" t="s">
-        <v>749</v>
+        <v>732</v>
       </c>
       <c r="B477" s="5">
         <v>1001301777332</v>
       </c>
       <c r="C477" s="6" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="478" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A478" s="7" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B478" s="5">
-        <v>1001303987333</v>
+        <v>1001301777332</v>
       </c>
       <c r="C478" s="6" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
     </row>
     <row r="479" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A479" s="7" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
       <c r="B479" s="5">
         <v>1001303987333</v>
       </c>
       <c r="C479" s="6" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
     </row>
     <row r="480" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A480" s="7" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="B480" s="5">
-        <v>1001012426220</v>
+        <v>1001303987333</v>
       </c>
       <c r="C480" s="6" t="s">
-        <v>193</v>
+        <v>739</v>
       </c>
     </row>
     <row r="481" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A481" s="7" t="s">
-        <v>748</v>
+        <v>734</v>
       </c>
       <c r="B481" s="5">
-        <v>1001300387157</v>
+        <v>1001012426220</v>
       </c>
       <c r="C481" s="6" t="s">
-        <v>743</v>
+        <v>193</v>
       </c>
     </row>
     <row r="482" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A482" s="7" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="B482" s="5">
         <v>1001300387157</v>
       </c>
       <c r="C482" s="6" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
     </row>
     <row r="483" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A483" s="7" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="B483" s="5">
-        <v>1001220226208</v>
+        <v>1001300387157</v>
       </c>
       <c r="C483" s="6" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
     </row>
     <row r="484" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A484" s="7" t="s">
-        <v>746</v>
+        <v>736</v>
       </c>
       <c r="B484" s="5">
         <v>1001220226208</v>
       </c>
       <c r="C484" s="6" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
     </row>
     <row r="485" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A485" s="7" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="B485" s="5">
-        <v>1001063656967</v>
+        <v>1001220226208</v>
       </c>
       <c r="C485" s="6" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A486" s="2" t="s">
-        <v>747</v>
+        <v>741</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A486" s="7" t="s">
+        <v>737</v>
       </c>
       <c r="B486" s="5">
         <v>1001063656967</v>
       </c>
       <c r="C486" s="6" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
     </row>
     <row r="487" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="B487" s="3">
-        <v>1001065616832</v>
-      </c>
-      <c r="C487" t="s">
-        <v>758</v>
+        <v>744</v>
+      </c>
+      <c r="B487" s="5">
+        <v>1001063656967</v>
+      </c>
+      <c r="C487" s="6" t="s">
+        <v>742</v>
       </c>
     </row>
     <row r="488" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
       <c r="B488" s="3">
-        <v>1001060677299</v>
+        <v>1001065616832</v>
       </c>
       <c r="C488" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
-        <v>765</v>
+        <v>755</v>
       </c>
       <c r="B489" s="3">
-        <v>1001223907288</v>
+        <v>1001060677299</v>
       </c>
       <c r="C489" t="s">
-        <v>766</v>
+        <v>756</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="B490" s="3">
         <v>1001223907288</v>
       </c>
       <c r="C490" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A491" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="B491" s="3">
+        <v>1001223907288</v>
+      </c>
+      <c r="C491" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A492" s="2" t="s">
+        <v>763</v>
+      </c>
+      <c r="B492" s="3">
+        <v>1001015026797</v>
+      </c>
+      <c r="C492" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A493" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B493" s="3">
+        <v>1001095226925</v>
+      </c>
+      <c r="C493" t="s">
         <v>766</v>
       </c>
     </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A494" s="2" t="s">
+        <v>767</v>
+      </c>
+      <c r="B494" s="3">
+        <v>1001035277059</v>
+      </c>
+      <c r="C494" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A495" s="2" t="s">
+        <v>769</v>
+      </c>
+      <c r="B495" s="3">
+        <v>1001025767461</v>
+      </c>
+      <c r="C495" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A496" s="2" t="s">
+        <v>771</v>
+      </c>
+      <c r="B496" s="3">
+        <v>1001303637564</v>
+      </c>
+      <c r="C496" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A497" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="B497" s="3">
+        <v>1001026947371</v>
+      </c>
+      <c r="C497" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A498" s="2" t="s">
+        <v>777</v>
+      </c>
+      <c r="B498" s="3">
+        <v>1001012427523</v>
+      </c>
+      <c r="C498" t="s">
+        <v>778</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C490" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
+  <autoFilter ref="A1:C498" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0757F952-716C-451D-8A80-2E30D351CA8E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F5E3BE-F82B-4E36-BB73-7C69CA93D9FA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,9 +16,9 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$498</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$501</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="780">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="784">
   <si>
     <t>1С</t>
   </si>
@@ -204,9 +204,6 @@
     <t>6353 ЭКСТРА Папа может вар п/о 0.4кг 8шт.  ОСТАНКИНО</t>
   </si>
   <si>
-    <t>ЭКСТРА Папа может вар п/о 0.4кг 8шт.</t>
-  </si>
-  <si>
     <t>СЕРВЕЛАТ КАРЕЛЬСКИЙ ПМ в/к в/у 0.28кг</t>
   </si>
   <si>
@@ -888,9 +885,6 @@
     <t>6470 ВЕТЧ.МРАМОРНАЯ в/у_45с  ОСТАНКИНО</t>
   </si>
   <si>
-    <t xml:space="preserve">ВЕТЧ.МРАМОРНАЯ в/у_45с </t>
-  </si>
-  <si>
     <t>СЛИВОЧНЫЕ ПМ сос п/о мгс 0.41кг 10шт.</t>
   </si>
   <si>
@@ -2374,6 +2368,24 @@
   </si>
   <si>
     <t>7539 ДОКТОРСКАЯ ГОСТ вар п/о 0,35кг ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>ЭКСТРА Папа может вар п/о 0.4кг 8шт_195к</t>
+  </si>
+  <si>
+    <t>6470 ВЕТЧ.МРАМОРНАЯ в/у_45с  Останкино</t>
+  </si>
+  <si>
+    <t>ВЕТЧ.МРАМОРНАЯ в/у_45с</t>
+  </si>
+  <si>
+    <t>7083 СЛИВОЧНЫЕ ПМ сос п/о мгс 1.5*4_А_50с  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>СЛИВОЧНЫЕ ПМ сос п/о мгс 1.5*4_А_50с</t>
+  </si>
+  <si>
+    <t>7603 БАЛЫКОВАЯ в/к в/у 0.33кг 8шт. ОСТАНКИНО</t>
   </si>
 </sst>
 </file>
@@ -2730,7 +2742,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F498"/>
+  <dimension ref="A1:F501"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" style="2" customWidth="1"/>
@@ -2820,68 +2832,68 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B8" s="3">
         <v>1001095716865</v>
       </c>
       <c r="C8" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B9" s="3">
         <v>1001095716866</v>
       </c>
       <c r="C9" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B10" s="3">
         <v>1001095716866</v>
       </c>
       <c r="C10" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B11" s="3">
         <v>1001095716866</v>
       </c>
       <c r="C11" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="B12" s="3">
         <v>1001095716866</v>
       </c>
       <c r="C12" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B13" s="3">
         <v>1001095716866</v>
       </c>
       <c r="C13" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -2892,12 +2904,12 @@
         <v>1001095716865</v>
       </c>
       <c r="C14" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B15" s="3">
         <v>1001092446756</v>
@@ -2958,29 +2970,29 @@
         <v>1001015646861</v>
       </c>
       <c r="C20" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B21" s="3">
         <v>1001015706862</v>
       </c>
       <c r="C21" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B22" s="3">
         <v>1001015706862</v>
       </c>
       <c r="C22" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -2991,29 +3003,29 @@
         <v>1001015706862</v>
       </c>
       <c r="C23" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B24" s="3">
         <v>1001303987166</v>
       </c>
       <c r="C24" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B25" s="3">
         <v>1001303987166</v>
       </c>
       <c r="C25" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -3046,29 +3058,29 @@
         <v>1001203117382</v>
       </c>
       <c r="C28" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B29" s="3">
         <v>1001203117382</v>
       </c>
       <c r="C29" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B30" s="3">
         <v>1001061973986</v>
       </c>
       <c r="C30" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -3079,7 +3091,7 @@
         <v>1001061973986</v>
       </c>
       <c r="C31" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -3117,13 +3129,13 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="B35" s="3">
         <v>1001060755931</v>
       </c>
       <c r="C35" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3134,7 +3146,7 @@
         <v>1001060755931</v>
       </c>
       <c r="C36" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3167,18 +3179,18 @@
         <v>1001024976829</v>
       </c>
       <c r="C39" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="B40" s="3">
         <v>1001084216206</v>
       </c>
       <c r="C40" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -3189,40 +3201,40 @@
         <v>1001084216206</v>
       </c>
       <c r="C41" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B42" s="3">
         <v>1001022557257</v>
       </c>
       <c r="C42" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B43" s="3">
         <v>1001022557257</v>
       </c>
       <c r="C43" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B44" s="3">
         <v>1001022557257</v>
       </c>
       <c r="C44" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -3233,7 +3245,7 @@
         <v>1001022556069</v>
       </c>
       <c r="C45" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F45" s="3"/>
     </row>
@@ -3264,488 +3276,488 @@
         <v>55</v>
       </c>
       <c r="B48" s="3">
-        <v>1001012506353</v>
+        <v>1001012507632</v>
       </c>
       <c r="C48" t="s">
-        <v>56</v>
+        <v>778</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B49" s="3">
         <v>1001304507236</v>
       </c>
       <c r="C49" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B50" s="3">
         <v>1001304507236</v>
       </c>
       <c r="C50" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B51" s="3">
         <v>1001304507236</v>
       </c>
       <c r="C51" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B52" s="3">
         <v>1001303056692</v>
       </c>
       <c r="C52" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B53" s="3">
         <v>1001303637149</v>
       </c>
       <c r="C53" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B54" s="3">
         <v>1001303637149</v>
       </c>
       <c r="C54" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B55" s="3">
         <v>1001013956426</v>
       </c>
       <c r="C55" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B56" s="3">
         <v>1001024636438</v>
       </c>
       <c r="C56" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B57" s="3">
         <v>1001234146448</v>
       </c>
       <c r="C57" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B58" s="3">
         <v>1001202506453</v>
       </c>
       <c r="C58" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B59" s="3">
         <v>1001202506453</v>
       </c>
       <c r="C59" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B60" s="3">
         <v>1001201976454</v>
       </c>
       <c r="C60" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B61" s="3">
         <v>1001025176475</v>
       </c>
       <c r="C61" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B62" s="3">
         <v>1001301876697</v>
       </c>
       <c r="C62" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B63" s="3">
         <v>1001024636517</v>
       </c>
       <c r="C63" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B64" s="3">
         <v>1001031076527</v>
       </c>
       <c r="C64" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B65" s="3">
         <v>1001304506562</v>
       </c>
       <c r="C65" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B66" s="3">
         <v>1001020846563</v>
       </c>
       <c r="C66" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B67" s="3">
         <v>1001020836589</v>
       </c>
       <c r="C67" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B68" s="3">
         <v>6751</v>
       </c>
       <c r="C68" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B69" s="3">
         <v>1001010016592</v>
       </c>
       <c r="C69" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B70" s="3">
         <v>1001010026594</v>
       </c>
       <c r="C70" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B71" s="3">
         <v>1001022296601</v>
       </c>
       <c r="C71" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B72" s="3">
         <v>1001031896648</v>
       </c>
       <c r="C72" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B73" s="3">
         <v>1001035266650</v>
       </c>
       <c r="C73" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B74" s="3">
         <v>1001305256658</v>
       </c>
       <c r="C74" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B75" s="3">
         <v>1001010016593</v>
       </c>
       <c r="C75" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B76" s="3">
         <v>1001010026595</v>
       </c>
       <c r="C76" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B77" s="3">
         <v>1001010036597</v>
       </c>
       <c r="C77" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B78" s="3">
         <v>1001020886646</v>
       </c>
       <c r="C78" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B79" s="3">
         <v>1001305306566</v>
       </c>
       <c r="C79" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B80" s="3">
         <v>1001305306566</v>
       </c>
       <c r="C80" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B81" s="3">
         <v>1001300387154</v>
       </c>
       <c r="C81" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B82" s="3">
         <v>1001300387154</v>
       </c>
       <c r="C82" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B83" s="3">
         <v>1001303987169</v>
       </c>
       <c r="C83" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B84" s="3">
         <v>1001303987169</v>
       </c>
       <c r="C84" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B85" s="3">
         <v>1001303106773</v>
       </c>
       <c r="C85" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B86" s="4">
         <v>1001303106773</v>
       </c>
       <c r="C86" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B87" s="4">
         <v>1001303106773</v>
       </c>
       <c r="C87" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B88" s="3">
         <v>1001303106773</v>
       </c>
       <c r="C88" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="B89" s="3">
         <v>1001303106773</v>
       </c>
       <c r="C89" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B90" s="3">
         <v>1001303106773</v>
       </c>
       <c r="C90" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B91" s="3">
         <v>1001303106773</v>
       </c>
       <c r="C91" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B92" s="3">
         <v>1001012566392</v>
@@ -3756,7 +3768,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B93" s="3">
         <v>1001012566392</v>
@@ -3767,7 +3779,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B94" s="3">
         <v>1001012566392</v>
@@ -3778,645 +3790,645 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B95" s="3">
         <v>1001302277173</v>
       </c>
       <c r="C95" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B96" s="3">
         <v>1001302277173</v>
       </c>
       <c r="C96" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B97" s="3">
         <v>1001012426268</v>
       </c>
       <c r="C97" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B98" s="3">
         <v>1001012426268</v>
       </c>
       <c r="C98" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B99" s="3">
         <v>1001024906041</v>
       </c>
       <c r="C99" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B100" s="3">
         <v>1001011086247</v>
       </c>
       <c r="C100" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B101" s="3">
         <v>1001014486158</v>
       </c>
       <c r="C101" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B102" s="3">
         <v>1001015356259</v>
       </c>
       <c r="C102" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B103" s="3">
         <v>1001012816716</v>
       </c>
       <c r="C103" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B104" s="3">
         <v>1001020966227</v>
       </c>
       <c r="C104" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B105" s="3">
         <v>1001020966227</v>
       </c>
       <c r="C105" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B106" s="3">
         <v>1001022726303</v>
       </c>
       <c r="C106" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B107" s="3">
         <v>1001022726303</v>
       </c>
       <c r="C107" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B108" s="3">
         <v>1001022726303</v>
       </c>
       <c r="C108" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B109" s="3">
         <v>1001022726303</v>
       </c>
       <c r="C109" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B110" s="3">
         <v>1001022466726</v>
       </c>
       <c r="C110" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B111" s="3">
         <v>1001020966144</v>
       </c>
       <c r="C111" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B112" s="3">
         <v>1001022376722</v>
       </c>
       <c r="C112" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B113" s="3">
         <v>1001022376955</v>
       </c>
       <c r="C113" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B114" s="3">
         <v>1001022376955</v>
       </c>
       <c r="C114" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B115" s="3">
         <v>1001022376955</v>
       </c>
       <c r="C115" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B116" s="3">
         <v>1001022246661</v>
       </c>
       <c r="C116" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="B117" s="3">
         <v>1001022246661</v>
       </c>
       <c r="C117" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B118" s="3">
         <v>1001022246661</v>
       </c>
       <c r="C118" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B119" s="3">
         <v>1001022246713</v>
       </c>
       <c r="C119" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B120" s="3">
         <v>1001025166241</v>
       </c>
       <c r="C120" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B121" s="3">
         <v>6606</v>
       </c>
       <c r="C121" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B122" s="3">
         <v>1001035326217</v>
       </c>
       <c r="C122" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B123" s="3">
         <v>1001303636301</v>
       </c>
       <c r="C123" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B124" s="3">
         <v>1001303636302</v>
       </c>
       <c r="C124" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B125" s="3">
         <v>1001305196215</v>
       </c>
       <c r="C125" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B126" s="3">
         <v>1001301876212</v>
       </c>
       <c r="C126" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B127" s="3">
         <v>1001301876213</v>
       </c>
       <c r="C127" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B128" s="3">
         <v>1001303636302</v>
       </c>
       <c r="C128" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B129" s="3">
         <v>6645</v>
       </c>
       <c r="C129" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B130" s="3">
         <v>1001225416228</v>
       </c>
       <c r="C130" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B131" s="3">
         <v>6225</v>
       </c>
       <c r="C131" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B132" s="3">
         <v>1001022376722</v>
       </c>
       <c r="C132" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B133" s="3">
         <v>1001022376722</v>
       </c>
       <c r="C133" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B134" s="3">
         <v>3297</v>
       </c>
       <c r="C134" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B135" s="3">
         <v>1001022466726</v>
       </c>
       <c r="C135" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B136" s="3">
         <v>1001022466726</v>
       </c>
       <c r="C136" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B137" s="3">
         <v>1001022466726</v>
       </c>
       <c r="C137" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B138" s="3">
         <v>1001021966602</v>
       </c>
       <c r="C138" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B139" s="3">
         <v>6233</v>
       </c>
       <c r="C139" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B140" s="3">
         <v>1001012816341</v>
       </c>
       <c r="C140" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B141" s="3">
         <v>1001012816341</v>
       </c>
       <c r="C141" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B142" s="3">
         <v>1001012816341</v>
       </c>
       <c r="C142" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B143" s="3">
         <v>1001012816341</v>
       </c>
       <c r="C143" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B144" s="3">
         <v>6750</v>
       </c>
       <c r="C144" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B145" s="3">
         <v>6751</v>
       </c>
       <c r="C145" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B146" s="3">
         <v>5982</v>
       </c>
       <c r="C146" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="B147" s="3">
         <v>1001022656854</v>
       </c>
       <c r="C147" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B148" s="3">
         <v>1001022656854</v>
       </c>
       <c r="C148" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B149" s="3">
         <v>1001022656854</v>
       </c>
       <c r="C149" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B150" s="3">
         <v>1001022656854</v>
       </c>
       <c r="C150" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B151" s="3">
         <v>1001094966025</v>
       </c>
       <c r="C151" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B152" s="3">
         <v>6025</v>
       </c>
       <c r="C152" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B153" s="3">
         <v>1001022373812</v>
@@ -4427,227 +4439,227 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B154" s="3">
         <v>1001100606827</v>
       </c>
       <c r="C154" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B155" s="3">
         <v>1001100606827</v>
       </c>
       <c r="C155" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B156" s="3">
         <v>1001100616826</v>
       </c>
       <c r="C156" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B157" s="3">
         <v>1001100616826</v>
       </c>
       <c r="C157" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B158" s="3">
         <v>1001100626828</v>
       </c>
       <c r="C158" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B159" s="3">
         <v>1001100626828</v>
       </c>
       <c r="C159" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B160" s="3">
         <v>1001035026308</v>
       </c>
       <c r="C160" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B161" s="3">
         <v>1001014486159</v>
       </c>
       <c r="C161" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B162" s="3">
         <v>1001014486159</v>
       </c>
       <c r="C162" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B163" s="3">
         <v>1001035326217</v>
       </c>
       <c r="C163" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B164" s="3">
         <v>1001012426220</v>
       </c>
       <c r="C164" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B165" s="3">
         <v>1001012426220</v>
       </c>
       <c r="C165" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B166" s="3">
         <v>1001022466236</v>
       </c>
       <c r="C166" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B167" s="3">
         <v>1001021966602</v>
       </c>
       <c r="C167" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B168" s="3">
         <v>1001022296656</v>
       </c>
       <c r="C168" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B169" s="3">
         <v>1001301876697</v>
       </c>
       <c r="C169" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B170" s="3">
         <v>1001022246713</v>
       </c>
       <c r="C170" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B171" s="3">
         <v>1001022376722</v>
       </c>
       <c r="C171" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B172" s="3">
         <v>1001020846751</v>
       </c>
       <c r="C172" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B173" s="3">
         <v>1001022725819</v>
       </c>
       <c r="C173" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B174" s="3">
         <v>1001012825337</v>
@@ -4658,7 +4670,7 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B175" s="3">
         <v>1001012815336</v>
@@ -4669,271 +4681,271 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B176" s="3">
         <v>1001234146448</v>
       </c>
       <c r="C176" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B177" s="3">
         <v>1001022725819</v>
       </c>
       <c r="C177" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B178" s="3">
         <v>1001092676027</v>
       </c>
       <c r="C178" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B179" s="3">
         <v>1001301876213</v>
       </c>
       <c r="C179" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B180" s="3">
         <v>1001035026308</v>
       </c>
       <c r="C180" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B181" s="3">
         <v>1001234146448</v>
       </c>
       <c r="C181" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B182" s="3">
         <v>1001201976454</v>
       </c>
       <c r="C182" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B183" s="3">
         <v>1001025176475</v>
       </c>
       <c r="C183" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B184" s="3">
         <v>1001012456498</v>
       </c>
       <c r="C184" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B185" s="3">
         <v>1001010036596</v>
       </c>
       <c r="C185" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B186" s="3">
         <v>1001033856608</v>
       </c>
       <c r="C186" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="B187" s="3">
         <v>1001033856608</v>
       </c>
       <c r="C187" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B188" s="3">
         <v>1001033856609</v>
       </c>
       <c r="C188" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B189" s="3">
         <v>1001033856609</v>
       </c>
       <c r="C189" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B190" s="3">
         <v>1001093345495</v>
       </c>
       <c r="C190" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B191" s="3">
         <v>6550</v>
       </c>
       <c r="C191" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B192" s="3">
         <v>1001304506684</v>
       </c>
       <c r="C192" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B193" s="3">
         <v>1001010113248</v>
       </c>
       <c r="C193" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B194" s="3">
         <v>1001063926780</v>
       </c>
       <c r="C194" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B195" s="3">
         <v>6586</v>
       </c>
       <c r="C195" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B196" s="3">
         <v>1001303636467</v>
       </c>
       <c r="C196" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B197" s="3">
         <v>1001304496701</v>
       </c>
       <c r="C197" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B198" s="3">
         <v>6144</v>
       </c>
       <c r="C198" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B199" s="3">
         <v>1001022725819</v>
       </c>
       <c r="C199" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B200" s="3">
         <v>1001022373812</v>
@@ -4944,40 +4956,40 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B201" s="3">
         <v>1001024906062</v>
       </c>
       <c r="C201" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B202" s="3">
         <v>1001303056692</v>
       </c>
       <c r="C202" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B203" s="3">
         <v>1001301876697</v>
       </c>
       <c r="C203" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B204" s="3">
         <v>1001012634574</v>
@@ -4988,1630 +5000,1630 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B205" s="3">
         <v>1001092485452</v>
       </c>
       <c r="C205" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B206" s="3">
         <v>1001020966144</v>
       </c>
       <c r="C206" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B207" s="3">
         <v>6586</v>
       </c>
       <c r="C207" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B208" s="3">
         <v>1001304496701</v>
       </c>
       <c r="C208" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B209" s="3">
         <v>1001063655015</v>
       </c>
       <c r="C209" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B210" s="3">
         <v>1001060763287</v>
       </c>
       <c r="C210" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B211" s="3">
         <v>1001225416228</v>
       </c>
       <c r="C211" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B212" s="3">
         <v>1001032736550</v>
       </c>
       <c r="C212" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B213" s="3">
         <v>6758</v>
       </c>
       <c r="C213" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B214" s="3">
         <v>1001020965976</v>
       </c>
       <c r="C214" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B215" s="3">
         <v>1001215576586</v>
       </c>
       <c r="C215" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B216" s="3">
         <v>1001094896026</v>
       </c>
       <c r="C216" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B217" s="3">
         <v>1001215576586</v>
       </c>
       <c r="C217" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B218" s="3">
         <v>1001215576586</v>
       </c>
       <c r="C218" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>283</v>
+        <v>779</v>
       </c>
       <c r="B219" s="3">
         <v>1001092436470</v>
       </c>
       <c r="C219" t="s">
-        <v>284</v>
+        <v>780</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="B220" s="3">
-        <v>1001203146555</v>
+        <v>1001092436470</v>
       </c>
       <c r="C220" t="s">
-        <v>289</v>
+        <v>780</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="B221" s="3">
-        <v>1001016747343</v>
+        <v>1001203146555</v>
       </c>
       <c r="C221" t="s">
-        <v>749</v>
+        <v>287</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>710</v>
+        <v>298</v>
       </c>
       <c r="B222" s="3">
         <v>1001016747343</v>
       </c>
       <c r="C222" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>291</v>
+        <v>708</v>
       </c>
       <c r="B223" s="3">
         <v>1001016747343</v>
       </c>
       <c r="C223" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>751</v>
+        <v>289</v>
       </c>
       <c r="B224" s="3">
         <v>1001016747343</v>
       </c>
       <c r="C224" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>293</v>
+        <v>749</v>
       </c>
       <c r="B225" s="3">
-        <v>1001014765993</v>
+        <v>1001016747343</v>
       </c>
       <c r="C225" t="s">
-        <v>292</v>
+        <v>747</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="B226" s="3">
-        <v>1001025166776</v>
+        <v>1001014765993</v>
       </c>
       <c r="C226" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B227" s="3">
-        <v>1001025506777</v>
+        <v>1001025166776</v>
       </c>
       <c r="C227" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="B228" s="3">
-        <v>1001025546822</v>
+        <v>1001025506777</v>
       </c>
       <c r="C228" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="B229" s="3">
         <v>1001025546822</v>
       </c>
       <c r="C229" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="B230" s="3">
         <v>1001025546822</v>
       </c>
       <c r="C230" t="s">
-        <v>547</v>
+        <v>297</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="B231" s="3">
         <v>1001025546822</v>
       </c>
       <c r="C231" t="s">
-        <v>299</v>
+        <v>545</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>657</v>
+        <v>296</v>
       </c>
       <c r="B232" s="3">
-        <v>1001024976616</v>
+        <v>1001025546822</v>
       </c>
       <c r="C232" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>302</v>
+        <v>655</v>
       </c>
       <c r="B233" s="3">
         <v>1001024976616</v>
       </c>
       <c r="C233" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B234" s="3">
-        <v>1001010855247</v>
+        <v>1001024976616</v>
       </c>
       <c r="C234" t="s">
-        <v>23</v>
+        <v>299</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>380</v>
+        <v>301</v>
       </c>
       <c r="B235" s="3">
-        <v>1001223296919</v>
+        <v>1001010855247</v>
       </c>
       <c r="C235" t="s">
-        <v>383</v>
+        <v>23</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>64</v>
+        <v>378</v>
       </c>
       <c r="B236" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C236" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>222</v>
+        <v>63</v>
       </c>
       <c r="B237" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C237" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>453</v>
+        <v>221</v>
       </c>
       <c r="B238" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C238" t="s">
-        <v>469</v>
+        <v>381</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>475</v>
+        <v>451</v>
       </c>
       <c r="B239" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C239" t="s">
-        <v>383</v>
+        <v>467</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>304</v>
+        <v>473</v>
       </c>
       <c r="B240" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C240" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B241" s="3">
-        <v>1001014765993</v>
+        <v>1001223296919</v>
       </c>
       <c r="C241" t="s">
-        <v>292</v>
+        <v>381</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B242" s="3">
-        <v>1001025166776</v>
+        <v>1001014765993</v>
       </c>
       <c r="C242" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B243" s="3">
-        <v>1001025506777</v>
+        <v>1001025166776</v>
       </c>
       <c r="C243" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="B244" s="3">
-        <v>1001025526778</v>
+        <v>1001025506777</v>
       </c>
       <c r="C244" t="s">
-        <v>311</v>
+        <v>295</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B245" s="3">
-        <v>1001304236685</v>
+        <v>1001025526778</v>
       </c>
       <c r="C245" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>339</v>
+        <v>312</v>
       </c>
       <c r="B246" s="3">
-        <v>1001015496769</v>
+        <v>1001304236685</v>
       </c>
       <c r="C246" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="B247" s="3">
         <v>1001015496769</v>
       </c>
       <c r="C247" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="B248" s="3">
-        <v>1001014766798</v>
+        <v>1001015496769</v>
       </c>
       <c r="C248" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B249" s="3">
-        <v>1001015026797</v>
+        <v>1001014766798</v>
       </c>
       <c r="C249" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B250" s="3">
-        <v>1001205386222</v>
+        <v>1001015026797</v>
       </c>
       <c r="C250" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="B251" s="3">
-        <v>1001092675224</v>
+        <v>1001205386222</v>
       </c>
       <c r="C251" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="B252" s="3">
-        <v>1001225406223</v>
+        <v>1001092675224</v>
       </c>
       <c r="C252" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B253" s="3">
-        <v>1001300366790</v>
+        <v>1001225406223</v>
       </c>
       <c r="C253" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>471</v>
+        <v>341</v>
       </c>
       <c r="B254" s="3">
-        <v>1001304096792</v>
+        <v>1001300366790</v>
       </c>
       <c r="C254" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>345</v>
+        <v>469</v>
       </c>
       <c r="B255" s="3">
         <v>1001304096792</v>
       </c>
       <c r="C255" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B256" s="3">
-        <v>1001303637603</v>
+        <v>1001304096792</v>
       </c>
       <c r="C256" t="s">
-        <v>773</v>
+        <v>354</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>391</v>
+        <v>368</v>
       </c>
       <c r="B257" s="3">
-        <v>1001303636794</v>
+        <v>1001303637603</v>
       </c>
       <c r="C257" t="s">
-        <v>357</v>
+        <v>771</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>491</v>
+        <v>388</v>
       </c>
       <c r="B258" s="3">
-        <v>1001303636794</v>
+        <v>1001303637603</v>
       </c>
       <c r="C258" t="s">
-        <v>357</v>
+        <v>771</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B259" s="3">
-        <v>1001303636794</v>
+        <v>1001303637603</v>
       </c>
       <c r="C259" t="s">
-        <v>357</v>
+        <v>771</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>348</v>
+        <v>783</v>
       </c>
       <c r="B260" s="3">
-        <v>1001302596795</v>
+        <v>1001303637603</v>
       </c>
       <c r="C260" t="s">
-        <v>358</v>
+        <v>771</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>349</v>
+        <v>389</v>
       </c>
       <c r="B261" s="3">
-        <v>1001302596796</v>
+        <v>1001303636794</v>
       </c>
       <c r="C261" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>350</v>
+        <v>489</v>
       </c>
       <c r="B262" s="3">
-        <v>1001300456804</v>
+        <v>1001303636794</v>
       </c>
       <c r="C262" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>440</v>
+        <v>345</v>
       </c>
       <c r="B263" s="3">
-        <v>1001300366806</v>
+        <v>1001303636794</v>
       </c>
       <c r="C263" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="B264" s="3">
-        <v>1001300366806</v>
+        <v>1001302596795</v>
       </c>
       <c r="C264" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B265" s="3">
-        <v>1001300516803</v>
+        <v>1001302596796</v>
       </c>
       <c r="C265" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="B266" s="3">
-        <v>1001300366807</v>
+        <v>1001300456804</v>
       </c>
       <c r="C266" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>364</v>
+        <v>438</v>
       </c>
       <c r="B267" s="3">
-        <v>1001300366807</v>
+        <v>1001300366806</v>
       </c>
       <c r="C267" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
       <c r="B268" s="3">
-        <v>1001300516785</v>
+        <v>1001300366806</v>
       </c>
       <c r="C268" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>533</v>
+        <v>350</v>
       </c>
       <c r="B269" s="3">
-        <v>1001300456787</v>
+        <v>1001300516803</v>
       </c>
       <c r="C269" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>548</v>
+        <v>351</v>
       </c>
       <c r="B270" s="3">
-        <v>1001300456787</v>
+        <v>1001300366807</v>
       </c>
       <c r="C270" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="B271" s="3">
-        <v>1001300456787</v>
+        <v>1001300366807</v>
       </c>
       <c r="C271" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
       <c r="B272" s="3">
-        <v>1001303637603</v>
+        <v>1001300516785</v>
       </c>
       <c r="C272" t="s">
-        <v>773</v>
+        <v>365</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>371</v>
+        <v>531</v>
       </c>
       <c r="B273" s="3">
-        <v>1001302596795</v>
+        <v>1001300456787</v>
       </c>
       <c r="C273" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>372</v>
+        <v>546</v>
       </c>
       <c r="B274" s="3">
-        <v>1001012486332</v>
+        <v>1001300456787</v>
       </c>
       <c r="C274" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B275" s="3">
-        <v>1001012566345</v>
+        <v>1001300456787</v>
       </c>
       <c r="C275" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="B276" s="3">
-        <v>1001031076528</v>
+        <v>1001302596795</v>
       </c>
       <c r="C276" t="s">
-        <v>378</v>
+        <v>356</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>408</v>
+        <v>370</v>
       </c>
       <c r="B277" s="3">
-        <v>1001020836761</v>
+        <v>1001012486332</v>
       </c>
       <c r="C277" t="s">
-        <v>385</v>
+        <v>371</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>413</v>
+        <v>372</v>
       </c>
       <c r="B278" s="3">
-        <v>1001020836761</v>
+        <v>1001012566345</v>
       </c>
       <c r="C278" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="B279" s="3">
-        <v>1001020836761</v>
+        <v>1001031076528</v>
       </c>
       <c r="C279" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B280" s="3">
-        <v>1001020846764</v>
+        <v>1001020836761</v>
       </c>
       <c r="C280" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B281" s="3">
-        <v>1001020846764</v>
+        <v>1001020836761</v>
       </c>
       <c r="C281" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B282" s="3">
-        <v>1001020846764</v>
+        <v>1001020836761</v>
       </c>
       <c r="C282" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>487</v>
+        <v>402</v>
       </c>
       <c r="B283" s="3">
-        <v>1001300366790</v>
+        <v>1001020846764</v>
       </c>
       <c r="C283" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>388</v>
+        <v>412</v>
       </c>
       <c r="B284" s="3">
-        <v>1001300366790</v>
+        <v>1001020846764</v>
       </c>
       <c r="C284" t="s">
-        <v>354</v>
+        <v>385</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>344</v>
+        <v>384</v>
       </c>
       <c r="B285" s="3">
-        <v>1001304096791</v>
+        <v>1001020846764</v>
       </c>
       <c r="C285" t="s">
-        <v>355</v>
+        <v>385</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>462</v>
+        <v>485</v>
       </c>
       <c r="B286" s="3">
-        <v>1001304096791</v>
+        <v>1001300366790</v>
       </c>
       <c r="C286" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B287" s="3">
-        <v>1001304096791</v>
+        <v>1001300366790</v>
       </c>
       <c r="C287" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>390</v>
+        <v>342</v>
       </c>
       <c r="B288" s="3">
-        <v>1001303637603</v>
+        <v>1001304096791</v>
       </c>
       <c r="C288" t="s">
-        <v>773</v>
+        <v>353</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>392</v>
+        <v>460</v>
       </c>
       <c r="B289" s="3">
-        <v>1001302596795</v>
+        <v>1001304096791</v>
       </c>
       <c r="C289" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="B290" s="3">
-        <v>1001300516803</v>
+        <v>1001304096791</v>
       </c>
       <c r="C290" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B291" s="3">
-        <v>1001300456804</v>
+        <v>1001302596795</v>
       </c>
       <c r="C291" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B292" s="3">
-        <v>1001300366807</v>
+        <v>1001300516803</v>
       </c>
       <c r="C292" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B293" s="3">
-        <v>1001302596796</v>
+        <v>1001300456804</v>
       </c>
       <c r="C293" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>446</v>
+        <v>393</v>
       </c>
       <c r="B294" s="3">
-        <v>1001023696765</v>
+        <v>1001300366807</v>
       </c>
       <c r="C294" t="s">
-        <v>399</v>
+        <v>361</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>465</v>
+        <v>394</v>
       </c>
       <c r="B295" s="3">
-        <v>1001023696765</v>
+        <v>1001302596796</v>
       </c>
       <c r="C295" t="s">
-        <v>399</v>
+        <v>357</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>398</v>
+        <v>444</v>
       </c>
       <c r="B296" s="3">
         <v>1001023696765</v>
       </c>
       <c r="C296" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>407</v>
+        <v>463</v>
       </c>
       <c r="B297" s="3">
-        <v>1001023696767</v>
+        <v>1001023696765</v>
       </c>
       <c r="C297" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>415</v>
+        <v>396</v>
       </c>
       <c r="B298" s="3">
-        <v>1001023696767</v>
+        <v>1001023696765</v>
       </c>
       <c r="C298" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B299" s="3">
         <v>1001023696767</v>
       </c>
       <c r="C299" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="B300" s="3">
-        <v>1001024976829</v>
+        <v>1001023696767</v>
       </c>
       <c r="C300" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="B301" s="3">
-        <v>1001024976829</v>
+        <v>1001023696767</v>
       </c>
       <c r="C301" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="B302" s="3">
-        <v>1001022376722</v>
+        <v>1001024976829</v>
       </c>
       <c r="C302" t="s">
-        <v>117</v>
+        <v>395</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>445</v>
+        <v>404</v>
       </c>
       <c r="B303" s="3">
-        <v>1001020846762</v>
+        <v>1001024976829</v>
       </c>
       <c r="C303" t="s">
-        <v>420</v>
+        <v>395</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>464</v>
+        <v>416</v>
       </c>
       <c r="B304" s="3">
-        <v>1001020846762</v>
+        <v>1001022376722</v>
       </c>
       <c r="C304" t="s">
-        <v>420</v>
+        <v>116</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="B305" s="3">
         <v>1001020846762</v>
       </c>
       <c r="C305" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>122</v>
+        <v>462</v>
       </c>
       <c r="B306" s="3">
-        <v>1001022656853</v>
+        <v>1001020846762</v>
       </c>
       <c r="C306" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>486</v>
+        <v>417</v>
       </c>
       <c r="B307" s="3">
-        <v>1001022656853</v>
+        <v>1001020846762</v>
       </c>
       <c r="C307" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>569</v>
+        <v>121</v>
       </c>
       <c r="B308" s="3">
-        <v>1001022656948</v>
+        <v>1001022656853</v>
       </c>
       <c r="C308" t="s">
-        <v>560</v>
+        <v>421</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>563</v>
+        <v>484</v>
       </c>
       <c r="B309" s="3">
-        <v>1001022656948</v>
+        <v>1001022656853</v>
       </c>
       <c r="C309" t="s">
-        <v>560</v>
+        <v>421</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>422</v>
+        <v>567</v>
       </c>
       <c r="B310" s="3">
         <v>1001022656948</v>
       </c>
       <c r="C310" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>428</v>
+        <v>561</v>
       </c>
       <c r="B311" s="3">
-        <v>1001022656852</v>
+        <v>1001022656948</v>
       </c>
       <c r="C311" t="s">
-        <v>429</v>
+        <v>558</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>447</v>
+        <v>420</v>
       </c>
       <c r="B312" s="3">
-        <v>1001020836759</v>
+        <v>1001022656948</v>
       </c>
       <c r="C312" t="s">
-        <v>431</v>
+        <v>558</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>463</v>
+        <v>426</v>
       </c>
       <c r="B313" s="3">
-        <v>1001020836759</v>
+        <v>1001022656852</v>
       </c>
       <c r="C313" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>430</v>
+        <v>445</v>
       </c>
       <c r="B314" s="3">
         <v>1001020836759</v>
       </c>
       <c r="C314" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>432</v>
+        <v>461</v>
       </c>
       <c r="B315" s="3">
-        <v>1001023856870</v>
+        <v>1001020836759</v>
       </c>
       <c r="C315" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="B316" s="3">
-        <v>1001013956426</v>
+        <v>1001020836759</v>
       </c>
       <c r="C316" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="B317" s="3">
-        <v>1001093345495</v>
+        <v>1001023856870</v>
       </c>
       <c r="C317" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="B318" s="3">
-        <v>1001022656868</v>
+        <v>1001013956426</v>
       </c>
       <c r="C318" t="s">
-        <v>452</v>
+        <v>424</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B319" s="3">
-        <v>1001022656868</v>
+        <v>1001093345495</v>
       </c>
       <c r="C319" t="s">
-        <v>452</v>
+        <v>435</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>164</v>
+        <v>477</v>
       </c>
       <c r="B320" s="3">
-        <v>1001034065698</v>
+        <v>1001022656868</v>
       </c>
       <c r="C320" t="s">
-        <v>424</v>
+        <v>450</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>182</v>
+        <v>449</v>
       </c>
       <c r="B321" s="3">
-        <v>1001034065698</v>
+        <v>1001022656868</v>
       </c>
       <c r="C321" t="s">
-        <v>424</v>
+        <v>450</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>477</v>
+        <v>163</v>
       </c>
       <c r="B322" s="3">
         <v>1001034065698</v>
       </c>
       <c r="C322" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>455</v>
+        <v>181</v>
       </c>
       <c r="B323" s="3">
         <v>1001034065698</v>
       </c>
       <c r="C323" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="B324" s="3">
-        <v>1001084216206</v>
+        <v>1001034065698</v>
       </c>
       <c r="C324" t="s">
-        <v>382</v>
+        <v>422</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="B325" s="3">
-        <v>1001015646861</v>
+        <v>1001034065698</v>
       </c>
       <c r="C325" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="B326" s="3">
-        <v>1001015646861</v>
+        <v>1001084216206</v>
       </c>
       <c r="C326" t="s">
-        <v>421</v>
+        <v>380</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>443</v>
+        <v>466</v>
       </c>
       <c r="B327" s="3">
-        <v>1001025176768</v>
+        <v>1001015646861</v>
       </c>
       <c r="C327" t="s">
-        <v>444</v>
+        <v>419</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="B328" s="3">
-        <v>1001025176768</v>
+        <v>1001015646861</v>
       </c>
       <c r="C328" t="s">
-        <v>444</v>
+        <v>419</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="B329" s="3">
         <v>1001025176768</v>
       </c>
       <c r="C329" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B330" s="3">
+        <v>1001025176768</v>
+      </c>
+      <c r="C330" t="s">
         <v>442</v>
-      </c>
-      <c r="B330" s="3">
-        <v>1001025486770</v>
-      </c>
-      <c r="C330" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="B331" s="3">
-        <v>1001025486770</v>
+        <v>1001025176768</v>
       </c>
       <c r="C331" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>459</v>
+        <v>440</v>
       </c>
       <c r="B332" s="3">
         <v>1001025486770</v>
       </c>
       <c r="C332" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
-        <v>205</v>
+        <v>465</v>
       </c>
       <c r="B333" s="3">
-        <v>1001012816340</v>
+        <v>1001025486770</v>
       </c>
       <c r="C333" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>481</v>
+        <v>457</v>
       </c>
       <c r="B334" s="3">
-        <v>1001012816340</v>
+        <v>1001025486770</v>
       </c>
       <c r="C334" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>460</v>
+        <v>204</v>
       </c>
       <c r="B335" s="3">
         <v>1001012816340</v>
       </c>
       <c r="C335" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>305</v>
+        <v>479</v>
       </c>
       <c r="B336" s="3">
-        <v>1001203146834</v>
+        <v>1001012816340</v>
       </c>
       <c r="C336" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B337" s="3">
-        <v>1001203146834</v>
+        <v>1001012816340</v>
       </c>
       <c r="C337" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>478</v>
+        <v>303</v>
       </c>
       <c r="B338" s="3">
         <v>1001203146834</v>
       </c>
       <c r="C338" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="B339" s="3">
         <v>1001203146834</v>
       </c>
       <c r="C339" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="B340" s="3">
-        <v>1001300456788</v>
+        <v>1001203146834</v>
       </c>
       <c r="C340" t="s">
-        <v>474</v>
+        <v>425</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
-        <v>488</v>
+        <v>459</v>
       </c>
       <c r="B341" s="3">
-        <v>1001300516786</v>
+        <v>1001203146834</v>
       </c>
       <c r="C341" t="s">
-        <v>489</v>
+        <v>425</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
-        <v>544</v>
+        <v>471</v>
       </c>
       <c r="B342" s="3">
-        <v>1001092436495</v>
+        <v>1001300456788</v>
       </c>
       <c r="C342" t="s">
-        <v>495</v>
+        <v>472</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>551</v>
+        <v>486</v>
       </c>
       <c r="B343" s="3">
-        <v>1001092436495</v>
+        <v>1001300516786</v>
       </c>
       <c r="C343" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>494</v>
+        <v>542</v>
       </c>
       <c r="B344" s="3">
         <v>1001092436495</v>
       </c>
       <c r="C344" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>496</v>
+        <v>549</v>
       </c>
       <c r="B345" s="3">
-        <v>1001025526901</v>
+        <v>1001092436495</v>
       </c>
       <c r="C345" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="B346" s="3">
-        <v>1001025546931</v>
+        <v>1001092436495</v>
       </c>
       <c r="C346" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>507</v>
+        <v>494</v>
       </c>
       <c r="B347" s="3">
-        <v>1001010017539</v>
+        <v>1001025526901</v>
       </c>
       <c r="C347" t="s">
-        <v>774</v>
+        <v>495</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>537</v>
+        <v>496</v>
       </c>
       <c r="B348" s="3">
-        <v>1001010017539</v>
+        <v>1001025546931</v>
       </c>
       <c r="C348" t="s">
-        <v>774</v>
+        <v>497</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B349" s="3">
         <v>1001010017539</v>
       </c>
       <c r="C349" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>779</v>
+        <v>535</v>
       </c>
       <c r="B350" s="3">
         <v>1001010017539</v>
       </c>
       <c r="C350" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="B351" s="3">
-        <v>1001025766909</v>
+        <v>1001010017539</v>
       </c>
       <c r="C351" t="s">
-        <v>503</v>
+        <v>772</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>538</v>
+        <v>777</v>
       </c>
       <c r="B352" s="3">
-        <v>1001025766909</v>
+        <v>1001010017539</v>
       </c>
       <c r="C352" t="s">
-        <v>503</v>
+        <v>772</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
@@ -6622,7 +6634,7 @@
         <v>1001025766909</v>
       </c>
       <c r="C353" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
@@ -6630,527 +6642,527 @@
         <v>536</v>
       </c>
       <c r="B354" s="3">
-        <v>1001010014558</v>
+        <v>1001025766909</v>
       </c>
       <c r="C354" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="B355" s="3">
-        <v>1001010014558</v>
+        <v>1001025766909</v>
       </c>
       <c r="C355" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B356" s="3">
-        <v>1001012596802</v>
+        <v>1001010014558</v>
       </c>
       <c r="C356" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>540</v>
+        <v>503</v>
       </c>
       <c r="B357" s="3">
-        <v>1001012596802</v>
+        <v>1001010014558</v>
       </c>
       <c r="C357" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="B358" s="3">
         <v>1001012596802</v>
       </c>
       <c r="C358" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="B359" s="3">
-        <v>1001012596801</v>
+        <v>1001012596802</v>
       </c>
       <c r="C359" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>539</v>
+        <v>506</v>
       </c>
       <c r="B360" s="3">
-        <v>1001012596801</v>
+        <v>1001012596802</v>
       </c>
       <c r="C360" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="B361" s="3">
         <v>1001012596801</v>
       </c>
       <c r="C361" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="B362" s="3">
-        <v>1001062353684</v>
+        <v>1001012596801</v>
       </c>
       <c r="C362" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
       <c r="B363" s="3">
-        <v>1001010014555</v>
+        <v>1001012596801</v>
       </c>
       <c r="C363" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="B364" s="3">
-        <v>1001083424691</v>
+        <v>1001062353684</v>
       </c>
       <c r="C364" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="B365" s="3">
-        <v>1001190765679</v>
+        <v>1001010014555</v>
       </c>
       <c r="C365" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="B366" s="3">
-        <v>1001085636200</v>
+        <v>1001083424691</v>
       </c>
       <c r="C366" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="B367" s="3">
-        <v>1001020836253</v>
+        <v>1001190765679</v>
       </c>
       <c r="C367" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="B368" s="3">
-        <v>1001084226492</v>
+        <v>1001085636200</v>
       </c>
       <c r="C368" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="B369" s="3">
-        <v>1001223296921</v>
+        <v>1001020836253</v>
       </c>
       <c r="C369" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="B370" s="3">
-        <v>1001053944786</v>
+        <v>1001084226492</v>
       </c>
       <c r="C370" t="s">
-        <v>530</v>
+        <v>523</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="B371" s="3">
-        <v>1001010016839</v>
+        <v>1001223296921</v>
       </c>
       <c r="C371" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>541</v>
+        <v>527</v>
       </c>
       <c r="B372" s="3">
-        <v>1001023857038</v>
+        <v>1001053944786</v>
       </c>
       <c r="C372" t="s">
-        <v>582</v>
+        <v>528</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>542</v>
+        <v>532</v>
       </c>
       <c r="B373" s="3">
-        <v>1001040434903</v>
+        <v>1001010016839</v>
       </c>
       <c r="C373" t="s">
-        <v>543</v>
+        <v>533</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
       <c r="B374" s="3">
-        <v>1001080216842</v>
+        <v>1001023857038</v>
       </c>
       <c r="C374" t="s">
-        <v>546</v>
+        <v>580</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>558</v>
+        <v>540</v>
       </c>
       <c r="B375" s="3">
-        <v>1001022466951</v>
+        <v>1001040434903</v>
       </c>
       <c r="C375" t="s">
-        <v>559</v>
+        <v>541</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>562</v>
+        <v>543</v>
       </c>
       <c r="B376" s="3">
-        <v>1001022466951</v>
+        <v>1001080216842</v>
       </c>
       <c r="C376" t="s">
-        <v>559</v>
+        <v>544</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>566</v>
+        <v>556</v>
       </c>
       <c r="B377" s="3">
-        <v>1001035276653</v>
+        <v>1001022466951</v>
       </c>
       <c r="C377" t="s">
-        <v>567</v>
+        <v>557</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="B378" s="3">
-        <v>1001062353680</v>
+        <v>1001022466951</v>
       </c>
       <c r="C378" t="s">
-        <v>572</v>
+        <v>557</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="B379" s="3">
-        <v>1001061971146</v>
+        <v>1001035276653</v>
       </c>
       <c r="C379" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="B380" s="3">
-        <v>1001225636201</v>
+        <v>1001062353680</v>
       </c>
       <c r="C380" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="B381" s="3">
-        <v>1001095227035</v>
+        <v>1001061971146</v>
       </c>
       <c r="C381" t="s">
-        <v>580</v>
+        <v>572</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B382" s="3">
-        <v>1001023857038</v>
+        <v>1001225636201</v>
       </c>
       <c r="C382" t="s">
-        <v>582</v>
+        <v>574</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="B383" s="3">
-        <v>1001025027040</v>
+        <v>1001095227035</v>
       </c>
       <c r="C383" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="B384" s="3">
-        <v>1001223297103</v>
+        <v>1001023857038</v>
       </c>
       <c r="C384" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="B385" s="3">
-        <v>1001223297103</v>
+        <v>1001025027040</v>
       </c>
       <c r="C385" t="s">
-        <v>586</v>
+        <v>582</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B386" s="3">
         <v>1001223297103</v>
       </c>
       <c r="C386" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>607</v>
+        <v>585</v>
       </c>
       <c r="B387" s="3">
-        <v>1001010032675</v>
+        <v>1001223297103</v>
       </c>
       <c r="C387" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B388" s="3">
-        <v>1001010032675</v>
+        <v>1001223297103</v>
       </c>
       <c r="C388" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>612</v>
+        <v>605</v>
       </c>
       <c r="B389" s="3">
-        <v>1001035937001</v>
+        <v>1001010032675</v>
       </c>
       <c r="C389" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="B390" s="3">
-        <v>1001035937001</v>
+        <v>1001010032675</v>
       </c>
       <c r="C390" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B391" s="3">
-        <v>1001084217090</v>
+        <v>1001035937001</v>
       </c>
       <c r="C391" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="B392" s="3">
-        <v>1001084217090</v>
+        <v>1001035937001</v>
       </c>
       <c r="C392" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B393" s="3">
-        <v>1001022377066</v>
+        <v>1001084217090</v>
       </c>
       <c r="C393" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B394" s="3">
-        <v>1001022377066</v>
+        <v>1001084217090</v>
       </c>
       <c r="C394" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B395" s="3">
-        <v>1001022467080</v>
+        <v>1001022377066</v>
       </c>
       <c r="C395" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="B396" s="3">
-        <v>1001022467080</v>
+        <v>1001022377066</v>
       </c>
       <c r="C396" t="s">
-        <v>597</v>
+        <v>593</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B397" s="3">
-        <v>1001025507255</v>
+        <v>1001022467080</v>
       </c>
       <c r="C397" t="s">
-        <v>750</v>
+        <v>595</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
-        <v>598</v>
+        <v>594</v>
       </c>
       <c r="B398" s="3">
-        <v>1001025507255</v>
+        <v>1001022467080</v>
       </c>
       <c r="C398" t="s">
-        <v>750</v>
+        <v>595</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
-        <v>757</v>
+        <v>614</v>
       </c>
       <c r="B399" s="3">
         <v>1001025507255</v>
       </c>
       <c r="C399" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
-        <v>619</v>
+        <v>596</v>
       </c>
       <c r="B400" s="3">
-        <v>1001022657075</v>
+        <v>1001025507255</v>
       </c>
       <c r="C400" t="s">
-        <v>600</v>
+        <v>748</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
-        <v>599</v>
+        <v>755</v>
       </c>
       <c r="B401" s="3">
-        <v>1001022657075</v>
+        <v>1001025507255</v>
       </c>
       <c r="C401" t="s">
-        <v>600</v>
+        <v>748</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
@@ -7158,153 +7170,153 @@
         <v>617</v>
       </c>
       <c r="B402" s="3">
-        <v>1001022467082</v>
+        <v>1001022657075</v>
       </c>
       <c r="C402" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="B403" s="3">
-        <v>1001022467082</v>
+        <v>1001022657075</v>
       </c>
       <c r="C403" t="s">
-        <v>602</v>
+        <v>598</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B404" s="3">
-        <v>1001022377070</v>
+        <v>1001022467082</v>
       </c>
       <c r="C404" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B405" s="3">
-        <v>1001022377070</v>
+        <v>1001022467082</v>
       </c>
       <c r="C405" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="B406" s="3">
-        <v>1001022657073</v>
+        <v>1001022377070</v>
       </c>
       <c r="C406" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B407" s="3">
-        <v>1001022657073</v>
+        <v>1001022377070</v>
       </c>
       <c r="C407" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
-        <v>631</v>
+        <v>618</v>
       </c>
       <c r="B408" s="3">
-        <v>1001010027126</v>
+        <v>1001022657073</v>
       </c>
       <c r="C408" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="B409" s="3">
-        <v>1001010027126</v>
+        <v>1001022657073</v>
       </c>
       <c r="C409" t="s">
-        <v>609</v>
+        <v>604</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
-        <v>610</v>
+        <v>629</v>
       </c>
       <c r="B410" s="3">
-        <v>1001010027125</v>
+        <v>1001010027126</v>
       </c>
       <c r="C410" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
-        <v>632</v>
+        <v>606</v>
       </c>
       <c r="B411" s="3">
-        <v>1001010027125</v>
+        <v>1001010027126</v>
       </c>
       <c r="C411" t="s">
-        <v>611</v>
+        <v>607</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
-        <v>654</v>
+        <v>608</v>
       </c>
       <c r="B412" s="3">
-        <v>1001016366888</v>
+        <v>1001010027125</v>
       </c>
       <c r="C412" t="s">
-        <v>634</v>
+        <v>609</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B413" s="3">
-        <v>1001016366888</v>
+        <v>1001010027125</v>
       </c>
       <c r="C413" t="s">
-        <v>634</v>
+        <v>609</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B414" s="3">
-        <v>1001300367133</v>
+        <v>1001016366888</v>
       </c>
       <c r="C414" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="B415" s="3">
-        <v>1001300367133</v>
+        <v>1001016366888</v>
       </c>
       <c r="C415" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
@@ -7312,285 +7324,285 @@
         <v>653</v>
       </c>
       <c r="B416" s="3">
-        <v>1001303637564</v>
+        <v>1001300367133</v>
       </c>
       <c r="C416" t="s">
-        <v>772</v>
+        <v>634</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="B417" s="3">
-        <v>1001303637564</v>
+        <v>1001300367133</v>
       </c>
       <c r="C417" t="s">
-        <v>772</v>
+        <v>634</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="B418" s="3">
-        <v>1001304527146</v>
+        <v>1001303637564</v>
       </c>
       <c r="C418" t="s">
-        <v>639</v>
+        <v>770</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="B419" s="3">
-        <v>1001304527146</v>
+        <v>1001303637564</v>
       </c>
       <c r="C419" t="s">
-        <v>639</v>
+        <v>770</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="B420" s="3">
-        <v>1001300517134</v>
+        <v>1001304527146</v>
       </c>
       <c r="C420" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B421" s="3">
-        <v>1001300517134</v>
+        <v>1001304527146</v>
       </c>
       <c r="C421" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="B422" s="3">
-        <v>1001300457135</v>
+        <v>1001300517134</v>
       </c>
       <c r="C422" t="s">
-        <v>643</v>
+        <v>639</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="B423" s="3">
-        <v>1001304527144</v>
+        <v>1001300517134</v>
       </c>
       <c r="C423" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
-        <v>652</v>
+        <v>640</v>
       </c>
       <c r="B424" s="3">
-        <v>1001304527144</v>
+        <v>1001300457135</v>
       </c>
       <c r="C424" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>676</v>
+        <v>642</v>
       </c>
       <c r="B425" s="3">
-        <v>1001081596620</v>
+        <v>1001304527144</v>
       </c>
       <c r="C425" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="B426" s="3">
-        <v>1001081596620</v>
+        <v>1001304527144</v>
       </c>
       <c r="C426" t="s">
-        <v>658</v>
+        <v>643</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>681</v>
+        <v>674</v>
       </c>
       <c r="B427" s="3">
-        <v>1001085637187</v>
+        <v>1001081596620</v>
       </c>
       <c r="C427" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B428" s="3">
-        <v>1001085637187</v>
+        <v>1001081596620</v>
       </c>
       <c r="C428" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B429" s="3">
-        <v>1001015676877</v>
+        <v>1001085637187</v>
       </c>
       <c r="C429" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="B430" s="3">
-        <v>1001015676877</v>
+        <v>1001085637187</v>
       </c>
       <c r="C430" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="B431" s="3">
-        <v>1001015686878</v>
+        <v>1001015676877</v>
       </c>
       <c r="C431" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B432" s="3">
-        <v>1001015686878</v>
+        <v>1001015676877</v>
       </c>
       <c r="C432" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
-        <v>666</v>
+        <v>681</v>
       </c>
       <c r="B433" s="3">
-        <v>1001302277232</v>
+        <v>1001015686878</v>
       </c>
       <c r="C433" t="s">
-        <v>669</v>
+        <v>662</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="B434" s="3">
-        <v>1001304497237</v>
+        <v>1001015686878</v>
       </c>
       <c r="C434" t="s">
-        <v>670</v>
+        <v>662</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="B435" s="3">
-        <v>1001303107241</v>
+        <v>1001302277232</v>
       </c>
       <c r="C435" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
-        <v>674</v>
+        <v>665</v>
       </c>
       <c r="B436" s="3">
-        <v>1002162216872</v>
+        <v>1001304497237</v>
       </c>
       <c r="C436" t="s">
-        <v>675</v>
+        <v>668</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
-        <v>682</v>
+        <v>666</v>
       </c>
       <c r="B437" s="3">
-        <v>1002162216872</v>
+        <v>1001303107241</v>
       </c>
       <c r="C437" t="s">
-        <v>675</v>
+        <v>669</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
-        <v>697</v>
+        <v>672</v>
       </c>
       <c r="B438" s="3">
-        <v>1001063237147</v>
+        <v>1002162216872</v>
       </c>
       <c r="C438" t="s">
-        <v>689</v>
+        <v>673</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B439" s="3">
-        <v>1001063237147</v>
+        <v>1002162216872</v>
       </c>
       <c r="C439" t="s">
-        <v>689</v>
+        <v>673</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B440" s="3">
-        <v>1001063097227</v>
+        <v>1001063237147</v>
       </c>
       <c r="C440" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B441" s="3">
-        <v>1001063097227</v>
+        <v>1001063237147</v>
       </c>
       <c r="C441" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
@@ -7598,630 +7610,663 @@
         <v>694</v>
       </c>
       <c r="B442" s="3">
-        <v>1001066537225</v>
+        <v>1001063097227</v>
       </c>
       <c r="C442" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B443" s="3">
-        <v>1001066537225</v>
+        <v>1001063097227</v>
       </c>
       <c r="C443" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B444" s="3">
-        <v>1001066527226</v>
+        <v>1001066537225</v>
       </c>
       <c r="C444" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="B445" s="3">
-        <v>1001066527226</v>
+        <v>1001066537225</v>
       </c>
       <c r="C445" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
-        <v>688</v>
+        <v>693</v>
       </c>
       <c r="B446" s="3">
-        <v>1001066547228</v>
+        <v>1001066527226</v>
       </c>
       <c r="C446" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
-        <v>704</v>
+        <v>685</v>
       </c>
       <c r="B447" s="3">
-        <v>1001063237229</v>
+        <v>1001066527226</v>
       </c>
       <c r="C447" t="s">
-        <v>701</v>
+        <v>690</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
-        <v>698</v>
+        <v>686</v>
       </c>
       <c r="B448" s="3">
-        <v>1001063237229</v>
+        <v>1001066547228</v>
       </c>
       <c r="C448" t="s">
-        <v>701</v>
+        <v>691</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="B449" s="3">
-        <v>1001063237150</v>
+        <v>1001063237229</v>
       </c>
       <c r="C449" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="B450" s="3">
+        <v>1001063237229</v>
+      </c>
+      <c r="C450" t="s">
         <v>699</v>
-      </c>
-      <c r="B450" s="3">
-        <v>1001063237150</v>
-      </c>
-      <c r="C450" t="s">
-        <v>702</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B451" s="3">
+        <v>1001063237150</v>
+      </c>
+      <c r="C451" t="s">
         <v>700</v>
-      </c>
-      <c r="B451" s="3">
-        <v>1001022467276</v>
-      </c>
-      <c r="C451" t="s">
-        <v>703</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="B452" s="3">
-        <v>1001022467276</v>
+        <v>1001063237150</v>
       </c>
       <c r="C452" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>483</v>
+        <v>698</v>
       </c>
       <c r="B453" s="3">
-        <v>1001022556837</v>
+        <v>1001022467276</v>
       </c>
       <c r="C453" t="s">
-        <v>484</v>
+        <v>701</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
-        <v>727</v>
+        <v>703</v>
       </c>
       <c r="B454" s="3">
-        <v>1001022556837</v>
+        <v>1001022467276</v>
       </c>
       <c r="C454" t="s">
-        <v>484</v>
+        <v>701</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="B455" s="5">
+        <v>481</v>
+      </c>
+      <c r="B455" s="3">
         <v>1001022556837</v>
       </c>
-      <c r="C455" s="6" t="s">
-        <v>484</v>
+      <c r="C455" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
-        <v>181</v>
+        <v>725</v>
       </c>
       <c r="B456" s="3">
-        <v>1001205376221</v>
+        <v>1001022556837</v>
       </c>
       <c r="C456" t="s">
-        <v>179</v>
+        <v>482</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="B457" s="3">
-        <v>1001205376221</v>
-      </c>
-      <c r="C457" t="s">
-        <v>179</v>
+        <v>706</v>
+      </c>
+      <c r="B457" s="5">
+        <v>1001022556837</v>
+      </c>
+      <c r="C457" s="6" t="s">
+        <v>482</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="B458" s="5">
+        <v>180</v>
+      </c>
+      <c r="B458" s="3">
         <v>1001205376221</v>
       </c>
-      <c r="C458" s="6" t="s">
-        <v>179</v>
+      <c r="C458" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
-        <v>492</v>
+        <v>723</v>
       </c>
       <c r="B459" s="3">
-        <v>1001214196459</v>
+        <v>1001205376221</v>
       </c>
       <c r="C459" t="s">
-        <v>493</v>
+        <v>178</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="B460" s="3">
-        <v>1001214196459</v>
-      </c>
-      <c r="C460" t="s">
-        <v>493</v>
+        <v>707</v>
+      </c>
+      <c r="B460" s="5">
+        <v>1001205376221</v>
+      </c>
+      <c r="C460" s="6" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="B461" s="5">
+        <v>490</v>
+      </c>
+      <c r="B461" s="3">
         <v>1001214196459</v>
       </c>
-      <c r="C461" s="6" t="s">
-        <v>493</v>
+      <c r="C461" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="B462" s="5">
-        <v>1001010106325</v>
-      </c>
-      <c r="C462" s="6" t="s">
-        <v>51</v>
+        <v>720</v>
+      </c>
+      <c r="B462" s="3">
+        <v>1001214196459</v>
+      </c>
+      <c r="C462" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
-        <v>723</v>
+        <v>709</v>
       </c>
       <c r="B463" s="5">
-        <v>1001013957231</v>
+        <v>1001214196459</v>
       </c>
       <c r="C463" s="6" t="s">
-        <v>719</v>
+        <v>491</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B464" s="5">
-        <v>1001013957231</v>
+        <v>1001010106325</v>
       </c>
       <c r="C464" s="6" t="s">
-        <v>719</v>
+        <v>51</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B465" s="3">
-        <v>1001220286279</v>
-      </c>
-      <c r="C465" t="s">
-        <v>47</v>
+        <v>721</v>
+      </c>
+      <c r="B465" s="5">
+        <v>1001013957231</v>
+      </c>
+      <c r="C465" s="6" t="s">
+        <v>717</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="B466" s="3">
-        <v>1001220286279</v>
-      </c>
-      <c r="C466" t="s">
-        <v>47</v>
+        <v>711</v>
+      </c>
+      <c r="B466" s="5">
+        <v>1001013957231</v>
+      </c>
+      <c r="C466" s="6" t="s">
+        <v>717</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="B467" s="5">
+        <v>46</v>
+      </c>
+      <c r="B467" s="3">
         <v>1001220286279</v>
       </c>
-      <c r="C467" s="6" t="s">
+      <c r="C467" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="B468" s="5">
-        <v>1001223297092</v>
-      </c>
-      <c r="C468" s="6" t="s">
-        <v>720</v>
+        <v>727</v>
+      </c>
+      <c r="B468" s="3">
+        <v>1001220286279</v>
+      </c>
+      <c r="C468" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="B469" s="5">
-        <v>1001223297092</v>
+        <v>1001220286279</v>
       </c>
       <c r="C469" s="6" t="s">
-        <v>720</v>
+        <v>47</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="B470" s="3">
-        <v>1001020836724</v>
-      </c>
-      <c r="C470" t="s">
-        <v>578</v>
+        <v>722</v>
+      </c>
+      <c r="B470" s="5">
+        <v>1001223297092</v>
+      </c>
+      <c r="C470" s="6" t="s">
+        <v>718</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
-        <v>726</v>
-      </c>
-      <c r="B471" s="3">
-        <v>1001020836724</v>
-      </c>
-      <c r="C471" t="s">
-        <v>578</v>
+        <v>713</v>
+      </c>
+      <c r="B471" s="5">
+        <v>1001223297092</v>
+      </c>
+      <c r="C471" s="6" t="s">
+        <v>718</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
-        <v>716</v>
-      </c>
-      <c r="B472" s="5">
+        <v>575</v>
+      </c>
+      <c r="B472" s="3">
         <v>1001020836724</v>
       </c>
-      <c r="C472" s="6" t="s">
-        <v>578</v>
+      <c r="C472" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
-        <v>728</v>
-      </c>
-      <c r="B473" s="5">
-        <v>1001062475707</v>
-      </c>
-      <c r="C473" s="6" t="s">
-        <v>721</v>
+        <v>724</v>
+      </c>
+      <c r="B473" s="3">
+        <v>1001020836724</v>
+      </c>
+      <c r="C473" t="s">
+        <v>576</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="B474" s="5">
-        <v>1001062475707</v>
+        <v>1001020836724</v>
       </c>
       <c r="C474" s="6" t="s">
-        <v>721</v>
+        <v>576</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="B475" s="5">
-        <v>1001033856609</v>
+        <v>1001062475707</v>
       </c>
       <c r="C475" s="6" t="s">
-        <v>230</v>
+        <v>719</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="B476" s="3">
+        <v>715</v>
+      </c>
+      <c r="B476" s="5">
+        <v>1001062475707</v>
+      </c>
+      <c r="C476" s="6" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A477" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="B477" s="5">
+        <v>1001033856609</v>
+      </c>
+      <c r="C477" s="6" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A478" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="B478" s="3">
         <v>1001025767284</v>
       </c>
-      <c r="C476" s="6" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="477" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A477" s="7" t="s">
-        <v>732</v>
-      </c>
-      <c r="B477" s="5">
-        <v>1001301777332</v>
-      </c>
-      <c r="C477" s="6" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="478" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A478" s="7" t="s">
-        <v>746</v>
-      </c>
-      <c r="B478" s="5">
-        <v>1001301777332</v>
-      </c>
       <c r="C478" s="6" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
     </row>
     <row r="479" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A479" s="7" t="s">
-        <v>747</v>
+        <v>730</v>
       </c>
       <c r="B479" s="5">
-        <v>1001303987333</v>
+        <v>1001301777332</v>
       </c>
       <c r="C479" s="6" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
     </row>
     <row r="480" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A480" s="7" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="B480" s="5">
-        <v>1001303987333</v>
+        <v>1001301777332</v>
       </c>
       <c r="C480" s="6" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
     </row>
     <row r="481" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A481" s="7" t="s">
-        <v>734</v>
+        <v>745</v>
       </c>
       <c r="B481" s="5">
-        <v>1001012426220</v>
+        <v>1001303987333</v>
       </c>
       <c r="C481" s="6" t="s">
-        <v>193</v>
+        <v>737</v>
       </c>
     </row>
     <row r="482" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A482" s="7" t="s">
-        <v>745</v>
+        <v>731</v>
       </c>
       <c r="B482" s="5">
-        <v>1001300387157</v>
+        <v>1001303987333</v>
       </c>
       <c r="C482" s="6" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
     </row>
     <row r="483" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A483" s="7" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="B483" s="5">
-        <v>1001300387157</v>
+        <v>1001012426220</v>
       </c>
       <c r="C483" s="6" t="s">
-        <v>740</v>
+        <v>192</v>
       </c>
     </row>
     <row r="484" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A484" s="7" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="B484" s="5">
-        <v>1001220226208</v>
+        <v>1001300387157</v>
       </c>
       <c r="C484" s="6" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="485" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A485" s="7" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
       <c r="B485" s="5">
-        <v>1001220226208</v>
+        <v>1001300387157</v>
       </c>
       <c r="C485" s="6" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
     </row>
     <row r="486" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A486" s="7" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="B486" s="5">
+        <v>1001220226208</v>
+      </c>
+      <c r="C486" s="6" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A487" s="7" t="s">
+        <v>741</v>
+      </c>
+      <c r="B487" s="5">
+        <v>1001220226208</v>
+      </c>
+      <c r="C487" s="6" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A488" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="B488" s="5">
         <v>1001063656967</v>
       </c>
-      <c r="C486" s="6" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A487" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="B487" s="5">
-        <v>1001063656967</v>
-      </c>
-      <c r="C487" s="6" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A488" s="2" t="s">
-        <v>753</v>
-      </c>
-      <c r="B488" s="3">
-        <v>1001065616832</v>
-      </c>
-      <c r="C488" t="s">
-        <v>754</v>
+      <c r="C488" s="6" t="s">
+        <v>740</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="B489" s="3">
-        <v>1001060677299</v>
-      </c>
-      <c r="C489" t="s">
-        <v>756</v>
+        <v>742</v>
+      </c>
+      <c r="B489" s="5">
+        <v>1001063656967</v>
+      </c>
+      <c r="C489" s="6" t="s">
+        <v>740</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
-        <v>760</v>
+        <v>751</v>
       </c>
       <c r="B490" s="3">
-        <v>1001223907288</v>
+        <v>1001065616832</v>
       </c>
       <c r="C490" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
       <c r="B491" s="3">
-        <v>1001223907288</v>
+        <v>1001060677299</v>
       </c>
       <c r="C491" t="s">
-        <v>761</v>
+        <v>754</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="B492" s="3">
-        <v>1001015026797</v>
+        <v>1001223907288</v>
       </c>
       <c r="C492" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="B493" s="3">
-        <v>1001095226925</v>
+        <v>1001223907288</v>
       </c>
       <c r="C493" t="s">
-        <v>766</v>
+        <v>759</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="B494" s="3">
-        <v>1001035277059</v>
+        <v>1001015026797</v>
       </c>
       <c r="C494" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
       <c r="B495" s="3">
-        <v>1001025767461</v>
+        <v>1001095226925</v>
       </c>
       <c r="C495" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="B496" s="3">
-        <v>1001303637564</v>
+        <v>1001035277059</v>
       </c>
       <c r="C496" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
-        <v>775</v>
+        <v>767</v>
       </c>
       <c r="B497" s="3">
-        <v>1001026947371</v>
+        <v>1001025767461</v>
       </c>
       <c r="C497" t="s">
-        <v>776</v>
+        <v>768</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
-        <v>777</v>
+        <v>769</v>
       </c>
       <c r="B498" s="3">
+        <v>1001303637564</v>
+      </c>
+      <c r="C498" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A499" s="2" t="s">
+        <v>773</v>
+      </c>
+      <c r="B499" s="3">
+        <v>1001026947371</v>
+      </c>
+      <c r="C499" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A500" s="2" t="s">
+        <v>775</v>
+      </c>
+      <c r="B500" s="3">
         <v>1001012427523</v>
       </c>
-      <c r="C498" t="s">
-        <v>778</v>
+      <c r="C500" t="s">
+        <v>776</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A501" s="2" t="s">
+        <v>781</v>
+      </c>
+      <c r="B501" s="3">
+        <v>1001022467083</v>
+      </c>
+      <c r="C501" t="s">
+        <v>782</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C498" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
+  <autoFilter ref="A1:C501" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F5E3BE-F82B-4E36-BB73-7C69CA93D9FA}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021805EC-D52D-4DF8-9739-3B0EB29DF3D3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="790">
   <si>
     <t>1С</t>
   </si>
@@ -2386,6 +2386,24 @@
   </si>
   <si>
     <t>7603 БАЛЫКОВАЯ в/к в/у 0.33кг 8шт. ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7489 СЫРРРВЕЛАТ Папа Может в/к в/у 0,28кг 8шт. ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>СЫРРРВЕЛАТ Папа может в/к в/у 0.28кг 8шт</t>
+  </si>
+  <si>
+    <t>7271 МЯСНЫЕ С ГОВЯДИНОЙ ПМ сос п/о мгс 1.5*4  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>МЯСНЫЕ С ГОВЯДИНОЙ ПМ сос п/о мгс 1.5*4</t>
+  </si>
+  <si>
+    <t>6008 САЛО СОЛЕНОЕ С ЧЕРНЫМ ПЕРЦЕМ мл/к в/у ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>САЛО СОЛЕНОЕ С ЧЕРНЫМ ПЕРЦЕМ мл/к в/у</t>
   </si>
 </sst>
 </file>
@@ -2742,7 +2760,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F501"/>
+  <dimension ref="A1:F504"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" style="2" customWidth="1"/>
@@ -8265,6 +8283,39 @@
         <v>782</v>
       </c>
     </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A502" s="2" t="s">
+        <v>784</v>
+      </c>
+      <c r="B502" s="3">
+        <v>1001307357489</v>
+      </c>
+      <c r="C502" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A503" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="B503" s="3">
+        <v>1001025507271</v>
+      </c>
+      <c r="C503" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A504" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="B504" s="3">
+        <v>1001084856008</v>
+      </c>
+      <c r="C504" t="s">
+        <v>789</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C501" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{021805EC-D52D-4DF8-9739-3B0EB29DF3D3}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21A773F-83EC-4C7C-87B8-22893FD70446}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1007" uniqueCount="790">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="792">
   <si>
     <t>1С</t>
   </si>
@@ -2404,6 +2404,12 @@
   </si>
   <si>
     <t>САЛО СОЛЕНОЕ С ЧЕРНЫМ ПЕРЦЕМ мл/к в/у</t>
+  </si>
+  <si>
+    <t>7422 НАБОР ДЛЯ ПИЦЦЫ с/к с/н мгс 3*3 HRC  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>НАБОР ДЛЯ ПИЦЦЫ с/к с/н мгс 3*3_HRC</t>
   </si>
 </sst>
 </file>
@@ -2760,7 +2766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F504"/>
+  <dimension ref="A1:F505"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" style="2" customWidth="1"/>
@@ -8316,6 +8322,17 @@
         <v>789</v>
       </c>
     </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A505" s="2" t="s">
+        <v>790</v>
+      </c>
+      <c r="B505" s="3">
+        <v>1001200677442</v>
+      </c>
+      <c r="C505" t="s">
+        <v>791</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C501" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D21A773F-83EC-4C7C-87B8-22893FD70446}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8977C8-FE91-4305-AF75-EC8B64AECEA0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1009" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="794">
   <si>
     <t>1С</t>
   </si>
@@ -2410,6 +2410,12 @@
   </si>
   <si>
     <t>НАБОР ДЛЯ ПИЦЦЫ с/к с/н мгс 3*3_HRC</t>
+  </si>
+  <si>
+    <t>6946 СЕРВЕЛАТ КРЕМЛЕВСКИЙ в/к в/у ВЕС  0,84кг ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>СЕРВЕЛАТ КРЕМЛЕВСКИЙ в/к в/у 0.84кг</t>
   </si>
 </sst>
 </file>
@@ -2766,7 +2772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F505"/>
+  <dimension ref="A1:F506"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" style="2" customWidth="1"/>
@@ -8333,6 +8339,17 @@
         <v>791</v>
       </c>
     </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A506" s="2" t="s">
+        <v>792</v>
+      </c>
+      <c r="B506" s="3">
+        <v>1001300456946</v>
+      </c>
+      <c r="C506" t="s">
+        <v>793</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C501" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A8977C8-FE91-4305-AF75-EC8B64AECEA0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F78850-EC94-4B4A-BEE6-BF4D02590B84}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,9 +16,9 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$501</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$506</definedName>
   </definedNames>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -231,15 +231,9 @@
     <t>6453 ЭКСТРА Папа может с/к с/н в/у 1/100 14шт.   ОСТАНКИНО</t>
   </si>
   <si>
-    <t>ЭКСТРА Папа может с/к с/н в/у 1/100_60с</t>
-  </si>
-  <si>
     <t>6454 АРОМАТНАЯ с/к с/н в/у 1/100 14шт.  ОСТАНКИНО</t>
   </si>
   <si>
-    <t>АРОМАТНАЯ с/к с/н в/у 1/100*8_60с</t>
-  </si>
-  <si>
     <t>6475 С СЫРОМ Папа может сос ц/о мгс 0.4кг6шт  ОСТАНКИНО</t>
   </si>
   <si>
@@ -1509,9 +1503,6 @@
     <t>6459 СЕРВЕЛАТ ШВЕЙЦАРСК. в/к с/н в/у 1/100*10  ОСТАНКИНО</t>
   </si>
   <si>
-    <t>СЕРВЕЛАТ ШВЕЙЦАРСК. в/к с/н в/у 1/100*10</t>
-  </si>
-  <si>
     <t>6495 ВЕТЧ.МРАМОРНАЯ в/у срез 0.3кг 6шт_45с  ОСТАНКИНО</t>
   </si>
   <si>
@@ -2416,6 +2407,15 @@
   </si>
   <si>
     <t>СЕРВЕЛАТ КРЕМЛЕВСКИЙ в/к в/у 0.84кг</t>
+  </si>
+  <si>
+    <t>АРОМАТНАЯ с/к с/н в/у 1/100 10шт_Л10</t>
+  </si>
+  <si>
+    <t>ЭКСТРА Папа может с/к с/н в/у 1/100_Л10</t>
+  </si>
+  <si>
+    <t>СЕРВЕЛАТ ШВЕЙЦАРСК.в/к с/н в/у 1/100_Л11</t>
   </si>
 </sst>
 </file>
@@ -2862,68 +2862,68 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="B8" s="3">
         <v>1001095716865</v>
       </c>
       <c r="C8" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B9" s="3">
         <v>1001095716866</v>
       </c>
       <c r="C9" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="B10" s="3">
         <v>1001095716866</v>
       </c>
       <c r="C10" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B11" s="3">
         <v>1001095716866</v>
       </c>
       <c r="C11" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="B12" s="3">
         <v>1001095716866</v>
       </c>
       <c r="C12" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="B13" s="3">
         <v>1001095716866</v>
       </c>
       <c r="C13" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -2934,12 +2934,12 @@
         <v>1001095716865</v>
       </c>
       <c r="C14" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B15" s="3">
         <v>1001092446756</v>
@@ -3000,29 +3000,29 @@
         <v>1001015646861</v>
       </c>
       <c r="C20" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B21" s="3">
         <v>1001015706862</v>
       </c>
       <c r="C21" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B22" s="3">
         <v>1001015706862</v>
       </c>
       <c r="C22" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
@@ -3033,29 +3033,29 @@
         <v>1001015706862</v>
       </c>
       <c r="C23" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="B24" s="3">
         <v>1001303987166</v>
       </c>
       <c r="C24" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="B25" s="3">
         <v>1001303987166</v>
       </c>
       <c r="C25" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
@@ -3088,29 +3088,29 @@
         <v>1001203117382</v>
       </c>
       <c r="C28" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="B29" s="3">
         <v>1001203117382</v>
       </c>
       <c r="C29" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B30" s="3">
         <v>1001061973986</v>
       </c>
       <c r="C30" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
@@ -3121,7 +3121,7 @@
         <v>1001061973986</v>
       </c>
       <c r="C31" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -3159,13 +3159,13 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="B35" s="3">
         <v>1001060755931</v>
       </c>
       <c r="C35" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3176,7 +3176,7 @@
         <v>1001060755931</v>
       </c>
       <c r="C36" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -3209,18 +3209,18 @@
         <v>1001024976829</v>
       </c>
       <c r="C39" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B40" s="3">
         <v>1001084216206</v>
       </c>
       <c r="C40" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -3231,40 +3231,40 @@
         <v>1001084216206</v>
       </c>
       <c r="C41" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="B42" s="3">
         <v>1001022557257</v>
       </c>
       <c r="C42" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="B43" s="3">
         <v>1001022557257</v>
       </c>
       <c r="C43" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B44" s="3">
         <v>1001022557257</v>
       </c>
       <c r="C44" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -3275,7 +3275,7 @@
         <v>1001022556069</v>
       </c>
       <c r="C45" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F45" s="3"/>
     </row>
@@ -3309,45 +3309,45 @@
         <v>1001012507632</v>
       </c>
       <c r="C48" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B49" s="3">
         <v>1001304507236</v>
       </c>
       <c r="C49" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B50" s="3">
         <v>1001304507236</v>
       </c>
       <c r="C50" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="B51" s="3">
         <v>1001304507236</v>
       </c>
       <c r="C51" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B52" s="3">
         <v>1001303056692</v>
@@ -3358,24 +3358,24 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="B53" s="3">
         <v>1001303637149</v>
       </c>
       <c r="C53" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="B54" s="3">
         <v>1001303637149</v>
       </c>
       <c r="C54" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -3386,7 +3386,7 @@
         <v>1001013956426</v>
       </c>
       <c r="C55" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
@@ -3413,13 +3413,13 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="B58" s="3">
-        <v>1001202506453</v>
+        <v>1001062507616</v>
       </c>
       <c r="C58" t="s">
-        <v>65</v>
+        <v>792</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
@@ -3427,367 +3427,367 @@
         <v>64</v>
       </c>
       <c r="B59" s="3">
-        <v>1001202506453</v>
+        <v>1001062507616</v>
       </c>
       <c r="C59" t="s">
-        <v>65</v>
+        <v>792</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B60" s="3">
-        <v>1001201976454</v>
+        <v>1001061977613</v>
       </c>
       <c r="C60" t="s">
-        <v>67</v>
+        <v>791</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B61" s="3">
         <v>1001025176475</v>
       </c>
       <c r="C61" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B62" s="3">
         <v>1001301876697</v>
       </c>
       <c r="C62" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B63" s="3">
         <v>1001024636517</v>
       </c>
       <c r="C63" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B64" s="3">
         <v>1001031076527</v>
       </c>
       <c r="C64" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B65" s="3">
         <v>1001304506562</v>
       </c>
       <c r="C65" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B66" s="3">
         <v>1001020846563</v>
       </c>
       <c r="C66" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B67" s="3">
         <v>1001020836589</v>
       </c>
       <c r="C67" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B68" s="3">
         <v>6751</v>
       </c>
       <c r="C68" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B69" s="3">
         <v>1001010016592</v>
       </c>
       <c r="C69" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B70" s="3">
         <v>1001010026594</v>
       </c>
       <c r="C70" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B71" s="3">
         <v>1001022296601</v>
       </c>
       <c r="C71" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B72" s="3">
         <v>1001031896648</v>
       </c>
       <c r="C72" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B73" s="3">
         <v>1001035266650</v>
       </c>
       <c r="C73" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B74" s="3">
         <v>1001305256658</v>
       </c>
       <c r="C74" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B75" s="3">
         <v>1001010016593</v>
       </c>
       <c r="C75" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B76" s="3">
         <v>1001010026595</v>
       </c>
       <c r="C76" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B77" s="3">
         <v>1001010036597</v>
       </c>
       <c r="C77" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B78" s="3">
         <v>1001020886646</v>
       </c>
       <c r="C78" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B79" s="3">
         <v>1001305306566</v>
       </c>
       <c r="C79" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B80" s="3">
         <v>1001305306566</v>
       </c>
       <c r="C80" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="B81" s="3">
         <v>1001300387154</v>
       </c>
       <c r="C81" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B82" s="3">
         <v>1001300387154</v>
       </c>
       <c r="C82" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="B83" s="3">
         <v>1001303987169</v>
       </c>
       <c r="C83" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="B84" s="3">
         <v>1001303987169</v>
       </c>
       <c r="C84" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="B85" s="3">
         <v>1001303106773</v>
       </c>
       <c r="C85" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B86" s="4">
         <v>1001303106773</v>
       </c>
       <c r="C86" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B87" s="4">
         <v>1001303106773</v>
       </c>
       <c r="C87" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B88" s="3">
         <v>1001303106773</v>
       </c>
       <c r="C88" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="B89" s="3">
         <v>1001303106773</v>
       </c>
       <c r="C89" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B90" s="3">
         <v>1001303106773</v>
       </c>
       <c r="C90" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B91" s="3">
         <v>1001303106773</v>
       </c>
       <c r="C91" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B92" s="3">
         <v>1001012566392</v>
@@ -3798,7 +3798,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="B93" s="3">
         <v>1001012566392</v>
@@ -3809,7 +3809,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B94" s="3">
         <v>1001012566392</v>
@@ -3820,645 +3820,645 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="B95" s="3">
         <v>1001302277173</v>
       </c>
       <c r="C95" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B96" s="3">
         <v>1001302277173</v>
       </c>
       <c r="C96" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="B97" s="3">
         <v>1001012426268</v>
       </c>
       <c r="C97" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B98" s="3">
         <v>1001012426268</v>
       </c>
       <c r="C98" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B99" s="3">
         <v>1001024906041</v>
       </c>
       <c r="C99" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B100" s="3">
         <v>1001011086247</v>
       </c>
       <c r="C100" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B101" s="3">
         <v>1001014486158</v>
       </c>
       <c r="C101" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B102" s="3">
         <v>1001015356259</v>
       </c>
       <c r="C102" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B103" s="3">
         <v>1001012816716</v>
       </c>
       <c r="C103" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B104" s="3">
         <v>1001020966227</v>
       </c>
       <c r="C104" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B105" s="3">
         <v>1001020966227</v>
       </c>
       <c r="C105" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B106" s="3">
         <v>1001022726303</v>
       </c>
       <c r="C106" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B107" s="3">
         <v>1001022726303</v>
       </c>
       <c r="C107" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B108" s="3">
         <v>1001022726303</v>
       </c>
       <c r="C108" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B109" s="3">
         <v>1001022726303</v>
       </c>
       <c r="C109" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B110" s="3">
         <v>1001022466726</v>
       </c>
       <c r="C110" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B111" s="3">
         <v>1001020966144</v>
       </c>
       <c r="C111" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B112" s="3">
         <v>1001022376722</v>
       </c>
       <c r="C112" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="B113" s="3">
         <v>1001022376955</v>
       </c>
       <c r="C113" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="B114" s="3">
         <v>1001022376955</v>
       </c>
       <c r="C114" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B115" s="3">
         <v>1001022376955</v>
       </c>
       <c r="C115" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B116" s="3">
         <v>1001022246661</v>
       </c>
       <c r="C116" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B117" s="3">
         <v>1001022246661</v>
       </c>
       <c r="C117" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B118" s="3">
         <v>1001022246661</v>
       </c>
       <c r="C118" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B119" s="3">
         <v>1001022246713</v>
       </c>
       <c r="C119" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B120" s="3">
         <v>1001025166241</v>
       </c>
       <c r="C120" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B121" s="3">
         <v>6606</v>
       </c>
       <c r="C121" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B122" s="3">
         <v>1001035326217</v>
       </c>
       <c r="C122" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B123" s="3">
         <v>1001303636301</v>
       </c>
       <c r="C123" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B124" s="3">
         <v>1001303636302</v>
       </c>
       <c r="C124" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B125" s="3">
         <v>1001305196215</v>
       </c>
       <c r="C125" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B126" s="3">
         <v>1001301876212</v>
       </c>
       <c r="C126" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="B127" s="3">
         <v>1001301876213</v>
       </c>
       <c r="C127" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B128" s="3">
         <v>1001303636302</v>
       </c>
       <c r="C128" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B129" s="3">
         <v>6645</v>
       </c>
       <c r="C129" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B130" s="3">
         <v>1001225416228</v>
       </c>
       <c r="C130" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B131" s="3">
         <v>6225</v>
       </c>
       <c r="C131" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B132" s="3">
         <v>1001022376722</v>
       </c>
       <c r="C132" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B133" s="3">
         <v>1001022376722</v>
       </c>
       <c r="C133" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B134" s="3">
         <v>3297</v>
       </c>
       <c r="C134" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B135" s="3">
         <v>1001022466726</v>
       </c>
       <c r="C135" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B136" s="3">
         <v>1001022466726</v>
       </c>
       <c r="C136" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B137" s="3">
         <v>1001022466726</v>
       </c>
       <c r="C137" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B138" s="3">
         <v>1001021966602</v>
       </c>
       <c r="C138" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B139" s="3">
         <v>6233</v>
       </c>
       <c r="C139" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B140" s="3">
         <v>1001012816341</v>
       </c>
       <c r="C140" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B141" s="3">
         <v>1001012816341</v>
       </c>
       <c r="C141" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B142" s="3">
         <v>1001012816341</v>
       </c>
       <c r="C142" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B143" s="3">
         <v>1001012816341</v>
       </c>
       <c r="C143" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B144" s="3">
         <v>6750</v>
       </c>
       <c r="C144" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B145" s="3">
         <v>6751</v>
       </c>
       <c r="C145" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B146" s="3">
         <v>5982</v>
       </c>
       <c r="C146" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="B147" s="3">
         <v>1001022656854</v>
       </c>
       <c r="C147" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="B148" s="3">
         <v>1001022656854</v>
       </c>
       <c r="C148" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="B149" s="3">
         <v>1001022656854</v>
       </c>
       <c r="C149" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B150" s="3">
         <v>1001022656854</v>
       </c>
       <c r="C150" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B151" s="3">
         <v>1001094966025</v>
       </c>
       <c r="C151" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B152" s="3">
         <v>6025</v>
       </c>
       <c r="C152" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B153" s="3">
         <v>1001022373812</v>
@@ -4469,227 +4469,227 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B154" s="3">
         <v>1001100606827</v>
       </c>
       <c r="C154" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B155" s="3">
         <v>1001100606827</v>
       </c>
       <c r="C155" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B156" s="3">
         <v>1001100616826</v>
       </c>
       <c r="C156" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B157" s="3">
         <v>1001100616826</v>
       </c>
       <c r="C157" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B158" s="3">
         <v>1001100626828</v>
       </c>
       <c r="C158" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B159" s="3">
         <v>1001100626828</v>
       </c>
       <c r="C159" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B160" s="3">
         <v>1001035026308</v>
       </c>
       <c r="C160" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="B161" s="3">
         <v>1001014486159</v>
       </c>
       <c r="C161" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B162" s="3">
         <v>1001014486159</v>
       </c>
       <c r="C162" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B163" s="3">
         <v>1001035326217</v>
       </c>
       <c r="C163" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B164" s="3">
         <v>1001012426220</v>
       </c>
       <c r="C164" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B165" s="3">
         <v>1001012426220</v>
       </c>
       <c r="C165" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B166" s="3">
         <v>1001022466236</v>
       </c>
       <c r="C166" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B167" s="3">
         <v>1001021966602</v>
       </c>
       <c r="C167" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B168" s="3">
         <v>1001022296656</v>
       </c>
       <c r="C168" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B169" s="3">
         <v>1001301876697</v>
       </c>
       <c r="C169" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B170" s="3">
         <v>1001022246713</v>
       </c>
       <c r="C170" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B171" s="3">
         <v>1001022376722</v>
       </c>
       <c r="C171" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B172" s="3">
         <v>1001020846751</v>
       </c>
       <c r="C172" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B173" s="3">
         <v>1001022725819</v>
       </c>
       <c r="C173" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B174" s="3">
         <v>1001012825337</v>
@@ -4700,7 +4700,7 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B175" s="3">
         <v>1001012815336</v>
@@ -4711,7 +4711,7 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B176" s="3">
         <v>1001234146448</v>
@@ -4722,51 +4722,51 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B177" s="3">
         <v>1001022725819</v>
       </c>
       <c r="C177" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B178" s="3">
         <v>1001092676027</v>
       </c>
       <c r="C178" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B179" s="3">
         <v>1001301876213</v>
       </c>
       <c r="C179" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B180" s="3">
         <v>1001035026308</v>
       </c>
       <c r="C180" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B181" s="3">
         <v>1001234146448</v>
@@ -4777,117 +4777,117 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B182" s="3">
-        <v>1001201976454</v>
+        <v>1001061977613</v>
       </c>
       <c r="C182" t="s">
-        <v>67</v>
+        <v>791</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B183" s="3">
         <v>1001025176475</v>
       </c>
       <c r="C183" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B184" s="3">
         <v>1001012456498</v>
       </c>
       <c r="C184" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B185" s="3">
         <v>1001010036596</v>
       </c>
       <c r="C185" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="B186" s="3">
         <v>1001033856608</v>
       </c>
       <c r="C186" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="B187" s="3">
         <v>1001033856608</v>
       </c>
       <c r="C187" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="B188" s="3">
         <v>1001033856609</v>
       </c>
       <c r="C188" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B189" s="3">
         <v>1001033856609</v>
       </c>
       <c r="C189" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B190" s="3">
         <v>1001093345495</v>
       </c>
       <c r="C190" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B191" s="3">
         <v>6550</v>
       </c>
       <c r="C191" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B192" s="3">
         <v>1001304506684</v>
@@ -4898,84 +4898,84 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B193" s="3">
         <v>1001010113248</v>
       </c>
       <c r="C193" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B194" s="3">
         <v>1001063926780</v>
       </c>
       <c r="C194" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B195" s="3">
         <v>6586</v>
       </c>
       <c r="C195" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B196" s="3">
         <v>1001303636467</v>
       </c>
       <c r="C196" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B197" s="3">
         <v>1001304496701</v>
       </c>
       <c r="C197" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B198" s="3">
         <v>6144</v>
       </c>
       <c r="C198" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B199" s="3">
         <v>1001022725819</v>
       </c>
       <c r="C199" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B200" s="3">
         <v>1001022373812</v>
@@ -4986,18 +4986,18 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B201" s="3">
         <v>1001024906062</v>
       </c>
       <c r="C201" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B202" s="3">
         <v>1001303056692</v>
@@ -5008,18 +5008,18 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="B203" s="3">
         <v>1001301876697</v>
       </c>
       <c r="C203" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B204" s="3">
         <v>1001012634574</v>
@@ -5030,337 +5030,337 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B205" s="3">
         <v>1001092485452</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B206" s="3">
         <v>1001020966144</v>
       </c>
       <c r="C206" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B207" s="3">
         <v>6586</v>
       </c>
       <c r="C207" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B208" s="3">
         <v>1001304496701</v>
       </c>
       <c r="C208" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B209" s="3">
         <v>1001063655015</v>
       </c>
       <c r="C209" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B210" s="3">
         <v>1001060763287</v>
       </c>
       <c r="C210" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="B211" s="3">
         <v>1001225416228</v>
       </c>
       <c r="C211" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B212" s="3">
         <v>1001032736550</v>
       </c>
       <c r="C212" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B213" s="3">
         <v>6758</v>
       </c>
       <c r="C213" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B214" s="3">
         <v>1001020965976</v>
       </c>
       <c r="C214" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B215" s="3">
         <v>1001215576586</v>
       </c>
       <c r="C215" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B216" s="3">
         <v>1001094896026</v>
       </c>
       <c r="C216" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B217" s="3">
         <v>1001215576586</v>
       </c>
       <c r="C217" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B218" s="3">
         <v>1001215576586</v>
       </c>
       <c r="C218" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="B219" s="3">
         <v>1001092436470</v>
       </c>
       <c r="C219" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B220" s="3">
         <v>1001092436470</v>
       </c>
       <c r="C220" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="B221" s="3">
         <v>1001203146555</v>
       </c>
       <c r="C221" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B222" s="3">
         <v>1001016747343</v>
       </c>
       <c r="C222" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="B223" s="3">
         <v>1001016747343</v>
       </c>
       <c r="C223" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B224" s="3">
         <v>1001016747343</v>
       </c>
       <c r="C224" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="B225" s="3">
         <v>1001016747343</v>
       </c>
       <c r="C225" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B226" s="3">
         <v>1001014765993</v>
       </c>
       <c r="C226" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B227" s="3">
         <v>1001025166776</v>
       </c>
       <c r="C227" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B228" s="3">
         <v>1001025506777</v>
       </c>
       <c r="C228" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B229" s="3">
         <v>1001025546822</v>
       </c>
       <c r="C229" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B230" s="3">
         <v>1001025546822</v>
       </c>
       <c r="C230" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B231" s="3">
         <v>1001025546822</v>
       </c>
       <c r="C231" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B232" s="3">
         <v>1001025546822</v>
       </c>
       <c r="C232" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="B233" s="3">
         <v>1001024976616</v>
       </c>
       <c r="C233" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B234" s="3">
         <v>1001024976616</v>
       </c>
       <c r="C234" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B235" s="3">
         <v>1001010855247</v>
@@ -5371,13 +5371,13 @@
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B236" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C236" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
@@ -5388,2498 +5388,2498 @@
         <v>1001223296919</v>
       </c>
       <c r="C237" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B238" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C238" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B239" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C239" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B240" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C240" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B241" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C241" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B242" s="3">
         <v>1001014765993</v>
       </c>
       <c r="C242" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B243" s="3">
         <v>1001025166776</v>
       </c>
       <c r="C243" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B244" s="3">
         <v>1001025506777</v>
       </c>
       <c r="C244" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B245" s="3">
         <v>1001025526778</v>
       </c>
       <c r="C245" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B246" s="3">
         <v>1001304236685</v>
       </c>
       <c r="C246" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="B247" s="3">
         <v>1001015496769</v>
       </c>
       <c r="C247" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B248" s="3">
         <v>1001015496769</v>
       </c>
       <c r="C248" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B249" s="3">
         <v>1001014766798</v>
       </c>
       <c r="C249" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B250" s="3">
         <v>1001015026797</v>
       </c>
       <c r="C250" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B251" s="3">
         <v>1001205386222</v>
       </c>
       <c r="C251" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B252" s="3">
         <v>1001092675224</v>
       </c>
       <c r="C252" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B253" s="3">
         <v>1001225406223</v>
       </c>
       <c r="C253" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B254" s="3">
         <v>1001300366790</v>
       </c>
       <c r="C254" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B255" s="3">
         <v>1001304096792</v>
       </c>
       <c r="C255" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B256" s="3">
         <v>1001304096792</v>
       </c>
       <c r="C256" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B257" s="3">
         <v>1001303637603</v>
       </c>
       <c r="C257" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B258" s="3">
         <v>1001303637603</v>
       </c>
       <c r="C258" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B259" s="3">
         <v>1001303637603</v>
       </c>
       <c r="C259" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="B260" s="3">
         <v>1001303637603</v>
       </c>
       <c r="C260" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="B261" s="3">
         <v>1001303636794</v>
       </c>
       <c r="C261" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B262" s="3">
         <v>1001303636794</v>
       </c>
       <c r="C262" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B263" s="3">
         <v>1001303636794</v>
       </c>
       <c r="C263" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B264" s="3">
         <v>1001302596795</v>
       </c>
       <c r="C264" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B265" s="3">
         <v>1001302596796</v>
       </c>
       <c r="C265" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B266" s="3">
         <v>1001300456804</v>
       </c>
       <c r="C266" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="B267" s="3">
         <v>1001300366806</v>
       </c>
       <c r="C267" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B268" s="3">
         <v>1001300366806</v>
       </c>
       <c r="C268" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B269" s="3">
         <v>1001300516803</v>
       </c>
       <c r="C269" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B270" s="3">
         <v>1001300366807</v>
       </c>
       <c r="C270" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B271" s="3">
         <v>1001300366807</v>
       </c>
       <c r="C271" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B272" s="3">
         <v>1001300516785</v>
       </c>
       <c r="C272" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B273" s="3">
         <v>1001300456787</v>
       </c>
       <c r="C273" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="B274" s="3">
         <v>1001300456787</v>
       </c>
       <c r="C274" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B275" s="3">
         <v>1001300456787</v>
       </c>
       <c r="C275" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B276" s="3">
         <v>1001302596795</v>
       </c>
       <c r="C276" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B277" s="3">
         <v>1001012486332</v>
       </c>
       <c r="C277" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B278" s="3">
         <v>1001012566345</v>
       </c>
       <c r="C278" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B279" s="3">
         <v>1001031076528</v>
       </c>
       <c r="C279" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="B280" s="3">
         <v>1001020836761</v>
       </c>
       <c r="C280" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B281" s="3">
         <v>1001020836761</v>
       </c>
       <c r="C281" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B282" s="3">
         <v>1001020836761</v>
       </c>
       <c r="C282" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B283" s="3">
         <v>1001020846764</v>
       </c>
       <c r="C283" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="B284" s="3">
         <v>1001020846764</v>
       </c>
       <c r="C284" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B285" s="3">
         <v>1001020846764</v>
       </c>
       <c r="C285" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B286" s="3">
         <v>1001300366790</v>
       </c>
       <c r="C286" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B287" s="3">
         <v>1001300366790</v>
       </c>
       <c r="C287" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B288" s="3">
         <v>1001304096791</v>
       </c>
       <c r="C288" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="B289" s="3">
         <v>1001304096791</v>
       </c>
       <c r="C289" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="B290" s="3">
         <v>1001304096791</v>
       </c>
       <c r="C290" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="B291" s="3">
         <v>1001302596795</v>
       </c>
       <c r="C291" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="B292" s="3">
         <v>1001300516803</v>
       </c>
       <c r="C292" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B293" s="3">
         <v>1001300456804</v>
       </c>
       <c r="C293" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="B294" s="3">
         <v>1001300366807</v>
       </c>
       <c r="C294" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B295" s="3">
         <v>1001302596796</v>
       </c>
       <c r="C295" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="B296" s="3">
         <v>1001023696765</v>
       </c>
       <c r="C296" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B297" s="3">
         <v>1001023696765</v>
       </c>
       <c r="C297" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="B298" s="3">
         <v>1001023696765</v>
       </c>
       <c r="C298" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="B299" s="3">
         <v>1001023696767</v>
       </c>
       <c r="C299" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B300" s="3">
         <v>1001023696767</v>
       </c>
       <c r="C300" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B301" s="3">
         <v>1001023696767</v>
       </c>
       <c r="C301" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="B302" s="3">
         <v>1001024976829</v>
       </c>
       <c r="C302" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B303" s="3">
         <v>1001024976829</v>
       </c>
       <c r="C303" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B304" s="3">
         <v>1001022376722</v>
       </c>
       <c r="C304" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="B305" s="3">
         <v>1001020846762</v>
       </c>
       <c r="C305" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B306" s="3">
         <v>1001020846762</v>
       </c>
       <c r="C306" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B307" s="3">
         <v>1001020846762</v>
       </c>
       <c r="C307" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B308" s="3">
         <v>1001022656853</v>
       </c>
       <c r="C308" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B309" s="3">
         <v>1001022656853</v>
       </c>
       <c r="C309" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="B310" s="3">
         <v>1001022656948</v>
       </c>
       <c r="C310" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="B311" s="3">
         <v>1001022656948</v>
       </c>
       <c r="C311" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B312" s="3">
         <v>1001022656948</v>
       </c>
       <c r="C312" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="B313" s="3">
         <v>1001022656852</v>
       </c>
       <c r="C313" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="B314" s="3">
         <v>1001020836759</v>
       </c>
       <c r="C314" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="B315" s="3">
         <v>1001020836759</v>
       </c>
       <c r="C315" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B316" s="3">
         <v>1001020836759</v>
       </c>
       <c r="C316" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B317" s="3">
         <v>1001023856870</v>
       </c>
       <c r="C317" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B318" s="3">
         <v>1001013956426</v>
       </c>
       <c r="C318" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="B319" s="3">
         <v>1001093345495</v>
       </c>
       <c r="C319" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B320" s="3">
         <v>1001022656868</v>
       </c>
       <c r="C320" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="B321" s="3">
         <v>1001022656868</v>
       </c>
       <c r="C321" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B322" s="3">
         <v>1001034065698</v>
       </c>
       <c r="C322" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B323" s="3">
         <v>1001034065698</v>
       </c>
       <c r="C323" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B324" s="3">
         <v>1001034065698</v>
       </c>
       <c r="C324" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="B325" s="3">
         <v>1001034065698</v>
       </c>
       <c r="C325" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="B326" s="3">
         <v>1001084216206</v>
       </c>
       <c r="C326" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B327" s="3">
         <v>1001015646861</v>
       </c>
       <c r="C327" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="B328" s="3">
         <v>1001015646861</v>
       </c>
       <c r="C328" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B329" s="3">
         <v>1001025176768</v>
       </c>
       <c r="C329" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B330" s="3">
         <v>1001025176768</v>
       </c>
       <c r="C330" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="B331" s="3">
         <v>1001025176768</v>
       </c>
       <c r="C331" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B332" s="3">
         <v>1001025486770</v>
       </c>
       <c r="C332" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B333" s="3">
         <v>1001025486770</v>
       </c>
       <c r="C333" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="B334" s="3">
         <v>1001025486770</v>
       </c>
       <c r="C334" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B335" s="3">
         <v>1001012816340</v>
       </c>
       <c r="C335" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B336" s="3">
         <v>1001012816340</v>
       </c>
       <c r="C336" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B337" s="3">
         <v>1001012816340</v>
       </c>
       <c r="C337" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B338" s="3">
         <v>1001203146834</v>
       </c>
       <c r="C338" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="B339" s="3">
         <v>1001203146834</v>
       </c>
       <c r="C339" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B340" s="3">
         <v>1001203146834</v>
       </c>
       <c r="C340" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B341" s="3">
         <v>1001203146834</v>
       </c>
       <c r="C341" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B342" s="3">
         <v>1001300456788</v>
       </c>
       <c r="C342" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B343" s="3">
         <v>1001300516786</v>
       </c>
       <c r="C343" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B344" s="3">
         <v>1001092436495</v>
       </c>
       <c r="C344" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="B345" s="3">
         <v>1001092436495</v>
       </c>
       <c r="C345" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="B346" s="3">
         <v>1001092436495</v>
       </c>
       <c r="C346" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B347" s="3">
         <v>1001025526901</v>
       </c>
       <c r="C347" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B348" s="3">
         <v>1001025546931</v>
       </c>
       <c r="C348" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="B349" s="3">
         <v>1001010017539</v>
       </c>
       <c r="C349" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B350" s="3">
         <v>1001010017539</v>
       </c>
       <c r="C350" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="B351" s="3">
         <v>1001010017539</v>
       </c>
       <c r="C351" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="B352" s="3">
         <v>1001010017539</v>
       </c>
       <c r="C352" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="B353" s="3">
         <v>1001025766909</v>
       </c>
       <c r="C353" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B354" s="3">
         <v>1001025766909</v>
       </c>
       <c r="C354" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B355" s="3">
         <v>1001025766909</v>
       </c>
       <c r="C355" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B356" s="3">
         <v>1001010014558</v>
       </c>
       <c r="C356" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="B357" s="3">
         <v>1001010014558</v>
       </c>
       <c r="C357" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="B358" s="3">
         <v>1001012596802</v>
       </c>
       <c r="C358" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B359" s="3">
         <v>1001012596802</v>
       </c>
       <c r="C359" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="B360" s="3">
         <v>1001012596802</v>
       </c>
       <c r="C360" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="B361" s="3">
         <v>1001012596801</v>
       </c>
       <c r="C361" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="B362" s="3">
         <v>1001012596801</v>
       </c>
       <c r="C362" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="B363" s="3">
         <v>1001012596801</v>
       </c>
       <c r="C363" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="B364" s="3">
         <v>1001062353684</v>
       </c>
       <c r="C364" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B365" s="3">
         <v>1001010014555</v>
       </c>
       <c r="C365" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="B366" s="3">
         <v>1001083424691</v>
       </c>
       <c r="C366" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="B367" s="3">
         <v>1001190765679</v>
       </c>
       <c r="C367" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B368" s="3">
         <v>1001085636200</v>
       </c>
       <c r="C368" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="B369" s="3">
         <v>1001020836253</v>
       </c>
       <c r="C369" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B370" s="3">
         <v>1001084226492</v>
       </c>
       <c r="C370" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B371" s="3">
         <v>1001223296921</v>
       </c>
       <c r="C371" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="B372" s="3">
         <v>1001053944786</v>
       </c>
       <c r="C372" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B373" s="3">
         <v>1001010016839</v>
       </c>
       <c r="C373" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B374" s="3">
         <v>1001023857038</v>
       </c>
       <c r="C374" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="B375" s="3">
         <v>1001040434903</v>
       </c>
       <c r="C375" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="B376" s="3">
         <v>1001080216842</v>
       </c>
       <c r="C376" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B377" s="3">
         <v>1001022466951</v>
       </c>
       <c r="C377" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="B378" s="3">
         <v>1001022466951</v>
       </c>
       <c r="C378" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="B379" s="3">
         <v>1001035276653</v>
       </c>
       <c r="C379" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="B380" s="3">
         <v>1001062353680</v>
       </c>
       <c r="C380" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="B381" s="3">
         <v>1001061971146</v>
       </c>
       <c r="C381" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="B382" s="3">
         <v>1001225636201</v>
       </c>
       <c r="C382" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="B383" s="3">
         <v>1001095227035</v>
       </c>
       <c r="C383" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="B384" s="3">
         <v>1001023857038</v>
       </c>
       <c r="C384" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="B385" s="3">
         <v>1001025027040</v>
       </c>
       <c r="C385" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="B386" s="3">
         <v>1001223297103</v>
       </c>
       <c r="C386" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B387" s="3">
         <v>1001223297103</v>
       </c>
       <c r="C387" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="B388" s="3">
         <v>1001223297103</v>
       </c>
       <c r="C388" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="B389" s="3">
         <v>1001010032675</v>
       </c>
       <c r="C389" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="B390" s="3">
         <v>1001010032675</v>
       </c>
       <c r="C390" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="B391" s="3">
         <v>1001035937001</v>
       </c>
       <c r="C391" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="B392" s="3">
         <v>1001035937001</v>
       </c>
       <c r="C392" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B393" s="3">
         <v>1001084217090</v>
       </c>
       <c r="C393" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="B394" s="3">
         <v>1001084217090</v>
       </c>
       <c r="C394" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="B395" s="3">
         <v>1001022377066</v>
       </c>
       <c r="C395" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="B396" s="3">
         <v>1001022377066</v>
       </c>
       <c r="C396" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="B397" s="3">
         <v>1001022467080</v>
       </c>
       <c r="C397" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B398" s="3">
         <v>1001022467080</v>
       </c>
       <c r="C398" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="B399" s="3">
         <v>1001025507255</v>
       </c>
       <c r="C399" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="B400" s="3">
         <v>1001025507255</v>
       </c>
       <c r="C400" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="B401" s="3">
         <v>1001025507255</v>
       </c>
       <c r="C401" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="B402" s="3">
         <v>1001022657075</v>
       </c>
       <c r="C402" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="B403" s="3">
         <v>1001022657075</v>
       </c>
       <c r="C403" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="B404" s="3">
         <v>1001022467082</v>
       </c>
       <c r="C404" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="B405" s="3">
         <v>1001022467082</v>
       </c>
       <c r="C405" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="B406" s="3">
         <v>1001022377070</v>
       </c>
       <c r="C406" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="B407" s="3">
         <v>1001022377070</v>
       </c>
       <c r="C407" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="B408" s="3">
         <v>1001022657073</v>
       </c>
       <c r="C408" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B409" s="3">
         <v>1001022657073</v>
       </c>
       <c r="C409" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="B410" s="3">
         <v>1001010027126</v>
       </c>
       <c r="C410" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B411" s="3">
         <v>1001010027126</v>
       </c>
       <c r="C411" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="B412" s="3">
         <v>1001010027125</v>
       </c>
       <c r="C412" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="B413" s="3">
         <v>1001010027125</v>
       </c>
       <c r="C413" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="B414" s="3">
         <v>1001016366888</v>
       </c>
       <c r="C414" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="B415" s="3">
         <v>1001016366888</v>
       </c>
       <c r="C415" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="B416" s="3">
         <v>1001300367133</v>
       </c>
       <c r="C416" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="B417" s="3">
         <v>1001300367133</v>
       </c>
       <c r="C417" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B418" s="3">
         <v>1001303637564</v>
       </c>
       <c r="C418" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="B419" s="3">
         <v>1001303637564</v>
       </c>
       <c r="C419" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B420" s="3">
         <v>1001304527146</v>
       </c>
       <c r="C420" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="B421" s="3">
         <v>1001304527146</v>
       </c>
       <c r="C421" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="B422" s="3">
         <v>1001300517134</v>
       </c>
       <c r="C422" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="B423" s="3">
         <v>1001300517134</v>
       </c>
       <c r="C423" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="B424" s="3">
         <v>1001300457135</v>
       </c>
       <c r="C424" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="B425" s="3">
         <v>1001304527144</v>
       </c>
       <c r="C425" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="B426" s="3">
         <v>1001304527144</v>
       </c>
       <c r="C426" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B427" s="3">
         <v>1001081596620</v>
       </c>
       <c r="C427" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="B428" s="3">
         <v>1001081596620</v>
       </c>
       <c r="C428" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="B429" s="3">
         <v>1001085637187</v>
       </c>
       <c r="C429" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="B430" s="3">
         <v>1001085637187</v>
       </c>
       <c r="C430" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B431" s="3">
         <v>1001015676877</v>
       </c>
       <c r="C431" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="B432" s="3">
         <v>1001015676877</v>
       </c>
       <c r="C432" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="B433" s="3">
         <v>1001015686878</v>
       </c>
       <c r="C433" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="B434" s="3">
         <v>1001015686878</v>
       </c>
       <c r="C434" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="B435" s="3">
         <v>1001302277232</v>
       </c>
       <c r="C435" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="B436" s="3">
         <v>1001304497237</v>
       </c>
       <c r="C436" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="B437" s="3">
         <v>1001303107241</v>
       </c>
       <c r="C437" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="B438" s="3">
         <v>1002162216872</v>
       </c>
       <c r="C438" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="B439" s="3">
         <v>1002162216872</v>
       </c>
       <c r="C439" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B440" s="3">
         <v>1001063237147</v>
       </c>
       <c r="C440" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B441" s="3">
         <v>1001063237147</v>
       </c>
       <c r="C441" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B442" s="3">
         <v>1001063097227</v>
       </c>
       <c r="C442" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B443" s="3">
         <v>1001063097227</v>
       </c>
       <c r="C443" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B444" s="3">
         <v>1001066537225</v>
       </c>
       <c r="C444" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="B445" s="3">
         <v>1001066537225</v>
       </c>
       <c r="C445" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B446" s="3">
         <v>1001066527226</v>
       </c>
       <c r="C446" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="B447" s="3">
         <v>1001066527226</v>
       </c>
       <c r="C447" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B448" s="3">
         <v>1001066547228</v>
       </c>
       <c r="C448" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="B449" s="3">
         <v>1001063237229</v>
       </c>
       <c r="C449" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B450" s="3">
         <v>1001063237229</v>
       </c>
       <c r="C450" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="B451" s="3">
         <v>1001063237150</v>
       </c>
       <c r="C451" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B452" s="3">
         <v>1001063237150</v>
       </c>
       <c r="C452" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B453" s="3">
         <v>1001022467276</v>
       </c>
       <c r="C453" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B454" s="3">
         <v>1001022467276</v>
       </c>
       <c r="C454" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B455" s="3">
         <v>1001022556837</v>
       </c>
       <c r="C455" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="B456" s="3">
         <v>1001022556837</v>
       </c>
       <c r="C456" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B457" s="5">
         <v>1001022556837</v>
       </c>
       <c r="C457" s="6" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B458" s="3">
         <v>1001205376221</v>
       </c>
       <c r="C458" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="B459" s="3">
         <v>1001205376221</v>
       </c>
       <c r="C459" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="B460" s="5">
         <v>1001205376221</v>
       </c>
       <c r="C460" s="6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B461" s="3">
-        <v>1001214196459</v>
+        <v>1001304197608</v>
       </c>
       <c r="C461" t="s">
-        <v>491</v>
+        <v>793</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="B462" s="3">
-        <v>1001214196459</v>
+        <v>1001304197608</v>
       </c>
       <c r="C462" t="s">
-        <v>491</v>
+        <v>793</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="B463" s="5">
-        <v>1001214196459</v>
-      </c>
-      <c r="C463" s="6" t="s">
-        <v>491</v>
+        <v>706</v>
+      </c>
+      <c r="B463" s="3">
+        <v>1001304197608</v>
+      </c>
+      <c r="C463" t="s">
+        <v>793</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="B464" s="5">
         <v>1001010106325</v>
@@ -7890,24 +7890,24 @@
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="B465" s="5">
         <v>1001013957231</v>
       </c>
       <c r="C465" s="6" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="B466" s="5">
         <v>1001013957231</v>
       </c>
       <c r="C466" s="6" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
@@ -7923,7 +7923,7 @@
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="B468" s="3">
         <v>1001220286279</v>
@@ -7934,7 +7934,7 @@
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="B469" s="5">
         <v>1001220286279</v>
@@ -7945,413 +7945,413 @@
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="B470" s="5">
         <v>1001223297092</v>
       </c>
       <c r="C470" s="6" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="B471" s="5">
         <v>1001223297092</v>
       </c>
       <c r="C471" s="6" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="B472" s="3">
         <v>1001020836724</v>
       </c>
       <c r="C472" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="B473" s="3">
         <v>1001020836724</v>
       </c>
       <c r="C473" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="B474" s="5">
         <v>1001020836724</v>
       </c>
       <c r="C474" s="6" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="B475" s="5">
         <v>1001062475707</v>
       </c>
       <c r="C475" s="6" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="B476" s="5">
         <v>1001062475707</v>
       </c>
       <c r="C476" s="6" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="B477" s="5">
         <v>1001033856609</v>
       </c>
       <c r="C477" s="6" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="B478" s="3">
         <v>1001025767284</v>
       </c>
       <c r="C478" s="6" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
     </row>
     <row r="479" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A479" s="7" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B479" s="5">
         <v>1001301777332</v>
       </c>
       <c r="C479" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="480" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A480" s="7" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="B480" s="5">
         <v>1001301777332</v>
       </c>
       <c r="C480" s="6" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
     </row>
     <row r="481" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A481" s="7" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="B481" s="5">
         <v>1001303987333</v>
       </c>
       <c r="C481" s="6" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
     </row>
     <row r="482" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A482" s="7" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="B482" s="5">
         <v>1001303987333</v>
       </c>
       <c r="C482" s="6" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
     </row>
     <row r="483" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A483" s="7" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="B483" s="5">
         <v>1001012426220</v>
       </c>
       <c r="C483" s="6" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="484" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A484" s="7" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B484" s="5">
         <v>1001300387157</v>
       </c>
       <c r="C484" s="6" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
     </row>
     <row r="485" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A485" s="7" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="B485" s="5">
         <v>1001300387157</v>
       </c>
       <c r="C485" s="6" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
     </row>
     <row r="486" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A486" s="7" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="B486" s="5">
         <v>1001220226208</v>
       </c>
       <c r="C486" s="6" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
     </row>
     <row r="487" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A487" s="7" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="B487" s="5">
         <v>1001220226208</v>
       </c>
       <c r="C487" s="6" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
     </row>
     <row r="488" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A488" s="7" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="B488" s="5">
         <v>1001063656967</v>
       </c>
       <c r="C488" s="6" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
     </row>
     <row r="489" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="B489" s="5">
         <v>1001063656967</v>
       </c>
       <c r="C489" s="6" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="B490" s="3">
         <v>1001065616832</v>
       </c>
       <c r="C490" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="B491" s="3">
         <v>1001060677299</v>
       </c>
       <c r="C491" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="B492" s="3">
         <v>1001223907288</v>
       </c>
       <c r="C492" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="B493" s="3">
         <v>1001223907288</v>
       </c>
       <c r="C493" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="B494" s="3">
         <v>1001015026797</v>
       </c>
       <c r="C494" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B495" s="3">
         <v>1001095226925</v>
       </c>
       <c r="C495" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B496" s="3">
         <v>1001035277059</v>
       </c>
       <c r="C496" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="B497" s="3">
         <v>1001025767461</v>
       </c>
       <c r="C497" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="B498" s="3">
         <v>1001303637564</v>
       </c>
       <c r="C498" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="B499" s="3">
         <v>1001026947371</v>
       </c>
       <c r="C499" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="B500" s="3">
         <v>1001012427523</v>
       </c>
       <c r="C500" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="B501" s="3">
         <v>1001022467083</v>
       </c>
       <c r="C501" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="B502" s="3">
         <v>1001307357489</v>
       </c>
       <c r="C502" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="B503" s="3">
         <v>1001025507271</v>
       </c>
       <c r="C503" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="B504" s="3">
         <v>1001084856008</v>
       </c>
       <c r="C504" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="B505" s="3">
         <v>1001200677442</v>
       </c>
       <c r="C505" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="B506" s="3">
         <v>1001300456946</v>
       </c>
       <c r="C506" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C501" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
+  <autoFilter ref="A1:C506" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F78850-EC94-4B4A-BEE6-BF4D02590B84}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2652FA7-7F12-46C9-A9D6-C072A9038291}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$506</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$507</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="795">
   <si>
     <t>1С</t>
   </si>
@@ -2304,9 +2304,6 @@
     <t>БАЛЫК с/к с/н в/у 1/100 10шт. (7288)</t>
   </si>
   <si>
-    <t>БАЛЫК с/к с/н в/у 1/100 10шт.</t>
-  </si>
-  <si>
     <t>7288 БАЛЫК с/к с/н в/у 1/100 10шт ОСТАНКИНО</t>
   </si>
   <si>
@@ -2416,6 +2413,12 @@
   </si>
   <si>
     <t>СЕРВЕЛАТ ШВЕЙЦАРСК.в/к с/н в/у 1/100_Л11</t>
+  </si>
+  <si>
+    <t>7632 ЭКСТРА Папа может вар п/о 0.4кг 8шт_195к  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>БАЛЫК с/к с/н в/у 1/100 10шт_Л11</t>
   </si>
 </sst>
 </file>
@@ -2772,7 +2775,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F506"/>
+  <dimension ref="A1:F507"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" style="2" customWidth="1"/>
@@ -3303,29 +3306,29 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>55</v>
+        <v>793</v>
       </c>
       <c r="B48" s="3">
         <v>1001012507632</v>
       </c>
       <c r="C48" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>197</v>
+        <v>55</v>
       </c>
       <c r="B49" s="3">
-        <v>1001304507236</v>
+        <v>1001012507632</v>
       </c>
       <c r="C49" t="s">
-        <v>668</v>
+        <v>774</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>110</v>
+        <v>197</v>
       </c>
       <c r="B50" s="3">
         <v>1001304507236</v>
@@ -3336,7 +3339,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>673</v>
+        <v>110</v>
       </c>
       <c r="B51" s="3">
         <v>1001304507236</v>
@@ -3347,29 +3350,29 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>111</v>
+        <v>673</v>
       </c>
       <c r="B52" s="3">
-        <v>1001303056692</v>
+        <v>1001304507236</v>
       </c>
       <c r="C52" t="s">
-        <v>57</v>
+        <v>668</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>644</v>
+        <v>111</v>
       </c>
       <c r="B53" s="3">
-        <v>1001303637149</v>
+        <v>1001303056692</v>
       </c>
       <c r="C53" t="s">
-        <v>619</v>
+        <v>57</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>618</v>
+        <v>644</v>
       </c>
       <c r="B54" s="3">
         <v>1001303637149</v>
@@ -3380,65 +3383,65 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>58</v>
+        <v>618</v>
       </c>
       <c r="B55" s="3">
-        <v>1001013956426</v>
+        <v>1001303637149</v>
       </c>
       <c r="C55" t="s">
-        <v>422</v>
+        <v>619</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B56" s="3">
-        <v>1001024636438</v>
+        <v>1001013956426</v>
       </c>
       <c r="C56" t="s">
-        <v>60</v>
+        <v>422</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B57" s="3">
-        <v>1001234146448</v>
+        <v>1001024636438</v>
       </c>
       <c r="C57" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>284</v>
+        <v>61</v>
       </c>
       <c r="B58" s="3">
-        <v>1001062507616</v>
+        <v>1001234146448</v>
       </c>
       <c r="C58" t="s">
-        <v>792</v>
+        <v>62</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>64</v>
+        <v>284</v>
       </c>
       <c r="B59" s="3">
         <v>1001062507616</v>
       </c>
       <c r="C59" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B60" s="3">
-        <v>1001061977613</v>
+        <v>1001062507616</v>
       </c>
       <c r="C60" t="s">
         <v>791</v>
@@ -3446,216 +3449,216 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B61" s="3">
-        <v>1001025176475</v>
+        <v>1001061977613</v>
       </c>
       <c r="C61" t="s">
-        <v>67</v>
+        <v>790</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="B62" s="3">
-        <v>1001301876697</v>
+        <v>1001025176475</v>
       </c>
       <c r="C62" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="B63" s="3">
-        <v>1001024636517</v>
+        <v>1001301876697</v>
       </c>
       <c r="C63" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B64" s="3">
-        <v>1001031076527</v>
+        <v>1001024636517</v>
       </c>
       <c r="C64" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B65" s="3">
-        <v>1001304506562</v>
+        <v>1001031076527</v>
       </c>
       <c r="C65" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B66" s="3">
-        <v>1001020846563</v>
+        <v>1001304506562</v>
       </c>
       <c r="C66" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B67" s="3">
-        <v>1001020836589</v>
+        <v>1001020846563</v>
       </c>
       <c r="C67" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B68" s="3">
-        <v>6751</v>
+        <v>1001020836589</v>
       </c>
       <c r="C68" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B69" s="3">
-        <v>1001010016592</v>
+        <v>6751</v>
       </c>
       <c r="C69" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B70" s="3">
-        <v>1001010026594</v>
+        <v>1001010016592</v>
       </c>
       <c r="C70" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B71" s="3">
-        <v>1001022296601</v>
+        <v>1001010026594</v>
       </c>
       <c r="C71" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B72" s="3">
-        <v>1001031896648</v>
+        <v>1001022296601</v>
       </c>
       <c r="C72" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B73" s="3">
-        <v>1001035266650</v>
+        <v>1001031896648</v>
       </c>
       <c r="C73" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B74" s="3">
-        <v>1001305256658</v>
+        <v>1001035266650</v>
       </c>
       <c r="C74" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B75" s="3">
-        <v>1001010016593</v>
+        <v>1001305256658</v>
       </c>
       <c r="C75" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B76" s="3">
-        <v>1001010026595</v>
+        <v>1001010016593</v>
       </c>
       <c r="C76" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B77" s="3">
-        <v>1001010036597</v>
+        <v>1001010026595</v>
       </c>
       <c r="C77" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="B78" s="3">
-        <v>1001020886646</v>
+        <v>1001010036597</v>
       </c>
       <c r="C78" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>308</v>
+        <v>107</v>
       </c>
       <c r="B79" s="3">
-        <v>1001305306566</v>
+        <v>1001020886646</v>
       </c>
       <c r="C79" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>108</v>
+        <v>308</v>
       </c>
       <c r="B80" s="3">
         <v>1001305306566</v>
@@ -3666,18 +3669,18 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>642</v>
+        <v>108</v>
       </c>
       <c r="B81" s="3">
-        <v>1001300387154</v>
+        <v>1001305306566</v>
       </c>
       <c r="C81" t="s">
-        <v>623</v>
+        <v>109</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>622</v>
+        <v>642</v>
       </c>
       <c r="B82" s="3">
         <v>1001300387154</v>
@@ -3688,18 +3691,18 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>643</v>
+        <v>622</v>
       </c>
       <c r="B83" s="3">
-        <v>1001303987169</v>
+        <v>1001300387154</v>
       </c>
       <c r="C83" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>624</v>
+        <v>643</v>
       </c>
       <c r="B84" s="3">
         <v>1001303987169</v>
@@ -3710,20 +3713,20 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>228</v>
+        <v>624</v>
       </c>
       <c r="B85" s="3">
-        <v>1001303106773</v>
+        <v>1001303987169</v>
       </c>
       <c r="C85" t="s">
-        <v>331</v>
+        <v>625</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="B86" s="4">
+        <v>228</v>
+      </c>
+      <c r="B86" s="3">
         <v>1001303106773</v>
       </c>
       <c r="C86" t="s">
@@ -3732,7 +3735,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>260</v>
+        <v>338</v>
       </c>
       <c r="B87" s="4">
         <v>1001303106773</v>
@@ -3743,9 +3746,9 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B88" s="3">
+        <v>260</v>
+      </c>
+      <c r="B88" s="4">
         <v>1001303106773</v>
       </c>
       <c r="C88" t="s">
@@ -3754,7 +3757,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>377</v>
+        <v>112</v>
       </c>
       <c r="B89" s="3">
         <v>1001303106773</v>
@@ -3765,7 +3768,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B90" s="3">
         <v>1001303106773</v>
@@ -3776,7 +3779,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B91" s="3">
         <v>1001303106773</v>
@@ -3787,18 +3790,18 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>217</v>
+        <v>372</v>
       </c>
       <c r="B92" s="3">
-        <v>1001012566392</v>
+        <v>1001303106773</v>
       </c>
       <c r="C92" t="s">
-        <v>54</v>
+        <v>331</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>407</v>
+        <v>217</v>
       </c>
       <c r="B93" s="3">
         <v>1001012566392</v>
@@ -3809,7 +3812,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>115</v>
+        <v>407</v>
       </c>
       <c r="B94" s="3">
         <v>1001012566392</v>
@@ -3820,18 +3823,18 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>645</v>
+        <v>115</v>
       </c>
       <c r="B95" s="3">
-        <v>1001302277173</v>
+        <v>1001012566392</v>
       </c>
       <c r="C95" t="s">
-        <v>621</v>
+        <v>54</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>620</v>
+        <v>645</v>
       </c>
       <c r="B96" s="3">
         <v>1001302277173</v>
@@ -3842,18 +3845,18 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>702</v>
+        <v>620</v>
       </c>
       <c r="B97" s="3">
-        <v>1001012426268</v>
+        <v>1001302277173</v>
       </c>
       <c r="C97" t="s">
-        <v>117</v>
+        <v>621</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>118</v>
+        <v>702</v>
       </c>
       <c r="B98" s="3">
         <v>1001012426268</v>
@@ -3864,95 +3867,95 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="B99" s="3">
-        <v>1001024906041</v>
+        <v>1001012426268</v>
       </c>
       <c r="C99" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B100" s="3">
-        <v>1001011086247</v>
+        <v>1001024906041</v>
       </c>
       <c r="C100" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>143</v>
+        <v>120</v>
       </c>
       <c r="B101" s="3">
-        <v>1001014486158</v>
+        <v>1001011086247</v>
       </c>
       <c r="C101" t="s">
-        <v>136</v>
+        <v>121</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B102" s="3">
-        <v>1001015356259</v>
+        <v>1001014486158</v>
       </c>
       <c r="C102" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B103" s="3">
-        <v>1001012816716</v>
+        <v>1001015356259</v>
       </c>
       <c r="C103" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>313</v>
+        <v>147</v>
       </c>
       <c r="B104" s="3">
-        <v>1001020966227</v>
+        <v>1001012816716</v>
       </c>
       <c r="C104" t="s">
-        <v>312</v>
+        <v>138</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>124</v>
+        <v>313</v>
       </c>
       <c r="B105" s="3">
         <v>1001020966227</v>
       </c>
       <c r="C105" t="s">
-        <v>125</v>
+        <v>312</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>215</v>
+        <v>124</v>
       </c>
       <c r="B106" s="3">
-        <v>1001022726303</v>
+        <v>1001020966227</v>
       </c>
       <c r="C106" t="s">
-        <v>248</v>
+        <v>125</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="B107" s="3">
         <v>1001022726303</v>
@@ -3963,7 +3966,7 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>330</v>
+        <v>247</v>
       </c>
       <c r="B108" s="3">
         <v>1001022726303</v>
@@ -3974,62 +3977,62 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>148</v>
+        <v>330</v>
       </c>
       <c r="B109" s="3">
         <v>1001022726303</v>
       </c>
       <c r="C109" t="s">
-        <v>150</v>
+        <v>248</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>103</v>
+        <v>148</v>
       </c>
       <c r="B110" s="3">
-        <v>1001022466726</v>
+        <v>1001022726303</v>
       </c>
       <c r="C110" t="s">
-        <v>104</v>
+        <v>150</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>142</v>
+        <v>103</v>
       </c>
       <c r="B111" s="3">
-        <v>1001020966144</v>
+        <v>1001022466726</v>
       </c>
       <c r="C111" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>116</v>
+        <v>142</v>
       </c>
       <c r="B112" s="3">
-        <v>1001022376722</v>
+        <v>1001020966144</v>
       </c>
       <c r="C112" t="s">
-        <v>114</v>
+        <v>139</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>565</v>
+        <v>116</v>
       </c>
       <c r="B113" s="3">
-        <v>1001022376955</v>
+        <v>1001022376722</v>
       </c>
       <c r="C113" t="s">
-        <v>556</v>
+        <v>114</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B114" s="3">
         <v>1001022376955</v>
@@ -4040,7 +4043,7 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>129</v>
+        <v>563</v>
       </c>
       <c r="B115" s="3">
         <v>1001022376955</v>
@@ -4051,18 +4054,18 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>240</v>
+        <v>129</v>
       </c>
       <c r="B116" s="3">
-        <v>1001022246661</v>
+        <v>1001022376955</v>
       </c>
       <c r="C116" t="s">
-        <v>241</v>
+        <v>556</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>309</v>
+        <v>240</v>
       </c>
       <c r="B117" s="3">
         <v>1001022246661</v>
@@ -4073,172 +4076,172 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>128</v>
+        <v>309</v>
       </c>
       <c r="B118" s="3">
         <v>1001022246661</v>
       </c>
       <c r="C118" t="s">
-        <v>130</v>
+        <v>241</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="B119" s="3">
-        <v>1001022246713</v>
+        <v>1001022246661</v>
       </c>
       <c r="C119" t="s">
-        <v>105</v>
+        <v>130</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B120" s="3">
-        <v>1001025166241</v>
+        <v>1001022246713</v>
       </c>
       <c r="C120" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="B121" s="3">
-        <v>6606</v>
+        <v>1001025166241</v>
       </c>
       <c r="C121" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>127</v>
+        <v>149</v>
       </c>
       <c r="B122" s="3">
-        <v>1001035326217</v>
+        <v>6606</v>
       </c>
       <c r="C122" t="s">
-        <v>126</v>
+        <v>151</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="B123" s="3">
-        <v>1001303636301</v>
+        <v>1001035326217</v>
       </c>
       <c r="C123" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>89</v>
+        <v>146</v>
       </c>
       <c r="B124" s="3">
-        <v>1001303636302</v>
+        <v>1001303636301</v>
       </c>
       <c r="C124" t="s">
-        <v>90</v>
+        <v>140</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>133</v>
+        <v>89</v>
       </c>
       <c r="B125" s="3">
-        <v>1001305196215</v>
+        <v>1001303636302</v>
       </c>
       <c r="C125" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="B126" s="3">
-        <v>1001301876212</v>
+        <v>1001305196215</v>
       </c>
       <c r="C126" t="s">
-        <v>141</v>
+        <v>74</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="B127" s="3">
-        <v>1001301876213</v>
+        <v>1001301876212</v>
       </c>
       <c r="C127" t="s">
-        <v>73</v>
+        <v>141</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="B128" s="3">
-        <v>1001303636302</v>
+        <v>1001301876213</v>
       </c>
       <c r="C128" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B129" s="3">
-        <v>6645</v>
+        <v>1001303636302</v>
       </c>
       <c r="C129" t="s">
-        <v>153</v>
+        <v>90</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B130" s="3">
-        <v>1001225416228</v>
+        <v>6645</v>
       </c>
       <c r="C130" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B131" s="3">
-        <v>6225</v>
+        <v>1001225416228</v>
       </c>
       <c r="C131" t="s">
-        <v>264</v>
+        <v>155</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B132" s="3">
-        <v>1001022376722</v>
+        <v>6225</v>
       </c>
       <c r="C132" t="s">
-        <v>114</v>
+        <v>264</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="B133" s="3">
         <v>1001022376722</v>
@@ -4249,29 +4252,29 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B134" s="3">
-        <v>3297</v>
+        <v>1001022376722</v>
       </c>
       <c r="C134" t="s">
-        <v>160</v>
+        <v>114</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>303</v>
+        <v>159</v>
       </c>
       <c r="B135" s="3">
-        <v>1001022466726</v>
+        <v>3297</v>
       </c>
       <c r="C135" t="s">
-        <v>281</v>
+        <v>160</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>282</v>
+        <v>303</v>
       </c>
       <c r="B136" s="3">
         <v>1001022466726</v>
@@ -4282,51 +4285,51 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>163</v>
+        <v>282</v>
       </c>
       <c r="B137" s="3">
         <v>1001022466726</v>
       </c>
       <c r="C137" t="s">
-        <v>104</v>
+        <v>281</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B138" s="3">
-        <v>1001021966602</v>
+        <v>1001022466726</v>
       </c>
       <c r="C138" t="s">
-        <v>275</v>
+        <v>104</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B139" s="3">
-        <v>6233</v>
+        <v>1001021966602</v>
       </c>
       <c r="C139" t="s">
-        <v>165</v>
+        <v>275</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>255</v>
+        <v>166</v>
       </c>
       <c r="B140" s="3">
-        <v>1001012816341</v>
+        <v>6233</v>
       </c>
       <c r="C140" t="s">
-        <v>432</v>
+        <v>165</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>478</v>
+        <v>255</v>
       </c>
       <c r="B141" s="3">
         <v>1001012816341</v>
@@ -4337,7 +4340,7 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B142" s="3">
         <v>1001012816341</v>
@@ -4348,7 +4351,7 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>167</v>
+        <v>481</v>
       </c>
       <c r="B143" s="3">
         <v>1001012816341</v>
@@ -4359,51 +4362,51 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B144" s="3">
-        <v>6750</v>
+        <v>1001012816341</v>
       </c>
       <c r="C144" t="s">
-        <v>80</v>
+        <v>432</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B145" s="3">
-        <v>6751</v>
+        <v>6750</v>
       </c>
       <c r="C145" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B146" s="3">
-        <v>5982</v>
+        <v>6751</v>
       </c>
       <c r="C146" t="s">
-        <v>171</v>
+        <v>82</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>527</v>
+        <v>170</v>
       </c>
       <c r="B147" s="3">
-        <v>1001022656854</v>
+        <v>5982</v>
       </c>
       <c r="C147" t="s">
-        <v>421</v>
+        <v>171</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>544</v>
+        <v>527</v>
       </c>
       <c r="B148" s="3">
         <v>1001022656854</v>
@@ -4414,7 +4417,7 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>445</v>
+        <v>544</v>
       </c>
       <c r="B149" s="3">
         <v>1001022656854</v>
@@ -4425,7 +4428,7 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>172</v>
+        <v>445</v>
       </c>
       <c r="B150" s="3">
         <v>1001022656854</v>
@@ -4436,21 +4439,21 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="B151" s="3">
-        <v>1001094966025</v>
+        <v>1001022656854</v>
       </c>
       <c r="C151" t="s">
-        <v>174</v>
+        <v>421</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B152" s="3">
-        <v>6025</v>
+        <v>1001094966025</v>
       </c>
       <c r="C152" t="s">
         <v>174</v>
@@ -4458,29 +4461,29 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B153" s="3">
-        <v>1001022373812</v>
+        <v>6025</v>
       </c>
       <c r="C153" t="s">
-        <v>3</v>
+        <v>174</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B154" s="3">
-        <v>1001100606827</v>
+        <v>1001022373812</v>
       </c>
       <c r="C154" t="s">
-        <v>320</v>
+        <v>3</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>332</v>
+        <v>181</v>
       </c>
       <c r="B155" s="3">
         <v>1001100606827</v>
@@ -4491,18 +4494,18 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>182</v>
+        <v>332</v>
       </c>
       <c r="B156" s="3">
-        <v>1001100616826</v>
+        <v>1001100606827</v>
       </c>
       <c r="C156" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>333</v>
+        <v>182</v>
       </c>
       <c r="B157" s="3">
         <v>1001100616826</v>
@@ -4513,18 +4516,18 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>183</v>
+        <v>333</v>
       </c>
       <c r="B158" s="3">
-        <v>1001100626828</v>
+        <v>1001100616826</v>
       </c>
       <c r="C158" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>334</v>
+        <v>183</v>
       </c>
       <c r="B159" s="3">
         <v>1001100626828</v>
@@ -4535,62 +4538,62 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>184</v>
+        <v>334</v>
       </c>
       <c r="B160" s="3">
-        <v>1001035026308</v>
+        <v>1001100626828</v>
       </c>
       <c r="C160" t="s">
-        <v>185</v>
+        <v>322</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>548</v>
+        <v>184</v>
       </c>
       <c r="B161" s="3">
-        <v>1001014486159</v>
+        <v>1001035026308</v>
       </c>
       <c r="C161" t="s">
-        <v>549</v>
+        <v>185</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>186</v>
+        <v>548</v>
       </c>
       <c r="B162" s="3">
         <v>1001014486159</v>
       </c>
       <c r="C162" t="s">
-        <v>187</v>
+        <v>549</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B163" s="3">
-        <v>1001035326217</v>
+        <v>1001014486159</v>
       </c>
       <c r="C163" t="s">
-        <v>279</v>
+        <v>187</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>495</v>
+        <v>188</v>
       </c>
       <c r="B164" s="3">
-        <v>1001012426220</v>
+        <v>1001035326217</v>
       </c>
       <c r="C164" t="s">
-        <v>190</v>
+        <v>279</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>189</v>
+        <v>495</v>
       </c>
       <c r="B165" s="3">
         <v>1001012426220</v>
@@ -4601,238 +4604,238 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B166" s="3">
-        <v>1001022466236</v>
+        <v>1001012426220</v>
       </c>
       <c r="C166" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B167" s="3">
-        <v>1001021966602</v>
+        <v>1001022466236</v>
       </c>
       <c r="C167" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B168" s="3">
-        <v>1001022296656</v>
+        <v>1001021966602</v>
       </c>
       <c r="C168" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B169" s="3">
-        <v>1001301876697</v>
+        <v>1001022296656</v>
       </c>
       <c r="C169" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B170" s="3">
-        <v>1001022246713</v>
+        <v>1001301876697</v>
       </c>
       <c r="C170" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B171" s="3">
-        <v>1001022376722</v>
+        <v>1001022246713</v>
       </c>
       <c r="C171" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B172" s="3">
-        <v>1001020846751</v>
+        <v>1001022376722</v>
       </c>
       <c r="C172" t="s">
-        <v>82</v>
+        <v>204</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B173" s="3">
-        <v>1001022725819</v>
+        <v>1001020846751</v>
       </c>
       <c r="C173" t="s">
-        <v>207</v>
+        <v>82</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B174" s="3">
-        <v>1001012825337</v>
+        <v>1001022725819</v>
       </c>
       <c r="C174" t="s">
-        <v>27</v>
+        <v>207</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B175" s="3">
-        <v>1001012815336</v>
+        <v>1001012825337</v>
       </c>
       <c r="C175" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B176" s="3">
-        <v>1001234146448</v>
+        <v>1001012815336</v>
       </c>
       <c r="C176" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B177" s="3">
-        <v>1001022725819</v>
+        <v>1001234146448</v>
       </c>
       <c r="C177" t="s">
-        <v>207</v>
+        <v>62</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B178" s="3">
-        <v>1001092676027</v>
+        <v>1001022725819</v>
       </c>
       <c r="C178" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B179" s="3">
-        <v>1001301876213</v>
+        <v>1001092676027</v>
       </c>
       <c r="C179" t="s">
-        <v>73</v>
+        <v>213</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B180" s="3">
-        <v>1001035026308</v>
+        <v>1001301876213</v>
       </c>
       <c r="C180" t="s">
-        <v>397</v>
+        <v>73</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B181" s="3">
-        <v>1001234146448</v>
+        <v>1001035026308</v>
       </c>
       <c r="C181" t="s">
-        <v>62</v>
+        <v>397</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B182" s="3">
-        <v>1001061977613</v>
+        <v>1001234146448</v>
       </c>
       <c r="C182" t="s">
-        <v>791</v>
+        <v>62</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B183" s="3">
-        <v>1001025176475</v>
+        <v>1001061977613</v>
       </c>
       <c r="C183" t="s">
-        <v>67</v>
+        <v>790</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B184" s="3">
-        <v>1001012456498</v>
+        <v>1001025176475</v>
       </c>
       <c r="C184" t="s">
-        <v>223</v>
+        <v>67</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B185" s="3">
-        <v>1001010036596</v>
+        <v>1001012456498</v>
       </c>
       <c r="C185" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>559</v>
+        <v>224</v>
       </c>
       <c r="B186" s="3">
-        <v>1001033856608</v>
+        <v>1001010036596</v>
       </c>
       <c r="C186" t="s">
-        <v>550</v>
+        <v>225</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="B187" s="3">
         <v>1001033856608</v>
@@ -4843,18 +4846,18 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="B188" s="3">
-        <v>1001033856609</v>
+        <v>1001033856608</v>
       </c>
       <c r="C188" t="s">
-        <v>227</v>
+        <v>550</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>226</v>
+        <v>560</v>
       </c>
       <c r="B189" s="3">
         <v>1001033856609</v>
@@ -4865,315 +4868,315 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B190" s="3">
-        <v>1001093345495</v>
+        <v>1001033856609</v>
       </c>
       <c r="C190" t="s">
-        <v>433</v>
+        <v>227</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B191" s="3">
-        <v>6550</v>
+        <v>1001093345495</v>
       </c>
       <c r="C191" t="s">
-        <v>232</v>
+        <v>433</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B192" s="3">
-        <v>1001304506684</v>
+        <v>6550</v>
       </c>
       <c r="C192" t="s">
-        <v>56</v>
+        <v>232</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B193" s="3">
-        <v>1001010113248</v>
+        <v>1001304506684</v>
       </c>
       <c r="C193" t="s">
-        <v>235</v>
+        <v>56</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>405</v>
+        <v>234</v>
       </c>
       <c r="B194" s="3">
-        <v>1001063926780</v>
+        <v>1001010113248</v>
       </c>
       <c r="C194" t="s">
-        <v>406</v>
+        <v>235</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>236</v>
+        <v>405</v>
       </c>
       <c r="B195" s="3">
-        <v>6586</v>
+        <v>1001063926780</v>
       </c>
       <c r="C195" t="s">
-        <v>237</v>
+        <v>406</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B196" s="3">
-        <v>1001303636467</v>
+        <v>6586</v>
       </c>
       <c r="C196" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B197" s="3">
-        <v>1001304496701</v>
+        <v>1001303636467</v>
       </c>
       <c r="C197" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B198" s="3">
-        <v>6144</v>
+        <v>1001304496701</v>
       </c>
       <c r="C198" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B199" s="3">
-        <v>1001022725819</v>
+        <v>6144</v>
       </c>
       <c r="C199" t="s">
-        <v>207</v>
+        <v>245</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B200" s="3">
-        <v>1001022373812</v>
+        <v>1001022725819</v>
       </c>
       <c r="C200" t="s">
-        <v>3</v>
+        <v>207</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B201" s="3">
-        <v>1001024906062</v>
+        <v>1001022373812</v>
       </c>
       <c r="C201" t="s">
-        <v>251</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B202" s="3">
-        <v>1001303056692</v>
+        <v>1001024906062</v>
       </c>
       <c r="C202" t="s">
-        <v>57</v>
+        <v>251</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B203" s="3">
-        <v>1001301876697</v>
+        <v>1001303056692</v>
       </c>
       <c r="C203" t="s">
-        <v>199</v>
+        <v>57</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B204" s="3">
-        <v>1001012634574</v>
+        <v>1001301876697</v>
       </c>
       <c r="C204" t="s">
-        <v>11</v>
+        <v>199</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B205" s="3">
-        <v>1001092485452</v>
+        <v>1001012634574</v>
       </c>
       <c r="C205" t="s">
-        <v>257</v>
+        <v>11</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B206" s="3">
-        <v>1001020966144</v>
+        <v>1001092485452</v>
       </c>
       <c r="C206" t="s">
-        <v>139</v>
+        <v>257</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B207" s="3">
-        <v>6586</v>
+        <v>1001020966144</v>
       </c>
       <c r="C207" t="s">
-        <v>237</v>
+        <v>139</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B208" s="3">
-        <v>1001304496701</v>
+        <v>6586</v>
       </c>
       <c r="C208" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B209" s="3">
-        <v>1001063655015</v>
+        <v>1001304496701</v>
       </c>
       <c r="C209" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B210" s="3">
-        <v>1001060763287</v>
+        <v>1001063655015</v>
       </c>
       <c r="C210" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B211" s="3">
-        <v>1001225416228</v>
+        <v>1001060763287</v>
       </c>
       <c r="C211" t="s">
-        <v>155</v>
+        <v>266</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B212" s="3">
-        <v>1001032736550</v>
+        <v>1001225416228</v>
       </c>
       <c r="C212" t="s">
-        <v>232</v>
+        <v>155</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B213" s="3">
-        <v>6758</v>
+        <v>1001032736550</v>
       </c>
       <c r="C213" t="s">
-        <v>270</v>
+        <v>232</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B214" s="3">
-        <v>1001020965976</v>
+        <v>6758</v>
       </c>
       <c r="C214" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="B215" s="3">
-        <v>1001215576586</v>
+        <v>1001020965976</v>
       </c>
       <c r="C215" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B216" s="3">
-        <v>1001094896026</v>
+        <v>1001215576586</v>
       </c>
       <c r="C216" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>486</v>
+        <v>276</v>
       </c>
       <c r="B217" s="3">
-        <v>1001215576586</v>
+        <v>1001094896026</v>
       </c>
       <c r="C217" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>278</v>
+        <v>486</v>
       </c>
       <c r="B218" s="3">
         <v>1001215576586</v>
@@ -5184,51 +5187,51 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>776</v>
+        <v>278</v>
       </c>
       <c r="B219" s="3">
-        <v>1001092436470</v>
+        <v>1001215576586</v>
       </c>
       <c r="C219" t="s">
-        <v>777</v>
+        <v>274</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>280</v>
+        <v>775</v>
       </c>
       <c r="B220" s="3">
         <v>1001092436470</v>
       </c>
       <c r="C220" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B221" s="3">
-        <v>1001203146555</v>
+        <v>1001092436470</v>
       </c>
       <c r="C221" t="s">
-        <v>285</v>
+        <v>776</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="B222" s="3">
-        <v>1001016747343</v>
+        <v>1001203146555</v>
       </c>
       <c r="C222" t="s">
-        <v>744</v>
+        <v>285</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>705</v>
+        <v>296</v>
       </c>
       <c r="B223" s="3">
         <v>1001016747343</v>
@@ -5239,7 +5242,7 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>287</v>
+        <v>705</v>
       </c>
       <c r="B224" s="3">
         <v>1001016747343</v>
@@ -5250,7 +5253,7 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>746</v>
+        <v>287</v>
       </c>
       <c r="B225" s="3">
         <v>1001016747343</v>
@@ -5261,51 +5264,51 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>289</v>
+        <v>746</v>
       </c>
       <c r="B226" s="3">
-        <v>1001014765993</v>
+        <v>1001016747343</v>
       </c>
       <c r="C226" t="s">
-        <v>288</v>
+        <v>744</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B227" s="3">
-        <v>1001025166776</v>
+        <v>1001014765993</v>
       </c>
       <c r="C227" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B228" s="3">
-        <v>1001025506777</v>
+        <v>1001025166776</v>
       </c>
       <c r="C228" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="B229" s="3">
-        <v>1001025546822</v>
+        <v>1001025506777</v>
       </c>
       <c r="C229" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B230" s="3">
         <v>1001025546822</v>
@@ -5316,40 +5319,40 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="B231" s="3">
         <v>1001025546822</v>
       </c>
       <c r="C231" t="s">
-        <v>542</v>
+        <v>295</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>294</v>
+        <v>327</v>
       </c>
       <c r="B232" s="3">
         <v>1001025546822</v>
       </c>
       <c r="C232" t="s">
-        <v>295</v>
+        <v>542</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>652</v>
+        <v>294</v>
       </c>
       <c r="B233" s="3">
-        <v>1001024976616</v>
+        <v>1001025546822</v>
       </c>
       <c r="C233" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>298</v>
+        <v>652</v>
       </c>
       <c r="B234" s="3">
         <v>1001024976616</v>
@@ -5360,29 +5363,29 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B235" s="3">
-        <v>1001010855247</v>
+        <v>1001024976616</v>
       </c>
       <c r="C235" t="s">
-        <v>23</v>
+        <v>297</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>376</v>
+        <v>299</v>
       </c>
       <c r="B236" s="3">
-        <v>1001223296919</v>
+        <v>1001010855247</v>
       </c>
       <c r="C236" t="s">
-        <v>379</v>
+        <v>23</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>63</v>
+        <v>376</v>
       </c>
       <c r="B237" s="3">
         <v>1001223296919</v>
@@ -5393,7 +5396,7 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>219</v>
+        <v>63</v>
       </c>
       <c r="B238" s="3">
         <v>1001223296919</v>
@@ -5404,29 +5407,29 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>449</v>
+        <v>219</v>
       </c>
       <c r="B239" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C239" t="s">
-        <v>465</v>
+        <v>379</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>471</v>
+        <v>449</v>
       </c>
       <c r="B240" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C240" t="s">
-        <v>379</v>
+        <v>465</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>300</v>
+        <v>471</v>
       </c>
       <c r="B241" s="3">
         <v>1001223296919</v>
@@ -5437,73 +5440,73 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B242" s="3">
-        <v>1001014765993</v>
+        <v>1001223296919</v>
       </c>
       <c r="C242" t="s">
-        <v>288</v>
+        <v>379</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B243" s="3">
-        <v>1001025166776</v>
+        <v>1001014765993</v>
       </c>
       <c r="C243" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B244" s="3">
-        <v>1001025506777</v>
+        <v>1001025166776</v>
       </c>
       <c r="C244" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B245" s="3">
-        <v>1001025526778</v>
+        <v>1001025506777</v>
       </c>
       <c r="C245" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B246" s="3">
-        <v>1001304236685</v>
+        <v>1001025526778</v>
       </c>
       <c r="C246" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="B247" s="3">
-        <v>1001015496769</v>
+        <v>1001304236685</v>
       </c>
       <c r="C247" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="B248" s="3">
         <v>1001015496769</v>
@@ -5514,84 +5517,84 @@
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B249" s="3">
-        <v>1001014766798</v>
+        <v>1001015496769</v>
       </c>
       <c r="C249" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B250" s="3">
-        <v>1001015026797</v>
+        <v>1001014766798</v>
       </c>
       <c r="C250" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B251" s="3">
-        <v>1001205386222</v>
+        <v>1001015026797</v>
       </c>
       <c r="C251" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B252" s="3">
-        <v>1001092675224</v>
+        <v>1001205386222</v>
       </c>
       <c r="C252" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B253" s="3">
-        <v>1001225406223</v>
+        <v>1001092675224</v>
       </c>
       <c r="C253" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="B254" s="3">
-        <v>1001300366790</v>
+        <v>1001225406223</v>
       </c>
       <c r="C254" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>467</v>
+        <v>339</v>
       </c>
       <c r="B255" s="3">
-        <v>1001304096792</v>
+        <v>1001300366790</v>
       </c>
       <c r="C255" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>341</v>
+        <v>467</v>
       </c>
       <c r="B256" s="3">
         <v>1001304096792</v>
@@ -5602,62 +5605,62 @@
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>366</v>
+        <v>341</v>
       </c>
       <c r="B257" s="3">
-        <v>1001303637603</v>
+        <v>1001304096792</v>
       </c>
       <c r="C257" t="s">
-        <v>768</v>
+        <v>352</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>386</v>
+        <v>366</v>
       </c>
       <c r="B258" s="3">
         <v>1001303637603</v>
       </c>
       <c r="C258" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>342</v>
+        <v>386</v>
       </c>
       <c r="B259" s="3">
         <v>1001303637603</v>
       </c>
       <c r="C259" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>780</v>
+        <v>342</v>
       </c>
       <c r="B260" s="3">
         <v>1001303637603</v>
       </c>
       <c r="C260" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>387</v>
+        <v>779</v>
       </c>
       <c r="B261" s="3">
-        <v>1001303636794</v>
+        <v>1001303637603</v>
       </c>
       <c r="C261" t="s">
-        <v>353</v>
+        <v>767</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>487</v>
+        <v>387</v>
       </c>
       <c r="B262" s="3">
         <v>1001303636794</v>
@@ -5668,7 +5671,7 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>343</v>
+        <v>487</v>
       </c>
       <c r="B263" s="3">
         <v>1001303636794</v>
@@ -5679,51 +5682,51 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B264" s="3">
-        <v>1001302596795</v>
+        <v>1001303636794</v>
       </c>
       <c r="C264" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B265" s="3">
-        <v>1001302596796</v>
+        <v>1001302596795</v>
       </c>
       <c r="C265" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B266" s="3">
-        <v>1001300456804</v>
+        <v>1001302596796</v>
       </c>
       <c r="C266" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>436</v>
+        <v>346</v>
       </c>
       <c r="B267" s="3">
-        <v>1001300366806</v>
+        <v>1001300456804</v>
       </c>
       <c r="C267" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>347</v>
+        <v>436</v>
       </c>
       <c r="B268" s="3">
         <v>1001300366806</v>
@@ -5734,62 +5737,62 @@
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B269" s="3">
-        <v>1001300516803</v>
+        <v>1001300366806</v>
       </c>
       <c r="C269" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B270" s="3">
-        <v>1001300366807</v>
+        <v>1001300516803</v>
       </c>
       <c r="C270" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>360</v>
+        <v>349</v>
       </c>
       <c r="B271" s="3">
         <v>1001300366807</v>
       </c>
       <c r="C271" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B272" s="3">
-        <v>1001300516785</v>
+        <v>1001300366807</v>
       </c>
       <c r="C272" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>528</v>
+        <v>362</v>
       </c>
       <c r="B273" s="3">
-        <v>1001300456787</v>
+        <v>1001300516785</v>
       </c>
       <c r="C273" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>543</v>
+        <v>528</v>
       </c>
       <c r="B274" s="3">
         <v>1001300456787</v>
@@ -5800,7 +5803,7 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>364</v>
+        <v>543</v>
       </c>
       <c r="B275" s="3">
         <v>1001300456787</v>
@@ -5811,62 +5814,62 @@
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B276" s="3">
-        <v>1001302596795</v>
+        <v>1001300456787</v>
       </c>
       <c r="C276" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B277" s="3">
-        <v>1001012486332</v>
+        <v>1001302596795</v>
       </c>
       <c r="C277" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B278" s="3">
-        <v>1001012566345</v>
+        <v>1001012486332</v>
       </c>
       <c r="C278" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B279" s="3">
-        <v>1001031076528</v>
+        <v>1001012566345</v>
       </c>
       <c r="C279" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>404</v>
+        <v>373</v>
       </c>
       <c r="B280" s="3">
-        <v>1001020836761</v>
+        <v>1001031076528</v>
       </c>
       <c r="C280" t="s">
-        <v>381</v>
+        <v>374</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B281" s="3">
         <v>1001020836761</v>
@@ -5877,7 +5880,7 @@
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>380</v>
+        <v>409</v>
       </c>
       <c r="B282" s="3">
         <v>1001020836761</v>
@@ -5888,18 +5891,18 @@
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="B283" s="3">
-        <v>1001020846764</v>
+        <v>1001020836761</v>
       </c>
       <c r="C283" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="B284" s="3">
         <v>1001020846764</v>
@@ -5910,7 +5913,7 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>382</v>
+        <v>410</v>
       </c>
       <c r="B285" s="3">
         <v>1001020846764</v>
@@ -5921,18 +5924,18 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>483</v>
+        <v>382</v>
       </c>
       <c r="B286" s="3">
-        <v>1001300366790</v>
+        <v>1001020846764</v>
       </c>
       <c r="C286" t="s">
-        <v>350</v>
+        <v>383</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>384</v>
+        <v>483</v>
       </c>
       <c r="B287" s="3">
         <v>1001300366790</v>
@@ -5943,18 +5946,18 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>340</v>
+        <v>384</v>
       </c>
       <c r="B288" s="3">
-        <v>1001304096791</v>
+        <v>1001300366790</v>
       </c>
       <c r="C288" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>458</v>
+        <v>340</v>
       </c>
       <c r="B289" s="3">
         <v>1001304096791</v>
@@ -5965,7 +5968,7 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>385</v>
+        <v>458</v>
       </c>
       <c r="B290" s="3">
         <v>1001304096791</v>
@@ -5976,73 +5979,73 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B291" s="3">
-        <v>1001302596795</v>
+        <v>1001304096791</v>
       </c>
       <c r="C291" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B292" s="3">
-        <v>1001300516803</v>
+        <v>1001302596795</v>
       </c>
       <c r="C292" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B293" s="3">
-        <v>1001300456804</v>
+        <v>1001300516803</v>
       </c>
       <c r="C293" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B294" s="3">
-        <v>1001300366807</v>
+        <v>1001300456804</v>
       </c>
       <c r="C294" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B295" s="3">
-        <v>1001302596796</v>
+        <v>1001300366807</v>
       </c>
       <c r="C295" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>442</v>
+        <v>392</v>
       </c>
       <c r="B296" s="3">
-        <v>1001023696765</v>
+        <v>1001302596796</v>
       </c>
       <c r="C296" t="s">
-        <v>395</v>
+        <v>355</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>461</v>
+        <v>442</v>
       </c>
       <c r="B297" s="3">
         <v>1001023696765</v>
@@ -6053,7 +6056,7 @@
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>394</v>
+        <v>461</v>
       </c>
       <c r="B298" s="3">
         <v>1001023696765</v>
@@ -6064,18 +6067,18 @@
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="B299" s="3">
-        <v>1001023696767</v>
+        <v>1001023696765</v>
       </c>
       <c r="C299" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="B300" s="3">
         <v>1001023696767</v>
@@ -6086,7 +6089,7 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>398</v>
+        <v>411</v>
       </c>
       <c r="B301" s="3">
         <v>1001023696767</v>
@@ -6097,18 +6100,18 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="B302" s="3">
-        <v>1001024976829</v>
+        <v>1001023696767</v>
       </c>
       <c r="C302" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B303" s="3">
         <v>1001024976829</v>
@@ -6119,29 +6122,29 @@
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="B304" s="3">
-        <v>1001022376722</v>
+        <v>1001024976829</v>
       </c>
       <c r="C304" t="s">
-        <v>114</v>
+        <v>393</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>441</v>
+        <v>414</v>
       </c>
       <c r="B305" s="3">
-        <v>1001020846762</v>
+        <v>1001022376722</v>
       </c>
       <c r="C305" t="s">
-        <v>416</v>
+        <v>114</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>460</v>
+        <v>441</v>
       </c>
       <c r="B306" s="3">
         <v>1001020846762</v>
@@ -6152,7 +6155,7 @@
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>415</v>
+        <v>460</v>
       </c>
       <c r="B307" s="3">
         <v>1001020846762</v>
@@ -6163,18 +6166,18 @@
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>119</v>
+        <v>415</v>
       </c>
       <c r="B308" s="3">
-        <v>1001022656853</v>
+        <v>1001020846762</v>
       </c>
       <c r="C308" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>482</v>
+        <v>119</v>
       </c>
       <c r="B309" s="3">
         <v>1001022656853</v>
@@ -6185,18 +6188,18 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>564</v>
+        <v>482</v>
       </c>
       <c r="B310" s="3">
-        <v>1001022656948</v>
+        <v>1001022656853</v>
       </c>
       <c r="C310" t="s">
-        <v>555</v>
+        <v>419</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>558</v>
+        <v>564</v>
       </c>
       <c r="B311" s="3">
         <v>1001022656948</v>
@@ -6207,7 +6210,7 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>418</v>
+        <v>558</v>
       </c>
       <c r="B312" s="3">
         <v>1001022656948</v>
@@ -6218,29 +6221,29 @@
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="B313" s="3">
-        <v>1001022656852</v>
+        <v>1001022656948</v>
       </c>
       <c r="C313" t="s">
-        <v>425</v>
+        <v>555</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>443</v>
+        <v>424</v>
       </c>
       <c r="B314" s="3">
-        <v>1001020836759</v>
+        <v>1001022656852</v>
       </c>
       <c r="C314" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="B315" s="3">
         <v>1001020836759</v>
@@ -6251,7 +6254,7 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>426</v>
+        <v>459</v>
       </c>
       <c r="B316" s="3">
         <v>1001020836759</v>
@@ -6262,51 +6265,51 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B317" s="3">
-        <v>1001023856870</v>
+        <v>1001020836759</v>
       </c>
       <c r="C317" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="B318" s="3">
-        <v>1001013956426</v>
+        <v>1001023856870</v>
       </c>
       <c r="C318" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="B319" s="3">
-        <v>1001093345495</v>
+        <v>1001013956426</v>
       </c>
       <c r="C319" t="s">
-        <v>433</v>
+        <v>422</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>475</v>
+        <v>446</v>
       </c>
       <c r="B320" s="3">
-        <v>1001022656868</v>
+        <v>1001093345495</v>
       </c>
       <c r="C320" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>447</v>
+        <v>475</v>
       </c>
       <c r="B321" s="3">
         <v>1001022656868</v>
@@ -6317,18 +6320,18 @@
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>161</v>
+        <v>447</v>
       </c>
       <c r="B322" s="3">
-        <v>1001034065698</v>
+        <v>1001022656868</v>
       </c>
       <c r="C322" t="s">
-        <v>420</v>
+        <v>448</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="B323" s="3">
         <v>1001034065698</v>
@@ -6339,7 +6342,7 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>473</v>
+        <v>179</v>
       </c>
       <c r="B324" s="3">
         <v>1001034065698</v>
@@ -6350,7 +6353,7 @@
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>451</v>
+        <v>473</v>
       </c>
       <c r="B325" s="3">
         <v>1001034065698</v>
@@ -6361,29 +6364,29 @@
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B326" s="3">
-        <v>1001084216206</v>
+        <v>1001034065698</v>
       </c>
       <c r="C326" t="s">
-        <v>378</v>
+        <v>420</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="B327" s="3">
-        <v>1001015646861</v>
+        <v>1001084216206</v>
       </c>
       <c r="C327" t="s">
-        <v>417</v>
+        <v>378</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="B328" s="3">
         <v>1001015646861</v>
@@ -6394,18 +6397,18 @@
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>439</v>
+        <v>453</v>
       </c>
       <c r="B329" s="3">
-        <v>1001025176768</v>
+        <v>1001015646861</v>
       </c>
       <c r="C329" t="s">
-        <v>440</v>
+        <v>417</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>462</v>
+        <v>439</v>
       </c>
       <c r="B330" s="3">
         <v>1001025176768</v>
@@ -6416,7 +6419,7 @@
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B331" s="3">
         <v>1001025176768</v>
@@ -6427,18 +6430,18 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>438</v>
+        <v>454</v>
       </c>
       <c r="B332" s="3">
-        <v>1001025486770</v>
+        <v>1001025176768</v>
       </c>
       <c r="C332" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
-        <v>463</v>
+        <v>438</v>
       </c>
       <c r="B333" s="3">
         <v>1001025486770</v>
@@ -6449,7 +6452,7 @@
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>455</v>
+        <v>463</v>
       </c>
       <c r="B334" s="3">
         <v>1001025486770</v>
@@ -6460,18 +6463,18 @@
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>202</v>
+        <v>455</v>
       </c>
       <c r="B335" s="3">
-        <v>1001012816340</v>
+        <v>1001025486770</v>
       </c>
       <c r="C335" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>477</v>
+        <v>202</v>
       </c>
       <c r="B336" s="3">
         <v>1001012816340</v>
@@ -6482,7 +6485,7 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>456</v>
+        <v>477</v>
       </c>
       <c r="B337" s="3">
         <v>1001012816340</v>
@@ -6493,18 +6496,18 @@
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>301</v>
+        <v>456</v>
       </c>
       <c r="B338" s="3">
-        <v>1001203146834</v>
+        <v>1001012816340</v>
       </c>
       <c r="C338" t="s">
-        <v>423</v>
+        <v>431</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>450</v>
+        <v>301</v>
       </c>
       <c r="B339" s="3">
         <v>1001203146834</v>
@@ -6515,7 +6518,7 @@
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>474</v>
+        <v>450</v>
       </c>
       <c r="B340" s="3">
         <v>1001203146834</v>
@@ -6526,7 +6529,7 @@
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="B341" s="3">
         <v>1001203146834</v>
@@ -6537,40 +6540,40 @@
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="B342" s="3">
-        <v>1001300456788</v>
+        <v>1001203146834</v>
       </c>
       <c r="C342" t="s">
-        <v>470</v>
+        <v>423</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="B343" s="3">
-        <v>1001300516786</v>
+        <v>1001300456788</v>
       </c>
       <c r="C343" t="s">
-        <v>485</v>
+        <v>470</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>539</v>
+        <v>484</v>
       </c>
       <c r="B344" s="3">
-        <v>1001092436495</v>
+        <v>1001300516786</v>
       </c>
       <c r="C344" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="B345" s="3">
         <v>1001092436495</v>
@@ -6581,7 +6584,7 @@
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>489</v>
+        <v>546</v>
       </c>
       <c r="B346" s="3">
         <v>1001092436495</v>
@@ -6592,84 +6595,84 @@
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B347" s="3">
-        <v>1001025526901</v>
+        <v>1001092436495</v>
       </c>
       <c r="C347" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="B348" s="3">
-        <v>1001025546931</v>
+        <v>1001025526901</v>
       </c>
       <c r="C348" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="B349" s="3">
-        <v>1001010017539</v>
+        <v>1001025546931</v>
       </c>
       <c r="C349" t="s">
-        <v>769</v>
+        <v>494</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>532</v>
+        <v>502</v>
       </c>
       <c r="B350" s="3">
         <v>1001010017539</v>
       </c>
       <c r="C350" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>496</v>
+        <v>532</v>
       </c>
       <c r="B351" s="3">
         <v>1001010017539</v>
       </c>
       <c r="C351" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>774</v>
+        <v>496</v>
       </c>
       <c r="B352" s="3">
         <v>1001010017539</v>
       </c>
       <c r="C352" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>499</v>
+        <v>773</v>
       </c>
       <c r="B353" s="3">
-        <v>1001025766909</v>
+        <v>1001010017539</v>
       </c>
       <c r="C353" t="s">
-        <v>498</v>
+        <v>768</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>533</v>
+        <v>499</v>
       </c>
       <c r="B354" s="3">
         <v>1001025766909</v>
@@ -6680,7 +6683,7 @@
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>497</v>
+        <v>533</v>
       </c>
       <c r="B355" s="3">
         <v>1001025766909</v>
@@ -6691,18 +6694,18 @@
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>531</v>
+        <v>497</v>
       </c>
       <c r="B356" s="3">
-        <v>1001010014558</v>
+        <v>1001025766909</v>
       </c>
       <c r="C356" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>500</v>
+        <v>531</v>
       </c>
       <c r="B357" s="3">
         <v>1001010014558</v>
@@ -6713,18 +6716,18 @@
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>526</v>
+        <v>500</v>
       </c>
       <c r="B358" s="3">
-        <v>1001012596802</v>
+        <v>1001010014558</v>
       </c>
       <c r="C358" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="B359" s="3">
         <v>1001012596802</v>
@@ -6735,7 +6738,7 @@
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>503</v>
+        <v>535</v>
       </c>
       <c r="B360" s="3">
         <v>1001012596802</v>
@@ -6746,18 +6749,18 @@
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>521</v>
+        <v>503</v>
       </c>
       <c r="B361" s="3">
-        <v>1001012596801</v>
+        <v>1001012596802</v>
       </c>
       <c r="C361" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="B362" s="3">
         <v>1001012596801</v>
@@ -6768,7 +6771,7 @@
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>505</v>
+        <v>534</v>
       </c>
       <c r="B363" s="3">
         <v>1001012596801</v>
@@ -6779,161 +6782,161 @@
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B364" s="3">
-        <v>1001062353684</v>
+        <v>1001012596801</v>
       </c>
       <c r="C364" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="B365" s="3">
-        <v>1001010014555</v>
+        <v>1001062353684</v>
       </c>
       <c r="C365" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="B366" s="3">
-        <v>1001083424691</v>
+        <v>1001010014555</v>
       </c>
       <c r="C366" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="B367" s="3">
-        <v>1001190765679</v>
+        <v>1001083424691</v>
       </c>
       <c r="C367" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B368" s="3">
-        <v>1001085636200</v>
+        <v>1001190765679</v>
       </c>
       <c r="C368" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="B369" s="3">
-        <v>1001020836253</v>
+        <v>1001085636200</v>
       </c>
       <c r="C369" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="B370" s="3">
-        <v>1001084226492</v>
+        <v>1001020836253</v>
       </c>
       <c r="C370" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="B371" s="3">
-        <v>1001223296921</v>
+        <v>1001084226492</v>
       </c>
       <c r="C371" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="B372" s="3">
-        <v>1001053944786</v>
+        <v>1001223296921</v>
       </c>
       <c r="C372" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="B373" s="3">
-        <v>1001010016839</v>
+        <v>1001053944786</v>
       </c>
       <c r="C373" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>536</v>
+        <v>529</v>
       </c>
       <c r="B374" s="3">
-        <v>1001023857038</v>
+        <v>1001010016839</v>
       </c>
       <c r="C374" t="s">
-        <v>577</v>
+        <v>530</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B375" s="3">
-        <v>1001040434903</v>
+        <v>1001023857038</v>
       </c>
       <c r="C375" t="s">
-        <v>538</v>
+        <v>577</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="B376" s="3">
-        <v>1001080216842</v>
+        <v>1001040434903</v>
       </c>
       <c r="C376" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>553</v>
+        <v>540</v>
       </c>
       <c r="B377" s="3">
-        <v>1001022466951</v>
+        <v>1001080216842</v>
       </c>
       <c r="C377" t="s">
-        <v>554</v>
+        <v>541</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="B378" s="3">
         <v>1001022466951</v>
@@ -6944,95 +6947,95 @@
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B379" s="3">
-        <v>1001035276653</v>
+        <v>1001022466951</v>
       </c>
       <c r="C379" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="B380" s="3">
-        <v>1001062353680</v>
+        <v>1001035276653</v>
       </c>
       <c r="C380" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="B381" s="3">
-        <v>1001061971146</v>
+        <v>1001062353680</v>
       </c>
       <c r="C381" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B382" s="3">
-        <v>1001225636201</v>
+        <v>1001061971146</v>
       </c>
       <c r="C382" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="B383" s="3">
-        <v>1001095227035</v>
+        <v>1001225636201</v>
       </c>
       <c r="C383" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B384" s="3">
-        <v>1001023857038</v>
+        <v>1001095227035</v>
       </c>
       <c r="C384" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B385" s="3">
-        <v>1001025027040</v>
+        <v>1001023857038</v>
       </c>
       <c r="C385" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B386" s="3">
-        <v>1001223297103</v>
+        <v>1001025027040</v>
       </c>
       <c r="C386" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B387" s="3">
         <v>1001223297103</v>
@@ -7043,7 +7046,7 @@
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B388" s="3">
         <v>1001223297103</v>
@@ -7054,18 +7057,18 @@
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>602</v>
+        <v>581</v>
       </c>
       <c r="B389" s="3">
-        <v>1001010032675</v>
+        <v>1001223297103</v>
       </c>
       <c r="C389" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
-        <v>583</v>
+        <v>602</v>
       </c>
       <c r="B390" s="3">
         <v>1001010032675</v>
@@ -7076,18 +7079,18 @@
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
-        <v>607</v>
+        <v>583</v>
       </c>
       <c r="B391" s="3">
-        <v>1001035937001</v>
+        <v>1001010032675</v>
       </c>
       <c r="C391" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
-        <v>585</v>
+        <v>607</v>
       </c>
       <c r="B392" s="3">
         <v>1001035937001</v>
@@ -7098,18 +7101,18 @@
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
-        <v>608</v>
+        <v>585</v>
       </c>
       <c r="B393" s="3">
-        <v>1001084217090</v>
+        <v>1001035937001</v>
       </c>
       <c r="C393" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
-        <v>587</v>
+        <v>608</v>
       </c>
       <c r="B394" s="3">
         <v>1001084217090</v>
@@ -7120,18 +7123,18 @@
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
-        <v>609</v>
+        <v>587</v>
       </c>
       <c r="B395" s="3">
-        <v>1001022377066</v>
+        <v>1001084217090</v>
       </c>
       <c r="C395" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
-        <v>589</v>
+        <v>609</v>
       </c>
       <c r="B396" s="3">
         <v>1001022377066</v>
@@ -7142,18 +7145,18 @@
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
-        <v>610</v>
+        <v>589</v>
       </c>
       <c r="B397" s="3">
-        <v>1001022467080</v>
+        <v>1001022377066</v>
       </c>
       <c r="C397" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
-        <v>591</v>
+        <v>610</v>
       </c>
       <c r="B398" s="3">
         <v>1001022467080</v>
@@ -7164,18 +7167,18 @@
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
-        <v>611</v>
+        <v>591</v>
       </c>
       <c r="B399" s="3">
-        <v>1001025507255</v>
+        <v>1001022467080</v>
       </c>
       <c r="C399" t="s">
-        <v>745</v>
+        <v>592</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
-        <v>593</v>
+        <v>611</v>
       </c>
       <c r="B400" s="3">
         <v>1001025507255</v>
@@ -7186,7 +7189,7 @@
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
-        <v>752</v>
+        <v>593</v>
       </c>
       <c r="B401" s="3">
         <v>1001025507255</v>
@@ -7197,18 +7200,18 @@
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
-        <v>614</v>
+        <v>752</v>
       </c>
       <c r="B402" s="3">
-        <v>1001022657075</v>
+        <v>1001025507255</v>
       </c>
       <c r="C402" t="s">
-        <v>595</v>
+        <v>745</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
-        <v>594</v>
+        <v>614</v>
       </c>
       <c r="B403" s="3">
         <v>1001022657075</v>
@@ -7219,18 +7222,18 @@
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
-        <v>612</v>
+        <v>594</v>
       </c>
       <c r="B404" s="3">
-        <v>1001022467082</v>
+        <v>1001022657075</v>
       </c>
       <c r="C404" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
-        <v>596</v>
+        <v>612</v>
       </c>
       <c r="B405" s="3">
         <v>1001022467082</v>
@@ -7241,18 +7244,18 @@
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
-        <v>613</v>
+        <v>596</v>
       </c>
       <c r="B406" s="3">
-        <v>1001022377070</v>
+        <v>1001022467082</v>
       </c>
       <c r="C406" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
-        <v>598</v>
+        <v>613</v>
       </c>
       <c r="B407" s="3">
         <v>1001022377070</v>
@@ -7263,18 +7266,18 @@
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
-        <v>615</v>
+        <v>598</v>
       </c>
       <c r="B408" s="3">
-        <v>1001022657073</v>
+        <v>1001022377070</v>
       </c>
       <c r="C408" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>600</v>
+        <v>615</v>
       </c>
       <c r="B409" s="3">
         <v>1001022657073</v>
@@ -7285,18 +7288,18 @@
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
-        <v>626</v>
+        <v>600</v>
       </c>
       <c r="B410" s="3">
-        <v>1001010027126</v>
+        <v>1001022657073</v>
       </c>
       <c r="C410" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
-        <v>603</v>
+        <v>626</v>
       </c>
       <c r="B411" s="3">
         <v>1001010027126</v>
@@ -7307,18 +7310,18 @@
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B412" s="3">
-        <v>1001010027125</v>
+        <v>1001010027126</v>
       </c>
       <c r="C412" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>627</v>
+        <v>605</v>
       </c>
       <c r="B413" s="3">
         <v>1001010027125</v>
@@ -7329,18 +7332,18 @@
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
-        <v>649</v>
+        <v>627</v>
       </c>
       <c r="B414" s="3">
-        <v>1001016366888</v>
+        <v>1001010027125</v>
       </c>
       <c r="C414" t="s">
-        <v>629</v>
+        <v>606</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>628</v>
+        <v>649</v>
       </c>
       <c r="B415" s="3">
         <v>1001016366888</v>
@@ -7351,18 +7354,18 @@
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
-        <v>650</v>
+        <v>628</v>
       </c>
       <c r="B416" s="3">
-        <v>1001300367133</v>
+        <v>1001016366888</v>
       </c>
       <c r="C416" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="B417" s="3">
         <v>1001300367133</v>
@@ -7373,40 +7376,40 @@
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
-        <v>648</v>
+        <v>630</v>
       </c>
       <c r="B418" s="3">
-        <v>1001303637564</v>
+        <v>1001300367133</v>
       </c>
       <c r="C418" t="s">
-        <v>767</v>
+        <v>631</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
-        <v>632</v>
+        <v>648</v>
       </c>
       <c r="B419" s="3">
         <v>1001303637564</v>
       </c>
       <c r="C419" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
-        <v>651</v>
+        <v>632</v>
       </c>
       <c r="B420" s="3">
-        <v>1001304527146</v>
+        <v>1001303637564</v>
       </c>
       <c r="C420" t="s">
-        <v>634</v>
+        <v>766</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>633</v>
+        <v>651</v>
       </c>
       <c r="B421" s="3">
         <v>1001304527146</v>
@@ -7417,18 +7420,18 @@
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>646</v>
+        <v>633</v>
       </c>
       <c r="B422" s="3">
-        <v>1001300517134</v>
+        <v>1001304527146</v>
       </c>
       <c r="C422" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
-        <v>635</v>
+        <v>646</v>
       </c>
       <c r="B423" s="3">
         <v>1001300517134</v>
@@ -7439,29 +7442,29 @@
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B424" s="3">
-        <v>1001300457135</v>
+        <v>1001300517134</v>
       </c>
       <c r="C424" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B425" s="3">
-        <v>1001304527144</v>
+        <v>1001300457135</v>
       </c>
       <c r="C425" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="B426" s="3">
         <v>1001304527144</v>
@@ -7472,18 +7475,18 @@
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>671</v>
+        <v>647</v>
       </c>
       <c r="B427" s="3">
-        <v>1001081596620</v>
+        <v>1001304527144</v>
       </c>
       <c r="C427" t="s">
-        <v>653</v>
+        <v>640</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>654</v>
+        <v>671</v>
       </c>
       <c r="B428" s="3">
         <v>1001081596620</v>
@@ -7494,18 +7497,18 @@
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>676</v>
+        <v>654</v>
       </c>
       <c r="B429" s="3">
-        <v>1001085637187</v>
+        <v>1001081596620</v>
       </c>
       <c r="C429" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="B430" s="3">
         <v>1001085637187</v>
@@ -7516,18 +7519,18 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
-        <v>675</v>
+        <v>656</v>
       </c>
       <c r="B431" s="3">
-        <v>1001015676877</v>
+        <v>1001085637187</v>
       </c>
       <c r="C431" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>658</v>
+        <v>675</v>
       </c>
       <c r="B432" s="3">
         <v>1001015676877</v>
@@ -7538,18 +7541,18 @@
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
-        <v>678</v>
+        <v>658</v>
       </c>
       <c r="B433" s="3">
-        <v>1001015686878</v>
+        <v>1001015676877</v>
       </c>
       <c r="C433" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
-        <v>660</v>
+        <v>678</v>
       </c>
       <c r="B434" s="3">
         <v>1001015686878</v>
@@ -7560,51 +7563,51 @@
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B435" s="3">
-        <v>1001302277232</v>
+        <v>1001015686878</v>
       </c>
       <c r="C435" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B436" s="3">
-        <v>1001304497237</v>
+        <v>1001302277232</v>
       </c>
       <c r="C436" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B437" s="3">
-        <v>1001303107241</v>
+        <v>1001304497237</v>
       </c>
       <c r="C437" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="B438" s="3">
-        <v>1002162216872</v>
+        <v>1001303107241</v>
       </c>
       <c r="C438" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="B439" s="3">
         <v>1002162216872</v>
@@ -7615,18 +7618,18 @@
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
-        <v>692</v>
+        <v>677</v>
       </c>
       <c r="B440" s="3">
-        <v>1001063237147</v>
+        <v>1002162216872</v>
       </c>
       <c r="C440" t="s">
-        <v>684</v>
+        <v>670</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
-        <v>679</v>
+        <v>692</v>
       </c>
       <c r="B441" s="3">
         <v>1001063237147</v>
@@ -7637,18 +7640,18 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
-        <v>691</v>
+        <v>679</v>
       </c>
       <c r="B442" s="3">
-        <v>1001063097227</v>
+        <v>1001063237147</v>
       </c>
       <c r="C442" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="B443" s="3">
         <v>1001063097227</v>
@@ -7659,18 +7662,18 @@
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
       <c r="B444" s="3">
-        <v>1001066537225</v>
+        <v>1001063097227</v>
       </c>
       <c r="C444" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="B445" s="3">
         <v>1001066537225</v>
@@ -7681,18 +7684,18 @@
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="B446" s="3">
-        <v>1001066527226</v>
+        <v>1001066537225</v>
       </c>
       <c r="C446" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="B447" s="3">
         <v>1001066527226</v>
@@ -7703,29 +7706,29 @@
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B448" s="3">
-        <v>1001066547228</v>
+        <v>1001066527226</v>
       </c>
       <c r="C448" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
-        <v>699</v>
+        <v>683</v>
       </c>
       <c r="B449" s="3">
-        <v>1001063237229</v>
+        <v>1001066547228</v>
       </c>
       <c r="C449" t="s">
-        <v>696</v>
+        <v>688</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="B450" s="3">
         <v>1001063237229</v>
@@ -7736,18 +7739,18 @@
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
-        <v>701</v>
+        <v>693</v>
       </c>
       <c r="B451" s="3">
-        <v>1001063237150</v>
+        <v>1001063237229</v>
       </c>
       <c r="C451" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="B452" s="3">
         <v>1001063237150</v>
@@ -7758,18 +7761,18 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B453" s="3">
-        <v>1001022467276</v>
+        <v>1001063237150</v>
       </c>
       <c r="C453" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="B454" s="3">
         <v>1001022467276</v>
@@ -7780,18 +7783,18 @@
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
-        <v>479</v>
+        <v>700</v>
       </c>
       <c r="B455" s="3">
-        <v>1001022556837</v>
+        <v>1001022467276</v>
       </c>
       <c r="C455" t="s">
-        <v>480</v>
+        <v>698</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
-        <v>722</v>
+        <v>479</v>
       </c>
       <c r="B456" s="3">
         <v>1001022556837</v>
@@ -7802,29 +7805,29 @@
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="B457" s="5">
+        <v>722</v>
+      </c>
+      <c r="B457" s="3">
         <v>1001022556837</v>
       </c>
-      <c r="C457" s="6" t="s">
+      <c r="C457" t="s">
         <v>480</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B458" s="3">
-        <v>1001205376221</v>
-      </c>
-      <c r="C458" t="s">
-        <v>176</v>
+        <v>703</v>
+      </c>
+      <c r="B458" s="5">
+        <v>1001022556837</v>
+      </c>
+      <c r="C458" s="6" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
-        <v>720</v>
+        <v>178</v>
       </c>
       <c r="B459" s="3">
         <v>1001205376221</v>
@@ -7835,73 +7838,73 @@
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="B460" s="5">
+        <v>720</v>
+      </c>
+      <c r="B460" s="3">
         <v>1001205376221</v>
       </c>
-      <c r="C460" s="6" t="s">
+      <c r="C460" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="B461" s="3">
-        <v>1001304197608</v>
-      </c>
-      <c r="C461" t="s">
-        <v>793</v>
+        <v>704</v>
+      </c>
+      <c r="B461" s="5">
+        <v>1001205376221</v>
+      </c>
+      <c r="C461" s="6" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>717</v>
+        <v>488</v>
       </c>
       <c r="B462" s="3">
         <v>1001304197608</v>
       </c>
       <c r="C462" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
-        <v>706</v>
+        <v>717</v>
       </c>
       <c r="B463" s="3">
         <v>1001304197608</v>
       </c>
       <c r="C463" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="B464" s="5">
-        <v>1001010106325</v>
-      </c>
-      <c r="C464" s="6" t="s">
-        <v>51</v>
+        <v>706</v>
+      </c>
+      <c r="B464" s="3">
+        <v>1001304197608</v>
+      </c>
+      <c r="C464" t="s">
+        <v>792</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
-        <v>718</v>
+        <v>707</v>
       </c>
       <c r="B465" s="5">
-        <v>1001013957231</v>
+        <v>1001010106325</v>
       </c>
       <c r="C465" s="6" t="s">
-        <v>714</v>
+        <v>51</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
-        <v>708</v>
+        <v>718</v>
       </c>
       <c r="B466" s="5">
         <v>1001013957231</v>
@@ -7912,18 +7915,18 @@
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B467" s="3">
-        <v>1001220286279</v>
-      </c>
-      <c r="C467" t="s">
-        <v>47</v>
+        <v>708</v>
+      </c>
+      <c r="B467" s="5">
+        <v>1001013957231</v>
+      </c>
+      <c r="C467" s="6" t="s">
+        <v>714</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
-        <v>724</v>
+        <v>46</v>
       </c>
       <c r="B468" s="3">
         <v>1001220286279</v>
@@ -7934,29 +7937,29 @@
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="B469" s="5">
+        <v>724</v>
+      </c>
+      <c r="B469" s="3">
         <v>1001220286279</v>
       </c>
-      <c r="C469" s="6" t="s">
+      <c r="C469" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
-        <v>719</v>
+        <v>709</v>
       </c>
       <c r="B470" s="5">
-        <v>1001223297092</v>
+        <v>1001220286279</v>
       </c>
       <c r="C470" s="6" t="s">
-        <v>715</v>
+        <v>47</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
-        <v>710</v>
+        <v>719</v>
       </c>
       <c r="B471" s="5">
         <v>1001223297092</v>
@@ -7967,18 +7970,18 @@
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="B472" s="3">
-        <v>1001020836724</v>
-      </c>
-      <c r="C472" t="s">
-        <v>573</v>
+        <v>710</v>
+      </c>
+      <c r="B472" s="5">
+        <v>1001223297092</v>
+      </c>
+      <c r="C472" s="6" t="s">
+        <v>715</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
-        <v>721</v>
+        <v>572</v>
       </c>
       <c r="B473" s="3">
         <v>1001020836724</v>
@@ -7989,29 +7992,29 @@
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="B474" s="5">
+        <v>721</v>
+      </c>
+      <c r="B474" s="3">
         <v>1001020836724</v>
       </c>
-      <c r="C474" s="6" t="s">
+      <c r="C474" t="s">
         <v>573</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
       <c r="B475" s="5">
-        <v>1001062475707</v>
+        <v>1001020836724</v>
       </c>
       <c r="C475" s="6" t="s">
-        <v>716</v>
+        <v>573</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
-        <v>712</v>
+        <v>723</v>
       </c>
       <c r="B476" s="5">
         <v>1001062475707</v>
@@ -8022,40 +8025,40 @@
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B477" s="5">
-        <v>1001033856609</v>
+        <v>1001062475707</v>
       </c>
       <c r="C477" s="6" t="s">
-        <v>227</v>
+        <v>716</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="B478" s="5">
+        <v>1001033856609</v>
+      </c>
+      <c r="C478" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A479" s="2" t="s">
         <v>725</v>
       </c>
-      <c r="B478" s="3">
+      <c r="B479" s="3">
         <v>1001025767284</v>
       </c>
-      <c r="C478" s="6" t="s">
+      <c r="C479" s="6" t="s">
         <v>726</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A479" s="7" t="s">
-        <v>727</v>
-      </c>
-      <c r="B479" s="5">
-        <v>1001301777332</v>
-      </c>
-      <c r="C479" s="6" t="s">
-        <v>733</v>
       </c>
     </row>
     <row r="480" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A480" s="7" t="s">
-        <v>741</v>
+        <v>727</v>
       </c>
       <c r="B480" s="5">
         <v>1001301777332</v>
@@ -8066,18 +8069,18 @@
     </row>
     <row r="481" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A481" s="7" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="B481" s="5">
-        <v>1001303987333</v>
+        <v>1001301777332</v>
       </c>
       <c r="C481" s="6" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="482" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A482" s="7" t="s">
-        <v>728</v>
+        <v>742</v>
       </c>
       <c r="B482" s="5">
         <v>1001303987333</v>
@@ -8088,29 +8091,29 @@
     </row>
     <row r="483" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A483" s="7" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B483" s="5">
-        <v>1001012426220</v>
+        <v>1001303987333</v>
       </c>
       <c r="C483" s="6" t="s">
-        <v>190</v>
+        <v>734</v>
       </c>
     </row>
     <row r="484" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A484" s="7" t="s">
-        <v>740</v>
+        <v>729</v>
       </c>
       <c r="B484" s="5">
-        <v>1001300387157</v>
+        <v>1001012426220</v>
       </c>
       <c r="C484" s="6" t="s">
-        <v>735</v>
+        <v>190</v>
       </c>
     </row>
     <row r="485" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A485" s="7" t="s">
-        <v>730</v>
+        <v>740</v>
       </c>
       <c r="B485" s="5">
         <v>1001300387157</v>
@@ -8121,18 +8124,18 @@
     </row>
     <row r="486" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A486" s="7" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B486" s="5">
-        <v>1001220226208</v>
+        <v>1001300387157</v>
       </c>
       <c r="C486" s="6" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="487" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A487" s="7" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="B487" s="5">
         <v>1001220226208</v>
@@ -8143,18 +8146,18 @@
     </row>
     <row r="488" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A488" s="7" t="s">
+        <v>738</v>
+      </c>
+      <c r="B488" s="5">
+        <v>1001220226208</v>
+      </c>
+      <c r="C488" s="6" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A489" s="7" t="s">
         <v>732</v>
-      </c>
-      <c r="B488" s="5">
-        <v>1001063656967</v>
-      </c>
-      <c r="C488" s="6" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A489" s="2" t="s">
-        <v>739</v>
       </c>
       <c r="B489" s="5">
         <v>1001063656967</v>
@@ -8165,193 +8168,204 @@
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
-        <v>748</v>
-      </c>
-      <c r="B490" s="3">
-        <v>1001065616832</v>
-      </c>
-      <c r="C490" t="s">
-        <v>749</v>
+        <v>739</v>
+      </c>
+      <c r="B490" s="5">
+        <v>1001063656967</v>
+      </c>
+      <c r="C490" s="6" t="s">
+        <v>737</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="B491" s="3">
-        <v>1001060677299</v>
+        <v>1001065616832</v>
       </c>
       <c r="C491" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="B492" s="3">
-        <v>1001223907288</v>
+        <v>1001060677299</v>
       </c>
       <c r="C492" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="B493" s="3">
-        <v>1001223907288</v>
+        <v>1001453907612</v>
       </c>
       <c r="C493" t="s">
-        <v>756</v>
+        <v>794</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B494" s="3">
-        <v>1001015026797</v>
+        <v>1001453907612</v>
       </c>
       <c r="C494" t="s">
-        <v>759</v>
+        <v>794</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="B495" s="3">
-        <v>1001095226925</v>
+        <v>1001015026797</v>
       </c>
       <c r="C495" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="B496" s="3">
-        <v>1001035277059</v>
+        <v>1001095226925</v>
       </c>
       <c r="C496" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="B497" s="3">
-        <v>1001025767461</v>
+        <v>1001035277059</v>
       </c>
       <c r="C497" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="B498" s="3">
-        <v>1001303637564</v>
+        <v>1001025767461</v>
       </c>
       <c r="C498" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="B499" s="3">
-        <v>1001026947371</v>
+        <v>1001303637564</v>
       </c>
       <c r="C499" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="B500" s="3">
-        <v>1001012427523</v>
+        <v>1001026947371</v>
       </c>
       <c r="C500" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="B501" s="3">
-        <v>1001022467083</v>
+        <v>1001012427523</v>
       </c>
       <c r="C501" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="B502" s="3">
-        <v>1001307357489</v>
+        <v>1001022467083</v>
       </c>
       <c r="C502" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="B503" s="3">
-        <v>1001025507271</v>
+        <v>1001307357489</v>
       </c>
       <c r="C503" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="B504" s="3">
-        <v>1001084856008</v>
+        <v>1001025507271</v>
       </c>
       <c r="C504" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="B505" s="3">
-        <v>1001200677442</v>
+        <v>1001084856008</v>
       </c>
       <c r="C505" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
+        <v>786</v>
+      </c>
+      <c r="B506" s="3">
+        <v>1001200677442</v>
+      </c>
+      <c r="C506" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A507" s="2" t="s">
+        <v>788</v>
+      </c>
+      <c r="B507" s="3">
+        <v>1001300456946</v>
+      </c>
+      <c r="C507" t="s">
         <v>789</v>
       </c>
-      <c r="B506" s="3">
-        <v>1001300456946</v>
-      </c>
-      <c r="C506" t="s">
-        <v>790</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C506" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
+  <autoFilter ref="A1:C507" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2652FA7-7F12-46C9-A9D6-C072A9038291}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B54395-E634-4F93-B8D2-03413A7F1A41}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$507</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$509</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="794">
   <si>
     <t>1С</t>
   </si>
@@ -93,9 +93,6 @@
     <t>4993 САЛЯМИ ИТАЛЬЯНСКАЯ с/к в/у 1/250*8_120c ОСТАНКИНО</t>
   </si>
   <si>
-    <t>САЛЯМИ ИТАЛЬЯНСКАЯ с/к в/у 1/250*8_120c</t>
-  </si>
-  <si>
     <t>5246 ДОКТОРСКАЯ ПРЕМИУМ вар б/о мгс_30с ОСТАНКИНО</t>
   </si>
   <si>
@@ -153,9 +150,6 @@
     <t>5851 ЭКСТРА Папа может вар п/о   ОСТАНКИНО</t>
   </si>
   <si>
-    <t>ЭКСТРА Папа может вар п/о.</t>
-  </si>
-  <si>
     <t>5931 ОХОТНИЧЬЯ Папа может с/к в/у 1/220 8шт.   ОСТАНКИНО</t>
   </si>
   <si>
@@ -198,9 +192,6 @@
     <t>МЯСНАЯ Папа может вар п/о 0.4кг 8шт.</t>
   </si>
   <si>
-    <t>ФИЛЕЙНАЯ Папа может вар п/о 0.4кг 8шт.</t>
-  </si>
-  <si>
     <t>6353 ЭКСТРА Папа может вар п/о 0.4кг 8шт.  ОСТАНКИНО</t>
   </si>
   <si>
@@ -252,9 +243,6 @@
     <t>6527 ШПИКАЧКИ СОЧНЫЕ ПМ сар б/о мгс 1*3 45с ОСТАНКИНО</t>
   </si>
   <si>
-    <t>ШПИКАЧКИ СОЧНЫЕ ПМ САР Б/О МГС 1*3 45с</t>
-  </si>
-  <si>
     <t>СЕРВЕЛАТ ФИНСКИЙ СН в/к п/о 0.35кг 8шт</t>
   </si>
   <si>
@@ -618,9 +606,6 @@
     <t>6602 БАВАРСКИЕ ПМ сос ц/о мгс 0,35кг 8шт  Останкино</t>
   </si>
   <si>
-    <t xml:space="preserve"> БАВАРСКИЕ ПМ сос ц/о мгс 0.35кг 8шт.</t>
-  </si>
-  <si>
     <t>6656 ГОВЯЖЬИ СН сос п/о мгс 2*2  ОСТАНКИНО</t>
   </si>
   <si>
@@ -759,9 +744,6 @@
     <t>6661 СОЧНЫЙ ГРИЛЬ ПМ сос п/о мгс 1,5*4_Маяк Останкино</t>
   </si>
   <si>
-    <t>СОЧНЫЙ ГРИЛЬ ПМ сос п/о мгс 1,5*4_Маяк</t>
-  </si>
-  <si>
     <t>6701 СЕРВЕЛАТ ШВАРЦЕР ПМ в/к в/у 0.28кг 8шт.  ОСТАНКИНО</t>
   </si>
   <si>
@@ -780,9 +762,6 @@
     <t>6303 МЯСНЫЕ Папа может сос п/о мгс  1.5*3</t>
   </si>
   <si>
-    <t>МЯСНЫЕ Папа может сос п/о мгс  1.5*3</t>
-  </si>
-  <si>
     <t>3678 СОЧНЫЕ сос п/о мгс 2*2     ОСТАНКИНО</t>
   </si>
   <si>
@@ -861,9 +840,6 @@
     <t>МРАМОРНАЯ И БАЛЫКОВАЯ в/к с/н мгс 1/90</t>
   </si>
   <si>
-    <t xml:space="preserve">БАВАРСКИЕ ПМ сос ц/о мгс 0,35кг 8шт.  </t>
-  </si>
-  <si>
     <t>6026 ВЕТЧ.ОСОБАЯ Коровино п/о   ОСТАНКИНО</t>
   </si>
   <si>
@@ -1215,9 +1191,6 @@
     <t>6796 ОСТАНКИНСКАЯ в/к в/у  Останкино</t>
   </si>
   <si>
-    <t>МОЛОЧНЫЕ КЛАССИЧЕСКИЕ сос п/о мгс 2*4</t>
-  </si>
-  <si>
     <t>6765 РУБЛЕНЫЕ сос ц/о мгс 0.36кг 6шт.  ОСТАНКИНО</t>
   </si>
   <si>
@@ -2214,9 +2187,6 @@
     <t>7284 ДЛЯ ДЕТЕЙ сос п/о мгс 0,33кг 6шт  Останкино</t>
   </si>
   <si>
-    <t>ДЛЯ ДЕТЕЙ сос п/о мгс 0,33кг 6шт</t>
-  </si>
-  <si>
     <t>БОЯРСКАЯ ПМ п/к в/у 0.28кг_СНГ (7332)</t>
   </si>
   <si>
@@ -2316,9 +2286,6 @@
     <t>6925 ВЕТЧ.КЛАССИЧЕСКАЯ в/у 0,6кг 8шт. ОСТАНКИНО</t>
   </si>
   <si>
-    <t>ВЕТЧ.КЛАССИЧЕСКАЯ в/у 0.6кг 8шт.</t>
-  </si>
-  <si>
     <t>7059 ШПИКАЧКИ СОЧНЫЕ С БЕК. п/о мгс 0,3кг 60с ОСТАНКИНО</t>
   </si>
   <si>
@@ -2328,97 +2295,127 @@
     <t>7461 ДЛЯ ДЕТЕЙ Папа Может сос п/о мгс 0,33кг ОСТАНКИНО</t>
   </si>
   <si>
+    <t>7564 Балыковая в/к в/у Останкино Вес  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>БАЛЫКОВАЯ Останкино в/к в/у</t>
+  </si>
+  <si>
+    <t>БАЛЫКОВАЯ Останкино в/к в/у 0.33кг 8шт.</t>
+  </si>
+  <si>
+    <t>ДОКТОРСКАЯ ГОСТ Останкино вар п/о 0.35кг</t>
+  </si>
+  <si>
+    <t>7371 БРЕСТСКИЕ сос п/о в/у 0,3кг 8шт. ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>БРЕСТСКИЕ сос п/о в/у 0.3кг 8шт.</t>
+  </si>
+  <si>
+    <t>7523 ГОВЯЖЬЯ Папа Может вар п/о 0,4кг 6шт. ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>ГОВЯЖЬЯ Папа может вар п/о 0.4кг 6шт.</t>
+  </si>
+  <si>
+    <t>7539 ДОКТОРСКАЯ ГОСТ вар п/о 0,35кг ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>ЭКСТРА Папа может вар п/о 0.4кг 8шт_195к</t>
+  </si>
+  <si>
+    <t>6470 ВЕТЧ.МРАМОРНАЯ в/у_45с  Останкино</t>
+  </si>
+  <si>
+    <t>ВЕТЧ.МРАМОРНАЯ в/у_45с</t>
+  </si>
+  <si>
+    <t>7083 СЛИВОЧНЫЕ ПМ сос п/о мгс 1.5*4_А_50с  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>СЛИВОЧНЫЕ ПМ сос п/о мгс 1.5*4_А_50с</t>
+  </si>
+  <si>
+    <t>7603 БАЛЫКОВАЯ в/к в/у 0.33кг 8шт. ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7489 СЫРРРВЕЛАТ Папа Может в/к в/у 0,28кг 8шт. ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>СЫРРРВЕЛАТ Папа может в/к в/у 0.28кг 8шт</t>
+  </si>
+  <si>
+    <t>7271 МЯСНЫЕ С ГОВЯДИНОЙ ПМ сос п/о мгс 1.5*4  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>МЯСНЫЕ С ГОВЯДИНОЙ ПМ сос п/о мгс 1.5*4</t>
+  </si>
+  <si>
+    <t>6008 САЛО СОЛЕНОЕ С ЧЕРНЫМ ПЕРЦЕМ мл/к в/у ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>САЛО СОЛЕНОЕ С ЧЕРНЫМ ПЕРЦЕМ мл/к в/у</t>
+  </si>
+  <si>
+    <t>7422 НАБОР ДЛЯ ПИЦЦЫ с/к с/н мгс 3*3 HRC  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>НАБОР ДЛЯ ПИЦЦЫ с/к с/н мгс 3*3_HRC</t>
+  </si>
+  <si>
+    <t>6946 СЕРВЕЛАТ КРЕМЛЕВСКИЙ в/к в/у ВЕС  0,84кг ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>СЕРВЕЛАТ КРЕМЛЕВСКИЙ в/к в/у 0.84кг</t>
+  </si>
+  <si>
+    <t>ЭКСТРА Папа может с/к с/н в/у 1/100_Л10</t>
+  </si>
+  <si>
+    <t>СЕРВЕЛАТ ШВЕЙЦАРСК.в/к с/н в/у 1/100_Л11</t>
+  </si>
+  <si>
+    <t>7632 ЭКСТРА Папа может вар п/о 0.4кг 8шт_195к  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>БАЛЫК с/к с/н в/у 1/100 10шт_Л11</t>
+  </si>
+  <si>
+    <t>САЛЯМИ ИТАЛЬЯНСКАЯ с/к в/у 1/250*8_120с</t>
+  </si>
+  <si>
+    <t>ЭКСТРА Папа может вар п/о</t>
+  </si>
+  <si>
+    <t>ФИЛЕЙНАЯ Папа может вар п/о 0.4кг</t>
+  </si>
+  <si>
+    <t>ШПИКАЧКИ СОЧНЫЕ ПМ сар б/о мгс 1*3_45с</t>
+  </si>
+  <si>
+    <t>МЯСНЫЕ Папа может сар б/о мгс 1*3_О_45с</t>
+  </si>
+  <si>
+    <t>МОЛОЧНЫЕ КЛАССИЧЕСКИЕ сос п/о мгс 2*4_С</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ВЕТЧ.КЛАССИЧЕСКАЯ в/у 0.6кг 8шт. </t>
+  </si>
+  <si>
+    <t>7616 ЭКСТРА Папа может с/к с/н в/у 1/100_  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>АРОМАТНАЯ с/к с/н в/у 1/100 10шт_Л10 (7613)</t>
+  </si>
+  <si>
+    <t>БАВАРСКИЕ ПМ сос ц/о мгс 0.35кг 8шт.</t>
+  </si>
+  <si>
     <t>ДЛЯ ДЕТЕЙ Папа может сос п/о мгс 0.33кг</t>
   </si>
   <si>
-    <t>7564 Балыковая в/к в/у Останкино Вес  ОСТАНКИНО</t>
-  </si>
-  <si>
-    <t>БАЛЫКОВАЯ Останкино в/к в/у</t>
-  </si>
-  <si>
-    <t>БАЛЫКОВАЯ Останкино в/к в/у 0.33кг 8шт.</t>
-  </si>
-  <si>
-    <t>ДОКТОРСКАЯ ГОСТ Останкино вар п/о 0.35кг</t>
-  </si>
-  <si>
-    <t>7371 БРЕСТСКИЕ сос п/о в/у 0,3кг 8шт. ОСТАНКИНО</t>
-  </si>
-  <si>
-    <t>БРЕСТСКИЕ сос п/о в/у 0.3кг 8шт.</t>
-  </si>
-  <si>
-    <t>7523 ГОВЯЖЬЯ Папа Может вар п/о 0,4кг 6шт. ОСТАНКИНО</t>
-  </si>
-  <si>
-    <t>ГОВЯЖЬЯ Папа может вар п/о 0.4кг 6шт.</t>
-  </si>
-  <si>
-    <t>7539 ДОКТОРСКАЯ ГОСТ вар п/о 0,35кг ОСТАНКИНО</t>
-  </si>
-  <si>
-    <t>ЭКСТРА Папа может вар п/о 0.4кг 8шт_195к</t>
-  </si>
-  <si>
-    <t>6470 ВЕТЧ.МРАМОРНАЯ в/у_45с  Останкино</t>
-  </si>
-  <si>
-    <t>ВЕТЧ.МРАМОРНАЯ в/у_45с</t>
-  </si>
-  <si>
-    <t>7083 СЛИВОЧНЫЕ ПМ сос п/о мгс 1.5*4_А_50с  ОСТАНКИНО</t>
-  </si>
-  <si>
-    <t>СЛИВОЧНЫЕ ПМ сос п/о мгс 1.5*4_А_50с</t>
-  </si>
-  <si>
-    <t>7603 БАЛЫКОВАЯ в/к в/у 0.33кг 8шт. ОСТАНКИНО</t>
-  </si>
-  <si>
-    <t>7489 СЫРРРВЕЛАТ Папа Может в/к в/у 0,28кг 8шт. ОСТАНКИНО</t>
-  </si>
-  <si>
-    <t>СЫРРРВЕЛАТ Папа может в/к в/у 0.28кг 8шт</t>
-  </si>
-  <si>
-    <t>7271 МЯСНЫЕ С ГОВЯДИНОЙ ПМ сос п/о мгс 1.5*4  ОСТАНКИНО</t>
-  </si>
-  <si>
-    <t>МЯСНЫЕ С ГОВЯДИНОЙ ПМ сос п/о мгс 1.5*4</t>
-  </si>
-  <si>
-    <t>6008 САЛО СОЛЕНОЕ С ЧЕРНЫМ ПЕРЦЕМ мл/к в/у ОСТАНКИНО</t>
-  </si>
-  <si>
-    <t>САЛО СОЛЕНОЕ С ЧЕРНЫМ ПЕРЦЕМ мл/к в/у</t>
-  </si>
-  <si>
-    <t>7422 НАБОР ДЛЯ ПИЦЦЫ с/к с/н мгс 3*3 HRC  ОСТАНКИНО</t>
-  </si>
-  <si>
-    <t>НАБОР ДЛЯ ПИЦЦЫ с/к с/н мгс 3*3_HRC</t>
-  </si>
-  <si>
-    <t>6946 СЕРВЕЛАТ КРЕМЛЕВСКИЙ в/к в/у ВЕС  0,84кг ОСТАНКИНО</t>
-  </si>
-  <si>
-    <t>СЕРВЕЛАТ КРЕМЛЕВСКИЙ в/к в/у 0.84кг</t>
-  </si>
-  <si>
-    <t>АРОМАТНАЯ с/к с/н в/у 1/100 10шт_Л10</t>
-  </si>
-  <si>
-    <t>ЭКСТРА Папа может с/к с/н в/у 1/100_Л10</t>
-  </si>
-  <si>
-    <t>СЕРВЕЛАТ ШВЕЙЦАРСК.в/к с/н в/у 1/100_Л11</t>
-  </si>
-  <si>
-    <t>7632 ЭКСТРА Папа может вар п/о 0.4кг 8шт_195к  ОСТАНКИНО</t>
-  </si>
-  <si>
-    <t>БАЛЫК с/к с/н в/у 1/100 10шт_Л11</t>
+    <t>7612 БАЛЫК с/к с/н в/у 1/100 10шт_  ОСТАНКИНО</t>
   </si>
 </sst>
 </file>
@@ -2775,7 +2772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F507"/>
+  <dimension ref="A1:F509"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" style="2" customWidth="1"/>
@@ -2865,68 +2862,68 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B8" s="3">
         <v>1001095716865</v>
       </c>
       <c r="C8" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="B9" s="3">
         <v>1001095716866</v>
       </c>
       <c r="C9" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>434</v>
+        <v>425</v>
       </c>
       <c r="B10" s="3">
         <v>1001095716866</v>
       </c>
       <c r="C10" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="B11" s="3">
         <v>1001095716866</v>
       </c>
       <c r="C11" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="B12" s="3">
         <v>1001095716866</v>
       </c>
       <c r="C12" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
       <c r="B13" s="3">
         <v>1001095716866</v>
       </c>
       <c r="C13" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -2937,12 +2934,12 @@
         <v>1001095716865</v>
       </c>
       <c r="C14" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="B15" s="3">
         <v>1001092446756</v>
@@ -2970,1493 +2967,1493 @@
         <v>1001060764993</v>
       </c>
       <c r="C17" t="s">
-        <v>19</v>
+        <v>782</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B18" s="3">
         <v>1001010105246</v>
       </c>
       <c r="C18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" s="3">
         <v>1001010855247</v>
       </c>
       <c r="C19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B20" s="3">
         <v>1001015646861</v>
       </c>
       <c r="C20" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="B21" s="3">
         <v>1001015706862</v>
       </c>
       <c r="C21" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="B22" s="3">
         <v>1001015706862</v>
       </c>
       <c r="C22" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" s="3">
         <v>1001015706862</v>
       </c>
       <c r="C23" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="B24" s="3">
         <v>1001303987166</v>
       </c>
       <c r="C24" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="B25" s="3">
         <v>1001303987166</v>
       </c>
       <c r="C25" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B26" s="3">
         <v>1001062505483</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B27" s="3">
         <v>1001051875544</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B28" s="3">
         <v>1001203117382</v>
       </c>
       <c r="C28" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>754</v>
+        <v>744</v>
       </c>
       <c r="B29" s="3">
         <v>1001203117382</v>
       </c>
       <c r="C29" t="s">
-        <v>753</v>
+        <v>743</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>747</v>
+        <v>737</v>
       </c>
       <c r="B30" s="3">
         <v>1001061973986</v>
       </c>
       <c r="C30" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B31" s="3">
         <v>1001061973986</v>
       </c>
       <c r="C31" t="s">
-        <v>743</v>
+        <v>733</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B32" s="3">
         <v>1001063145708</v>
       </c>
       <c r="C32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B33" s="3">
         <v>1001022465820</v>
       </c>
       <c r="C33" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" s="3">
         <v>1001012505851</v>
       </c>
       <c r="C34" t="s">
-        <v>39</v>
+        <v>783</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="B35" s="3">
         <v>1001060755931</v>
       </c>
       <c r="C35" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B36" s="3">
         <v>1001060755931</v>
       </c>
       <c r="C36" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B37" s="3">
         <v>1001012815997</v>
       </c>
       <c r="C37" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B38" s="3">
         <v>1001024906042</v>
       </c>
       <c r="C38" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B39" s="3">
         <v>1001024976829</v>
       </c>
       <c r="C39" t="s">
-        <v>393</v>
+        <v>787</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>435</v>
+        <v>426</v>
       </c>
       <c r="B40" s="3">
         <v>1001084216206</v>
       </c>
       <c r="C40" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B41" s="3">
         <v>1001084216206</v>
       </c>
       <c r="C41" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
       <c r="B42" s="3">
         <v>1001022557257</v>
       </c>
       <c r="C42" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>674</v>
+        <v>665</v>
       </c>
       <c r="B43" s="3">
         <v>1001022557257</v>
       </c>
       <c r="C43" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="B44" s="3">
         <v>1001022557257</v>
       </c>
       <c r="C44" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B45" s="3">
         <v>1001022556069</v>
       </c>
       <c r="C45" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
       <c r="F45" s="3"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B46" s="3">
         <v>1001010106325</v>
       </c>
       <c r="C46" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B47" s="3">
         <v>1001012486333</v>
       </c>
       <c r="C47" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>793</v>
+        <v>780</v>
       </c>
       <c r="B48" s="3">
         <v>1001012507632</v>
       </c>
       <c r="C48" t="s">
-        <v>774</v>
+        <v>762</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B49" s="3">
         <v>1001012507632</v>
       </c>
       <c r="C49" t="s">
-        <v>774</v>
+        <v>762</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="B50" s="3">
         <v>1001304507236</v>
       </c>
       <c r="C50" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B51" s="3">
         <v>1001304507236</v>
       </c>
       <c r="C51" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>673</v>
+        <v>664</v>
       </c>
       <c r="B52" s="3">
         <v>1001304507236</v>
       </c>
       <c r="C52" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B53" s="3">
         <v>1001303056692</v>
       </c>
       <c r="C53" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="B54" s="3">
         <v>1001303637149</v>
       </c>
       <c r="C54" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="B55" s="3">
         <v>1001303637149</v>
       </c>
       <c r="C55" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B56" s="3">
         <v>1001013956426</v>
       </c>
       <c r="C56" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B57" s="3">
         <v>1001024636438</v>
       </c>
       <c r="C57" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B58" s="3">
         <v>1001234146448</v>
       </c>
       <c r="C58" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="B59" s="3">
         <v>1001062507616</v>
       </c>
       <c r="C59" t="s">
-        <v>791</v>
+        <v>778</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>64</v>
+        <v>789</v>
       </c>
       <c r="B60" s="3">
         <v>1001062507616</v>
       </c>
       <c r="C60" t="s">
-        <v>791</v>
+        <v>778</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B61" s="3">
-        <v>1001061977613</v>
+        <v>1001062507616</v>
       </c>
       <c r="C61" t="s">
-        <v>790</v>
+        <v>778</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B62" s="3">
-        <v>1001025176475</v>
+        <v>1001061977613</v>
       </c>
       <c r="C62" t="s">
-        <v>67</v>
+        <v>790</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="B63" s="3">
-        <v>1001301876697</v>
+        <v>1001025176475</v>
       </c>
       <c r="C63" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>69</v>
+        <v>109</v>
       </c>
       <c r="B64" s="3">
-        <v>1001024636517</v>
+        <v>1001301876697</v>
       </c>
       <c r="C64" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B65" s="3">
-        <v>1001031076527</v>
+        <v>1001024636517</v>
       </c>
       <c r="C65" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B66" s="3">
-        <v>1001304506562</v>
+        <v>1001031076527</v>
       </c>
       <c r="C66" t="s">
-        <v>76</v>
+        <v>785</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="B67" s="3">
-        <v>1001020846563</v>
+        <v>1001304506562</v>
       </c>
       <c r="C67" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="B68" s="3">
-        <v>1001020836589</v>
+        <v>1001020846563</v>
       </c>
       <c r="C68" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="B69" s="3">
-        <v>6751</v>
+        <v>1001020836589</v>
       </c>
       <c r="C69" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="B70" s="3">
-        <v>1001010016592</v>
+        <v>6751</v>
       </c>
       <c r="C70" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B71" s="3">
-        <v>1001010026594</v>
+        <v>1001010016592</v>
       </c>
       <c r="C71" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B72" s="3">
-        <v>1001022296601</v>
+        <v>1001010026594</v>
       </c>
       <c r="C72" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="B73" s="3">
-        <v>1001031896648</v>
+        <v>1001022296601</v>
       </c>
       <c r="C73" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B74" s="3">
-        <v>1001035266650</v>
+        <v>1001031896648</v>
       </c>
       <c r="C74" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B75" s="3">
-        <v>1001305256658</v>
+        <v>1001035266650</v>
       </c>
       <c r="C75" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="B76" s="3">
-        <v>1001010016593</v>
+        <v>1001305256658</v>
       </c>
       <c r="C76" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="B77" s="3">
-        <v>1001010026595</v>
+        <v>1001010016593</v>
       </c>
       <c r="C77" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B78" s="3">
-        <v>1001010036597</v>
+        <v>1001010026595</v>
       </c>
       <c r="C78" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="B79" s="3">
-        <v>1001020886646</v>
+        <v>1001010036597</v>
       </c>
       <c r="C79" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>308</v>
+        <v>103</v>
       </c>
       <c r="B80" s="3">
-        <v>1001305306566</v>
+        <v>1001020886646</v>
       </c>
       <c r="C80" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>108</v>
+        <v>300</v>
       </c>
       <c r="B81" s="3">
         <v>1001305306566</v>
       </c>
       <c r="C81" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>642</v>
+        <v>104</v>
       </c>
       <c r="B82" s="3">
-        <v>1001300387154</v>
+        <v>1001305306566</v>
       </c>
       <c r="C82" t="s">
-        <v>623</v>
+        <v>105</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="B83" s="3">
         <v>1001300387154</v>
       </c>
       <c r="C83" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>643</v>
+        <v>613</v>
       </c>
       <c r="B84" s="3">
-        <v>1001303987169</v>
+        <v>1001300387154</v>
       </c>
       <c r="C84" t="s">
-        <v>625</v>
+        <v>614</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>624</v>
+        <v>634</v>
       </c>
       <c r="B85" s="3">
         <v>1001303987169</v>
       </c>
       <c r="C85" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>228</v>
+        <v>615</v>
       </c>
       <c r="B86" s="3">
-        <v>1001303106773</v>
+        <v>1001303987169</v>
       </c>
       <c r="C86" t="s">
-        <v>331</v>
+        <v>616</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="B87" s="4">
+        <v>223</v>
+      </c>
+      <c r="B87" s="3">
         <v>1001303106773</v>
       </c>
       <c r="C87" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>260</v>
+        <v>330</v>
       </c>
       <c r="B88" s="4">
         <v>1001303106773</v>
       </c>
       <c r="C88" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="B89" s="3">
+        <v>253</v>
+      </c>
+      <c r="B89" s="4">
         <v>1001303106773</v>
       </c>
       <c r="C89" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>377</v>
+        <v>108</v>
       </c>
       <c r="B90" s="3">
         <v>1001303106773</v>
       </c>
       <c r="C90" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
       <c r="B91" s="3">
         <v>1001303106773</v>
       </c>
       <c r="C91" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="B92" s="3">
         <v>1001303106773</v>
       </c>
       <c r="C92" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>217</v>
+        <v>364</v>
       </c>
       <c r="B93" s="3">
-        <v>1001012566392</v>
+        <v>1001303106773</v>
       </c>
       <c r="C93" t="s">
-        <v>54</v>
+        <v>323</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>407</v>
+        <v>212</v>
       </c>
       <c r="B94" s="3">
         <v>1001012566392</v>
       </c>
       <c r="C94" t="s">
-        <v>54</v>
+        <v>784</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>115</v>
+        <v>398</v>
       </c>
       <c r="B95" s="3">
         <v>1001012566392</v>
       </c>
       <c r="C95" t="s">
-        <v>54</v>
+        <v>784</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>645</v>
+        <v>111</v>
       </c>
       <c r="B96" s="3">
-        <v>1001302277173</v>
+        <v>1001012566392</v>
       </c>
       <c r="C96" t="s">
-        <v>621</v>
+        <v>784</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>620</v>
+        <v>636</v>
       </c>
       <c r="B97" s="3">
         <v>1001302277173</v>
       </c>
       <c r="C97" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>702</v>
+        <v>611</v>
       </c>
       <c r="B98" s="3">
-        <v>1001012426268</v>
+        <v>1001302277173</v>
       </c>
       <c r="C98" t="s">
-        <v>117</v>
+        <v>612</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>118</v>
+        <v>693</v>
       </c>
       <c r="B99" s="3">
         <v>1001012426268</v>
       </c>
       <c r="C99" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="B100" s="3">
-        <v>1001024906041</v>
+        <v>1001012426268</v>
       </c>
       <c r="C100" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B101" s="3">
-        <v>1001011086247</v>
+        <v>1001024906041</v>
       </c>
       <c r="C101" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="B102" s="3">
-        <v>1001014486158</v>
+        <v>1001011086247</v>
       </c>
       <c r="C102" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B103" s="3">
-        <v>1001015356259</v>
+        <v>1001014486158</v>
       </c>
       <c r="C103" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B104" s="3">
-        <v>1001012816716</v>
+        <v>1001015356259</v>
       </c>
       <c r="C104" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>313</v>
+        <v>143</v>
       </c>
       <c r="B105" s="3">
-        <v>1001020966227</v>
+        <v>1001012816716</v>
       </c>
       <c r="C105" t="s">
-        <v>312</v>
+        <v>134</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>124</v>
+        <v>305</v>
       </c>
       <c r="B106" s="3">
         <v>1001020966227</v>
       </c>
       <c r="C106" t="s">
-        <v>125</v>
+        <v>304</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>215</v>
+        <v>120</v>
       </c>
       <c r="B107" s="3">
-        <v>1001022726303</v>
+        <v>1001020966227</v>
       </c>
       <c r="C107" t="s">
-        <v>248</v>
+        <v>121</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="B108" s="3">
         <v>1001022726303</v>
       </c>
       <c r="C108" t="s">
-        <v>248</v>
+        <v>146</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>330</v>
+        <v>241</v>
       </c>
       <c r="B109" s="3">
         <v>1001022726303</v>
       </c>
       <c r="C109" t="s">
-        <v>248</v>
+        <v>146</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>148</v>
+        <v>322</v>
       </c>
       <c r="B110" s="3">
         <v>1001022726303</v>
       </c>
       <c r="C110" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="B111" s="3">
-        <v>1001022466726</v>
+        <v>1001022726303</v>
       </c>
       <c r="C111" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="B112" s="3">
-        <v>1001020966144</v>
+        <v>1001022466726</v>
       </c>
       <c r="C112" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B113" s="3">
-        <v>1001022376722</v>
+        <v>1001020966144</v>
       </c>
       <c r="C113" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>565</v>
+        <v>112</v>
       </c>
       <c r="B114" s="3">
-        <v>1001022376955</v>
+        <v>1001022376722</v>
       </c>
       <c r="C114" t="s">
-        <v>556</v>
+        <v>110</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>563</v>
+        <v>556</v>
       </c>
       <c r="B115" s="3">
         <v>1001022376955</v>
       </c>
       <c r="C115" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>129</v>
+        <v>554</v>
       </c>
       <c r="B116" s="3">
         <v>1001022376955</v>
       </c>
       <c r="C116" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>240</v>
+        <v>125</v>
       </c>
       <c r="B117" s="3">
-        <v>1001022246661</v>
+        <v>1001022376955</v>
       </c>
       <c r="C117" t="s">
-        <v>241</v>
+        <v>547</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>309</v>
+        <v>235</v>
       </c>
       <c r="B118" s="3">
         <v>1001022246661</v>
       </c>
       <c r="C118" t="s">
-        <v>241</v>
+        <v>126</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>128</v>
+        <v>301</v>
       </c>
       <c r="B119" s="3">
         <v>1001022246661</v>
       </c>
       <c r="C119" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="B120" s="3">
-        <v>1001022246713</v>
+        <v>1001022246661</v>
       </c>
       <c r="C120" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B121" s="3">
-        <v>1001025166241</v>
+        <v>1001022246713</v>
       </c>
       <c r="C121" t="s">
-        <v>135</v>
+        <v>101</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="B122" s="3">
-        <v>6606</v>
+        <v>1001025166241</v>
       </c>
       <c r="C122" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="B123" s="3">
-        <v>1001035326217</v>
+        <v>6606</v>
       </c>
       <c r="C123" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="B124" s="3">
-        <v>1001303636301</v>
+        <v>1001035326217</v>
       </c>
       <c r="C124" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>89</v>
+        <v>142</v>
       </c>
       <c r="B125" s="3">
-        <v>1001303636302</v>
+        <v>1001303636301</v>
       </c>
       <c r="C125" t="s">
-        <v>90</v>
+        <v>136</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="B126" s="3">
-        <v>1001305196215</v>
+        <v>1001303636302</v>
       </c>
       <c r="C126" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="B127" s="3">
-        <v>1001301876212</v>
+        <v>1001305196215</v>
       </c>
       <c r="C127" t="s">
-        <v>141</v>
+        <v>70</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B128" s="3">
-        <v>1001301876213</v>
+        <v>1001301876212</v>
       </c>
       <c r="C128" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="B129" s="3">
-        <v>1001303636302</v>
+        <v>1001301876213</v>
       </c>
       <c r="C129" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B130" s="3">
-        <v>6645</v>
+        <v>1001303636302</v>
       </c>
       <c r="C130" t="s">
-        <v>153</v>
+        <v>86</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B131" s="3">
-        <v>1001225416228</v>
+        <v>6645</v>
       </c>
       <c r="C131" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="B132" s="3">
-        <v>6225</v>
+        <v>1001225416228</v>
       </c>
       <c r="C132" t="s">
-        <v>264</v>
+        <v>151</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B133" s="3">
-        <v>1001022376722</v>
+        <v>6225</v>
       </c>
       <c r="C133" t="s">
-        <v>114</v>
+        <v>257</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="B134" s="3">
         <v>1001022376722</v>
       </c>
       <c r="C134" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B135" s="3">
-        <v>3297</v>
+        <v>1001022376722</v>
       </c>
       <c r="C135" t="s">
-        <v>160</v>
+        <v>110</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>303</v>
+        <v>155</v>
       </c>
       <c r="B136" s="3">
-        <v>1001022466726</v>
+        <v>3297</v>
       </c>
       <c r="C136" t="s">
-        <v>281</v>
+        <v>156</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="B137" s="3">
         <v>1001022466726</v>
       </c>
       <c r="C137" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>163</v>
+        <v>274</v>
       </c>
       <c r="B138" s="3">
         <v>1001022466726</v>
       </c>
       <c r="C138" t="s">
-        <v>104</v>
+        <v>273</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B139" s="3">
-        <v>1001021966602</v>
+        <v>1001022466726</v>
       </c>
       <c r="C139" t="s">
-        <v>275</v>
+        <v>100</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="B140" s="3">
-        <v>6233</v>
+        <v>1001021966602</v>
       </c>
       <c r="C140" t="s">
-        <v>165</v>
+        <v>791</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>255</v>
+        <v>162</v>
       </c>
       <c r="B141" s="3">
-        <v>1001012816341</v>
+        <v>6233</v>
       </c>
       <c r="C141" t="s">
-        <v>432</v>
+        <v>161</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>478</v>
+        <v>248</v>
       </c>
       <c r="B142" s="3">
         <v>1001012816341</v>
       </c>
       <c r="C142" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="B143" s="3">
         <v>1001012816341</v>
       </c>
       <c r="C143" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>167</v>
+        <v>472</v>
       </c>
       <c r="B144" s="3">
         <v>1001012816341</v>
       </c>
       <c r="C144" t="s">
-        <v>432</v>
+        <v>423</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B145" s="3">
-        <v>6750</v>
+        <v>1001012816341</v>
       </c>
       <c r="C145" t="s">
-        <v>80</v>
+        <v>423</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B146" s="3">
-        <v>6751</v>
+        <v>6750</v>
       </c>
       <c r="C146" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B147" s="3">
-        <v>5982</v>
+        <v>6751</v>
       </c>
       <c r="C147" t="s">
-        <v>171</v>
+        <v>78</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>527</v>
+        <v>166</v>
       </c>
       <c r="B148" s="3">
-        <v>1001022656854</v>
+        <v>5982</v>
       </c>
       <c r="C148" t="s">
-        <v>421</v>
+        <v>167</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>544</v>
+        <v>518</v>
       </c>
       <c r="B149" s="3">
         <v>1001022656854</v>
       </c>
       <c r="C149" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>445</v>
+        <v>535</v>
       </c>
       <c r="B150" s="3">
         <v>1001022656854</v>
       </c>
       <c r="C150" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>172</v>
+        <v>436</v>
       </c>
       <c r="B151" s="3">
         <v>1001022656854</v>
       </c>
       <c r="C151" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="B152" s="3">
-        <v>1001094966025</v>
+        <v>1001022656854</v>
       </c>
       <c r="C152" t="s">
-        <v>174</v>
+        <v>412</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -4464,3508 +4461,3508 @@
         <v>173</v>
       </c>
       <c r="B153" s="3">
-        <v>6025</v>
+        <v>1001094966025</v>
       </c>
       <c r="C153" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="B154" s="3">
-        <v>1001022373812</v>
+        <v>6025</v>
       </c>
       <c r="C154" t="s">
-        <v>3</v>
+        <v>170</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="B155" s="3">
-        <v>1001100606827</v>
+        <v>1001022373812</v>
       </c>
       <c r="C155" t="s">
-        <v>320</v>
+        <v>3</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>332</v>
+        <v>177</v>
       </c>
       <c r="B156" s="3">
         <v>1001100606827</v>
       </c>
       <c r="C156" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>182</v>
+        <v>324</v>
       </c>
       <c r="B157" s="3">
-        <v>1001100616826</v>
+        <v>1001100606827</v>
       </c>
       <c r="C157" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>333</v>
+        <v>178</v>
       </c>
       <c r="B158" s="3">
         <v>1001100616826</v>
       </c>
       <c r="C158" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>183</v>
+        <v>325</v>
       </c>
       <c r="B159" s="3">
-        <v>1001100626828</v>
+        <v>1001100616826</v>
       </c>
       <c r="C159" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>334</v>
+        <v>179</v>
       </c>
       <c r="B160" s="3">
         <v>1001100626828</v>
       </c>
       <c r="C160" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>184</v>
+        <v>326</v>
       </c>
       <c r="B161" s="3">
-        <v>1001035026308</v>
+        <v>1001100626828</v>
       </c>
       <c r="C161" t="s">
-        <v>185</v>
+        <v>314</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>548</v>
+        <v>180</v>
       </c>
       <c r="B162" s="3">
-        <v>1001014486159</v>
+        <v>1001035026308</v>
       </c>
       <c r="C162" t="s">
-        <v>549</v>
+        <v>181</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>186</v>
+        <v>539</v>
       </c>
       <c r="B163" s="3">
         <v>1001014486159</v>
       </c>
       <c r="C163" t="s">
-        <v>187</v>
+        <v>540</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="B164" s="3">
-        <v>1001035326217</v>
+        <v>1001014486159</v>
       </c>
       <c r="C164" t="s">
-        <v>279</v>
+        <v>183</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>495</v>
+        <v>184</v>
       </c>
       <c r="B165" s="3">
-        <v>1001012426220</v>
+        <v>1001035326217</v>
       </c>
       <c r="C165" t="s">
-        <v>190</v>
+        <v>271</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>189</v>
+        <v>486</v>
       </c>
       <c r="B166" s="3">
         <v>1001012426220</v>
       </c>
       <c r="C166" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B167" s="3">
-        <v>1001022466236</v>
+        <v>1001012426220</v>
       </c>
       <c r="C167" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="B168" s="3">
-        <v>1001021966602</v>
+        <v>1001022466236</v>
       </c>
       <c r="C168" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="B169" s="3">
-        <v>1001022296656</v>
+        <v>1001021966602</v>
       </c>
       <c r="C169" t="s">
-        <v>196</v>
+        <v>791</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B170" s="3">
-        <v>1001301876697</v>
+        <v>1001022296656</v>
       </c>
       <c r="C170" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="B171" s="3">
-        <v>1001022246713</v>
+        <v>1001301876697</v>
       </c>
       <c r="C171" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="B172" s="3">
-        <v>1001022376722</v>
+        <v>1001022246713</v>
       </c>
       <c r="C172" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="B173" s="3">
-        <v>1001020846751</v>
+        <v>1001022376722</v>
       </c>
       <c r="C173" t="s">
-        <v>82</v>
+        <v>199</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="B174" s="3">
-        <v>1001022725819</v>
+        <v>1001020846751</v>
       </c>
       <c r="C174" t="s">
-        <v>207</v>
+        <v>78</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="B175" s="3">
-        <v>1001012825337</v>
+        <v>1001022725819</v>
       </c>
       <c r="C175" t="s">
-        <v>27</v>
+        <v>202</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B176" s="3">
-        <v>1001012815336</v>
+        <v>1001012825337</v>
       </c>
       <c r="C176" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="B177" s="3">
-        <v>1001234146448</v>
+        <v>1001012815336</v>
       </c>
       <c r="C177" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="B178" s="3">
-        <v>1001022725819</v>
+        <v>1001234146448</v>
       </c>
       <c r="C178" t="s">
-        <v>207</v>
+        <v>59</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B179" s="3">
-        <v>1001092676027</v>
+        <v>1001022725819</v>
       </c>
       <c r="C179" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="B180" s="3">
-        <v>1001301876213</v>
+        <v>1001092676027</v>
       </c>
       <c r="C180" t="s">
-        <v>73</v>
+        <v>208</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="B181" s="3">
-        <v>1001035026308</v>
+        <v>1001301876213</v>
       </c>
       <c r="C181" t="s">
-        <v>397</v>
+        <v>69</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="B182" s="3">
-        <v>1001234146448</v>
+        <v>1001035026308</v>
       </c>
       <c r="C182" t="s">
-        <v>62</v>
+        <v>388</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="B183" s="3">
-        <v>1001061977613</v>
+        <v>1001234146448</v>
       </c>
       <c r="C183" t="s">
-        <v>790</v>
+        <v>59</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="B184" s="3">
-        <v>1001025176475</v>
+        <v>1001061977613</v>
       </c>
       <c r="C184" t="s">
-        <v>67</v>
+        <v>790</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="B185" s="3">
-        <v>1001012456498</v>
+        <v>1001025176475</v>
       </c>
       <c r="C185" t="s">
-        <v>223</v>
+        <v>64</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="B186" s="3">
-        <v>1001010036596</v>
+        <v>1001012456498</v>
       </c>
       <c r="C186" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>559</v>
+        <v>219</v>
       </c>
       <c r="B187" s="3">
-        <v>1001033856608</v>
+        <v>1001010036596</v>
       </c>
       <c r="C187" t="s">
-        <v>550</v>
+        <v>220</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="B188" s="3">
         <v>1001033856608</v>
       </c>
       <c r="C188" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>560</v>
+        <v>543</v>
       </c>
       <c r="B189" s="3">
-        <v>1001033856609</v>
+        <v>1001033856608</v>
       </c>
       <c r="C189" t="s">
-        <v>227</v>
+        <v>541</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>226</v>
+        <v>551</v>
       </c>
       <c r="B190" s="3">
         <v>1001033856609</v>
       </c>
       <c r="C190" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="B191" s="3">
-        <v>1001093345495</v>
+        <v>1001033856609</v>
       </c>
       <c r="C191" t="s">
-        <v>433</v>
+        <v>222</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="B192" s="3">
-        <v>6550</v>
+        <v>1001093345495</v>
       </c>
       <c r="C192" t="s">
-        <v>232</v>
+        <v>424</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B193" s="3">
-        <v>1001304506684</v>
+        <v>6550</v>
       </c>
       <c r="C193" t="s">
-        <v>56</v>
+        <v>227</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="B194" s="3">
-        <v>1001010113248</v>
+        <v>1001304506684</v>
       </c>
       <c r="C194" t="s">
-        <v>235</v>
+        <v>53</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>405</v>
+        <v>229</v>
       </c>
       <c r="B195" s="3">
-        <v>1001063926780</v>
+        <v>1001010113248</v>
       </c>
       <c r="C195" t="s">
-        <v>406</v>
+        <v>230</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>236</v>
+        <v>396</v>
       </c>
       <c r="B196" s="3">
-        <v>6586</v>
+        <v>1001063926780</v>
       </c>
       <c r="C196" t="s">
-        <v>237</v>
+        <v>397</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B197" s="3">
-        <v>1001303636467</v>
+        <v>6586</v>
       </c>
       <c r="C197" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="B198" s="3">
-        <v>1001304496701</v>
+        <v>1001303636467</v>
       </c>
       <c r="C198" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="B199" s="3">
-        <v>6144</v>
+        <v>1001304496701</v>
       </c>
       <c r="C199" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="B200" s="3">
-        <v>1001022725819</v>
+        <v>6144</v>
       </c>
       <c r="C200" t="s">
-        <v>207</v>
+        <v>239</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="B201" s="3">
-        <v>1001022373812</v>
+        <v>1001022725819</v>
       </c>
       <c r="C201" t="s">
-        <v>3</v>
+        <v>202</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B202" s="3">
-        <v>1001024906062</v>
+        <v>1001022373812</v>
       </c>
       <c r="C202" t="s">
-        <v>251</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="B203" s="3">
-        <v>1001303056692</v>
+        <v>1001024906062</v>
       </c>
       <c r="C203" t="s">
-        <v>57</v>
+        <v>244</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="B204" s="3">
-        <v>1001301876697</v>
+        <v>1001303056692</v>
       </c>
       <c r="C204" t="s">
-        <v>199</v>
+        <v>54</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="B205" s="3">
-        <v>1001012634574</v>
+        <v>1001301876697</v>
       </c>
       <c r="C205" t="s">
-        <v>11</v>
+        <v>194</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="B206" s="3">
-        <v>1001092485452</v>
+        <v>1001012634574</v>
       </c>
       <c r="C206" t="s">
-        <v>257</v>
+        <v>11</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="B207" s="3">
-        <v>1001020966144</v>
+        <v>1001092485452</v>
       </c>
       <c r="C207" t="s">
-        <v>139</v>
+        <v>250</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B208" s="3">
-        <v>6586</v>
+        <v>1001020966144</v>
       </c>
       <c r="C208" t="s">
-        <v>237</v>
+        <v>135</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="B209" s="3">
-        <v>1001304496701</v>
+        <v>6586</v>
       </c>
       <c r="C209" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B210" s="3">
-        <v>1001063655015</v>
+        <v>1001304496701</v>
       </c>
       <c r="C210" t="s">
-        <v>263</v>
+        <v>237</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="B211" s="3">
-        <v>1001060763287</v>
+        <v>1001063655015</v>
       </c>
       <c r="C211" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="B212" s="3">
-        <v>1001225416228</v>
+        <v>1001060763287</v>
       </c>
       <c r="C212" t="s">
-        <v>155</v>
+        <v>259</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="B213" s="3">
-        <v>1001032736550</v>
+        <v>1001225416228</v>
       </c>
       <c r="C213" t="s">
-        <v>232</v>
+        <v>151</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B214" s="3">
-        <v>6758</v>
+        <v>1001032736550</v>
       </c>
       <c r="C214" t="s">
-        <v>270</v>
+        <v>786</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="B215" s="3">
-        <v>1001020965976</v>
+        <v>6758</v>
       </c>
       <c r="C215" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="B216" s="3">
-        <v>1001215576586</v>
+        <v>1001020965976</v>
       </c>
       <c r="C216" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="B217" s="3">
-        <v>1001094896026</v>
+        <v>1001215576586</v>
       </c>
       <c r="C217" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>486</v>
+        <v>268</v>
       </c>
       <c r="B218" s="3">
-        <v>1001215576586</v>
+        <v>1001094896026</v>
       </c>
       <c r="C218" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>278</v>
+        <v>477</v>
       </c>
       <c r="B219" s="3">
         <v>1001215576586</v>
       </c>
       <c r="C219" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>775</v>
+        <v>270</v>
       </c>
       <c r="B220" s="3">
-        <v>1001092436470</v>
+        <v>1001215576586</v>
       </c>
       <c r="C220" t="s">
-        <v>776</v>
+        <v>267</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>280</v>
+        <v>763</v>
       </c>
       <c r="B221" s="3">
         <v>1001092436470</v>
       </c>
       <c r="C221" t="s">
-        <v>776</v>
+        <v>764</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>286</v>
+        <v>272</v>
       </c>
       <c r="B222" s="3">
-        <v>1001203146555</v>
+        <v>1001092436470</v>
       </c>
       <c r="C222" t="s">
-        <v>285</v>
+        <v>764</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="B223" s="3">
-        <v>1001016747343</v>
+        <v>1001203146555</v>
       </c>
       <c r="C223" t="s">
-        <v>744</v>
+        <v>277</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>705</v>
+        <v>288</v>
       </c>
       <c r="B224" s="3">
         <v>1001016747343</v>
       </c>
       <c r="C224" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>287</v>
+        <v>696</v>
       </c>
       <c r="B225" s="3">
         <v>1001016747343</v>
       </c>
       <c r="C225" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>746</v>
+        <v>279</v>
       </c>
       <c r="B226" s="3">
         <v>1001016747343</v>
       </c>
       <c r="C226" t="s">
-        <v>744</v>
+        <v>734</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>289</v>
+        <v>736</v>
       </c>
       <c r="B227" s="3">
-        <v>1001014765993</v>
+        <v>1001016747343</v>
       </c>
       <c r="C227" t="s">
-        <v>288</v>
+        <v>734</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="B228" s="3">
-        <v>1001025166776</v>
+        <v>1001014765993</v>
       </c>
       <c r="C228" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="B229" s="3">
-        <v>1001025506777</v>
+        <v>1001025166776</v>
       </c>
       <c r="C229" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>314</v>
+        <v>284</v>
       </c>
       <c r="B230" s="3">
-        <v>1001025546822</v>
+        <v>1001025506777</v>
       </c>
       <c r="C230" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
       <c r="B231" s="3">
         <v>1001025546822</v>
       </c>
       <c r="C231" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="B232" s="3">
         <v>1001025546822</v>
       </c>
       <c r="C232" t="s">
-        <v>542</v>
+        <v>287</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>294</v>
+        <v>319</v>
       </c>
       <c r="B233" s="3">
         <v>1001025546822</v>
       </c>
       <c r="C233" t="s">
-        <v>295</v>
+        <v>533</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>652</v>
+        <v>286</v>
       </c>
       <c r="B234" s="3">
-        <v>1001024976616</v>
+        <v>1001025546822</v>
       </c>
       <c r="C234" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>298</v>
+        <v>643</v>
       </c>
       <c r="B235" s="3">
         <v>1001024976616</v>
       </c>
       <c r="C235" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="B236" s="3">
-        <v>1001010855247</v>
+        <v>1001024976616</v>
       </c>
       <c r="C236" t="s">
-        <v>23</v>
+        <v>289</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>376</v>
+        <v>291</v>
       </c>
       <c r="B237" s="3">
-        <v>1001223296919</v>
+        <v>1001010855247</v>
       </c>
       <c r="C237" t="s">
-        <v>379</v>
+        <v>22</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>63</v>
+        <v>368</v>
       </c>
       <c r="B238" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C238" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>219</v>
+        <v>60</v>
       </c>
       <c r="B239" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C239" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>449</v>
+        <v>214</v>
       </c>
       <c r="B240" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C240" t="s">
-        <v>465</v>
+        <v>371</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>471</v>
+        <v>440</v>
       </c>
       <c r="B241" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C241" t="s">
-        <v>379</v>
+        <v>456</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>300</v>
+        <v>462</v>
       </c>
       <c r="B242" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C242" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="B243" s="3">
-        <v>1001014765993</v>
+        <v>1001223296919</v>
       </c>
       <c r="C243" t="s">
-        <v>288</v>
+        <v>371</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="B244" s="3">
-        <v>1001025166776</v>
+        <v>1001014765993</v>
       </c>
       <c r="C244" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="B245" s="3">
-        <v>1001025506777</v>
+        <v>1001025166776</v>
       </c>
       <c r="C245" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="B246" s="3">
-        <v>1001025526778</v>
+        <v>1001025506777</v>
       </c>
       <c r="C246" t="s">
-        <v>307</v>
+        <v>285</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="B247" s="3">
-        <v>1001304236685</v>
+        <v>1001025526778</v>
       </c>
       <c r="C247" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>335</v>
+        <v>302</v>
       </c>
       <c r="B248" s="3">
-        <v>1001015496769</v>
+        <v>1001304236685</v>
       </c>
       <c r="C248" t="s">
-        <v>316</v>
+        <v>303</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B249" s="3">
         <v>1001015496769</v>
       </c>
       <c r="C249" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="B250" s="3">
-        <v>1001014766798</v>
+        <v>1001015496769</v>
       </c>
       <c r="C250" t="s">
-        <v>319</v>
+        <v>308</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="B251" s="3">
-        <v>1001015026797</v>
+        <v>1001014766798</v>
       </c>
       <c r="C251" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="B252" s="3">
-        <v>1001205386222</v>
+        <v>1001015026797</v>
       </c>
       <c r="C252" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="B253" s="3">
-        <v>1001092675224</v>
+        <v>1001205386222</v>
       </c>
       <c r="C253" t="s">
-        <v>329</v>
+        <v>318</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>336</v>
+        <v>320</v>
       </c>
       <c r="B254" s="3">
-        <v>1001225406223</v>
+        <v>1001092675224</v>
       </c>
       <c r="C254" t="s">
-        <v>337</v>
+        <v>321</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="B255" s="3">
-        <v>1001300366790</v>
+        <v>1001225406223</v>
       </c>
       <c r="C255" t="s">
-        <v>350</v>
+        <v>329</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>467</v>
+        <v>331</v>
       </c>
       <c r="B256" s="3">
-        <v>1001304096792</v>
+        <v>1001300366790</v>
       </c>
       <c r="C256" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>341</v>
+        <v>458</v>
       </c>
       <c r="B257" s="3">
         <v>1001304096792</v>
       </c>
       <c r="C257" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>366</v>
+        <v>333</v>
       </c>
       <c r="B258" s="3">
-        <v>1001303637603</v>
+        <v>1001304096792</v>
       </c>
       <c r="C258" t="s">
-        <v>767</v>
+        <v>344</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>386</v>
+        <v>358</v>
       </c>
       <c r="B259" s="3">
         <v>1001303637603</v>
       </c>
       <c r="C259" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="B260" s="3">
         <v>1001303637603</v>
       </c>
       <c r="C260" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>779</v>
+        <v>334</v>
       </c>
       <c r="B261" s="3">
         <v>1001303637603</v>
       </c>
       <c r="C261" t="s">
-        <v>767</v>
+        <v>755</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>387</v>
+        <v>767</v>
       </c>
       <c r="B262" s="3">
-        <v>1001303636794</v>
+        <v>1001303637603</v>
       </c>
       <c r="C262" t="s">
-        <v>353</v>
+        <v>755</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>487</v>
+        <v>379</v>
       </c>
       <c r="B263" s="3">
         <v>1001303636794</v>
       </c>
       <c r="C263" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>343</v>
+        <v>478</v>
       </c>
       <c r="B264" s="3">
         <v>1001303636794</v>
       </c>
       <c r="C264" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="B265" s="3">
-        <v>1001302596795</v>
+        <v>1001303636794</v>
       </c>
       <c r="C265" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="B266" s="3">
-        <v>1001302596796</v>
+        <v>1001302596795</v>
       </c>
       <c r="C266" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="B267" s="3">
-        <v>1001300456804</v>
+        <v>1001302596796</v>
       </c>
       <c r="C267" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>436</v>
+        <v>338</v>
       </c>
       <c r="B268" s="3">
-        <v>1001300366806</v>
+        <v>1001300456804</v>
       </c>
       <c r="C268" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>347</v>
+        <v>427</v>
       </c>
       <c r="B269" s="3">
         <v>1001300366806</v>
       </c>
       <c r="C269" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="B270" s="3">
-        <v>1001300516803</v>
+        <v>1001300366806</v>
       </c>
       <c r="C270" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="B271" s="3">
-        <v>1001300366807</v>
+        <v>1001300516803</v>
       </c>
       <c r="C271" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>360</v>
+        <v>341</v>
       </c>
       <c r="B272" s="3">
         <v>1001300366807</v>
       </c>
       <c r="C272" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="B273" s="3">
-        <v>1001300516785</v>
+        <v>1001300366807</v>
       </c>
       <c r="C273" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>528</v>
+        <v>354</v>
       </c>
       <c r="B274" s="3">
-        <v>1001300456787</v>
+        <v>1001300516785</v>
       </c>
       <c r="C274" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>543</v>
+        <v>519</v>
       </c>
       <c r="B275" s="3">
         <v>1001300456787</v>
       </c>
       <c r="C275" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>364</v>
+        <v>534</v>
       </c>
       <c r="B276" s="3">
         <v>1001300456787</v>
       </c>
       <c r="C276" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="B277" s="3">
-        <v>1001302596795</v>
+        <v>1001300456787</v>
       </c>
       <c r="C277" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
       <c r="B278" s="3">
-        <v>1001012486332</v>
+        <v>1001302596795</v>
       </c>
       <c r="C278" t="s">
-        <v>369</v>
+        <v>346</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="B279" s="3">
-        <v>1001012566345</v>
+        <v>1001012486332</v>
       </c>
       <c r="C279" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="B280" s="3">
-        <v>1001031076528</v>
+        <v>1001012566345</v>
       </c>
       <c r="C280" t="s">
-        <v>374</v>
+        <v>363</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>404</v>
+        <v>365</v>
       </c>
       <c r="B281" s="3">
-        <v>1001020836761</v>
+        <v>1001031076528</v>
       </c>
       <c r="C281" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>409</v>
+        <v>395</v>
       </c>
       <c r="B282" s="3">
         <v>1001020836761</v>
       </c>
       <c r="C282" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>380</v>
+        <v>400</v>
       </c>
       <c r="B283" s="3">
         <v>1001020836761</v>
       </c>
       <c r="C283" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>400</v>
+        <v>372</v>
       </c>
       <c r="B284" s="3">
-        <v>1001020846764</v>
+        <v>1001020836761</v>
       </c>
       <c r="C284" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>410</v>
+        <v>391</v>
       </c>
       <c r="B285" s="3">
         <v>1001020846764</v>
       </c>
       <c r="C285" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="B286" s="3">
         <v>1001020846764</v>
       </c>
       <c r="C286" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>483</v>
+        <v>374</v>
       </c>
       <c r="B287" s="3">
-        <v>1001300366790</v>
+        <v>1001020846764</v>
       </c>
       <c r="C287" t="s">
-        <v>350</v>
+        <v>375</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>384</v>
+        <v>474</v>
       </c>
       <c r="B288" s="3">
         <v>1001300366790</v>
       </c>
       <c r="C288" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>340</v>
+        <v>376</v>
       </c>
       <c r="B289" s="3">
-        <v>1001304096791</v>
+        <v>1001300366790</v>
       </c>
       <c r="C289" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>458</v>
+        <v>332</v>
       </c>
       <c r="B290" s="3">
         <v>1001304096791</v>
       </c>
       <c r="C290" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>385</v>
+        <v>449</v>
       </c>
       <c r="B291" s="3">
         <v>1001304096791</v>
       </c>
       <c r="C291" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="B292" s="3">
-        <v>1001302596795</v>
+        <v>1001304096791</v>
       </c>
       <c r="C292" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="B293" s="3">
-        <v>1001300516803</v>
+        <v>1001302596795</v>
       </c>
       <c r="C293" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B294" s="3">
-        <v>1001300456804</v>
+        <v>1001300516803</v>
       </c>
       <c r="C294" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="B295" s="3">
-        <v>1001300366807</v>
+        <v>1001300456804</v>
       </c>
       <c r="C295" t="s">
-        <v>359</v>
+        <v>348</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B296" s="3">
-        <v>1001302596796</v>
+        <v>1001300366807</v>
       </c>
       <c r="C296" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>442</v>
+        <v>384</v>
       </c>
       <c r="B297" s="3">
-        <v>1001023696765</v>
+        <v>1001302596796</v>
       </c>
       <c r="C297" t="s">
-        <v>395</v>
+        <v>347</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>461</v>
+        <v>433</v>
       </c>
       <c r="B298" s="3">
         <v>1001023696765</v>
       </c>
       <c r="C298" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>394</v>
+        <v>452</v>
       </c>
       <c r="B299" s="3">
         <v>1001023696765</v>
       </c>
       <c r="C299" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="B300" s="3">
-        <v>1001023696767</v>
+        <v>1001023696765</v>
       </c>
       <c r="C300" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>411</v>
+        <v>394</v>
       </c>
       <c r="B301" s="3">
         <v>1001023696767</v>
       </c>
       <c r="C301" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="B302" s="3">
         <v>1001023696767</v>
       </c>
       <c r="C302" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="B303" s="3">
-        <v>1001024976829</v>
+        <v>1001023696767</v>
       </c>
       <c r="C303" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="B304" s="3">
         <v>1001024976829</v>
       </c>
       <c r="C304" t="s">
-        <v>393</v>
+        <v>787</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>414</v>
+        <v>393</v>
       </c>
       <c r="B305" s="3">
-        <v>1001022376722</v>
+        <v>1001024976829</v>
       </c>
       <c r="C305" t="s">
-        <v>114</v>
+        <v>787</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>441</v>
+        <v>405</v>
       </c>
       <c r="B306" s="3">
-        <v>1001020846762</v>
+        <v>1001022376722</v>
       </c>
       <c r="C306" t="s">
-        <v>416</v>
+        <v>110</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>460</v>
+        <v>432</v>
       </c>
       <c r="B307" s="3">
         <v>1001020846762</v>
       </c>
       <c r="C307" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>415</v>
+        <v>451</v>
       </c>
       <c r="B308" s="3">
         <v>1001020846762</v>
       </c>
       <c r="C308" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>119</v>
+        <v>406</v>
       </c>
       <c r="B309" s="3">
-        <v>1001022656853</v>
+        <v>1001020846762</v>
       </c>
       <c r="C309" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>482</v>
+        <v>115</v>
       </c>
       <c r="B310" s="3">
         <v>1001022656853</v>
       </c>
       <c r="C310" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>564</v>
+        <v>473</v>
       </c>
       <c r="B311" s="3">
-        <v>1001022656948</v>
+        <v>1001022656853</v>
       </c>
       <c r="C311" t="s">
-        <v>555</v>
+        <v>410</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="B312" s="3">
         <v>1001022656948</v>
       </c>
       <c r="C312" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>418</v>
+        <v>549</v>
       </c>
       <c r="B313" s="3">
         <v>1001022656948</v>
       </c>
       <c r="C313" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="B314" s="3">
-        <v>1001022656852</v>
+        <v>1001022656948</v>
       </c>
       <c r="C314" t="s">
-        <v>425</v>
+        <v>546</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>443</v>
+        <v>415</v>
       </c>
       <c r="B315" s="3">
-        <v>1001020836759</v>
+        <v>1001022656852</v>
       </c>
       <c r="C315" t="s">
-        <v>427</v>
+        <v>416</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>459</v>
+        <v>434</v>
       </c>
       <c r="B316" s="3">
         <v>1001020836759</v>
       </c>
       <c r="C316" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
-        <v>426</v>
+        <v>450</v>
       </c>
       <c r="B317" s="3">
         <v>1001020836759</v>
       </c>
       <c r="C317" t="s">
-        <v>427</v>
+        <v>418</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>428</v>
+        <v>417</v>
       </c>
       <c r="B318" s="3">
-        <v>1001023856870</v>
+        <v>1001020836759</v>
       </c>
       <c r="C318" t="s">
-        <v>429</v>
+        <v>418</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>444</v>
+        <v>419</v>
       </c>
       <c r="B319" s="3">
-        <v>1001013956426</v>
+        <v>1001023856870</v>
       </c>
       <c r="C319" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="B320" s="3">
-        <v>1001093345495</v>
+        <v>1001013956426</v>
       </c>
       <c r="C320" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>475</v>
+        <v>437</v>
       </c>
       <c r="B321" s="3">
-        <v>1001022656868</v>
+        <v>1001093345495</v>
       </c>
       <c r="C321" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>447</v>
+        <v>466</v>
       </c>
       <c r="B322" s="3">
         <v>1001022656868</v>
       </c>
       <c r="C322" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>161</v>
+        <v>438</v>
       </c>
       <c r="B323" s="3">
-        <v>1001034065698</v>
+        <v>1001022656868</v>
       </c>
       <c r="C323" t="s">
-        <v>420</v>
+        <v>439</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>179</v>
+        <v>157</v>
       </c>
       <c r="B324" s="3">
         <v>1001034065698</v>
       </c>
       <c r="C324" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>473</v>
+        <v>175</v>
       </c>
       <c r="B325" s="3">
         <v>1001034065698</v>
       </c>
       <c r="C325" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>451</v>
+        <v>464</v>
       </c>
       <c r="B326" s="3">
         <v>1001034065698</v>
       </c>
       <c r="C326" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="B327" s="3">
-        <v>1001084216206</v>
+        <v>1001034065698</v>
       </c>
       <c r="C327" t="s">
-        <v>378</v>
+        <v>411</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>464</v>
+        <v>443</v>
       </c>
       <c r="B328" s="3">
-        <v>1001015646861</v>
+        <v>1001084216206</v>
       </c>
       <c r="C328" t="s">
-        <v>417</v>
+        <v>370</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B329" s="3">
         <v>1001015646861</v>
       </c>
       <c r="C329" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="B330" s="3">
-        <v>1001025176768</v>
+        <v>1001015646861</v>
       </c>
       <c r="C330" t="s">
-        <v>440</v>
+        <v>408</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>462</v>
+        <v>430</v>
       </c>
       <c r="B331" s="3">
         <v>1001025176768</v>
       </c>
       <c r="C331" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B332" s="3">
         <v>1001025176768</v>
       </c>
       <c r="C332" t="s">
-        <v>440</v>
+        <v>431</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
-        <v>438</v>
+        <v>445</v>
       </c>
       <c r="B333" s="3">
-        <v>1001025486770</v>
+        <v>1001025176768</v>
       </c>
       <c r="C333" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>463</v>
+        <v>429</v>
       </c>
       <c r="B334" s="3">
         <v>1001025486770</v>
       </c>
       <c r="C334" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B335" s="3">
         <v>1001025486770</v>
       </c>
       <c r="C335" t="s">
-        <v>437</v>
+        <v>428</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>202</v>
+        <v>446</v>
       </c>
       <c r="B336" s="3">
-        <v>1001012816340</v>
+        <v>1001025486770</v>
       </c>
       <c r="C336" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>477</v>
+        <v>197</v>
       </c>
       <c r="B337" s="3">
         <v>1001012816340</v>
       </c>
       <c r="C337" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="B338" s="3">
         <v>1001012816340</v>
       </c>
       <c r="C338" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>301</v>
+        <v>447</v>
       </c>
       <c r="B339" s="3">
-        <v>1001203146834</v>
+        <v>1001012816340</v>
       </c>
       <c r="C339" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>450</v>
+        <v>293</v>
       </c>
       <c r="B340" s="3">
         <v>1001203146834</v>
       </c>
       <c r="C340" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
-        <v>474</v>
+        <v>441</v>
       </c>
       <c r="B341" s="3">
         <v>1001203146834</v>
       </c>
       <c r="C341" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="B342" s="3">
         <v>1001203146834</v>
       </c>
       <c r="C342" t="s">
-        <v>423</v>
+        <v>414</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>469</v>
+        <v>448</v>
       </c>
       <c r="B343" s="3">
-        <v>1001300456788</v>
+        <v>1001203146834</v>
       </c>
       <c r="C343" t="s">
-        <v>470</v>
+        <v>414</v>
       </c>
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>484</v>
+        <v>460</v>
       </c>
       <c r="B344" s="3">
-        <v>1001300516786</v>
+        <v>1001300456788</v>
       </c>
       <c r="C344" t="s">
-        <v>485</v>
+        <v>461</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>539</v>
+        <v>475</v>
       </c>
       <c r="B345" s="3">
-        <v>1001092436495</v>
+        <v>1001300516786</v>
       </c>
       <c r="C345" t="s">
-        <v>490</v>
+        <v>476</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="B346" s="3">
         <v>1001092436495</v>
       </c>
       <c r="C346" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>489</v>
+        <v>537</v>
       </c>
       <c r="B347" s="3">
         <v>1001092436495</v>
       </c>
       <c r="C347" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>491</v>
+        <v>480</v>
       </c>
       <c r="B348" s="3">
-        <v>1001025526901</v>
+        <v>1001092436495</v>
       </c>
       <c r="C348" t="s">
-        <v>492</v>
+        <v>481</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>493</v>
+        <v>482</v>
       </c>
       <c r="B349" s="3">
-        <v>1001025546931</v>
+        <v>1001025526901</v>
       </c>
       <c r="C349" t="s">
-        <v>494</v>
+        <v>483</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="B350" s="3">
-        <v>1001010017539</v>
+        <v>1001025546931</v>
       </c>
       <c r="C350" t="s">
-        <v>768</v>
+        <v>485</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>532</v>
+        <v>493</v>
       </c>
       <c r="B351" s="3">
         <v>1001010017539</v>
       </c>
       <c r="C351" t="s">
-        <v>768</v>
+        <v>756</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>496</v>
+        <v>523</v>
       </c>
       <c r="B352" s="3">
         <v>1001010017539</v>
       </c>
       <c r="C352" t="s">
-        <v>768</v>
+        <v>756</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>773</v>
+        <v>487</v>
       </c>
       <c r="B353" s="3">
         <v>1001010017539</v>
       </c>
       <c r="C353" t="s">
-        <v>768</v>
+        <v>756</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>499</v>
+        <v>761</v>
       </c>
       <c r="B354" s="3">
-        <v>1001025766909</v>
+        <v>1001010017539</v>
       </c>
       <c r="C354" t="s">
-        <v>498</v>
+        <v>756</v>
       </c>
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>533</v>
+        <v>490</v>
       </c>
       <c r="B355" s="3">
         <v>1001025766909</v>
       </c>
       <c r="C355" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>497</v>
+        <v>524</v>
       </c>
       <c r="B356" s="3">
         <v>1001025766909</v>
       </c>
       <c r="C356" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>531</v>
+        <v>488</v>
       </c>
       <c r="B357" s="3">
-        <v>1001010014558</v>
+        <v>1001025766909</v>
       </c>
       <c r="C357" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>500</v>
+        <v>522</v>
       </c>
       <c r="B358" s="3">
         <v>1001010014558</v>
       </c>
       <c r="C358" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
-        <v>526</v>
+        <v>491</v>
       </c>
       <c r="B359" s="3">
-        <v>1001012596802</v>
+        <v>1001010014558</v>
       </c>
       <c r="C359" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>535</v>
+        <v>517</v>
       </c>
       <c r="B360" s="3">
         <v>1001012596802</v>
       </c>
       <c r="C360" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>503</v>
+        <v>526</v>
       </c>
       <c r="B361" s="3">
         <v>1001012596802</v>
       </c>
       <c r="C361" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>521</v>
+        <v>494</v>
       </c>
       <c r="B362" s="3">
-        <v>1001012596801</v>
+        <v>1001012596802</v>
       </c>
       <c r="C362" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>534</v>
+        <v>512</v>
       </c>
       <c r="B363" s="3">
         <v>1001012596801</v>
       </c>
       <c r="C363" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>505</v>
+        <v>525</v>
       </c>
       <c r="B364" s="3">
         <v>1001012596801</v>
       </c>
       <c r="C364" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="B365" s="3">
-        <v>1001062353684</v>
+        <v>1001012596801</v>
       </c>
       <c r="C365" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
       <c r="B366" s="3">
-        <v>1001010014555</v>
+        <v>1001062353684</v>
       </c>
       <c r="C366" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="B367" s="3">
-        <v>1001083424691</v>
+        <v>1001010014555</v>
       </c>
       <c r="C367" t="s">
-        <v>512</v>
+        <v>501</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="B368" s="3">
-        <v>1001190765679</v>
+        <v>1001083424691</v>
       </c>
       <c r="C368" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="B369" s="3">
-        <v>1001085636200</v>
+        <v>1001190765679</v>
       </c>
       <c r="C369" t="s">
-        <v>516</v>
+        <v>505</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="B370" s="3">
-        <v>1001020836253</v>
+        <v>1001085636200</v>
       </c>
       <c r="C370" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="B371" s="3">
-        <v>1001084226492</v>
+        <v>1001020836253</v>
       </c>
       <c r="C371" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="B372" s="3">
-        <v>1001223296921</v>
+        <v>1001084226492</v>
       </c>
       <c r="C372" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>524</v>
+        <v>513</v>
       </c>
       <c r="B373" s="3">
-        <v>1001053944786</v>
+        <v>1001223296921</v>
       </c>
       <c r="C373" t="s">
-        <v>525</v>
+        <v>514</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>529</v>
+        <v>515</v>
       </c>
       <c r="B374" s="3">
-        <v>1001010016839</v>
+        <v>1001053944786</v>
       </c>
       <c r="C374" t="s">
-        <v>530</v>
+        <v>516</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="B375" s="3">
-        <v>1001023857038</v>
+        <v>1001010016839</v>
       </c>
       <c r="C375" t="s">
-        <v>577</v>
+        <v>521</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>537</v>
+        <v>527</v>
       </c>
       <c r="B376" s="3">
-        <v>1001040434903</v>
+        <v>1001023857038</v>
       </c>
       <c r="C376" t="s">
-        <v>538</v>
+        <v>568</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="B377" s="3">
-        <v>1001080216842</v>
+        <v>1001040434903</v>
       </c>
       <c r="C377" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>553</v>
+        <v>531</v>
       </c>
       <c r="B378" s="3">
-        <v>1001022466951</v>
+        <v>1001080216842</v>
       </c>
       <c r="C378" t="s">
-        <v>554</v>
+        <v>532</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>557</v>
+        <v>544</v>
       </c>
       <c r="B379" s="3">
         <v>1001022466951</v>
       </c>
       <c r="C379" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>561</v>
+        <v>548</v>
       </c>
       <c r="B380" s="3">
-        <v>1001035276653</v>
+        <v>1001022466951</v>
       </c>
       <c r="C380" t="s">
-        <v>562</v>
+        <v>545</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
       <c r="B381" s="3">
-        <v>1001062353680</v>
+        <v>1001035276653</v>
       </c>
       <c r="C381" t="s">
-        <v>567</v>
+        <v>553</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="B382" s="3">
-        <v>1001061971146</v>
+        <v>1001062353680</v>
       </c>
       <c r="C382" t="s">
-        <v>569</v>
+        <v>558</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>570</v>
+        <v>559</v>
       </c>
       <c r="B383" s="3">
-        <v>1001225636201</v>
+        <v>1001061971146</v>
       </c>
       <c r="C383" t="s">
-        <v>571</v>
+        <v>560</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>574</v>
+        <v>561</v>
       </c>
       <c r="B384" s="3">
-        <v>1001095227035</v>
+        <v>1001225636201</v>
       </c>
       <c r="C384" t="s">
-        <v>575</v>
+        <v>562</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>576</v>
+        <v>565</v>
       </c>
       <c r="B385" s="3">
-        <v>1001023857038</v>
+        <v>1001095227035</v>
       </c>
       <c r="C385" t="s">
-        <v>577</v>
+        <v>566</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>578</v>
+        <v>567</v>
       </c>
       <c r="B386" s="3">
-        <v>1001025027040</v>
+        <v>1001023857038</v>
       </c>
       <c r="C386" t="s">
-        <v>579</v>
+        <v>568</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>580</v>
+        <v>569</v>
       </c>
       <c r="B387" s="3">
-        <v>1001223297103</v>
+        <v>1001025027040</v>
       </c>
       <c r="C387" t="s">
-        <v>581</v>
+        <v>570</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>582</v>
+        <v>571</v>
       </c>
       <c r="B388" s="3">
         <v>1001223297103</v>
       </c>
       <c r="C388" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="B389" s="3">
         <v>1001223297103</v>
       </c>
       <c r="C389" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
-        <v>602</v>
+        <v>572</v>
       </c>
       <c r="B390" s="3">
-        <v>1001010032675</v>
+        <v>1001223297103</v>
       </c>
       <c r="C390" t="s">
-        <v>584</v>
+        <v>572</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
-        <v>583</v>
+        <v>593</v>
       </c>
       <c r="B391" s="3">
         <v>1001010032675</v>
       </c>
       <c r="C391" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
-        <v>607</v>
+        <v>574</v>
       </c>
       <c r="B392" s="3">
-        <v>1001035937001</v>
+        <v>1001010032675</v>
       </c>
       <c r="C392" t="s">
-        <v>586</v>
+        <v>575</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
-        <v>585</v>
+        <v>598</v>
       </c>
       <c r="B393" s="3">
         <v>1001035937001</v>
       </c>
       <c r="C393" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
-        <v>608</v>
+        <v>576</v>
       </c>
       <c r="B394" s="3">
-        <v>1001084217090</v>
+        <v>1001035937001</v>
       </c>
       <c r="C394" t="s">
-        <v>588</v>
+        <v>577</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="B395" s="3">
         <v>1001084217090</v>
       </c>
       <c r="C395" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
-        <v>609</v>
+        <v>578</v>
       </c>
       <c r="B396" s="3">
-        <v>1001022377066</v>
+        <v>1001084217090</v>
       </c>
       <c r="C396" t="s">
-        <v>590</v>
+        <v>579</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="B397" s="3">
         <v>1001022377066</v>
       </c>
       <c r="C397" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
-        <v>610</v>
+        <v>580</v>
       </c>
       <c r="B398" s="3">
-        <v>1001022467080</v>
+        <v>1001022377066</v>
       </c>
       <c r="C398" t="s">
-        <v>592</v>
+        <v>581</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
-        <v>591</v>
+        <v>601</v>
       </c>
       <c r="B399" s="3">
         <v>1001022467080</v>
       </c>
       <c r="C399" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
-        <v>611</v>
+        <v>582</v>
       </c>
       <c r="B400" s="3">
-        <v>1001025507255</v>
+        <v>1001022467080</v>
       </c>
       <c r="C400" t="s">
-        <v>745</v>
+        <v>583</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="B401" s="3">
         <v>1001025507255</v>
       </c>
       <c r="C401" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
-        <v>752</v>
+        <v>584</v>
       </c>
       <c r="B402" s="3">
         <v>1001025507255</v>
       </c>
       <c r="C402" t="s">
-        <v>745</v>
+        <v>735</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
-        <v>614</v>
+        <v>742</v>
       </c>
       <c r="B403" s="3">
-        <v>1001022657075</v>
+        <v>1001025507255</v>
       </c>
       <c r="C403" t="s">
-        <v>595</v>
+        <v>735</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
-        <v>594</v>
+        <v>605</v>
       </c>
       <c r="B404" s="3">
         <v>1001022657075</v>
       </c>
       <c r="C404" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="B405" s="3">
-        <v>1001022467082</v>
+        <v>1001022657075</v>
       </c>
       <c r="C405" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="B406" s="3">
         <v>1001022467082</v>
       </c>
       <c r="C406" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
-        <v>613</v>
+        <v>587</v>
       </c>
       <c r="B407" s="3">
-        <v>1001022377070</v>
+        <v>1001022467082</v>
       </c>
       <c r="C407" t="s">
-        <v>599</v>
+        <v>588</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
-        <v>598</v>
+        <v>604</v>
       </c>
       <c r="B408" s="3">
         <v>1001022377070</v>
       </c>
       <c r="C408" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>615</v>
+        <v>589</v>
       </c>
       <c r="B409" s="3">
-        <v>1001022657073</v>
+        <v>1001022377070</v>
       </c>
       <c r="C409" t="s">
-        <v>601</v>
+        <v>590</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
-        <v>600</v>
+        <v>606</v>
       </c>
       <c r="B410" s="3">
         <v>1001022657073</v>
       </c>
       <c r="C410" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
-        <v>626</v>
+        <v>591</v>
       </c>
       <c r="B411" s="3">
-        <v>1001010027126</v>
+        <v>1001022657073</v>
       </c>
       <c r="C411" t="s">
-        <v>604</v>
+        <v>592</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
-        <v>603</v>
+        <v>617</v>
       </c>
       <c r="B412" s="3">
         <v>1001010027126</v>
       </c>
       <c r="C412" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>605</v>
+        <v>594</v>
       </c>
       <c r="B413" s="3">
-        <v>1001010027125</v>
+        <v>1001010027126</v>
       </c>
       <c r="C413" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
-        <v>627</v>
+        <v>596</v>
       </c>
       <c r="B414" s="3">
         <v>1001010027125</v>
       </c>
       <c r="C414" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>649</v>
+        <v>618</v>
       </c>
       <c r="B415" s="3">
-        <v>1001016366888</v>
+        <v>1001010027125</v>
       </c>
       <c r="C415" t="s">
-        <v>629</v>
+        <v>597</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="B416" s="3">
         <v>1001016366888</v>
       </c>
       <c r="C416" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
-        <v>650</v>
+        <v>619</v>
       </c>
       <c r="B417" s="3">
-        <v>1001300367133</v>
+        <v>1001016366888</v>
       </c>
       <c r="C417" t="s">
-        <v>631</v>
+        <v>620</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="B418" s="3">
         <v>1001300367133</v>
       </c>
       <c r="C418" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
-        <v>648</v>
+        <v>621</v>
       </c>
       <c r="B419" s="3">
-        <v>1001303637564</v>
+        <v>1001300367133</v>
       </c>
       <c r="C419" t="s">
-        <v>766</v>
+        <v>622</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="B420" s="3">
         <v>1001303637564</v>
       </c>
       <c r="C420" t="s">
-        <v>766</v>
+        <v>754</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>651</v>
+        <v>623</v>
       </c>
       <c r="B421" s="3">
-        <v>1001304527146</v>
+        <v>1001303637564</v>
       </c>
       <c r="C421" t="s">
-        <v>634</v>
+        <v>754</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>633</v>
+        <v>642</v>
       </c>
       <c r="B422" s="3">
         <v>1001304527146</v>
       </c>
       <c r="C422" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
-        <v>646</v>
+        <v>624</v>
       </c>
       <c r="B423" s="3">
-        <v>1001300517134</v>
+        <v>1001304527146</v>
       </c>
       <c r="C423" t="s">
-        <v>636</v>
+        <v>625</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B424" s="3">
         <v>1001300517134</v>
       </c>
       <c r="C424" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>637</v>
+        <v>626</v>
       </c>
       <c r="B425" s="3">
-        <v>1001300457135</v>
+        <v>1001300517134</v>
       </c>
       <c r="C425" t="s">
-        <v>638</v>
+        <v>627</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
-        <v>639</v>
+        <v>628</v>
       </c>
       <c r="B426" s="3">
-        <v>1001304527144</v>
+        <v>1001300457135</v>
       </c>
       <c r="C426" t="s">
-        <v>640</v>
+        <v>629</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>647</v>
+        <v>630</v>
       </c>
       <c r="B427" s="3">
         <v>1001304527144</v>
       </c>
       <c r="C427" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>671</v>
+        <v>638</v>
       </c>
       <c r="B428" s="3">
-        <v>1001081596620</v>
+        <v>1001304527144</v>
       </c>
       <c r="C428" t="s">
-        <v>653</v>
+        <v>631</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="B429" s="3">
         <v>1001081596620</v>
       </c>
       <c r="C429" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>676</v>
+        <v>645</v>
       </c>
       <c r="B430" s="3">
-        <v>1001085637187</v>
+        <v>1001081596620</v>
       </c>
       <c r="C430" t="s">
-        <v>655</v>
+        <v>644</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="B431" s="3">
         <v>1001085637187</v>
       </c>
       <c r="C431" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>675</v>
+        <v>647</v>
       </c>
       <c r="B432" s="3">
-        <v>1001015676877</v>
+        <v>1001085637187</v>
       </c>
       <c r="C432" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="B433" s="3">
         <v>1001015676877</v>
       </c>
       <c r="C433" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
-        <v>678</v>
+        <v>649</v>
       </c>
       <c r="B434" s="3">
-        <v>1001015686878</v>
+        <v>1001015676877</v>
       </c>
       <c r="C434" t="s">
-        <v>659</v>
+        <v>648</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
-        <v>660</v>
+        <v>669</v>
       </c>
       <c r="B435" s="3">
         <v>1001015686878</v>
       </c>
       <c r="C435" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
-        <v>661</v>
+        <v>651</v>
       </c>
       <c r="B436" s="3">
-        <v>1001302277232</v>
+        <v>1001015686878</v>
       </c>
       <c r="C436" t="s">
-        <v>664</v>
+        <v>650</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="B437" s="3">
-        <v>1001304497237</v>
+        <v>1001302277232</v>
       </c>
       <c r="C437" t="s">
-        <v>665</v>
+        <v>655</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
-        <v>663</v>
+        <v>653</v>
       </c>
       <c r="B438" s="3">
-        <v>1001303107241</v>
+        <v>1001304497237</v>
       </c>
       <c r="C438" t="s">
-        <v>666</v>
+        <v>656</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
-        <v>669</v>
+        <v>654</v>
       </c>
       <c r="B439" s="3">
-        <v>1002162216872</v>
+        <v>1001303107241</v>
       </c>
       <c r="C439" t="s">
-        <v>670</v>
+        <v>657</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
-        <v>677</v>
+        <v>660</v>
       </c>
       <c r="B440" s="3">
         <v>1002162216872</v>
       </c>
       <c r="C440" t="s">
-        <v>670</v>
+        <v>661</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
-        <v>692</v>
+        <v>668</v>
       </c>
       <c r="B441" s="3">
-        <v>1001063237147</v>
+        <v>1002162216872</v>
       </c>
       <c r="C441" t="s">
-        <v>684</v>
+        <v>661</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="B442" s="3">
         <v>1001063237147</v>
       </c>
       <c r="C442" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
-        <v>691</v>
+        <v>670</v>
       </c>
       <c r="B443" s="3">
-        <v>1001063097227</v>
+        <v>1001063237147</v>
       </c>
       <c r="C443" t="s">
-        <v>685</v>
+        <v>675</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B444" s="3">
         <v>1001063097227</v>
       </c>
       <c r="C444" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
-        <v>689</v>
+        <v>671</v>
       </c>
       <c r="B445" s="3">
-        <v>1001066537225</v>
+        <v>1001063097227</v>
       </c>
       <c r="C445" t="s">
-        <v>686</v>
+        <v>676</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B446" s="3">
         <v>1001066537225</v>
       </c>
       <c r="C446" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
-        <v>690</v>
+        <v>672</v>
       </c>
       <c r="B447" s="3">
-        <v>1001066527226</v>
+        <v>1001066537225</v>
       </c>
       <c r="C447" t="s">
-        <v>687</v>
+        <v>677</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B448" s="3">
         <v>1001066527226</v>
       </c>
       <c r="C448" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
-        <v>683</v>
+        <v>673</v>
       </c>
       <c r="B449" s="3">
-        <v>1001066547228</v>
+        <v>1001066527226</v>
       </c>
       <c r="C449" t="s">
-        <v>688</v>
+        <v>678</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
-        <v>699</v>
+        <v>674</v>
       </c>
       <c r="B450" s="3">
-        <v>1001063237229</v>
+        <v>1001066547228</v>
       </c>
       <c r="C450" t="s">
-        <v>696</v>
+        <v>679</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B451" s="3">
         <v>1001063237229</v>
       </c>
       <c r="C451" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
-        <v>701</v>
+        <v>684</v>
       </c>
       <c r="B452" s="3">
-        <v>1001063237150</v>
+        <v>1001063237229</v>
       </c>
       <c r="C452" t="s">
-        <v>697</v>
+        <v>687</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B453" s="3">
         <v>1001063237150</v>
       </c>
       <c r="C453" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
-        <v>695</v>
+        <v>685</v>
       </c>
       <c r="B454" s="3">
-        <v>1001022467276</v>
+        <v>1001063237150</v>
       </c>
       <c r="C454" t="s">
-        <v>698</v>
+        <v>688</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
-        <v>700</v>
+        <v>686</v>
       </c>
       <c r="B455" s="3">
         <v>1001022467276</v>
       </c>
       <c r="C455" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
-        <v>479</v>
+        <v>691</v>
       </c>
       <c r="B456" s="3">
-        <v>1001022556837</v>
+        <v>1001022467276</v>
       </c>
       <c r="C456" t="s">
-        <v>480</v>
+        <v>689</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
-        <v>722</v>
+        <v>470</v>
       </c>
       <c r="B457" s="3">
         <v>1001022556837</v>
       </c>
       <c r="C457" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="B458" s="5">
+        <v>713</v>
+      </c>
+      <c r="B458" s="3">
         <v>1001022556837</v>
       </c>
-      <c r="C458" s="6" t="s">
-        <v>480</v>
+      <c r="C458" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B459" s="3">
-        <v>1001205376221</v>
-      </c>
-      <c r="C459" t="s">
-        <v>176</v>
+        <v>694</v>
+      </c>
+      <c r="B459" s="5">
+        <v>1001022556837</v>
+      </c>
+      <c r="C459" s="6" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
-        <v>720</v>
+        <v>174</v>
       </c>
       <c r="B460" s="3">
         <v>1001205376221</v>
       </c>
       <c r="C460" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
-        <v>704</v>
-      </c>
-      <c r="B461" s="5">
+        <v>711</v>
+      </c>
+      <c r="B461" s="3">
         <v>1001205376221</v>
       </c>
-      <c r="C461" s="6" t="s">
-        <v>176</v>
+      <c r="C461" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="B462" s="3">
-        <v>1001304197608</v>
-      </c>
-      <c r="C462" t="s">
-        <v>792</v>
+        <v>695</v>
+      </c>
+      <c r="B462" s="5">
+        <v>1001205376221</v>
+      </c>
+      <c r="C462" s="6" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
-        <v>717</v>
+        <v>479</v>
       </c>
       <c r="B463" s="3">
         <v>1001304197608</v>
       </c>
       <c r="C463" t="s">
-        <v>792</v>
+        <v>779</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B464" s="3">
         <v>1001304197608</v>
       </c>
       <c r="C464" t="s">
-        <v>792</v>
+        <v>779</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
-        <v>707</v>
-      </c>
-      <c r="B465" s="5">
-        <v>1001010106325</v>
-      </c>
-      <c r="C465" s="6" t="s">
-        <v>51</v>
+        <v>697</v>
+      </c>
+      <c r="B465" s="3">
+        <v>1001304197608</v>
+      </c>
+      <c r="C465" t="s">
+        <v>779</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
-        <v>718</v>
+        <v>698</v>
       </c>
       <c r="B466" s="5">
-        <v>1001013957231</v>
+        <v>1001010106325</v>
       </c>
       <c r="C466" s="6" t="s">
-        <v>714</v>
+        <v>49</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B467" s="5">
         <v>1001013957231</v>
       </c>
       <c r="C467" s="6" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B468" s="3">
-        <v>1001220286279</v>
-      </c>
-      <c r="C468" t="s">
-        <v>47</v>
+        <v>699</v>
+      </c>
+      <c r="B468" s="5">
+        <v>1001013957231</v>
+      </c>
+      <c r="C468" s="6" t="s">
+        <v>705</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
-        <v>724</v>
+        <v>44</v>
       </c>
       <c r="B469" s="3">
         <v>1001220286279</v>
       </c>
       <c r="C469" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="B470" s="5">
+        <v>715</v>
+      </c>
+      <c r="B470" s="3">
         <v>1001220286279</v>
       </c>
-      <c r="C470" s="6" t="s">
-        <v>47</v>
+      <c r="C470" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
-        <v>719</v>
+        <v>700</v>
       </c>
       <c r="B471" s="5">
-        <v>1001223297092</v>
+        <v>1001220286279</v>
       </c>
       <c r="C471" s="6" t="s">
-        <v>715</v>
+        <v>45</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
@@ -7976,150 +7973,150 @@
         <v>1001223297092</v>
       </c>
       <c r="C472" s="6" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="B473" s="3">
-        <v>1001020836724</v>
-      </c>
-      <c r="C473" t="s">
-        <v>573</v>
+        <v>701</v>
+      </c>
+      <c r="B473" s="5">
+        <v>1001223297092</v>
+      </c>
+      <c r="C473" s="6" t="s">
+        <v>706</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
-        <v>721</v>
+        <v>563</v>
       </c>
       <c r="B474" s="3">
         <v>1001020836724</v>
       </c>
       <c r="C474" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="B475" s="5">
+        <v>712</v>
+      </c>
+      <c r="B475" s="3">
         <v>1001020836724</v>
       </c>
-      <c r="C475" s="6" t="s">
-        <v>573</v>
+      <c r="C475" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
-        <v>723</v>
+        <v>702</v>
       </c>
       <c r="B476" s="5">
-        <v>1001062475707</v>
+        <v>1001020836724</v>
       </c>
       <c r="C476" s="6" t="s">
-        <v>716</v>
+        <v>564</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B477" s="5">
         <v>1001062475707</v>
       </c>
       <c r="C477" s="6" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
-        <v>713</v>
+        <v>703</v>
       </c>
       <c r="B478" s="5">
-        <v>1001033856609</v>
+        <v>1001062475707</v>
       </c>
       <c r="C478" s="6" t="s">
-        <v>227</v>
+        <v>707</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
-        <v>725</v>
-      </c>
-      <c r="B479" s="3">
+        <v>704</v>
+      </c>
+      <c r="B479" s="5">
+        <v>1001033856609</v>
+      </c>
+      <c r="C479" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A480" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="B480" s="3">
         <v>1001025767284</v>
       </c>
-      <c r="C479" s="6" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A480" s="7" t="s">
-        <v>727</v>
-      </c>
-      <c r="B480" s="5">
-        <v>1001301777332</v>
-      </c>
       <c r="C480" s="6" t="s">
-        <v>733</v>
+        <v>489</v>
       </c>
     </row>
     <row r="481" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A481" s="7" t="s">
-        <v>741</v>
+        <v>717</v>
       </c>
       <c r="B481" s="5">
         <v>1001301777332</v>
       </c>
       <c r="C481" s="6" t="s">
-        <v>733</v>
+        <v>723</v>
       </c>
     </row>
     <row r="482" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A482" s="7" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="B482" s="5">
-        <v>1001303987333</v>
+        <v>1001301777332</v>
       </c>
       <c r="C482" s="6" t="s">
-        <v>734</v>
+        <v>723</v>
       </c>
     </row>
     <row r="483" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A483" s="7" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="B483" s="5">
         <v>1001303987333</v>
       </c>
       <c r="C483" s="6" t="s">
-        <v>734</v>
+        <v>724</v>
       </c>
     </row>
     <row r="484" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A484" s="7" t="s">
-        <v>729</v>
+        <v>718</v>
       </c>
       <c r="B484" s="5">
-        <v>1001012426220</v>
+        <v>1001303987333</v>
       </c>
       <c r="C484" s="6" t="s">
-        <v>190</v>
+        <v>724</v>
       </c>
     </row>
     <row r="485" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A485" s="7" t="s">
-        <v>740</v>
+        <v>719</v>
       </c>
       <c r="B485" s="5">
-        <v>1001300387157</v>
+        <v>1001012426220</v>
       </c>
       <c r="C485" s="6" t="s">
-        <v>735</v>
+        <v>186</v>
       </c>
     </row>
     <row r="486" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
@@ -8130,242 +8127,264 @@
         <v>1001300387157</v>
       </c>
       <c r="C486" s="6" t="s">
-        <v>735</v>
+        <v>725</v>
       </c>
     </row>
     <row r="487" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A487" s="7" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="B487" s="5">
-        <v>1001220226208</v>
+        <v>1001300387157</v>
       </c>
       <c r="C487" s="6" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
     </row>
     <row r="488" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A488" s="7" t="s">
-        <v>738</v>
+        <v>721</v>
       </c>
       <c r="B488" s="5">
         <v>1001220226208</v>
       </c>
       <c r="C488" s="6" t="s">
-        <v>736</v>
+        <v>726</v>
       </c>
     </row>
     <row r="489" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A489" s="7" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="B489" s="5">
-        <v>1001063656967</v>
+        <v>1001220226208</v>
       </c>
       <c r="C489" s="6" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A490" s="2" t="s">
-        <v>739</v>
+        <v>726</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A490" s="7" t="s">
+        <v>722</v>
       </c>
       <c r="B490" s="5">
         <v>1001063656967</v>
       </c>
       <c r="C490" s="6" t="s">
-        <v>737</v>
+        <v>727</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
-        <v>748</v>
-      </c>
-      <c r="B491" s="3">
-        <v>1001065616832</v>
-      </c>
-      <c r="C491" t="s">
-        <v>749</v>
+        <v>729</v>
+      </c>
+      <c r="B491" s="5">
+        <v>1001063656967</v>
+      </c>
+      <c r="C491" s="6" t="s">
+        <v>727</v>
       </c>
     </row>
     <row r="492" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
-        <v>750</v>
+        <v>738</v>
       </c>
       <c r="B492" s="3">
-        <v>1001060677299</v>
+        <v>1001065616832</v>
       </c>
       <c r="C492" t="s">
-        <v>751</v>
+        <v>739</v>
       </c>
     </row>
     <row r="493" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
-        <v>755</v>
+        <v>740</v>
       </c>
       <c r="B493" s="3">
-        <v>1001453907612</v>
+        <v>1001060677299</v>
       </c>
       <c r="C493" t="s">
-        <v>794</v>
+        <v>741</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
-        <v>756</v>
+        <v>745</v>
       </c>
       <c r="B494" s="3">
         <v>1001453907612</v>
       </c>
       <c r="C494" t="s">
-        <v>794</v>
+        <v>781</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
-        <v>757</v>
+        <v>793</v>
       </c>
       <c r="B495" s="3">
-        <v>1001015026797</v>
+        <v>1001453907612</v>
       </c>
       <c r="C495" t="s">
-        <v>758</v>
+        <v>781</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
-        <v>759</v>
+        <v>746</v>
       </c>
       <c r="B496" s="3">
-        <v>1001095226925</v>
+        <v>1001453907612</v>
       </c>
       <c r="C496" t="s">
-        <v>760</v>
+        <v>781</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
-        <v>761</v>
+        <v>747</v>
       </c>
       <c r="B497" s="3">
-        <v>1001035277059</v>
+        <v>1001015026797</v>
       </c>
       <c r="C497" t="s">
-        <v>762</v>
+        <v>748</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
-        <v>763</v>
+        <v>749</v>
       </c>
       <c r="B498" s="3">
-        <v>1001025767461</v>
+        <v>1001095226925</v>
       </c>
       <c r="C498" t="s">
-        <v>764</v>
+        <v>788</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
-        <v>765</v>
+        <v>750</v>
       </c>
       <c r="B499" s="3">
-        <v>1001303637564</v>
+        <v>1001035277059</v>
       </c>
       <c r="C499" t="s">
-        <v>766</v>
+        <v>751</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
-        <v>769</v>
+        <v>752</v>
       </c>
       <c r="B500" s="3">
-        <v>1001026947371</v>
+        <v>1001025767461</v>
       </c>
       <c r="C500" t="s">
-        <v>770</v>
+        <v>792</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
-        <v>771</v>
+        <v>753</v>
       </c>
       <c r="B501" s="3">
-        <v>1001012427523</v>
+        <v>1001303637564</v>
       </c>
       <c r="C501" t="s">
-        <v>772</v>
+        <v>754</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
-        <v>777</v>
+        <v>757</v>
       </c>
       <c r="B502" s="3">
-        <v>1001022467083</v>
+        <v>1001026947371</v>
       </c>
       <c r="C502" t="s">
-        <v>778</v>
+        <v>758</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
-        <v>780</v>
+        <v>759</v>
       </c>
       <c r="B503" s="3">
-        <v>1001307357489</v>
+        <v>1001012427523</v>
       </c>
       <c r="C503" t="s">
-        <v>781</v>
+        <v>760</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
-        <v>782</v>
+        <v>765</v>
       </c>
       <c r="B504" s="3">
-        <v>1001025507271</v>
+        <v>1001022467083</v>
       </c>
       <c r="C504" t="s">
-        <v>783</v>
+        <v>766</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
-        <v>784</v>
+        <v>768</v>
       </c>
       <c r="B505" s="3">
-        <v>1001084856008</v>
+        <v>1001307357489</v>
       </c>
       <c r="C505" t="s">
-        <v>785</v>
+        <v>769</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
-        <v>786</v>
+        <v>770</v>
       </c>
       <c r="B506" s="3">
-        <v>1001200677442</v>
+        <v>1001025507271</v>
       </c>
       <c r="C506" t="s">
-        <v>787</v>
+        <v>771</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
-        <v>788</v>
+        <v>772</v>
       </c>
       <c r="B507" s="3">
+        <v>1001084856008</v>
+      </c>
+      <c r="C507" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A508" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="B508" s="3">
+        <v>1001200677442</v>
+      </c>
+      <c r="C508" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A509" s="2" t="s">
+        <v>776</v>
+      </c>
+      <c r="B509" s="3">
         <v>1001300456946</v>
       </c>
-      <c r="C507" t="s">
-        <v>789</v>
+      <c r="C509" t="s">
+        <v>777</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C507" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
+  <autoFilter ref="A1:C509" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42B54395-E634-4F93-B8D2-03413A7F1A41}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5731CA60-E6EE-47A7-B42C-CBC486BF6FEF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$509</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$515</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1017" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="803">
   <si>
     <t>1С</t>
   </si>
@@ -2416,6 +2416,33 @@
   </si>
   <si>
     <t>7612 БАЛЫК с/к с/н в/у 1/100 10шт_  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7040 С ИНДЕЙКОЙ ПМ сос ц/о в/у 1/270 8шт.</t>
+  </si>
+  <si>
+    <t>6411 ВЕТЧ.РУБЛЕНАЯ ПМ в/у срез 0.3кг 6шт.</t>
+  </si>
+  <si>
+    <t>ВЕТЧ.РУБЛЕНАЯ ПМ в/у срез 0.3кг 6шт.</t>
+  </si>
+  <si>
+    <t>7608 СЕРВЕЛАТ ШВЕЙЦАРСК.в/к с/н в/у 1/100_Л11  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7647  ХОЧУ ВЕТЧ. ИЗ СВИН.ОТРУБА с/н мгс 1/100</t>
+  </si>
+  <si>
+    <t>ХОЧУ ВЕТЧ. ИЗ СВИН.ОТРУБА с/н мгс 1/100</t>
+  </si>
+  <si>
+    <t>7651  ХОЧУ ВЕТЧ. МРАМОР. ПМ с/н мгс 1/100_Л11</t>
+  </si>
+  <si>
+    <t>ХОЧУ ВЕТЧ. МРАМОР. ПМ с/н мгс 1/100_Л11</t>
+  </si>
+  <si>
+    <t>7613 АРОМАТНАЯ с/к с/н в/у 1/100 10шт_Л10</t>
   </si>
 </sst>
 </file>
@@ -2772,7 +2799,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F509"/>
+  <dimension ref="A1:F515"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" style="2" customWidth="1"/>
@@ -3468,295 +3495,295 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>63</v>
+        <v>215</v>
       </c>
       <c r="B63" s="3">
-        <v>1001025176475</v>
+        <v>1001061977613</v>
       </c>
       <c r="C63" t="s">
-        <v>64</v>
+        <v>790</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>109</v>
+        <v>802</v>
       </c>
       <c r="B64" s="3">
-        <v>1001301876697</v>
+        <v>1001061977613</v>
       </c>
       <c r="C64" t="s">
-        <v>65</v>
+        <v>790</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B65" s="3">
-        <v>1001024636517</v>
+        <v>1001025176475</v>
       </c>
       <c r="C65" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="B66" s="3">
-        <v>1001031076527</v>
+        <v>1001301876697</v>
       </c>
       <c r="C66" t="s">
-        <v>785</v>
+        <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B67" s="3">
-        <v>1001304506562</v>
+        <v>1001024636517</v>
       </c>
       <c r="C67" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="B68" s="3">
-        <v>1001020846563</v>
+        <v>1001031076527</v>
       </c>
       <c r="C68" t="s">
-        <v>74</v>
+        <v>785</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B69" s="3">
-        <v>1001020836589</v>
+        <v>1001304506562</v>
       </c>
       <c r="C69" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B70" s="3">
-        <v>6751</v>
+        <v>1001020846563</v>
       </c>
       <c r="C70" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B71" s="3">
-        <v>1001010016592</v>
+        <v>1001020836589</v>
       </c>
       <c r="C71" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B72" s="3">
-        <v>1001010026594</v>
+        <v>6751</v>
       </c>
       <c r="C72" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B73" s="3">
-        <v>1001022296601</v>
+        <v>1001010016592</v>
       </c>
       <c r="C73" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B74" s="3">
-        <v>1001031896648</v>
+        <v>1001010026594</v>
       </c>
       <c r="C74" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B75" s="3">
-        <v>1001035266650</v>
+        <v>1001022296601</v>
       </c>
       <c r="C75" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B76" s="3">
-        <v>1001305256658</v>
+        <v>1001031896648</v>
       </c>
       <c r="C76" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B77" s="3">
-        <v>1001010016593</v>
+        <v>1001035266650</v>
       </c>
       <c r="C77" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B78" s="3">
-        <v>1001010026595</v>
+        <v>1001305256658</v>
       </c>
       <c r="C78" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B79" s="3">
-        <v>1001010036597</v>
+        <v>1001010016593</v>
       </c>
       <c r="C79" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="B80" s="3">
-        <v>1001020886646</v>
+        <v>1001010026595</v>
       </c>
       <c r="C80" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>300</v>
+        <v>97</v>
       </c>
       <c r="B81" s="3">
-        <v>1001305306566</v>
+        <v>1001010036597</v>
       </c>
       <c r="C81" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B82" s="3">
-        <v>1001305306566</v>
+        <v>1001020886646</v>
       </c>
       <c r="C82" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>633</v>
+        <v>300</v>
       </c>
       <c r="B83" s="3">
-        <v>1001300387154</v>
+        <v>1001305306566</v>
       </c>
       <c r="C83" t="s">
-        <v>614</v>
+        <v>105</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>613</v>
+        <v>104</v>
       </c>
       <c r="B84" s="3">
-        <v>1001300387154</v>
+        <v>1001305306566</v>
       </c>
       <c r="C84" t="s">
-        <v>614</v>
+        <v>105</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B85" s="3">
-        <v>1001303987169</v>
+        <v>1001300387154</v>
       </c>
       <c r="C85" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B86" s="3">
-        <v>1001303987169</v>
+        <v>1001300387154</v>
       </c>
       <c r="C86" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>223</v>
+        <v>634</v>
       </c>
       <c r="B87" s="3">
-        <v>1001303106773</v>
+        <v>1001303987169</v>
       </c>
       <c r="C87" t="s">
-        <v>323</v>
+        <v>616</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="B88" s="4">
-        <v>1001303106773</v>
+        <v>615</v>
+      </c>
+      <c r="B88" s="3">
+        <v>1001303987169</v>
       </c>
       <c r="C88" t="s">
-        <v>323</v>
+        <v>616</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B89" s="4">
+        <v>223</v>
+      </c>
+      <c r="B89" s="3">
         <v>1001303106773</v>
       </c>
       <c r="C89" t="s">
@@ -3765,9 +3792,9 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B90" s="3">
+        <v>330</v>
+      </c>
+      <c r="B90" s="4">
         <v>1001303106773</v>
       </c>
       <c r="C90" t="s">
@@ -3776,9 +3803,9 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="B91" s="3">
+        <v>253</v>
+      </c>
+      <c r="B91" s="4">
         <v>1001303106773</v>
       </c>
       <c r="C91" t="s">
@@ -3787,7 +3814,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>367</v>
+        <v>108</v>
       </c>
       <c r="B92" s="3">
         <v>1001303106773</v>
@@ -3798,7 +3825,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="B93" s="3">
         <v>1001303106773</v>
@@ -3809,29 +3836,29 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>212</v>
+        <v>367</v>
       </c>
       <c r="B94" s="3">
-        <v>1001012566392</v>
+        <v>1001303106773</v>
       </c>
       <c r="C94" t="s">
-        <v>784</v>
+        <v>323</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>398</v>
+        <v>364</v>
       </c>
       <c r="B95" s="3">
-        <v>1001012566392</v>
+        <v>1001303106773</v>
       </c>
       <c r="C95" t="s">
-        <v>784</v>
+        <v>323</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
       <c r="B96" s="3">
         <v>1001012566392</v>
@@ -3842,150 +3869,150 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>636</v>
+        <v>398</v>
       </c>
       <c r="B97" s="3">
-        <v>1001302277173</v>
+        <v>1001012566392</v>
       </c>
       <c r="C97" t="s">
-        <v>612</v>
+        <v>784</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>611</v>
+        <v>111</v>
       </c>
       <c r="B98" s="3">
-        <v>1001302277173</v>
+        <v>1001012566392</v>
       </c>
       <c r="C98" t="s">
-        <v>612</v>
+        <v>784</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>693</v>
+        <v>636</v>
       </c>
       <c r="B99" s="3">
-        <v>1001012426268</v>
+        <v>1001302277173</v>
       </c>
       <c r="C99" t="s">
-        <v>113</v>
+        <v>612</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>114</v>
+        <v>611</v>
       </c>
       <c r="B100" s="3">
-        <v>1001012426268</v>
+        <v>1001302277173</v>
       </c>
       <c r="C100" t="s">
-        <v>113</v>
+        <v>612</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>119</v>
+        <v>693</v>
       </c>
       <c r="B101" s="3">
-        <v>1001024906041</v>
+        <v>1001012426268</v>
       </c>
       <c r="C101" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B102" s="3">
-        <v>1001011086247</v>
+        <v>1001012426268</v>
       </c>
       <c r="C102" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="B103" s="3">
-        <v>1001014486158</v>
+        <v>1001024906041</v>
       </c>
       <c r="C103" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>141</v>
+        <v>116</v>
       </c>
       <c r="B104" s="3">
-        <v>1001015356259</v>
+        <v>1001011086247</v>
       </c>
       <c r="C104" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B105" s="3">
-        <v>1001012816716</v>
+        <v>1001014486158</v>
       </c>
       <c r="C105" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>305</v>
+        <v>141</v>
       </c>
       <c r="B106" s="3">
-        <v>1001020966227</v>
+        <v>1001015356259</v>
       </c>
       <c r="C106" t="s">
-        <v>304</v>
+        <v>133</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="B107" s="3">
-        <v>1001020966227</v>
+        <v>1001012816716</v>
       </c>
       <c r="C107" t="s">
-        <v>121</v>
+        <v>134</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>210</v>
+        <v>305</v>
       </c>
       <c r="B108" s="3">
-        <v>1001022726303</v>
+        <v>1001020966227</v>
       </c>
       <c r="C108" t="s">
-        <v>146</v>
+        <v>304</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>241</v>
+        <v>120</v>
       </c>
       <c r="B109" s="3">
-        <v>1001022726303</v>
+        <v>1001020966227</v>
       </c>
       <c r="C109" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>322</v>
+        <v>210</v>
       </c>
       <c r="B110" s="3">
         <v>1001022726303</v>
@@ -3996,7 +4023,7 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>144</v>
+        <v>241</v>
       </c>
       <c r="B111" s="3">
         <v>1001022726303</v>
@@ -4007,62 +4034,62 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>99</v>
+        <v>322</v>
       </c>
       <c r="B112" s="3">
-        <v>1001022466726</v>
+        <v>1001022726303</v>
       </c>
       <c r="C112" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B113" s="3">
-        <v>1001020966144</v>
+        <v>1001022726303</v>
       </c>
       <c r="C113" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="B114" s="3">
-        <v>1001022376722</v>
+        <v>1001022466726</v>
       </c>
       <c r="C114" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>556</v>
+        <v>138</v>
       </c>
       <c r="B115" s="3">
-        <v>1001022376955</v>
+        <v>1001020966144</v>
       </c>
       <c r="C115" t="s">
-        <v>547</v>
+        <v>135</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>554</v>
+        <v>112</v>
       </c>
       <c r="B116" s="3">
-        <v>1001022376955</v>
+        <v>1001022376722</v>
       </c>
       <c r="C116" t="s">
-        <v>547</v>
+        <v>110</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>125</v>
+        <v>556</v>
       </c>
       <c r="B117" s="3">
         <v>1001022376955</v>
@@ -4073,29 +4100,29 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>235</v>
+        <v>554</v>
       </c>
       <c r="B118" s="3">
-        <v>1001022246661</v>
+        <v>1001022376955</v>
       </c>
       <c r="C118" t="s">
-        <v>126</v>
+        <v>547</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>301</v>
+        <v>125</v>
       </c>
       <c r="B119" s="3">
-        <v>1001022246661</v>
+        <v>1001022376955</v>
       </c>
       <c r="C119" t="s">
-        <v>126</v>
+        <v>547</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>124</v>
+        <v>235</v>
       </c>
       <c r="B120" s="3">
         <v>1001022246661</v>
@@ -4106,260 +4133,260 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>130</v>
+        <v>301</v>
       </c>
       <c r="B121" s="3">
-        <v>1001022246713</v>
+        <v>1001022246661</v>
       </c>
       <c r="C121" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B122" s="3">
-        <v>1001025166241</v>
+        <v>1001022246661</v>
       </c>
       <c r="C122" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B123" s="3">
-        <v>6606</v>
+        <v>1001022246713</v>
       </c>
       <c r="C123" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B124" s="3">
-        <v>1001035326217</v>
+        <v>1001025166241</v>
       </c>
       <c r="C124" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="B125" s="3">
-        <v>1001303636301</v>
+        <v>6606</v>
       </c>
       <c r="C125" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="B126" s="3">
-        <v>1001303636302</v>
+        <v>1001035326217</v>
       </c>
       <c r="C126" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B127" s="3">
-        <v>1001305196215</v>
+        <v>1001303636301</v>
       </c>
       <c r="C127" t="s">
-        <v>70</v>
+        <v>136</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="B128" s="3">
-        <v>1001301876212</v>
+        <v>1001303636302</v>
       </c>
       <c r="C128" t="s">
-        <v>137</v>
+        <v>86</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B129" s="3">
-        <v>1001301876213</v>
+        <v>1001305196215</v>
       </c>
       <c r="C129" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B130" s="3">
-        <v>1001303636302</v>
+        <v>1001301876212</v>
       </c>
       <c r="C130" t="s">
-        <v>86</v>
+        <v>137</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="B131" s="3">
-        <v>6645</v>
+        <v>1001301876213</v>
       </c>
       <c r="C131" t="s">
-        <v>149</v>
+        <v>69</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B132" s="3">
-        <v>1001225416228</v>
+        <v>1001303636302</v>
       </c>
       <c r="C132" t="s">
-        <v>151</v>
+        <v>86</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B133" s="3">
-        <v>6225</v>
+        <v>6645</v>
       </c>
       <c r="C133" t="s">
-        <v>257</v>
+        <v>149</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B134" s="3">
-        <v>1001022376722</v>
+        <v>1001225416228</v>
       </c>
       <c r="C134" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="B135" s="3">
-        <v>1001022376722</v>
+        <v>6225</v>
       </c>
       <c r="C135" t="s">
-        <v>110</v>
+        <v>257</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B136" s="3">
-        <v>3297</v>
+        <v>1001022376722</v>
       </c>
       <c r="C136" t="s">
-        <v>156</v>
+        <v>110</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>295</v>
+        <v>158</v>
       </c>
       <c r="B137" s="3">
-        <v>1001022466726</v>
+        <v>1001022376722</v>
       </c>
       <c r="C137" t="s">
-        <v>273</v>
+        <v>110</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>274</v>
+        <v>155</v>
       </c>
       <c r="B138" s="3">
-        <v>1001022466726</v>
+        <v>3297</v>
       </c>
       <c r="C138" t="s">
-        <v>273</v>
+        <v>156</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>159</v>
+        <v>295</v>
       </c>
       <c r="B139" s="3">
         <v>1001022466726</v>
       </c>
       <c r="C139" t="s">
-        <v>100</v>
+        <v>273</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>160</v>
+        <v>274</v>
       </c>
       <c r="B140" s="3">
-        <v>1001021966602</v>
+        <v>1001022466726</v>
       </c>
       <c r="C140" t="s">
-        <v>791</v>
+        <v>273</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B141" s="3">
-        <v>6233</v>
+        <v>1001022466726</v>
       </c>
       <c r="C141" t="s">
-        <v>161</v>
+        <v>100</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>248</v>
+        <v>160</v>
       </c>
       <c r="B142" s="3">
-        <v>1001012816341</v>
+        <v>1001021966602</v>
       </c>
       <c r="C142" t="s">
-        <v>423</v>
+        <v>791</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>469</v>
+        <v>162</v>
       </c>
       <c r="B143" s="3">
-        <v>1001012816341</v>
+        <v>6233</v>
       </c>
       <c r="C143" t="s">
-        <v>423</v>
+        <v>161</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>472</v>
+        <v>248</v>
       </c>
       <c r="B144" s="3">
         <v>1001012816341</v>
@@ -4370,7 +4397,7 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>163</v>
+        <v>469</v>
       </c>
       <c r="B145" s="3">
         <v>1001012816341</v>
@@ -4381,62 +4408,62 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>164</v>
+        <v>472</v>
       </c>
       <c r="B146" s="3">
-        <v>6750</v>
+        <v>1001012816341</v>
       </c>
       <c r="C146" t="s">
-        <v>76</v>
+        <v>423</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B147" s="3">
-        <v>6751</v>
+        <v>1001012816341</v>
       </c>
       <c r="C147" t="s">
-        <v>78</v>
+        <v>423</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B148" s="3">
-        <v>5982</v>
+        <v>6750</v>
       </c>
       <c r="C148" t="s">
-        <v>167</v>
+        <v>76</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>518</v>
+        <v>165</v>
       </c>
       <c r="B149" s="3">
-        <v>1001022656854</v>
+        <v>6751</v>
       </c>
       <c r="C149" t="s">
-        <v>412</v>
+        <v>78</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>535</v>
+        <v>166</v>
       </c>
       <c r="B150" s="3">
-        <v>1001022656854</v>
+        <v>5982</v>
       </c>
       <c r="C150" t="s">
-        <v>412</v>
+        <v>167</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>436</v>
+        <v>518</v>
       </c>
       <c r="B151" s="3">
         <v>1001022656854</v>
@@ -4447,7 +4474,7 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>168</v>
+        <v>535</v>
       </c>
       <c r="B152" s="3">
         <v>1001022656854</v>
@@ -4458,403 +4485,403 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>173</v>
+        <v>436</v>
       </c>
       <c r="B153" s="3">
-        <v>1001094966025</v>
+        <v>1001022656854</v>
       </c>
       <c r="C153" t="s">
-        <v>170</v>
+        <v>412</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B154" s="3">
-        <v>6025</v>
+        <v>1001022656854</v>
       </c>
       <c r="C154" t="s">
-        <v>170</v>
+        <v>412</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B155" s="3">
-        <v>1001022373812</v>
+        <v>1001094966025</v>
       </c>
       <c r="C155" t="s">
-        <v>3</v>
+        <v>170</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B156" s="3">
-        <v>1001100606827</v>
+        <v>6025</v>
       </c>
       <c r="C156" t="s">
-        <v>312</v>
+        <v>170</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>324</v>
+        <v>176</v>
       </c>
       <c r="B157" s="3">
-        <v>1001100606827</v>
+        <v>1001022373812</v>
       </c>
       <c r="C157" t="s">
-        <v>312</v>
+        <v>3</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B158" s="3">
-        <v>1001100616826</v>
+        <v>1001100606827</v>
       </c>
       <c r="C158" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B159" s="3">
-        <v>1001100616826</v>
+        <v>1001100606827</v>
       </c>
       <c r="C159" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B160" s="3">
-        <v>1001100626828</v>
+        <v>1001100616826</v>
       </c>
       <c r="C160" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B161" s="3">
-        <v>1001100626828</v>
+        <v>1001100616826</v>
       </c>
       <c r="C161" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B162" s="3">
-        <v>1001035026308</v>
+        <v>1001100626828</v>
       </c>
       <c r="C162" t="s">
-        <v>181</v>
+        <v>314</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>539</v>
+        <v>326</v>
       </c>
       <c r="B163" s="3">
-        <v>1001014486159</v>
+        <v>1001100626828</v>
       </c>
       <c r="C163" t="s">
-        <v>540</v>
+        <v>314</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B164" s="3">
-        <v>1001014486159</v>
+        <v>1001035026308</v>
       </c>
       <c r="C164" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>184</v>
+        <v>539</v>
       </c>
       <c r="B165" s="3">
-        <v>1001035326217</v>
+        <v>1001014486159</v>
       </c>
       <c r="C165" t="s">
-        <v>271</v>
+        <v>540</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>486</v>
+        <v>182</v>
       </c>
       <c r="B166" s="3">
-        <v>1001012426220</v>
+        <v>1001014486159</v>
       </c>
       <c r="C166" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B167" s="3">
-        <v>1001012426220</v>
+        <v>1001035326217</v>
       </c>
       <c r="C167" t="s">
-        <v>186</v>
+        <v>271</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>187</v>
+        <v>486</v>
       </c>
       <c r="B168" s="3">
-        <v>1001022466236</v>
+        <v>1001012426220</v>
       </c>
       <c r="C168" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B169" s="3">
-        <v>1001021966602</v>
+        <v>1001012426220</v>
       </c>
       <c r="C169" t="s">
-        <v>791</v>
+        <v>186</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B170" s="3">
-        <v>1001022296656</v>
+        <v>1001022466236</v>
       </c>
       <c r="C170" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="B171" s="3">
-        <v>1001301876697</v>
+        <v>1001021966602</v>
       </c>
       <c r="C171" t="s">
-        <v>194</v>
+        <v>791</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="B172" s="3">
-        <v>1001022246713</v>
+        <v>1001022296656</v>
       </c>
       <c r="C172" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B173" s="3">
-        <v>1001022376722</v>
+        <v>1001301876697</v>
       </c>
       <c r="C173" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B174" s="3">
-        <v>1001020846751</v>
+        <v>1001022246713</v>
       </c>
       <c r="C174" t="s">
-        <v>78</v>
+        <v>196</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B175" s="3">
-        <v>1001022725819</v>
+        <v>1001022376722</v>
       </c>
       <c r="C175" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B176" s="3">
-        <v>1001012825337</v>
+        <v>1001020846751</v>
       </c>
       <c r="C176" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B177" s="3">
-        <v>1001012815336</v>
+        <v>1001022725819</v>
       </c>
       <c r="C177" t="s">
-        <v>24</v>
+        <v>202</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B178" s="3">
-        <v>1001234146448</v>
+        <v>1001012825337</v>
       </c>
       <c r="C178" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B179" s="3">
-        <v>1001022725819</v>
+        <v>1001012815336</v>
       </c>
       <c r="C179" t="s">
-        <v>202</v>
+        <v>24</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B180" s="3">
-        <v>1001092676027</v>
+        <v>1001234146448</v>
       </c>
       <c r="C180" t="s">
-        <v>208</v>
+        <v>59</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B181" s="3">
-        <v>1001301876213</v>
+        <v>1001022725819</v>
       </c>
       <c r="C181" t="s">
-        <v>69</v>
+        <v>202</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="B182" s="3">
-        <v>1001035026308</v>
+        <v>1001092676027</v>
       </c>
       <c r="C182" t="s">
-        <v>388</v>
+        <v>208</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="B183" s="3">
-        <v>1001234146448</v>
+        <v>1001301876213</v>
       </c>
       <c r="C183" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B184" s="3">
-        <v>1001061977613</v>
+        <v>1001035026308</v>
       </c>
       <c r="C184" t="s">
-        <v>790</v>
+        <v>388</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B185" s="3">
-        <v>1001025176475</v>
+        <v>1001234146448</v>
       </c>
       <c r="C185" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B186" s="3">
-        <v>1001012456498</v>
+        <v>1001025176475</v>
       </c>
       <c r="C186" t="s">
-        <v>218</v>
+        <v>64</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B187" s="3">
-        <v>1001010036596</v>
+        <v>1001012456498</v>
       </c>
       <c r="C187" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>550</v>
+        <v>219</v>
       </c>
       <c r="B188" s="3">
-        <v>1001033856608</v>
+        <v>1001010036596</v>
       </c>
       <c r="C188" t="s">
-        <v>541</v>
+        <v>220</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="B189" s="3">
         <v>1001033856608</v>
@@ -4865,18 +4892,18 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="B190" s="3">
-        <v>1001033856609</v>
+        <v>1001033856608</v>
       </c>
       <c r="C190" t="s">
-        <v>222</v>
+        <v>541</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>221</v>
+        <v>551</v>
       </c>
       <c r="B191" s="3">
         <v>1001033856609</v>
@@ -4887,315 +4914,315 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B192" s="3">
-        <v>1001093345495</v>
+        <v>1001033856609</v>
       </c>
       <c r="C192" t="s">
-        <v>424</v>
+        <v>222</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B193" s="3">
-        <v>6550</v>
+        <v>1001093345495</v>
       </c>
       <c r="C193" t="s">
-        <v>227</v>
+        <v>424</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B194" s="3">
-        <v>1001304506684</v>
+        <v>6550</v>
       </c>
       <c r="C194" t="s">
-        <v>53</v>
+        <v>227</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B195" s="3">
-        <v>1001010113248</v>
+        <v>1001304506684</v>
       </c>
       <c r="C195" t="s">
-        <v>230</v>
+        <v>53</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>396</v>
+        <v>229</v>
       </c>
       <c r="B196" s="3">
-        <v>1001063926780</v>
+        <v>1001010113248</v>
       </c>
       <c r="C196" t="s">
-        <v>397</v>
+        <v>230</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>231</v>
+        <v>396</v>
       </c>
       <c r="B197" s="3">
-        <v>6586</v>
+        <v>1001063926780</v>
       </c>
       <c r="C197" t="s">
-        <v>232</v>
+        <v>397</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B198" s="3">
-        <v>1001303636467</v>
+        <v>6586</v>
       </c>
       <c r="C198" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B199" s="3">
-        <v>1001304496701</v>
+        <v>1001303636467</v>
       </c>
       <c r="C199" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B200" s="3">
-        <v>6144</v>
+        <v>1001304496701</v>
       </c>
       <c r="C200" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B201" s="3">
-        <v>1001022725819</v>
+        <v>6144</v>
       </c>
       <c r="C201" t="s">
-        <v>202</v>
+        <v>239</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B202" s="3">
-        <v>1001022373812</v>
+        <v>1001022725819</v>
       </c>
       <c r="C202" t="s">
-        <v>3</v>
+        <v>202</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B203" s="3">
-        <v>1001024906062</v>
+        <v>1001022373812</v>
       </c>
       <c r="C203" t="s">
-        <v>244</v>
+        <v>3</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B204" s="3">
-        <v>1001303056692</v>
+        <v>1001024906062</v>
       </c>
       <c r="C204" t="s">
-        <v>54</v>
+        <v>244</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B205" s="3">
-        <v>1001301876697</v>
+        <v>1001303056692</v>
       </c>
       <c r="C205" t="s">
-        <v>194</v>
+        <v>54</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B206" s="3">
-        <v>1001012634574</v>
+        <v>1001301876697</v>
       </c>
       <c r="C206" t="s">
-        <v>11</v>
+        <v>194</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B207" s="3">
-        <v>1001092485452</v>
+        <v>1001012634574</v>
       </c>
       <c r="C207" t="s">
-        <v>250</v>
+        <v>11</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B208" s="3">
-        <v>1001020966144</v>
+        <v>1001092485452</v>
       </c>
       <c r="C208" t="s">
-        <v>135</v>
+        <v>250</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B209" s="3">
-        <v>6586</v>
+        <v>1001020966144</v>
       </c>
       <c r="C209" t="s">
-        <v>232</v>
+        <v>135</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B210" s="3">
-        <v>1001304496701</v>
+        <v>6586</v>
       </c>
       <c r="C210" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B211" s="3">
-        <v>1001063655015</v>
+        <v>1001304496701</v>
       </c>
       <c r="C211" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B212" s="3">
-        <v>1001060763287</v>
+        <v>1001063655015</v>
       </c>
       <c r="C212" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B213" s="3">
-        <v>1001225416228</v>
+        <v>1001060763287</v>
       </c>
       <c r="C213" t="s">
-        <v>151</v>
+        <v>259</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B214" s="3">
-        <v>1001032736550</v>
+        <v>1001225416228</v>
       </c>
       <c r="C214" t="s">
-        <v>786</v>
+        <v>151</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B215" s="3">
-        <v>6758</v>
+        <v>1001032736550</v>
       </c>
       <c r="C215" t="s">
-        <v>263</v>
+        <v>786</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B216" s="3">
-        <v>1001020965976</v>
+        <v>6758</v>
       </c>
       <c r="C216" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B217" s="3">
-        <v>1001215576586</v>
+        <v>1001020965976</v>
       </c>
       <c r="C217" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B218" s="3">
-        <v>1001094896026</v>
+        <v>1001215576586</v>
       </c>
       <c r="C218" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>477</v>
+        <v>268</v>
       </c>
       <c r="B219" s="3">
-        <v>1001215576586</v>
+        <v>1001094896026</v>
       </c>
       <c r="C219" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>270</v>
+        <v>477</v>
       </c>
       <c r="B220" s="3">
         <v>1001215576586</v>
@@ -5206,18 +5233,18 @@
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>763</v>
+        <v>270</v>
       </c>
       <c r="B221" s="3">
-        <v>1001092436470</v>
+        <v>1001215576586</v>
       </c>
       <c r="C221" t="s">
-        <v>764</v>
+        <v>267</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>272</v>
+        <v>763</v>
       </c>
       <c r="B222" s="3">
         <v>1001092436470</v>
@@ -5228,29 +5255,29 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B223" s="3">
-        <v>1001203146555</v>
+        <v>1001092436470</v>
       </c>
       <c r="C223" t="s">
-        <v>277</v>
+        <v>764</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="B224" s="3">
-        <v>1001016747343</v>
+        <v>1001203146555</v>
       </c>
       <c r="C224" t="s">
-        <v>734</v>
+        <v>277</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>696</v>
+        <v>288</v>
       </c>
       <c r="B225" s="3">
         <v>1001016747343</v>
@@ -5261,7 +5288,7 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>279</v>
+        <v>696</v>
       </c>
       <c r="B226" s="3">
         <v>1001016747343</v>
@@ -5272,7 +5299,7 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>736</v>
+        <v>279</v>
       </c>
       <c r="B227" s="3">
         <v>1001016747343</v>
@@ -5283,51 +5310,51 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>281</v>
+        <v>736</v>
       </c>
       <c r="B228" s="3">
-        <v>1001014765993</v>
+        <v>1001016747343</v>
       </c>
       <c r="C228" t="s">
-        <v>280</v>
+        <v>734</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B229" s="3">
-        <v>1001025166776</v>
+        <v>1001014765993</v>
       </c>
       <c r="C229" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B230" s="3">
-        <v>1001025506777</v>
+        <v>1001025166776</v>
       </c>
       <c r="C230" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="B231" s="3">
-        <v>1001025546822</v>
+        <v>1001025506777</v>
       </c>
       <c r="C231" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B232" s="3">
         <v>1001025546822</v>
@@ -5338,40 +5365,40 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="B233" s="3">
         <v>1001025546822</v>
       </c>
       <c r="C233" t="s">
-        <v>533</v>
+        <v>287</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>286</v>
+        <v>319</v>
       </c>
       <c r="B234" s="3">
         <v>1001025546822</v>
       </c>
       <c r="C234" t="s">
-        <v>287</v>
+        <v>533</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>643</v>
+        <v>286</v>
       </c>
       <c r="B235" s="3">
-        <v>1001024976616</v>
+        <v>1001025546822</v>
       </c>
       <c r="C235" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>290</v>
+        <v>643</v>
       </c>
       <c r="B236" s="3">
         <v>1001024976616</v>
@@ -5382,29 +5409,29 @@
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B237" s="3">
-        <v>1001010855247</v>
+        <v>1001024976616</v>
       </c>
       <c r="C237" t="s">
-        <v>22</v>
+        <v>289</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>368</v>
+        <v>291</v>
       </c>
       <c r="B238" s="3">
-        <v>1001223296919</v>
+        <v>1001010855247</v>
       </c>
       <c r="C238" t="s">
-        <v>371</v>
+        <v>22</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>60</v>
+        <v>368</v>
       </c>
       <c r="B239" s="3">
         <v>1001223296919</v>
@@ -5415,7 +5442,7 @@
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>214</v>
+        <v>60</v>
       </c>
       <c r="B240" s="3">
         <v>1001223296919</v>
@@ -5426,29 +5453,29 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>440</v>
+        <v>214</v>
       </c>
       <c r="B241" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C241" t="s">
-        <v>456</v>
+        <v>371</v>
       </c>
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="B242" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C242" t="s">
-        <v>371</v>
+        <v>456</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>292</v>
+        <v>462</v>
       </c>
       <c r="B243" s="3">
         <v>1001223296919</v>
@@ -5459,73 +5486,73 @@
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B244" s="3">
-        <v>1001014765993</v>
+        <v>1001223296919</v>
       </c>
       <c r="C244" t="s">
-        <v>280</v>
+        <v>371</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B245" s="3">
-        <v>1001025166776</v>
+        <v>1001014765993</v>
       </c>
       <c r="C245" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B246" s="3">
-        <v>1001025506777</v>
+        <v>1001025166776</v>
       </c>
       <c r="C246" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B247" s="3">
-        <v>1001025526778</v>
+        <v>1001025506777</v>
       </c>
       <c r="C247" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B248" s="3">
-        <v>1001304236685</v>
+        <v>1001025526778</v>
       </c>
       <c r="C248" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="B249" s="3">
-        <v>1001015496769</v>
+        <v>1001304236685</v>
       </c>
       <c r="C249" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="B250" s="3">
         <v>1001015496769</v>
@@ -5536,84 +5563,84 @@
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B251" s="3">
-        <v>1001014766798</v>
+        <v>1001015496769</v>
       </c>
       <c r="C251" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B252" s="3">
-        <v>1001015026797</v>
+        <v>1001014766798</v>
       </c>
       <c r="C252" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B253" s="3">
-        <v>1001205386222</v>
+        <v>1001015026797</v>
       </c>
       <c r="C253" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B254" s="3">
-        <v>1001092675224</v>
+        <v>1001205386222</v>
       </c>
       <c r="C254" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B255" s="3">
-        <v>1001225406223</v>
+        <v>1001092675224</v>
       </c>
       <c r="C255" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B256" s="3">
-        <v>1001300366790</v>
+        <v>1001225406223</v>
       </c>
       <c r="C256" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>458</v>
+        <v>331</v>
       </c>
       <c r="B257" s="3">
-        <v>1001304096792</v>
+        <v>1001300366790</v>
       </c>
       <c r="C257" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>333</v>
+        <v>458</v>
       </c>
       <c r="B258" s="3">
         <v>1001304096792</v>
@@ -5624,18 +5651,18 @@
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>358</v>
+        <v>333</v>
       </c>
       <c r="B259" s="3">
-        <v>1001303637603</v>
+        <v>1001304096792</v>
       </c>
       <c r="C259" t="s">
-        <v>755</v>
+        <v>344</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="B260" s="3">
         <v>1001303637603</v>
@@ -5646,7 +5673,7 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>334</v>
+        <v>378</v>
       </c>
       <c r="B261" s="3">
         <v>1001303637603</v>
@@ -5657,7 +5684,7 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>767</v>
+        <v>334</v>
       </c>
       <c r="B262" s="3">
         <v>1001303637603</v>
@@ -5668,18 +5695,18 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>379</v>
+        <v>767</v>
       </c>
       <c r="B263" s="3">
-        <v>1001303636794</v>
+        <v>1001303637603</v>
       </c>
       <c r="C263" t="s">
-        <v>345</v>
+        <v>755</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>478</v>
+        <v>379</v>
       </c>
       <c r="B264" s="3">
         <v>1001303636794</v>
@@ -5690,7 +5717,7 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>335</v>
+        <v>478</v>
       </c>
       <c r="B265" s="3">
         <v>1001303636794</v>
@@ -5701,51 +5728,51 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B266" s="3">
-        <v>1001302596795</v>
+        <v>1001303636794</v>
       </c>
       <c r="C266" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B267" s="3">
-        <v>1001302596796</v>
+        <v>1001302596795</v>
       </c>
       <c r="C267" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B268" s="3">
-        <v>1001300456804</v>
+        <v>1001302596796</v>
       </c>
       <c r="C268" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>427</v>
+        <v>338</v>
       </c>
       <c r="B269" s="3">
-        <v>1001300366806</v>
+        <v>1001300456804</v>
       </c>
       <c r="C269" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>339</v>
+        <v>427</v>
       </c>
       <c r="B270" s="3">
         <v>1001300366806</v>
@@ -5756,62 +5783,62 @@
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B271" s="3">
-        <v>1001300516803</v>
+        <v>1001300366806</v>
       </c>
       <c r="C271" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B272" s="3">
-        <v>1001300366807</v>
+        <v>1001300516803</v>
       </c>
       <c r="C272" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="B273" s="3">
         <v>1001300366807</v>
       </c>
       <c r="C273" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B274" s="3">
-        <v>1001300516785</v>
+        <v>1001300366807</v>
       </c>
       <c r="C274" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>519</v>
+        <v>354</v>
       </c>
       <c r="B275" s="3">
-        <v>1001300456787</v>
+        <v>1001300516785</v>
       </c>
       <c r="C275" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>534</v>
+        <v>519</v>
       </c>
       <c r="B276" s="3">
         <v>1001300456787</v>
@@ -5822,7 +5849,7 @@
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>356</v>
+        <v>534</v>
       </c>
       <c r="B277" s="3">
         <v>1001300456787</v>
@@ -5833,62 +5860,62 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B278" s="3">
-        <v>1001302596795</v>
+        <v>1001300456787</v>
       </c>
       <c r="C278" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B279" s="3">
-        <v>1001012486332</v>
+        <v>1001302596795</v>
       </c>
       <c r="C279" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B280" s="3">
-        <v>1001012566345</v>
+        <v>1001012486332</v>
       </c>
       <c r="C280" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B281" s="3">
-        <v>1001031076528</v>
+        <v>1001012566345</v>
       </c>
       <c r="C281" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="B282" s="3">
-        <v>1001020836761</v>
+        <v>1001031076528</v>
       </c>
       <c r="C282" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B283" s="3">
         <v>1001020836761</v>
@@ -5899,7 +5926,7 @@
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>372</v>
+        <v>400</v>
       </c>
       <c r="B284" s="3">
         <v>1001020836761</v>
@@ -5910,18 +5937,18 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="B285" s="3">
-        <v>1001020846764</v>
+        <v>1001020836761</v>
       </c>
       <c r="C285" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="B286" s="3">
         <v>1001020846764</v>
@@ -5932,7 +5959,7 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="B287" s="3">
         <v>1001020846764</v>
@@ -5943,18 +5970,18 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>474</v>
+        <v>374</v>
       </c>
       <c r="B288" s="3">
-        <v>1001300366790</v>
+        <v>1001020846764</v>
       </c>
       <c r="C288" t="s">
-        <v>342</v>
+        <v>375</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>376</v>
+        <v>474</v>
       </c>
       <c r="B289" s="3">
         <v>1001300366790</v>
@@ -5965,18 +5992,18 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>332</v>
+        <v>376</v>
       </c>
       <c r="B290" s="3">
-        <v>1001304096791</v>
+        <v>1001300366790</v>
       </c>
       <c r="C290" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>449</v>
+        <v>332</v>
       </c>
       <c r="B291" s="3">
         <v>1001304096791</v>
@@ -5987,7 +6014,7 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>377</v>
+        <v>449</v>
       </c>
       <c r="B292" s="3">
         <v>1001304096791</v>
@@ -5998,73 +6025,73 @@
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B293" s="3">
-        <v>1001302596795</v>
+        <v>1001304096791</v>
       </c>
       <c r="C293" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B294" s="3">
-        <v>1001300516803</v>
+        <v>1001302596795</v>
       </c>
       <c r="C294" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B295" s="3">
-        <v>1001300456804</v>
+        <v>1001300516803</v>
       </c>
       <c r="C295" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B296" s="3">
-        <v>1001300366807</v>
+        <v>1001300456804</v>
       </c>
       <c r="C296" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B297" s="3">
-        <v>1001302596796</v>
+        <v>1001300366807</v>
       </c>
       <c r="C297" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>433</v>
+        <v>384</v>
       </c>
       <c r="B298" s="3">
-        <v>1001023696765</v>
+        <v>1001302596796</v>
       </c>
       <c r="C298" t="s">
-        <v>386</v>
+        <v>347</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>452</v>
+        <v>433</v>
       </c>
       <c r="B299" s="3">
         <v>1001023696765</v>
@@ -6075,7 +6102,7 @@
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>385</v>
+        <v>452</v>
       </c>
       <c r="B300" s="3">
         <v>1001023696765</v>
@@ -6086,18 +6113,18 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B301" s="3">
-        <v>1001023696767</v>
+        <v>1001023696765</v>
       </c>
       <c r="C301" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="B302" s="3">
         <v>1001023696767</v>
@@ -6108,7 +6135,7 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="B303" s="3">
         <v>1001023696767</v>
@@ -6119,18 +6146,18 @@
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B304" s="3">
-        <v>1001024976829</v>
+        <v>1001023696767</v>
       </c>
       <c r="C304" t="s">
-        <v>787</v>
+        <v>390</v>
       </c>
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B305" s="3">
         <v>1001024976829</v>
@@ -6141,29 +6168,29 @@
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="B306" s="3">
-        <v>1001022376722</v>
+        <v>1001024976829</v>
       </c>
       <c r="C306" t="s">
-        <v>110</v>
+        <v>787</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>432</v>
+        <v>405</v>
       </c>
       <c r="B307" s="3">
-        <v>1001020846762</v>
+        <v>1001022376722</v>
       </c>
       <c r="C307" t="s">
-        <v>407</v>
+        <v>110</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>451</v>
+        <v>432</v>
       </c>
       <c r="B308" s="3">
         <v>1001020846762</v>
@@ -6174,7 +6201,7 @@
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>406</v>
+        <v>451</v>
       </c>
       <c r="B309" s="3">
         <v>1001020846762</v>
@@ -6185,18 +6212,18 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>115</v>
+        <v>406</v>
       </c>
       <c r="B310" s="3">
-        <v>1001022656853</v>
+        <v>1001020846762</v>
       </c>
       <c r="C310" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>473</v>
+        <v>115</v>
       </c>
       <c r="B311" s="3">
         <v>1001022656853</v>
@@ -6207,18 +6234,18 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>555</v>
+        <v>473</v>
       </c>
       <c r="B312" s="3">
-        <v>1001022656948</v>
+        <v>1001022656853</v>
       </c>
       <c r="C312" t="s">
-        <v>546</v>
+        <v>410</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="B313" s="3">
         <v>1001022656948</v>
@@ -6229,7 +6256,7 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>409</v>
+        <v>549</v>
       </c>
       <c r="B314" s="3">
         <v>1001022656948</v>
@@ -6240,29 +6267,29 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="B315" s="3">
-        <v>1001022656852</v>
+        <v>1001022656948</v>
       </c>
       <c r="C315" t="s">
-        <v>416</v>
+        <v>546</v>
       </c>
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>434</v>
+        <v>415</v>
       </c>
       <c r="B316" s="3">
-        <v>1001020836759</v>
+        <v>1001022656852</v>
       </c>
       <c r="C316" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
-        <v>450</v>
+        <v>434</v>
       </c>
       <c r="B317" s="3">
         <v>1001020836759</v>
@@ -6273,7 +6300,7 @@
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>417</v>
+        <v>450</v>
       </c>
       <c r="B318" s="3">
         <v>1001020836759</v>
@@ -6284,51 +6311,51 @@
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B319" s="3">
-        <v>1001023856870</v>
+        <v>1001020836759</v>
       </c>
       <c r="C319" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>435</v>
+        <v>419</v>
       </c>
       <c r="B320" s="3">
-        <v>1001013956426</v>
+        <v>1001023856870</v>
       </c>
       <c r="C320" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B321" s="3">
-        <v>1001093345495</v>
+        <v>1001013956426</v>
       </c>
       <c r="C321" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>466</v>
+        <v>437</v>
       </c>
       <c r="B322" s="3">
-        <v>1001022656868</v>
+        <v>1001093345495</v>
       </c>
       <c r="C322" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c r="B323" s="3">
         <v>1001022656868</v>
@@ -6339,18 +6366,18 @@
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>157</v>
+        <v>438</v>
       </c>
       <c r="B324" s="3">
-        <v>1001034065698</v>
+        <v>1001022656868</v>
       </c>
       <c r="C324" t="s">
-        <v>411</v>
+        <v>439</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B325" s="3">
         <v>1001034065698</v>
@@ -6361,7 +6388,7 @@
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>464</v>
+        <v>175</v>
       </c>
       <c r="B326" s="3">
         <v>1001034065698</v>
@@ -6372,7 +6399,7 @@
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
       <c r="B327" s="3">
         <v>1001034065698</v>
@@ -6383,29 +6410,29 @@
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B328" s="3">
-        <v>1001084216206</v>
+        <v>1001034065698</v>
       </c>
       <c r="C328" t="s">
-        <v>370</v>
+        <v>411</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="B329" s="3">
-        <v>1001015646861</v>
+        <v>1001084216206</v>
       </c>
       <c r="C329" t="s">
-        <v>408</v>
+        <v>370</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="B330" s="3">
         <v>1001015646861</v>
@@ -6416,18 +6443,18 @@
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="B331" s="3">
-        <v>1001025176768</v>
+        <v>1001015646861</v>
       </c>
       <c r="C331" t="s">
-        <v>431</v>
+        <v>408</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="B332" s="3">
         <v>1001025176768</v>
@@ -6438,7 +6465,7 @@
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B333" s="3">
         <v>1001025176768</v>
@@ -6449,18 +6476,18 @@
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="B334" s="3">
-        <v>1001025486770</v>
+        <v>1001025176768</v>
       </c>
       <c r="C334" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="B335" s="3">
         <v>1001025486770</v>
@@ -6471,7 +6498,7 @@
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="B336" s="3">
         <v>1001025486770</v>
@@ -6482,18 +6509,18 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>197</v>
+        <v>446</v>
       </c>
       <c r="B337" s="3">
-        <v>1001012816340</v>
+        <v>1001025486770</v>
       </c>
       <c r="C337" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>468</v>
+        <v>197</v>
       </c>
       <c r="B338" s="3">
         <v>1001012816340</v>
@@ -6504,7 +6531,7 @@
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="B339" s="3">
         <v>1001012816340</v>
@@ -6515,18 +6542,18 @@
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>293</v>
+        <v>447</v>
       </c>
       <c r="B340" s="3">
-        <v>1001203146834</v>
+        <v>1001012816340</v>
       </c>
       <c r="C340" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
-        <v>441</v>
+        <v>293</v>
       </c>
       <c r="B341" s="3">
         <v>1001203146834</v>
@@ -6537,7 +6564,7 @@
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="B342" s="3">
         <v>1001203146834</v>
@@ -6548,7 +6575,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="B343" s="3">
         <v>1001203146834</v>
@@ -6559,40 +6586,40 @@
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="B344" s="3">
-        <v>1001300456788</v>
+        <v>1001203146834</v>
       </c>
       <c r="C344" t="s">
-        <v>461</v>
+        <v>414</v>
       </c>
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="B345" s="3">
-        <v>1001300516786</v>
+        <v>1001300456788</v>
       </c>
       <c r="C345" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>530</v>
+        <v>475</v>
       </c>
       <c r="B346" s="3">
-        <v>1001092436495</v>
+        <v>1001300516786</v>
       </c>
       <c r="C346" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="B347" s="3">
         <v>1001092436495</v>
@@ -6603,7 +6630,7 @@
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>480</v>
+        <v>537</v>
       </c>
       <c r="B348" s="3">
         <v>1001092436495</v>
@@ -6614,40 +6641,40 @@
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B349" s="3">
-        <v>1001025526901</v>
+        <v>1001092436495</v>
       </c>
       <c r="C349" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B350" s="3">
-        <v>1001025546931</v>
+        <v>1001025526901</v>
       </c>
       <c r="C350" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="B351" s="3">
-        <v>1001010017539</v>
+        <v>1001025546931</v>
       </c>
       <c r="C351" t="s">
-        <v>756</v>
+        <v>485</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>523</v>
+        <v>493</v>
       </c>
       <c r="B352" s="3">
         <v>1001010017539</v>
@@ -6658,7 +6685,7 @@
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>487</v>
+        <v>523</v>
       </c>
       <c r="B353" s="3">
         <v>1001010017539</v>
@@ -6669,7 +6696,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>761</v>
+        <v>487</v>
       </c>
       <c r="B354" s="3">
         <v>1001010017539</v>
@@ -6680,18 +6707,18 @@
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>490</v>
+        <v>761</v>
       </c>
       <c r="B355" s="3">
-        <v>1001025766909</v>
+        <v>1001010017539</v>
       </c>
       <c r="C355" t="s">
-        <v>489</v>
+        <v>756</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>524</v>
+        <v>490</v>
       </c>
       <c r="B356" s="3">
         <v>1001025766909</v>
@@ -6702,7 +6729,7 @@
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>488</v>
+        <v>524</v>
       </c>
       <c r="B357" s="3">
         <v>1001025766909</v>
@@ -6713,18 +6740,18 @@
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>522</v>
+        <v>488</v>
       </c>
       <c r="B358" s="3">
-        <v>1001010014558</v>
+        <v>1001025766909</v>
       </c>
       <c r="C358" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
-        <v>491</v>
+        <v>522</v>
       </c>
       <c r="B359" s="3">
         <v>1001010014558</v>
@@ -6735,18 +6762,18 @@
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>517</v>
+        <v>491</v>
       </c>
       <c r="B360" s="3">
-        <v>1001012596802</v>
+        <v>1001010014558</v>
       </c>
       <c r="C360" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="B361" s="3">
         <v>1001012596802</v>
@@ -6757,7 +6784,7 @@
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>494</v>
+        <v>526</v>
       </c>
       <c r="B362" s="3">
         <v>1001012596802</v>
@@ -6768,18 +6795,18 @@
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="B363" s="3">
-        <v>1001012596801</v>
+        <v>1001012596802</v>
       </c>
       <c r="C363" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="B364" s="3">
         <v>1001012596801</v>
@@ -6790,7 +6817,7 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>496</v>
+        <v>525</v>
       </c>
       <c r="B365" s="3">
         <v>1001012596801</v>
@@ -6801,161 +6828,161 @@
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B366" s="3">
-        <v>1001062353684</v>
+        <v>1001012596801</v>
       </c>
       <c r="C366" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B367" s="3">
-        <v>1001010014555</v>
+        <v>1001062353684</v>
       </c>
       <c r="C367" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B368" s="3">
-        <v>1001083424691</v>
+        <v>1001010014555</v>
       </c>
       <c r="C368" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B369" s="3">
-        <v>1001190765679</v>
+        <v>1001083424691</v>
       </c>
       <c r="C369" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B370" s="3">
-        <v>1001085636200</v>
+        <v>1001190765679</v>
       </c>
       <c r="C370" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B371" s="3">
-        <v>1001020836253</v>
+        <v>1001085636200</v>
       </c>
       <c r="C371" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B372" s="3">
-        <v>1001084226492</v>
+        <v>1001020836253</v>
       </c>
       <c r="C372" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B373" s="3">
-        <v>1001223296921</v>
+        <v>1001084226492</v>
       </c>
       <c r="C373" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B374" s="3">
-        <v>1001053944786</v>
+        <v>1001223296921</v>
       </c>
       <c r="C374" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="B375" s="3">
-        <v>1001010016839</v>
+        <v>1001053944786</v>
       </c>
       <c r="C375" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="B376" s="3">
-        <v>1001023857038</v>
+        <v>1001010016839</v>
       </c>
       <c r="C376" t="s">
-        <v>568</v>
+        <v>521</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B377" s="3">
-        <v>1001040434903</v>
+        <v>1001023857038</v>
       </c>
       <c r="C377" t="s">
-        <v>529</v>
+        <v>568</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B378" s="3">
-        <v>1001080216842</v>
+        <v>1001040434903</v>
       </c>
       <c r="C378" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="B379" s="3">
-        <v>1001022466951</v>
+        <v>1001080216842</v>
       </c>
       <c r="C379" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B380" s="3">
         <v>1001022466951</v>
@@ -6966,106 +6993,106 @@
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="B381" s="3">
-        <v>1001035276653</v>
+        <v>1001022466951</v>
       </c>
       <c r="C381" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="B382" s="3">
-        <v>1001062353680</v>
+        <v>1001035276653</v>
       </c>
       <c r="C382" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B383" s="3">
-        <v>1001061971146</v>
+        <v>1001062353680</v>
       </c>
       <c r="C383" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B384" s="3">
-        <v>1001225636201</v>
+        <v>1001061971146</v>
       </c>
       <c r="C384" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B385" s="3">
-        <v>1001095227035</v>
+        <v>1001225636201</v>
       </c>
       <c r="C385" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B386" s="3">
-        <v>1001023857038</v>
+        <v>1001095227035</v>
       </c>
       <c r="C386" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B387" s="3">
-        <v>1001025027040</v>
+        <v>1001023857038</v>
       </c>
       <c r="C387" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>571</v>
+        <v>794</v>
       </c>
       <c r="B388" s="3">
-        <v>1001223297103</v>
+        <v>1001025027040</v>
       </c>
       <c r="C388" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="B389" s="3">
-        <v>1001223297103</v>
+        <v>1001025027040</v>
       </c>
       <c r="C389" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B390" s="3">
         <v>1001223297103</v>
@@ -7076,139 +7103,139 @@
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
-        <v>593</v>
+        <v>573</v>
       </c>
       <c r="B391" s="3">
-        <v>1001010032675</v>
+        <v>1001223297103</v>
       </c>
       <c r="C391" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="B392" s="3">
-        <v>1001010032675</v>
+        <v>1001223297103</v>
       </c>
       <c r="C392" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="B393" s="3">
-        <v>1001035937001</v>
+        <v>1001010032675</v>
       </c>
       <c r="C393" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B394" s="3">
-        <v>1001035937001</v>
+        <v>1001010032675</v>
       </c>
       <c r="C394" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="B395" s="3">
-        <v>1001084217090</v>
+        <v>1001035937001</v>
       </c>
       <c r="C395" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="B396" s="3">
-        <v>1001084217090</v>
+        <v>1001035937001</v>
       </c>
       <c r="C396" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B397" s="3">
-        <v>1001022377066</v>
+        <v>1001084217090</v>
       </c>
       <c r="C397" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="B398" s="3">
-        <v>1001022377066</v>
+        <v>1001084217090</v>
       </c>
       <c r="C398" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B399" s="3">
-        <v>1001022467080</v>
+        <v>1001022377066</v>
       </c>
       <c r="C399" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B400" s="3">
-        <v>1001022467080</v>
+        <v>1001022377066</v>
       </c>
       <c r="C400" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B401" s="3">
-        <v>1001025507255</v>
+        <v>1001022467080</v>
       </c>
       <c r="C401" t="s">
-        <v>735</v>
+        <v>583</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B402" s="3">
-        <v>1001025507255</v>
+        <v>1001022467080</v>
       </c>
       <c r="C402" t="s">
-        <v>735</v>
+        <v>583</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
-        <v>742</v>
+        <v>602</v>
       </c>
       <c r="B403" s="3">
         <v>1001025507255</v>
@@ -7219,678 +7246,678 @@
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
-        <v>605</v>
+        <v>584</v>
       </c>
       <c r="B404" s="3">
-        <v>1001022657075</v>
+        <v>1001025507255</v>
       </c>
       <c r="C404" t="s">
-        <v>586</v>
+        <v>735</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
-        <v>585</v>
+        <v>742</v>
       </c>
       <c r="B405" s="3">
-        <v>1001022657075</v>
+        <v>1001025507255</v>
       </c>
       <c r="C405" t="s">
-        <v>586</v>
+        <v>735</v>
       </c>
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B406" s="3">
-        <v>1001022467082</v>
+        <v>1001022657075</v>
       </c>
       <c r="C406" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B407" s="3">
-        <v>1001022467082</v>
+        <v>1001022657075</v>
       </c>
       <c r="C407" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B408" s="3">
-        <v>1001022377070</v>
+        <v>1001022467082</v>
       </c>
       <c r="C408" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="B409" s="3">
-        <v>1001022377070</v>
+        <v>1001022467082</v>
       </c>
       <c r="C409" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B410" s="3">
-        <v>1001022657073</v>
+        <v>1001022377070</v>
       </c>
       <c r="C410" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="B411" s="3">
-        <v>1001022657073</v>
+        <v>1001022377070</v>
       </c>
       <c r="C411" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
-        <v>617</v>
+        <v>606</v>
       </c>
       <c r="B412" s="3">
-        <v>1001010027126</v>
+        <v>1001022657073</v>
       </c>
       <c r="C412" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="B413" s="3">
-        <v>1001010027126</v>
+        <v>1001022657073</v>
       </c>
       <c r="C413" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
-        <v>596</v>
+        <v>617</v>
       </c>
       <c r="B414" s="3">
-        <v>1001010027125</v>
+        <v>1001010027126</v>
       </c>
       <c r="C414" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>618</v>
+        <v>594</v>
       </c>
       <c r="B415" s="3">
-        <v>1001010027125</v>
+        <v>1001010027126</v>
       </c>
       <c r="C415" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
-        <v>640</v>
+        <v>596</v>
       </c>
       <c r="B416" s="3">
-        <v>1001016366888</v>
+        <v>1001010027125</v>
       </c>
       <c r="C416" t="s">
-        <v>620</v>
+        <v>597</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B417" s="3">
-        <v>1001016366888</v>
+        <v>1001010027125</v>
       </c>
       <c r="C417" t="s">
-        <v>620</v>
+        <v>597</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B418" s="3">
-        <v>1001300367133</v>
+        <v>1001016366888</v>
       </c>
       <c r="C418" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B419" s="3">
-        <v>1001300367133</v>
+        <v>1001016366888</v>
       </c>
       <c r="C419" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B420" s="3">
-        <v>1001303637564</v>
+        <v>1001300367133</v>
       </c>
       <c r="C420" t="s">
-        <v>754</v>
+        <v>622</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B421" s="3">
-        <v>1001303637564</v>
+        <v>1001300367133</v>
       </c>
       <c r="C421" t="s">
-        <v>754</v>
+        <v>622</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="B422" s="3">
-        <v>1001304527146</v>
+        <v>1001303637564</v>
       </c>
       <c r="C422" t="s">
-        <v>625</v>
+        <v>754</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B423" s="3">
-        <v>1001304527146</v>
+        <v>1001303637564</v>
       </c>
       <c r="C423" t="s">
-        <v>625</v>
+        <v>754</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="B424" s="3">
-        <v>1001300517134</v>
+        <v>1001304527146</v>
       </c>
       <c r="C424" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B425" s="3">
-        <v>1001300517134</v>
+        <v>1001304527146</v>
       </c>
       <c r="C425" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
-        <v>628</v>
+        <v>637</v>
       </c>
       <c r="B426" s="3">
-        <v>1001300457135</v>
+        <v>1001300517134</v>
       </c>
       <c r="C426" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B427" s="3">
-        <v>1001304527144</v>
+        <v>1001300517134</v>
       </c>
       <c r="C427" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="B428" s="3">
-        <v>1001304527144</v>
+        <v>1001300457135</v>
       </c>
       <c r="C428" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>662</v>
+        <v>630</v>
       </c>
       <c r="B429" s="3">
-        <v>1001081596620</v>
+        <v>1001304527144</v>
       </c>
       <c r="C429" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>645</v>
+        <v>638</v>
       </c>
       <c r="B430" s="3">
-        <v>1001081596620</v>
+        <v>1001304527144</v>
       </c>
       <c r="C430" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
-        <v>667</v>
+        <v>662</v>
       </c>
       <c r="B431" s="3">
-        <v>1001085637187</v>
+        <v>1001081596620</v>
       </c>
       <c r="C431" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B432" s="3">
-        <v>1001085637187</v>
+        <v>1001081596620</v>
       </c>
       <c r="C432" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B433" s="3">
-        <v>1001015676877</v>
+        <v>1001085637187</v>
       </c>
       <c r="C433" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B434" s="3">
-        <v>1001015676877</v>
+        <v>1001085637187</v>
       </c>
       <c r="C434" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="B435" s="3">
-        <v>1001015686878</v>
+        <v>1001015676877</v>
       </c>
       <c r="C435" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B436" s="3">
-        <v>1001015686878</v>
+        <v>1001015676877</v>
       </c>
       <c r="C436" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
-        <v>652</v>
+        <v>669</v>
       </c>
       <c r="B437" s="3">
-        <v>1001302277232</v>
+        <v>1001015686878</v>
       </c>
       <c r="C437" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B438" s="3">
-        <v>1001304497237</v>
+        <v>1001015686878</v>
       </c>
       <c r="C438" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B439" s="3">
-        <v>1001303107241</v>
+        <v>1001302277232</v>
       </c>
       <c r="C439" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
-        <v>660</v>
+        <v>653</v>
       </c>
       <c r="B440" s="3">
-        <v>1002162216872</v>
+        <v>1001304497237</v>
       </c>
       <c r="C440" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
-        <v>668</v>
+        <v>654</v>
       </c>
       <c r="B441" s="3">
-        <v>1002162216872</v>
+        <v>1001303107241</v>
       </c>
       <c r="C441" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
-        <v>683</v>
+        <v>660</v>
       </c>
       <c r="B442" s="3">
-        <v>1001063237147</v>
+        <v>1002162216872</v>
       </c>
       <c r="C442" t="s">
-        <v>675</v>
+        <v>661</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B443" s="3">
-        <v>1001063237147</v>
+        <v>1002162216872</v>
       </c>
       <c r="C443" t="s">
-        <v>675</v>
+        <v>661</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B444" s="3">
-        <v>1001063097227</v>
+        <v>1001063237147</v>
       </c>
       <c r="C444" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B445" s="3">
-        <v>1001063097227</v>
+        <v>1001063237147</v>
       </c>
       <c r="C445" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B446" s="3">
-        <v>1001066537225</v>
+        <v>1001063097227</v>
       </c>
       <c r="C446" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B447" s="3">
-        <v>1001066537225</v>
+        <v>1001063097227</v>
       </c>
       <c r="C447" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B448" s="3">
-        <v>1001066527226</v>
+        <v>1001066537225</v>
       </c>
       <c r="C448" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="B449" s="3">
-        <v>1001066527226</v>
+        <v>1001066537225</v>
       </c>
       <c r="C449" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="B450" s="3">
-        <v>1001066547228</v>
+        <v>1001066527226</v>
       </c>
       <c r="C450" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
-        <v>690</v>
+        <v>673</v>
       </c>
       <c r="B451" s="3">
-        <v>1001063237229</v>
+        <v>1001066527226</v>
       </c>
       <c r="C451" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
-        <v>684</v>
+        <v>674</v>
       </c>
       <c r="B452" s="3">
-        <v>1001063237229</v>
+        <v>1001066547228</v>
       </c>
       <c r="C452" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B453" s="3">
-        <v>1001063237150</v>
+        <v>1001063237229</v>
       </c>
       <c r="C453" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B454" s="3">
-        <v>1001063237150</v>
+        <v>1001063237229</v>
       </c>
       <c r="C454" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
-        <v>686</v>
+        <v>692</v>
       </c>
       <c r="B455" s="3">
-        <v>1001022467276</v>
+        <v>1001063237150</v>
       </c>
       <c r="C455" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="B456" s="3">
-        <v>1001022467276</v>
+        <v>1001063237150</v>
       </c>
       <c r="C456" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
-        <v>470</v>
+        <v>686</v>
       </c>
       <c r="B457" s="3">
-        <v>1001022556837</v>
+        <v>1001022467276</v>
       </c>
       <c r="C457" t="s">
-        <v>471</v>
+        <v>689</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
-        <v>713</v>
+        <v>691</v>
       </c>
       <c r="B458" s="3">
-        <v>1001022556837</v>
+        <v>1001022467276</v>
       </c>
       <c r="C458" t="s">
-        <v>471</v>
+        <v>689</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="B459" s="5">
+        <v>470</v>
+      </c>
+      <c r="B459" s="3">
         <v>1001022556837</v>
       </c>
-      <c r="C459" s="6" t="s">
+      <c r="C459" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
-        <v>174</v>
+        <v>713</v>
       </c>
       <c r="B460" s="3">
-        <v>1001205376221</v>
+        <v>1001022556837</v>
       </c>
       <c r="C460" t="s">
-        <v>172</v>
+        <v>471</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="B461" s="3">
-        <v>1001205376221</v>
-      </c>
-      <c r="C461" t="s">
-        <v>172</v>
+        <v>694</v>
+      </c>
+      <c r="B461" s="5">
+        <v>1001022556837</v>
+      </c>
+      <c r="C461" s="6" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="B462" s="5">
+        <v>174</v>
+      </c>
+      <c r="B462" s="3">
         <v>1001205376221</v>
       </c>
-      <c r="C462" s="6" t="s">
+      <c r="C462" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
-        <v>479</v>
+        <v>711</v>
       </c>
       <c r="B463" s="3">
-        <v>1001304197608</v>
+        <v>1001205376221</v>
       </c>
       <c r="C463" t="s">
-        <v>779</v>
+        <v>172</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="B464" s="3">
-        <v>1001304197608</v>
-      </c>
-      <c r="C464" t="s">
-        <v>779</v>
+        <v>695</v>
+      </c>
+      <c r="B464" s="5">
+        <v>1001205376221</v>
+      </c>
+      <c r="C464" s="6" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
-        <v>697</v>
+        <v>479</v>
       </c>
       <c r="B465" s="3">
         <v>1001304197608</v>
@@ -7901,490 +7928,556 @@
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="B466" s="5">
-        <v>1001010106325</v>
-      </c>
-      <c r="C466" s="6" t="s">
-        <v>49</v>
+        <v>708</v>
+      </c>
+      <c r="B466" s="3">
+        <v>1001304197608</v>
+      </c>
+      <c r="C466" t="s">
+        <v>779</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="B467" s="5">
-        <v>1001013957231</v>
-      </c>
-      <c r="C467" s="6" t="s">
-        <v>705</v>
+        <v>697</v>
+      </c>
+      <c r="B467" s="3">
+        <v>1001304197608</v>
+      </c>
+      <c r="C467" t="s">
+        <v>779</v>
       </c>
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="B468" s="5">
-        <v>1001013957231</v>
-      </c>
-      <c r="C468" s="6" t="s">
-        <v>705</v>
+        <v>797</v>
+      </c>
+      <c r="B468" s="3">
+        <v>1001304197608</v>
+      </c>
+      <c r="C468" t="s">
+        <v>779</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B469" s="3">
-        <v>1001220286279</v>
-      </c>
-      <c r="C469" t="s">
-        <v>45</v>
+        <v>698</v>
+      </c>
+      <c r="B469" s="5">
+        <v>1001010106325</v>
+      </c>
+      <c r="C469" s="6" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
-        <v>715</v>
-      </c>
-      <c r="B470" s="3">
-        <v>1001220286279</v>
-      </c>
-      <c r="C470" t="s">
-        <v>45</v>
+        <v>709</v>
+      </c>
+      <c r="B470" s="5">
+        <v>1001013957231</v>
+      </c>
+      <c r="C470" s="6" t="s">
+        <v>705</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B471" s="5">
-        <v>1001220286279</v>
+        <v>1001013957231</v>
       </c>
       <c r="C471" s="6" t="s">
-        <v>45</v>
+        <v>705</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="B472" s="5">
-        <v>1001223297092</v>
-      </c>
-      <c r="C472" s="6" t="s">
-        <v>706</v>
+        <v>44</v>
+      </c>
+      <c r="B472" s="3">
+        <v>1001220286279</v>
+      </c>
+      <c r="C472" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="B473" s="5">
-        <v>1001223297092</v>
-      </c>
-      <c r="C473" s="6" t="s">
-        <v>706</v>
+        <v>715</v>
+      </c>
+      <c r="B473" s="3">
+        <v>1001220286279</v>
+      </c>
+      <c r="C473" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="B474" s="3">
-        <v>1001020836724</v>
-      </c>
-      <c r="C474" t="s">
-        <v>564</v>
+        <v>700</v>
+      </c>
+      <c r="B474" s="5">
+        <v>1001220286279</v>
+      </c>
+      <c r="C474" s="6" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="B475" s="3">
-        <v>1001020836724</v>
-      </c>
-      <c r="C475" t="s">
-        <v>564</v>
+        <v>710</v>
+      </c>
+      <c r="B475" s="5">
+        <v>1001223297092</v>
+      </c>
+      <c r="C475" s="6" t="s">
+        <v>706</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B476" s="5">
-        <v>1001020836724</v>
+        <v>1001223297092</v>
       </c>
       <c r="C476" s="6" t="s">
-        <v>564</v>
+        <v>706</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
-        <v>714</v>
-      </c>
-      <c r="B477" s="5">
-        <v>1001062475707</v>
-      </c>
-      <c r="C477" s="6" t="s">
-        <v>707</v>
+        <v>563</v>
+      </c>
+      <c r="B477" s="3">
+        <v>1001020836724</v>
+      </c>
+      <c r="C477" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="B478" s="5">
-        <v>1001062475707</v>
-      </c>
-      <c r="C478" s="6" t="s">
-        <v>707</v>
+        <v>712</v>
+      </c>
+      <c r="B478" s="3">
+        <v>1001020836724</v>
+      </c>
+      <c r="C478" t="s">
+        <v>564</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B479" s="5">
-        <v>1001033856609</v>
+        <v>1001020836724</v>
       </c>
       <c r="C479" s="6" t="s">
-        <v>222</v>
+        <v>564</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="B480" s="5">
+        <v>1001062475707</v>
+      </c>
+      <c r="C480" s="6" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A481" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="B481" s="5">
+        <v>1001062475707</v>
+      </c>
+      <c r="C481" s="6" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A482" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B482" s="5">
+        <v>1001033856609</v>
+      </c>
+      <c r="C482" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A483" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="B480" s="3">
+      <c r="B483" s="3">
         <v>1001025767284</v>
       </c>
-      <c r="C480" s="6" t="s">
+      <c r="C483" s="6" t="s">
         <v>489</v>
-      </c>
-    </row>
-    <row r="481" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A481" s="7" t="s">
-        <v>717</v>
-      </c>
-      <c r="B481" s="5">
-        <v>1001301777332</v>
-      </c>
-      <c r="C481" s="6" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="482" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A482" s="7" t="s">
-        <v>731</v>
-      </c>
-      <c r="B482" s="5">
-        <v>1001301777332</v>
-      </c>
-      <c r="C482" s="6" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="483" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A483" s="7" t="s">
-        <v>732</v>
-      </c>
-      <c r="B483" s="5">
-        <v>1001303987333</v>
-      </c>
-      <c r="C483" s="6" t="s">
-        <v>724</v>
       </c>
     </row>
     <row r="484" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A484" s="7" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B484" s="5">
-        <v>1001303987333</v>
+        <v>1001301777332</v>
       </c>
       <c r="C484" s="6" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="485" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A485" s="7" t="s">
-        <v>719</v>
+        <v>731</v>
       </c>
       <c r="B485" s="5">
-        <v>1001012426220</v>
+        <v>1001301777332</v>
       </c>
       <c r="C485" s="6" t="s">
-        <v>186</v>
+        <v>723</v>
       </c>
     </row>
     <row r="486" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A486" s="7" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B486" s="5">
-        <v>1001300387157</v>
+        <v>1001303987333</v>
       </c>
       <c r="C486" s="6" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="487" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A487" s="7" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B487" s="5">
-        <v>1001300387157</v>
+        <v>1001303987333</v>
       </c>
       <c r="C487" s="6" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="488" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A488" s="7" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B488" s="5">
-        <v>1001220226208</v>
+        <v>1001012426220</v>
       </c>
       <c r="C488" s="6" t="s">
-        <v>726</v>
+        <v>186</v>
       </c>
     </row>
     <row r="489" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A489" s="7" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B489" s="5">
-        <v>1001220226208</v>
+        <v>1001300387157</v>
       </c>
       <c r="C489" s="6" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="490" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A490" s="7" t="s">
+        <v>720</v>
+      </c>
+      <c r="B490" s="5">
+        <v>1001300387157</v>
+      </c>
+      <c r="C490" s="6" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A491" s="7" t="s">
+        <v>721</v>
+      </c>
+      <c r="B491" s="5">
+        <v>1001220226208</v>
+      </c>
+      <c r="C491" s="6" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A492" s="7" t="s">
+        <v>728</v>
+      </c>
+      <c r="B492" s="5">
+        <v>1001220226208</v>
+      </c>
+      <c r="C492" s="6" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A493" s="7" t="s">
         <v>722</v>
       </c>
-      <c r="B490" s="5">
+      <c r="B493" s="5">
         <v>1001063656967</v>
       </c>
-      <c r="C490" s="6" t="s">
+      <c r="C493" s="6" t="s">
         <v>727</v>
-      </c>
-    </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A491" s="2" t="s">
-        <v>729</v>
-      </c>
-      <c r="B491" s="5">
-        <v>1001063656967</v>
-      </c>
-      <c r="C491" s="6" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A492" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="B492" s="3">
-        <v>1001065616832</v>
-      </c>
-      <c r="C492" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A493" s="2" t="s">
-        <v>740</v>
-      </c>
-      <c r="B493" s="3">
-        <v>1001060677299</v>
-      </c>
-      <c r="C493" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="494" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="B494" s="3">
-        <v>1001453907612</v>
-      </c>
-      <c r="C494" t="s">
-        <v>781</v>
+        <v>729</v>
+      </c>
+      <c r="B494" s="5">
+        <v>1001063656967</v>
+      </c>
+      <c r="C494" s="6" t="s">
+        <v>727</v>
       </c>
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
-        <v>793</v>
+        <v>738</v>
       </c>
       <c r="B495" s="3">
-        <v>1001453907612</v>
+        <v>1001065616832</v>
       </c>
       <c r="C495" t="s">
-        <v>781</v>
+        <v>739</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="B496" s="3">
-        <v>1001453907612</v>
+        <v>1001060677299</v>
       </c>
       <c r="C496" t="s">
-        <v>781</v>
+        <v>741</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B497" s="3">
-        <v>1001015026797</v>
+        <v>1001453907612</v>
       </c>
       <c r="C497" t="s">
-        <v>748</v>
+        <v>781</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
-        <v>749</v>
+        <v>793</v>
       </c>
       <c r="B498" s="3">
-        <v>1001095226925</v>
+        <v>1001453907612</v>
       </c>
       <c r="C498" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="B499" s="3">
-        <v>1001035277059</v>
+        <v>1001453907612</v>
       </c>
       <c r="C499" t="s">
-        <v>751</v>
+        <v>781</v>
       </c>
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="B500" s="3">
-        <v>1001025767461</v>
+        <v>1001015026797</v>
       </c>
       <c r="C500" t="s">
-        <v>792</v>
+        <v>748</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="B501" s="3">
-        <v>1001303637564</v>
+        <v>1001095226925</v>
       </c>
       <c r="C501" t="s">
-        <v>754</v>
+        <v>788</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
-        <v>757</v>
+        <v>750</v>
       </c>
       <c r="B502" s="3">
-        <v>1001026947371</v>
+        <v>1001035277059</v>
       </c>
       <c r="C502" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="B503" s="3">
-        <v>1001012427523</v>
+        <v>1001025767461</v>
       </c>
       <c r="C503" t="s">
-        <v>760</v>
+        <v>792</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
-        <v>765</v>
+        <v>753</v>
       </c>
       <c r="B504" s="3">
-        <v>1001022467083</v>
+        <v>1001303637564</v>
       </c>
       <c r="C504" t="s">
-        <v>766</v>
+        <v>754</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
-        <v>768</v>
+        <v>757</v>
       </c>
       <c r="B505" s="3">
-        <v>1001307357489</v>
+        <v>1001026947371</v>
       </c>
       <c r="C505" t="s">
-        <v>769</v>
+        <v>758</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
-        <v>770</v>
+        <v>759</v>
       </c>
       <c r="B506" s="3">
-        <v>1001025507271</v>
+        <v>1001012427523</v>
       </c>
       <c r="C506" t="s">
-        <v>771</v>
+        <v>760</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="B507" s="3">
-        <v>1001084856008</v>
+        <v>1001022467083</v>
       </c>
       <c r="C507" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="B508" s="3">
-        <v>1001200677442</v>
+        <v>1001307357489</v>
       </c>
       <c r="C508" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
+        <v>770</v>
+      </c>
+      <c r="B509" s="3">
+        <v>1001025507271</v>
+      </c>
+      <c r="C509" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A510" s="2" t="s">
+        <v>772</v>
+      </c>
+      <c r="B510" s="3">
+        <v>1001084856008</v>
+      </c>
+      <c r="C510" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A511" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="B511" s="3">
+        <v>1001200677442</v>
+      </c>
+      <c r="C511" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A512" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="B509" s="3">
+      <c r="B512" s="3">
         <v>1001300456946</v>
       </c>
-      <c r="C509" t="s">
+      <c r="C512" t="s">
         <v>777</v>
       </c>
     </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A513" s="2" t="s">
+        <v>795</v>
+      </c>
+      <c r="B513" s="3">
+        <v>1001093316411</v>
+      </c>
+      <c r="C513" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A514" s="2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B514" s="3">
+        <v>1001097747647</v>
+      </c>
+      <c r="C514" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A515" s="2" t="s">
+        <v>800</v>
+      </c>
+      <c r="B515" s="3">
+        <v>1001097767651</v>
+      </c>
+      <c r="C515" t="s">
+        <v>801</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C509" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
+  <autoFilter ref="A1:C515" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5731CA60-E6EE-47A7-B42C-CBC486BF6FEF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5677E2-660D-4CD6-8EB9-B17665C0C09C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="811">
   <si>
     <t>1С</t>
   </si>
@@ -2443,6 +2443,30 @@
   </si>
   <si>
     <t>7613 АРОМАТНАЯ с/к с/н в/у 1/100 10шт_Л10</t>
+  </si>
+  <si>
+    <t>ВОСКРЕСЕНСКАЯ ВЯЛЕНАЯ в/к в/у срез 1/260</t>
+  </si>
+  <si>
+    <t>КРАКОВСКАЯ ГОСТ Останкино п/к н/о мгс</t>
+  </si>
+  <si>
+    <t>НОВОМОСКОВСКАЯ в/к в/у срез 0.31кг</t>
+  </si>
+  <si>
+    <t>РИЕТ МЯСНОЙ С ГРИБАМИ ПМ п/о 1/150</t>
+  </si>
+  <si>
+    <t>7513 ВОСКРЕСЕНСКАЯ ВЯЛЕНАЯ в/к в/у срез 1/260</t>
+  </si>
+  <si>
+    <t>7562 КРАКОВСКАЯ ГОСТ Останкино п/к н/о мгс</t>
+  </si>
+  <si>
+    <t>7516 НОВОМОСКОВСКАЯ в/к в/у срез 0.31кг</t>
+  </si>
+  <si>
+    <t>7485 РИЕТ МЯСНОЙ С ГРИБАМИ ПМ п/о 1/150</t>
   </si>
 </sst>
 </file>
@@ -2799,7 +2823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F515"/>
+  <dimension ref="A1:F519"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" style="2" customWidth="1"/>
@@ -8476,6 +8500,50 @@
         <v>801</v>
       </c>
     </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A516" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="B516" s="3">
+        <v>1001307077513</v>
+      </c>
+      <c r="C516" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A517" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="B517" s="3">
+        <v>1001307587562</v>
+      </c>
+      <c r="C517" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A518" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="B518" s="3">
+        <v>1001307107516</v>
+      </c>
+      <c r="C518" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A519" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="B519" s="3">
+        <v>1001107397485</v>
+      </c>
+      <c r="C519" t="s">
+        <v>806</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:C515" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5677E2-660D-4CD6-8EB9-B17665C0C09C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18DD39FD-81D8-4C36-87A6-C9D82CD4471C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$515</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$521</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1037" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="813">
   <si>
     <t>1С</t>
   </si>
@@ -2467,6 +2467,12 @@
   </si>
   <si>
     <t>7485 РИЕТ МЯСНОЙ С ГРИБАМИ ПМ п/о 1/150</t>
+  </si>
+  <si>
+    <t>7647 ХОЧУ ВЕТЧ.ИЗ СВ.ОТРУБА с/н мгс 1/100_Л11  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7651 ХОЧУ ВЕТЧ.МРАМОР. ПМ с/н мгс 1/100_Л11  ОСТАНКИНО</t>
   </si>
 </sst>
 </file>
@@ -2823,7 +2829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F519"/>
+  <dimension ref="A1:F521"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" style="2" customWidth="1"/>
@@ -8491,61 +8497,83 @@
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
-        <v>800</v>
+        <v>811</v>
       </c>
       <c r="B515" s="3">
-        <v>1001097767651</v>
+        <v>1001097747647</v>
       </c>
       <c r="C515" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="B516" s="3">
-        <v>1001307077513</v>
+        <v>1001097767651</v>
       </c>
       <c r="C516" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="B517" s="3">
-        <v>1001307587562</v>
+        <v>1001097767651</v>
       </c>
       <c r="C517" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="B518" s="3">
-        <v>1001307107516</v>
+        <v>1001307077513</v>
       </c>
       <c r="C518" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="B519" s="3">
+        <v>1001307587562</v>
+      </c>
+      <c r="C519" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A520" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="B520" s="3">
+        <v>1001307107516</v>
+      </c>
+      <c r="C520" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A521" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="B519" s="3">
+      <c r="B521" s="3">
         <v>1001107397485</v>
       </c>
-      <c r="C519" t="s">
+      <c r="C521" t="s">
         <v>806</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C515" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
+  <autoFilter ref="A1:C521" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18DD39FD-81D8-4C36-87A6-C9D82CD4471C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A741CE-41D3-49D3-9CFD-B875F606173D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$521</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$527</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1041" uniqueCount="813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="819">
   <si>
     <t>1С</t>
   </si>
@@ -2473,6 +2473,24 @@
   </si>
   <si>
     <t>7651 ХОЧУ ВЕТЧ.МРАМОР. ПМ с/н мгс 1/100_Л11  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7485 РИЕТ МЯСНОЙ С ГРИБАМИ ПМ п/о 1/150  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7513 ВОСКРЕСЕНСКАЯ ВЯЛЕНАЯ в/к в/у срез 1/260  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7516 НОВОМОСКОВСКАЯ в/к в/у срез 0.31кг  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7562 КРАКОВСКАЯ ГОСТ Останкино п/к н/о мгс  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7613 АРОМАТНАЯ с/к с/н в/у 1/100 10шт_Л10  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>6411 ВЕТЧ.РУБЛЕНАЯ ПМ в/у срез 0.3кг 6шт.  ОСТАНКИНО</t>
   </si>
 </sst>
 </file>
@@ -2829,7 +2847,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F521"/>
+  <dimension ref="A1:F527"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" style="2" customWidth="1"/>
@@ -3536,7 +3554,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>802</v>
+        <v>817</v>
       </c>
       <c r="B64" s="3">
         <v>1001061977613</v>
@@ -3547,216 +3565,216 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>63</v>
+        <v>802</v>
       </c>
       <c r="B65" s="3">
-        <v>1001025176475</v>
+        <v>1001061977613</v>
       </c>
       <c r="C65" t="s">
-        <v>64</v>
+        <v>790</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>109</v>
+        <v>63</v>
       </c>
       <c r="B66" s="3">
-        <v>1001301876697</v>
+        <v>1001025176475</v>
       </c>
       <c r="C66" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="B67" s="3">
-        <v>1001024636517</v>
+        <v>1001301876697</v>
       </c>
       <c r="C67" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B68" s="3">
-        <v>1001031076527</v>
+        <v>1001024636517</v>
       </c>
       <c r="C68" t="s">
-        <v>785</v>
+        <v>67</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B69" s="3">
-        <v>1001304506562</v>
+        <v>1001031076527</v>
       </c>
       <c r="C69" t="s">
-        <v>72</v>
+        <v>785</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B70" s="3">
-        <v>1001020846563</v>
+        <v>1001304506562</v>
       </c>
       <c r="C70" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B71" s="3">
-        <v>1001020836589</v>
+        <v>1001020846563</v>
       </c>
       <c r="C71" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B72" s="3">
-        <v>6751</v>
+        <v>1001020836589</v>
       </c>
       <c r="C72" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B73" s="3">
-        <v>1001010016592</v>
+        <v>6751</v>
       </c>
       <c r="C73" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B74" s="3">
-        <v>1001010026594</v>
+        <v>1001010016592</v>
       </c>
       <c r="C74" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B75" s="3">
-        <v>1001022296601</v>
+        <v>1001010026594</v>
       </c>
       <c r="C75" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B76" s="3">
-        <v>1001031896648</v>
+        <v>1001022296601</v>
       </c>
       <c r="C76" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B77" s="3">
-        <v>1001035266650</v>
+        <v>1001031896648</v>
       </c>
       <c r="C77" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B78" s="3">
-        <v>1001305256658</v>
+        <v>1001035266650</v>
       </c>
       <c r="C78" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B79" s="3">
-        <v>1001010016593</v>
+        <v>1001305256658</v>
       </c>
       <c r="C79" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B80" s="3">
-        <v>1001010026595</v>
+        <v>1001010016593</v>
       </c>
       <c r="C80" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B81" s="3">
-        <v>1001010036597</v>
+        <v>1001010026595</v>
       </c>
       <c r="C81" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B82" s="3">
-        <v>1001020886646</v>
+        <v>1001010036597</v>
       </c>
       <c r="C82" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>300</v>
+        <v>103</v>
       </c>
       <c r="B83" s="3">
-        <v>1001305306566</v>
+        <v>1001020886646</v>
       </c>
       <c r="C83" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>104</v>
+        <v>300</v>
       </c>
       <c r="B84" s="3">
         <v>1001305306566</v>
@@ -3767,18 +3785,18 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>633</v>
+        <v>104</v>
       </c>
       <c r="B85" s="3">
-        <v>1001300387154</v>
+        <v>1001305306566</v>
       </c>
       <c r="C85" t="s">
-        <v>614</v>
+        <v>105</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>613</v>
+        <v>633</v>
       </c>
       <c r="B86" s="3">
         <v>1001300387154</v>
@@ -3789,18 +3807,18 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>634</v>
+        <v>613</v>
       </c>
       <c r="B87" s="3">
-        <v>1001303987169</v>
+        <v>1001300387154</v>
       </c>
       <c r="C87" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>615</v>
+        <v>634</v>
       </c>
       <c r="B88" s="3">
         <v>1001303987169</v>
@@ -3811,20 +3829,20 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>223</v>
+        <v>615</v>
       </c>
       <c r="B89" s="3">
-        <v>1001303106773</v>
+        <v>1001303987169</v>
       </c>
       <c r="C89" t="s">
-        <v>323</v>
+        <v>616</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="B90" s="4">
+        <v>223</v>
+      </c>
+      <c r="B90" s="3">
         <v>1001303106773</v>
       </c>
       <c r="C90" t="s">
@@ -3833,7 +3851,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>253</v>
+        <v>330</v>
       </c>
       <c r="B91" s="4">
         <v>1001303106773</v>
@@ -3844,9 +3862,9 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="B92" s="3">
+        <v>253</v>
+      </c>
+      <c r="B92" s="4">
         <v>1001303106773</v>
       </c>
       <c r="C92" t="s">
@@ -3855,7 +3873,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>369</v>
+        <v>108</v>
       </c>
       <c r="B93" s="3">
         <v>1001303106773</v>
@@ -3866,7 +3884,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B94" s="3">
         <v>1001303106773</v>
@@ -3877,7 +3895,7 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B95" s="3">
         <v>1001303106773</v>
@@ -3888,18 +3906,18 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>212</v>
+        <v>364</v>
       </c>
       <c r="B96" s="3">
-        <v>1001012566392</v>
+        <v>1001303106773</v>
       </c>
       <c r="C96" t="s">
-        <v>784</v>
+        <v>323</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>398</v>
+        <v>212</v>
       </c>
       <c r="B97" s="3">
         <v>1001012566392</v>
@@ -3910,7 +3928,7 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>111</v>
+        <v>398</v>
       </c>
       <c r="B98" s="3">
         <v>1001012566392</v>
@@ -3921,18 +3939,18 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>636</v>
+        <v>111</v>
       </c>
       <c r="B99" s="3">
-        <v>1001302277173</v>
+        <v>1001012566392</v>
       </c>
       <c r="C99" t="s">
-        <v>612</v>
+        <v>784</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>611</v>
+        <v>636</v>
       </c>
       <c r="B100" s="3">
         <v>1001302277173</v>
@@ -3943,18 +3961,18 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>693</v>
+        <v>611</v>
       </c>
       <c r="B101" s="3">
-        <v>1001012426268</v>
+        <v>1001302277173</v>
       </c>
       <c r="C101" t="s">
-        <v>113</v>
+        <v>612</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>114</v>
+        <v>693</v>
       </c>
       <c r="B102" s="3">
         <v>1001012426268</v>
@@ -3965,95 +3983,95 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="B103" s="3">
-        <v>1001024906041</v>
+        <v>1001012426268</v>
       </c>
       <c r="C103" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B104" s="3">
-        <v>1001011086247</v>
+        <v>1001024906041</v>
       </c>
       <c r="C104" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="B105" s="3">
-        <v>1001014486158</v>
+        <v>1001011086247</v>
       </c>
       <c r="C105" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B106" s="3">
-        <v>1001015356259</v>
+        <v>1001014486158</v>
       </c>
       <c r="C106" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B107" s="3">
-        <v>1001012816716</v>
+        <v>1001015356259</v>
       </c>
       <c r="C107" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>305</v>
+        <v>143</v>
       </c>
       <c r="B108" s="3">
-        <v>1001020966227</v>
+        <v>1001012816716</v>
       </c>
       <c r="C108" t="s">
-        <v>304</v>
+        <v>134</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>120</v>
+        <v>305</v>
       </c>
       <c r="B109" s="3">
         <v>1001020966227</v>
       </c>
       <c r="C109" t="s">
-        <v>121</v>
+        <v>304</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>210</v>
+        <v>120</v>
       </c>
       <c r="B110" s="3">
-        <v>1001022726303</v>
+        <v>1001020966227</v>
       </c>
       <c r="C110" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="B111" s="3">
         <v>1001022726303</v>
@@ -4064,7 +4082,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>322</v>
+        <v>241</v>
       </c>
       <c r="B112" s="3">
         <v>1001022726303</v>
@@ -4075,7 +4093,7 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>144</v>
+        <v>322</v>
       </c>
       <c r="B113" s="3">
         <v>1001022726303</v>
@@ -4086,51 +4104,51 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="B114" s="3">
-        <v>1001022466726</v>
+        <v>1001022726303</v>
       </c>
       <c r="C114" t="s">
-        <v>100</v>
+        <v>146</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="B115" s="3">
-        <v>1001020966144</v>
+        <v>1001022466726</v>
       </c>
       <c r="C115" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>112</v>
+        <v>138</v>
       </c>
       <c r="B116" s="3">
-        <v>1001022376722</v>
+        <v>1001020966144</v>
       </c>
       <c r="C116" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>556</v>
+        <v>112</v>
       </c>
       <c r="B117" s="3">
-        <v>1001022376955</v>
+        <v>1001022376722</v>
       </c>
       <c r="C117" t="s">
-        <v>547</v>
+        <v>110</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B118" s="3">
         <v>1001022376955</v>
@@ -4141,7 +4159,7 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>125</v>
+        <v>554</v>
       </c>
       <c r="B119" s="3">
         <v>1001022376955</v>
@@ -4152,18 +4170,18 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>235</v>
+        <v>125</v>
       </c>
       <c r="B120" s="3">
-        <v>1001022246661</v>
+        <v>1001022376955</v>
       </c>
       <c r="C120" t="s">
-        <v>126</v>
+        <v>547</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>301</v>
+        <v>235</v>
       </c>
       <c r="B121" s="3">
         <v>1001022246661</v>
@@ -4174,7 +4192,7 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>124</v>
+        <v>301</v>
       </c>
       <c r="B122" s="3">
         <v>1001022246661</v>
@@ -4185,161 +4203,161 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B123" s="3">
-        <v>1001022246713</v>
+        <v>1001022246661</v>
       </c>
       <c r="C123" t="s">
-        <v>101</v>
+        <v>126</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B124" s="3">
-        <v>1001025166241</v>
+        <v>1001022246713</v>
       </c>
       <c r="C124" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>145</v>
+        <v>127</v>
       </c>
       <c r="B125" s="3">
-        <v>6606</v>
+        <v>1001025166241</v>
       </c>
       <c r="C125" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>123</v>
+        <v>145</v>
       </c>
       <c r="B126" s="3">
-        <v>1001035326217</v>
+        <v>6606</v>
       </c>
       <c r="C126" t="s">
-        <v>122</v>
+        <v>147</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>142</v>
+        <v>123</v>
       </c>
       <c r="B127" s="3">
-        <v>1001303636301</v>
+        <v>1001035326217</v>
       </c>
       <c r="C127" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="B128" s="3">
-        <v>1001303636302</v>
+        <v>1001303636301</v>
       </c>
       <c r="C128" t="s">
-        <v>86</v>
+        <v>136</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>129</v>
+        <v>85</v>
       </c>
       <c r="B129" s="3">
-        <v>1001305196215</v>
+        <v>1001303636302</v>
       </c>
       <c r="C129" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B130" s="3">
-        <v>1001301876212</v>
+        <v>1001305196215</v>
       </c>
       <c r="C130" t="s">
-        <v>137</v>
+        <v>70</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B131" s="3">
-        <v>1001301876213</v>
+        <v>1001301876212</v>
       </c>
       <c r="C131" t="s">
-        <v>69</v>
+        <v>137</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="B132" s="3">
-        <v>1001303636302</v>
+        <v>1001301876213</v>
       </c>
       <c r="C132" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="B133" s="3">
-        <v>6645</v>
+        <v>1001303636302</v>
       </c>
       <c r="C133" t="s">
-        <v>149</v>
+        <v>86</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B134" s="3">
-        <v>1001225416228</v>
+        <v>6645</v>
       </c>
       <c r="C134" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B135" s="3">
-        <v>6225</v>
+        <v>1001225416228</v>
       </c>
       <c r="C135" t="s">
-        <v>257</v>
+        <v>151</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B136" s="3">
-        <v>1001022376722</v>
+        <v>6225</v>
       </c>
       <c r="C136" t="s">
-        <v>110</v>
+        <v>257</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="B137" s="3">
         <v>1001022376722</v>
@@ -4350,29 +4368,29 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B138" s="3">
-        <v>3297</v>
+        <v>1001022376722</v>
       </c>
       <c r="C138" t="s">
-        <v>156</v>
+        <v>110</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>295</v>
+        <v>155</v>
       </c>
       <c r="B139" s="3">
-        <v>1001022466726</v>
+        <v>3297</v>
       </c>
       <c r="C139" t="s">
-        <v>273</v>
+        <v>156</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>274</v>
+        <v>295</v>
       </c>
       <c r="B140" s="3">
         <v>1001022466726</v>
@@ -4383,51 +4401,51 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>159</v>
+        <v>274</v>
       </c>
       <c r="B141" s="3">
         <v>1001022466726</v>
       </c>
       <c r="C141" t="s">
-        <v>100</v>
+        <v>273</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B142" s="3">
-        <v>1001021966602</v>
+        <v>1001022466726</v>
       </c>
       <c r="C142" t="s">
-        <v>791</v>
+        <v>100</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B143" s="3">
-        <v>6233</v>
+        <v>1001021966602</v>
       </c>
       <c r="C143" t="s">
-        <v>161</v>
+        <v>791</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>248</v>
+        <v>162</v>
       </c>
       <c r="B144" s="3">
-        <v>1001012816341</v>
+        <v>6233</v>
       </c>
       <c r="C144" t="s">
-        <v>423</v>
+        <v>161</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>469</v>
+        <v>248</v>
       </c>
       <c r="B145" s="3">
         <v>1001012816341</v>
@@ -4438,7 +4456,7 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="B146" s="3">
         <v>1001012816341</v>
@@ -4449,7 +4467,7 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>163</v>
+        <v>472</v>
       </c>
       <c r="B147" s="3">
         <v>1001012816341</v>
@@ -4460,51 +4478,51 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B148" s="3">
-        <v>6750</v>
+        <v>1001012816341</v>
       </c>
       <c r="C148" t="s">
-        <v>76</v>
+        <v>423</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B149" s="3">
-        <v>6751</v>
+        <v>6750</v>
       </c>
       <c r="C149" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B150" s="3">
-        <v>5982</v>
+        <v>6751</v>
       </c>
       <c r="C150" t="s">
-        <v>167</v>
+        <v>78</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>518</v>
+        <v>166</v>
       </c>
       <c r="B151" s="3">
-        <v>1001022656854</v>
+        <v>5982</v>
       </c>
       <c r="C151" t="s">
-        <v>412</v>
+        <v>167</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>535</v>
+        <v>518</v>
       </c>
       <c r="B152" s="3">
         <v>1001022656854</v>
@@ -4515,7 +4533,7 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>436</v>
+        <v>535</v>
       </c>
       <c r="B153" s="3">
         <v>1001022656854</v>
@@ -4526,7 +4544,7 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>168</v>
+        <v>436</v>
       </c>
       <c r="B154" s="3">
         <v>1001022656854</v>
@@ -4537,21 +4555,21 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="B155" s="3">
-        <v>1001094966025</v>
+        <v>1001022656854</v>
       </c>
       <c r="C155" t="s">
-        <v>170</v>
+        <v>412</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B156" s="3">
-        <v>6025</v>
+        <v>1001094966025</v>
       </c>
       <c r="C156" t="s">
         <v>170</v>
@@ -4559,29 +4577,29 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="B157" s="3">
-        <v>1001022373812</v>
+        <v>6025</v>
       </c>
       <c r="C157" t="s">
-        <v>3</v>
+        <v>170</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B158" s="3">
-        <v>1001100606827</v>
+        <v>1001022373812</v>
       </c>
       <c r="C158" t="s">
-        <v>312</v>
+        <v>3</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>324</v>
+        <v>177</v>
       </c>
       <c r="B159" s="3">
         <v>1001100606827</v>
@@ -4592,18 +4610,18 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>178</v>
+        <v>324</v>
       </c>
       <c r="B160" s="3">
-        <v>1001100616826</v>
+        <v>1001100606827</v>
       </c>
       <c r="C160" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>325</v>
+        <v>178</v>
       </c>
       <c r="B161" s="3">
         <v>1001100616826</v>
@@ -4614,18 +4632,18 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>179</v>
+        <v>325</v>
       </c>
       <c r="B162" s="3">
-        <v>1001100626828</v>
+        <v>1001100616826</v>
       </c>
       <c r="C162" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>326</v>
+        <v>179</v>
       </c>
       <c r="B163" s="3">
         <v>1001100626828</v>
@@ -4636,62 +4654,62 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>180</v>
+        <v>326</v>
       </c>
       <c r="B164" s="3">
-        <v>1001035026308</v>
+        <v>1001100626828</v>
       </c>
       <c r="C164" t="s">
-        <v>181</v>
+        <v>314</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>539</v>
+        <v>180</v>
       </c>
       <c r="B165" s="3">
-        <v>1001014486159</v>
+        <v>1001035026308</v>
       </c>
       <c r="C165" t="s">
-        <v>540</v>
+        <v>181</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>182</v>
+        <v>539</v>
       </c>
       <c r="B166" s="3">
         <v>1001014486159</v>
       </c>
       <c r="C166" t="s">
-        <v>183</v>
+        <v>540</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B167" s="3">
-        <v>1001035326217</v>
+        <v>1001014486159</v>
       </c>
       <c r="C167" t="s">
-        <v>271</v>
+        <v>183</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>486</v>
+        <v>184</v>
       </c>
       <c r="B168" s="3">
-        <v>1001012426220</v>
+        <v>1001035326217</v>
       </c>
       <c r="C168" t="s">
-        <v>186</v>
+        <v>271</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>185</v>
+        <v>486</v>
       </c>
       <c r="B169" s="3">
         <v>1001012426220</v>
@@ -4702,227 +4720,227 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B170" s="3">
-        <v>1001022466236</v>
+        <v>1001012426220</v>
       </c>
       <c r="C170" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B171" s="3">
-        <v>1001021966602</v>
+        <v>1001022466236</v>
       </c>
       <c r="C171" t="s">
-        <v>791</v>
+        <v>188</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B172" s="3">
-        <v>1001022296656</v>
+        <v>1001021966602</v>
       </c>
       <c r="C172" t="s">
-        <v>191</v>
+        <v>791</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B173" s="3">
-        <v>1001301876697</v>
+        <v>1001022296656</v>
       </c>
       <c r="C173" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B174" s="3">
-        <v>1001022246713</v>
+        <v>1001301876697</v>
       </c>
       <c r="C174" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B175" s="3">
-        <v>1001022376722</v>
+        <v>1001022246713</v>
       </c>
       <c r="C175" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B176" s="3">
-        <v>1001020846751</v>
+        <v>1001022376722</v>
       </c>
       <c r="C176" t="s">
-        <v>78</v>
+        <v>199</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B177" s="3">
-        <v>1001022725819</v>
+        <v>1001020846751</v>
       </c>
       <c r="C177" t="s">
-        <v>202</v>
+        <v>78</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B178" s="3">
-        <v>1001012825337</v>
+        <v>1001022725819</v>
       </c>
       <c r="C178" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B179" s="3">
-        <v>1001012815336</v>
+        <v>1001012825337</v>
       </c>
       <c r="C179" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B180" s="3">
-        <v>1001234146448</v>
+        <v>1001012815336</v>
       </c>
       <c r="C180" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B181" s="3">
-        <v>1001022725819</v>
+        <v>1001234146448</v>
       </c>
       <c r="C181" t="s">
-        <v>202</v>
+        <v>59</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B182" s="3">
-        <v>1001092676027</v>
+        <v>1001022725819</v>
       </c>
       <c r="C182" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B183" s="3">
-        <v>1001301876213</v>
+        <v>1001092676027</v>
       </c>
       <c r="C183" t="s">
-        <v>69</v>
+        <v>208</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B184" s="3">
-        <v>1001035026308</v>
+        <v>1001301876213</v>
       </c>
       <c r="C184" t="s">
-        <v>388</v>
+        <v>69</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B185" s="3">
-        <v>1001234146448</v>
+        <v>1001035026308</v>
       </c>
       <c r="C185" t="s">
-        <v>59</v>
+        <v>388</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B186" s="3">
-        <v>1001025176475</v>
+        <v>1001234146448</v>
       </c>
       <c r="C186" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B187" s="3">
-        <v>1001012456498</v>
+        <v>1001025176475</v>
       </c>
       <c r="C187" t="s">
-        <v>218</v>
+        <v>64</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B188" s="3">
-        <v>1001010036596</v>
+        <v>1001012456498</v>
       </c>
       <c r="C188" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>550</v>
+        <v>219</v>
       </c>
       <c r="B189" s="3">
-        <v>1001033856608</v>
+        <v>1001010036596</v>
       </c>
       <c r="C189" t="s">
-        <v>541</v>
+        <v>220</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="B190" s="3">
         <v>1001033856608</v>
@@ -4933,18 +4951,18 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="B191" s="3">
-        <v>1001033856609</v>
+        <v>1001033856608</v>
       </c>
       <c r="C191" t="s">
-        <v>222</v>
+        <v>541</v>
       </c>
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>221</v>
+        <v>551</v>
       </c>
       <c r="B192" s="3">
         <v>1001033856609</v>
@@ -4955,315 +4973,315 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B193" s="3">
-        <v>1001093345495</v>
+        <v>1001033856609</v>
       </c>
       <c r="C193" t="s">
-        <v>424</v>
+        <v>222</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B194" s="3">
-        <v>6550</v>
+        <v>1001093345495</v>
       </c>
       <c r="C194" t="s">
-        <v>227</v>
+        <v>424</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B195" s="3">
-        <v>1001304506684</v>
+        <v>6550</v>
       </c>
       <c r="C195" t="s">
-        <v>53</v>
+        <v>227</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B196" s="3">
-        <v>1001010113248</v>
+        <v>1001304506684</v>
       </c>
       <c r="C196" t="s">
-        <v>230</v>
+        <v>53</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>396</v>
+        <v>229</v>
       </c>
       <c r="B197" s="3">
-        <v>1001063926780</v>
+        <v>1001010113248</v>
       </c>
       <c r="C197" t="s">
-        <v>397</v>
+        <v>230</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>231</v>
+        <v>396</v>
       </c>
       <c r="B198" s="3">
-        <v>6586</v>
+        <v>1001063926780</v>
       </c>
       <c r="C198" t="s">
-        <v>232</v>
+        <v>397</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B199" s="3">
-        <v>1001303636467</v>
+        <v>6586</v>
       </c>
       <c r="C199" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B200" s="3">
-        <v>1001304496701</v>
+        <v>1001303636467</v>
       </c>
       <c r="C200" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B201" s="3">
-        <v>6144</v>
+        <v>1001304496701</v>
       </c>
       <c r="C201" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B202" s="3">
-        <v>1001022725819</v>
+        <v>6144</v>
       </c>
       <c r="C202" t="s">
-        <v>202</v>
+        <v>239</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B203" s="3">
-        <v>1001022373812</v>
+        <v>1001022725819</v>
       </c>
       <c r="C203" t="s">
-        <v>3</v>
+        <v>202</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B204" s="3">
-        <v>1001024906062</v>
+        <v>1001022373812</v>
       </c>
       <c r="C204" t="s">
-        <v>244</v>
+        <v>3</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B205" s="3">
-        <v>1001303056692</v>
+        <v>1001024906062</v>
       </c>
       <c r="C205" t="s">
-        <v>54</v>
+        <v>244</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B206" s="3">
-        <v>1001301876697</v>
+        <v>1001303056692</v>
       </c>
       <c r="C206" t="s">
-        <v>194</v>
+        <v>54</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B207" s="3">
-        <v>1001012634574</v>
+        <v>1001301876697</v>
       </c>
       <c r="C207" t="s">
-        <v>11</v>
+        <v>194</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B208" s="3">
-        <v>1001092485452</v>
+        <v>1001012634574</v>
       </c>
       <c r="C208" t="s">
-        <v>250</v>
+        <v>11</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B209" s="3">
-        <v>1001020966144</v>
+        <v>1001092485452</v>
       </c>
       <c r="C209" t="s">
-        <v>135</v>
+        <v>250</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B210" s="3">
-        <v>6586</v>
+        <v>1001020966144</v>
       </c>
       <c r="C210" t="s">
-        <v>232</v>
+        <v>135</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B211" s="3">
-        <v>1001304496701</v>
+        <v>6586</v>
       </c>
       <c r="C211" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B212" s="3">
-        <v>1001063655015</v>
+        <v>1001304496701</v>
       </c>
       <c r="C212" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B213" s="3">
-        <v>1001060763287</v>
+        <v>1001063655015</v>
       </c>
       <c r="C213" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B214" s="3">
-        <v>1001225416228</v>
+        <v>1001060763287</v>
       </c>
       <c r="C214" t="s">
-        <v>151</v>
+        <v>259</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B215" s="3">
-        <v>1001032736550</v>
+        <v>1001225416228</v>
       </c>
       <c r="C215" t="s">
-        <v>786</v>
+        <v>151</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B216" s="3">
-        <v>6758</v>
+        <v>1001032736550</v>
       </c>
       <c r="C216" t="s">
-        <v>263</v>
+        <v>786</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B217" s="3">
-        <v>1001020965976</v>
+        <v>6758</v>
       </c>
       <c r="C217" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B218" s="3">
-        <v>1001215576586</v>
+        <v>1001020965976</v>
       </c>
       <c r="C218" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B219" s="3">
-        <v>1001094896026</v>
+        <v>1001215576586</v>
       </c>
       <c r="C219" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>477</v>
+        <v>268</v>
       </c>
       <c r="B220" s="3">
-        <v>1001215576586</v>
+        <v>1001094896026</v>
       </c>
       <c r="C220" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>270</v>
+        <v>477</v>
       </c>
       <c r="B221" s="3">
         <v>1001215576586</v>
@@ -5274,18 +5292,18 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>763</v>
+        <v>270</v>
       </c>
       <c r="B222" s="3">
-        <v>1001092436470</v>
+        <v>1001215576586</v>
       </c>
       <c r="C222" t="s">
-        <v>764</v>
+        <v>267</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>272</v>
+        <v>763</v>
       </c>
       <c r="B223" s="3">
         <v>1001092436470</v>
@@ -5296,29 +5314,29 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B224" s="3">
-        <v>1001203146555</v>
+        <v>1001092436470</v>
       </c>
       <c r="C224" t="s">
-        <v>277</v>
+        <v>764</v>
       </c>
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="B225" s="3">
-        <v>1001016747343</v>
+        <v>1001203146555</v>
       </c>
       <c r="C225" t="s">
-        <v>734</v>
+        <v>277</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>696</v>
+        <v>288</v>
       </c>
       <c r="B226" s="3">
         <v>1001016747343</v>
@@ -5329,7 +5347,7 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>279</v>
+        <v>696</v>
       </c>
       <c r="B227" s="3">
         <v>1001016747343</v>
@@ -5340,7 +5358,7 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>736</v>
+        <v>279</v>
       </c>
       <c r="B228" s="3">
         <v>1001016747343</v>
@@ -5351,51 +5369,51 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>281</v>
+        <v>736</v>
       </c>
       <c r="B229" s="3">
-        <v>1001014765993</v>
+        <v>1001016747343</v>
       </c>
       <c r="C229" t="s">
-        <v>280</v>
+        <v>734</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B230" s="3">
-        <v>1001025166776</v>
+        <v>1001014765993</v>
       </c>
       <c r="C230" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B231" s="3">
-        <v>1001025506777</v>
+        <v>1001025166776</v>
       </c>
       <c r="C231" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="B232" s="3">
-        <v>1001025546822</v>
+        <v>1001025506777</v>
       </c>
       <c r="C232" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B233" s="3">
         <v>1001025546822</v>
@@ -5406,40 +5424,40 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="B234" s="3">
         <v>1001025546822</v>
       </c>
       <c r="C234" t="s">
-        <v>533</v>
+        <v>287</v>
       </c>
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>286</v>
+        <v>319</v>
       </c>
       <c r="B235" s="3">
         <v>1001025546822</v>
       </c>
       <c r="C235" t="s">
-        <v>287</v>
+        <v>533</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>643</v>
+        <v>286</v>
       </c>
       <c r="B236" s="3">
-        <v>1001024976616</v>
+        <v>1001025546822</v>
       </c>
       <c r="C236" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>290</v>
+        <v>643</v>
       </c>
       <c r="B237" s="3">
         <v>1001024976616</v>
@@ -5450,29 +5468,29 @@
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B238" s="3">
-        <v>1001010855247</v>
+        <v>1001024976616</v>
       </c>
       <c r="C238" t="s">
-        <v>22</v>
+        <v>289</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>368</v>
+        <v>291</v>
       </c>
       <c r="B239" s="3">
-        <v>1001223296919</v>
+        <v>1001010855247</v>
       </c>
       <c r="C239" t="s">
-        <v>371</v>
+        <v>22</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>60</v>
+        <v>368</v>
       </c>
       <c r="B240" s="3">
         <v>1001223296919</v>
@@ -5483,7 +5501,7 @@
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>214</v>
+        <v>60</v>
       </c>
       <c r="B241" s="3">
         <v>1001223296919</v>
@@ -5494,29 +5512,29 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>440</v>
+        <v>214</v>
       </c>
       <c r="B242" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C242" t="s">
-        <v>456</v>
+        <v>371</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="B243" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C243" t="s">
-        <v>371</v>
+        <v>456</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>292</v>
+        <v>462</v>
       </c>
       <c r="B244" s="3">
         <v>1001223296919</v>
@@ -5527,73 +5545,73 @@
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B245" s="3">
-        <v>1001014765993</v>
+        <v>1001223296919</v>
       </c>
       <c r="C245" t="s">
-        <v>280</v>
+        <v>371</v>
       </c>
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B246" s="3">
-        <v>1001025166776</v>
+        <v>1001014765993</v>
       </c>
       <c r="C246" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B247" s="3">
-        <v>1001025506777</v>
+        <v>1001025166776</v>
       </c>
       <c r="C247" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B248" s="3">
-        <v>1001025526778</v>
+        <v>1001025506777</v>
       </c>
       <c r="C248" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B249" s="3">
-        <v>1001304236685</v>
+        <v>1001025526778</v>
       </c>
       <c r="C249" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="B250" s="3">
-        <v>1001015496769</v>
+        <v>1001304236685</v>
       </c>
       <c r="C250" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="B251" s="3">
         <v>1001015496769</v>
@@ -5604,84 +5622,84 @@
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B252" s="3">
-        <v>1001014766798</v>
+        <v>1001015496769</v>
       </c>
       <c r="C252" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B253" s="3">
-        <v>1001015026797</v>
+        <v>1001014766798</v>
       </c>
       <c r="C253" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B254" s="3">
-        <v>1001205386222</v>
+        <v>1001015026797</v>
       </c>
       <c r="C254" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B255" s="3">
-        <v>1001092675224</v>
+        <v>1001205386222</v>
       </c>
       <c r="C255" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B256" s="3">
-        <v>1001225406223</v>
+        <v>1001092675224</v>
       </c>
       <c r="C256" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B257" s="3">
-        <v>1001300366790</v>
+        <v>1001225406223</v>
       </c>
       <c r="C257" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>458</v>
+        <v>331</v>
       </c>
       <c r="B258" s="3">
-        <v>1001304096792</v>
+        <v>1001300366790</v>
       </c>
       <c r="C258" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>333</v>
+        <v>458</v>
       </c>
       <c r="B259" s="3">
         <v>1001304096792</v>
@@ -5692,18 +5710,18 @@
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>358</v>
+        <v>333</v>
       </c>
       <c r="B260" s="3">
-        <v>1001303637603</v>
+        <v>1001304096792</v>
       </c>
       <c r="C260" t="s">
-        <v>755</v>
+        <v>344</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="B261" s="3">
         <v>1001303637603</v>
@@ -5714,7 +5732,7 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>334</v>
+        <v>378</v>
       </c>
       <c r="B262" s="3">
         <v>1001303637603</v>
@@ -5725,7 +5743,7 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>767</v>
+        <v>334</v>
       </c>
       <c r="B263" s="3">
         <v>1001303637603</v>
@@ -5736,18 +5754,18 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>379</v>
+        <v>767</v>
       </c>
       <c r="B264" s="3">
-        <v>1001303636794</v>
+        <v>1001303637603</v>
       </c>
       <c r="C264" t="s">
-        <v>345</v>
+        <v>755</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>478</v>
+        <v>379</v>
       </c>
       <c r="B265" s="3">
         <v>1001303636794</v>
@@ -5758,7 +5776,7 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>335</v>
+        <v>478</v>
       </c>
       <c r="B266" s="3">
         <v>1001303636794</v>
@@ -5769,51 +5787,51 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B267" s="3">
-        <v>1001302596795</v>
+        <v>1001303636794</v>
       </c>
       <c r="C267" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B268" s="3">
-        <v>1001302596796</v>
+        <v>1001302596795</v>
       </c>
       <c r="C268" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B269" s="3">
-        <v>1001300456804</v>
+        <v>1001302596796</v>
       </c>
       <c r="C269" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>427</v>
+        <v>338</v>
       </c>
       <c r="B270" s="3">
-        <v>1001300366806</v>
+        <v>1001300456804</v>
       </c>
       <c r="C270" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>339</v>
+        <v>427</v>
       </c>
       <c r="B271" s="3">
         <v>1001300366806</v>
@@ -5824,62 +5842,62 @@
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B272" s="3">
-        <v>1001300516803</v>
+        <v>1001300366806</v>
       </c>
       <c r="C272" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B273" s="3">
-        <v>1001300366807</v>
+        <v>1001300516803</v>
       </c>
       <c r="C273" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="B274" s="3">
         <v>1001300366807</v>
       </c>
       <c r="C274" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B275" s="3">
-        <v>1001300516785</v>
+        <v>1001300366807</v>
       </c>
       <c r="C275" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>519</v>
+        <v>354</v>
       </c>
       <c r="B276" s="3">
-        <v>1001300456787</v>
+        <v>1001300516785</v>
       </c>
       <c r="C276" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>534</v>
+        <v>519</v>
       </c>
       <c r="B277" s="3">
         <v>1001300456787</v>
@@ -5890,7 +5908,7 @@
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>356</v>
+        <v>534</v>
       </c>
       <c r="B278" s="3">
         <v>1001300456787</v>
@@ -5901,62 +5919,62 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B279" s="3">
-        <v>1001302596795</v>
+        <v>1001300456787</v>
       </c>
       <c r="C279" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B280" s="3">
-        <v>1001012486332</v>
+        <v>1001302596795</v>
       </c>
       <c r="C280" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B281" s="3">
-        <v>1001012566345</v>
+        <v>1001012486332</v>
       </c>
       <c r="C281" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B282" s="3">
-        <v>1001031076528</v>
+        <v>1001012566345</v>
       </c>
       <c r="C282" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="B283" s="3">
-        <v>1001020836761</v>
+        <v>1001031076528</v>
       </c>
       <c r="C283" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B284" s="3">
         <v>1001020836761</v>
@@ -5967,7 +5985,7 @@
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>372</v>
+        <v>400</v>
       </c>
       <c r="B285" s="3">
         <v>1001020836761</v>
@@ -5978,18 +5996,18 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="B286" s="3">
-        <v>1001020846764</v>
+        <v>1001020836761</v>
       </c>
       <c r="C286" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="B287" s="3">
         <v>1001020846764</v>
@@ -6000,7 +6018,7 @@
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="B288" s="3">
         <v>1001020846764</v>
@@ -6011,18 +6029,18 @@
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>474</v>
+        <v>374</v>
       </c>
       <c r="B289" s="3">
-        <v>1001300366790</v>
+        <v>1001020846764</v>
       </c>
       <c r="C289" t="s">
-        <v>342</v>
+        <v>375</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>376</v>
+        <v>474</v>
       </c>
       <c r="B290" s="3">
         <v>1001300366790</v>
@@ -6033,18 +6051,18 @@
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>332</v>
+        <v>376</v>
       </c>
       <c r="B291" s="3">
-        <v>1001304096791</v>
+        <v>1001300366790</v>
       </c>
       <c r="C291" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>449</v>
+        <v>332</v>
       </c>
       <c r="B292" s="3">
         <v>1001304096791</v>
@@ -6055,7 +6073,7 @@
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>377</v>
+        <v>449</v>
       </c>
       <c r="B293" s="3">
         <v>1001304096791</v>
@@ -6066,73 +6084,73 @@
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B294" s="3">
-        <v>1001302596795</v>
+        <v>1001304096791</v>
       </c>
       <c r="C294" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B295" s="3">
-        <v>1001300516803</v>
+        <v>1001302596795</v>
       </c>
       <c r="C295" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B296" s="3">
-        <v>1001300456804</v>
+        <v>1001300516803</v>
       </c>
       <c r="C296" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B297" s="3">
-        <v>1001300366807</v>
+        <v>1001300456804</v>
       </c>
       <c r="C297" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B298" s="3">
-        <v>1001302596796</v>
+        <v>1001300366807</v>
       </c>
       <c r="C298" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>433</v>
+        <v>384</v>
       </c>
       <c r="B299" s="3">
-        <v>1001023696765</v>
+        <v>1001302596796</v>
       </c>
       <c r="C299" t="s">
-        <v>386</v>
+        <v>347</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>452</v>
+        <v>433</v>
       </c>
       <c r="B300" s="3">
         <v>1001023696765</v>
@@ -6143,7 +6161,7 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>385</v>
+        <v>452</v>
       </c>
       <c r="B301" s="3">
         <v>1001023696765</v>
@@ -6154,18 +6172,18 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B302" s="3">
-        <v>1001023696767</v>
+        <v>1001023696765</v>
       </c>
       <c r="C302" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="B303" s="3">
         <v>1001023696767</v>
@@ -6176,7 +6194,7 @@
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="B304" s="3">
         <v>1001023696767</v>
@@ -6187,18 +6205,18 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B305" s="3">
-        <v>1001024976829</v>
+        <v>1001023696767</v>
       </c>
       <c r="C305" t="s">
-        <v>787</v>
+        <v>390</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B306" s="3">
         <v>1001024976829</v>
@@ -6209,29 +6227,29 @@
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="B307" s="3">
-        <v>1001022376722</v>
+        <v>1001024976829</v>
       </c>
       <c r="C307" t="s">
-        <v>110</v>
+        <v>787</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>432</v>
+        <v>405</v>
       </c>
       <c r="B308" s="3">
-        <v>1001020846762</v>
+        <v>1001022376722</v>
       </c>
       <c r="C308" t="s">
-        <v>407</v>
+        <v>110</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>451</v>
+        <v>432</v>
       </c>
       <c r="B309" s="3">
         <v>1001020846762</v>
@@ -6242,7 +6260,7 @@
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>406</v>
+        <v>451</v>
       </c>
       <c r="B310" s="3">
         <v>1001020846762</v>
@@ -6253,18 +6271,18 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>115</v>
+        <v>406</v>
       </c>
       <c r="B311" s="3">
-        <v>1001022656853</v>
+        <v>1001020846762</v>
       </c>
       <c r="C311" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>473</v>
+        <v>115</v>
       </c>
       <c r="B312" s="3">
         <v>1001022656853</v>
@@ -6275,18 +6293,18 @@
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>555</v>
+        <v>473</v>
       </c>
       <c r="B313" s="3">
-        <v>1001022656948</v>
+        <v>1001022656853</v>
       </c>
       <c r="C313" t="s">
-        <v>546</v>
+        <v>410</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="B314" s="3">
         <v>1001022656948</v>
@@ -6297,7 +6315,7 @@
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>409</v>
+        <v>549</v>
       </c>
       <c r="B315" s="3">
         <v>1001022656948</v>
@@ -6308,29 +6326,29 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="B316" s="3">
-        <v>1001022656852</v>
+        <v>1001022656948</v>
       </c>
       <c r="C316" t="s">
-        <v>416</v>
+        <v>546</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
-        <v>434</v>
+        <v>415</v>
       </c>
       <c r="B317" s="3">
-        <v>1001020836759</v>
+        <v>1001022656852</v>
       </c>
       <c r="C317" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>450</v>
+        <v>434</v>
       </c>
       <c r="B318" s="3">
         <v>1001020836759</v>
@@ -6341,7 +6359,7 @@
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>417</v>
+        <v>450</v>
       </c>
       <c r="B319" s="3">
         <v>1001020836759</v>
@@ -6352,51 +6370,51 @@
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B320" s="3">
-        <v>1001023856870</v>
+        <v>1001020836759</v>
       </c>
       <c r="C320" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>435</v>
+        <v>419</v>
       </c>
       <c r="B321" s="3">
-        <v>1001013956426</v>
+        <v>1001023856870</v>
       </c>
       <c r="C321" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B322" s="3">
-        <v>1001093345495</v>
+        <v>1001013956426</v>
       </c>
       <c r="C322" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>466</v>
+        <v>437</v>
       </c>
       <c r="B323" s="3">
-        <v>1001022656868</v>
+        <v>1001093345495</v>
       </c>
       <c r="C323" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c r="B324" s="3">
         <v>1001022656868</v>
@@ -6407,18 +6425,18 @@
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>157</v>
+        <v>438</v>
       </c>
       <c r="B325" s="3">
-        <v>1001034065698</v>
+        <v>1001022656868</v>
       </c>
       <c r="C325" t="s">
-        <v>411</v>
+        <v>439</v>
       </c>
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B326" s="3">
         <v>1001034065698</v>
@@ -6429,7 +6447,7 @@
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>464</v>
+        <v>175</v>
       </c>
       <c r="B327" s="3">
         <v>1001034065698</v>
@@ -6440,7 +6458,7 @@
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
       <c r="B328" s="3">
         <v>1001034065698</v>
@@ -6451,29 +6469,29 @@
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B329" s="3">
-        <v>1001084216206</v>
+        <v>1001034065698</v>
       </c>
       <c r="C329" t="s">
-        <v>370</v>
+        <v>411</v>
       </c>
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="B330" s="3">
-        <v>1001015646861</v>
+        <v>1001084216206</v>
       </c>
       <c r="C330" t="s">
-        <v>408</v>
+        <v>370</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="B331" s="3">
         <v>1001015646861</v>
@@ -6484,18 +6502,18 @@
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="B332" s="3">
-        <v>1001025176768</v>
+        <v>1001015646861</v>
       </c>
       <c r="C332" t="s">
-        <v>431</v>
+        <v>408</v>
       </c>
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="B333" s="3">
         <v>1001025176768</v>
@@ -6506,7 +6524,7 @@
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B334" s="3">
         <v>1001025176768</v>
@@ -6517,18 +6535,18 @@
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="B335" s="3">
-        <v>1001025486770</v>
+        <v>1001025176768</v>
       </c>
       <c r="C335" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="B336" s="3">
         <v>1001025486770</v>
@@ -6539,7 +6557,7 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="B337" s="3">
         <v>1001025486770</v>
@@ -6550,18 +6568,18 @@
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>197</v>
+        <v>446</v>
       </c>
       <c r="B338" s="3">
-        <v>1001012816340</v>
+        <v>1001025486770</v>
       </c>
       <c r="C338" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>468</v>
+        <v>197</v>
       </c>
       <c r="B339" s="3">
         <v>1001012816340</v>
@@ -6572,7 +6590,7 @@
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="B340" s="3">
         <v>1001012816340</v>
@@ -6583,18 +6601,18 @@
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
-        <v>293</v>
+        <v>447</v>
       </c>
       <c r="B341" s="3">
-        <v>1001203146834</v>
+        <v>1001012816340</v>
       </c>
       <c r="C341" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
-        <v>441</v>
+        <v>293</v>
       </c>
       <c r="B342" s="3">
         <v>1001203146834</v>
@@ -6605,7 +6623,7 @@
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="B343" s="3">
         <v>1001203146834</v>
@@ -6616,7 +6634,7 @@
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="B344" s="3">
         <v>1001203146834</v>
@@ -6627,40 +6645,40 @@
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="B345" s="3">
-        <v>1001300456788</v>
+        <v>1001203146834</v>
       </c>
       <c r="C345" t="s">
-        <v>461</v>
+        <v>414</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="B346" s="3">
-        <v>1001300516786</v>
+        <v>1001300456788</v>
       </c>
       <c r="C346" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>530</v>
+        <v>475</v>
       </c>
       <c r="B347" s="3">
-        <v>1001092436495</v>
+        <v>1001300516786</v>
       </c>
       <c r="C347" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="B348" s="3">
         <v>1001092436495</v>
@@ -6671,7 +6689,7 @@
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>480</v>
+        <v>537</v>
       </c>
       <c r="B349" s="3">
         <v>1001092436495</v>
@@ -6682,40 +6700,40 @@
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B350" s="3">
-        <v>1001025526901</v>
+        <v>1001092436495</v>
       </c>
       <c r="C350" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B351" s="3">
-        <v>1001025546931</v>
+        <v>1001025526901</v>
       </c>
       <c r="C351" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="B352" s="3">
-        <v>1001010017539</v>
+        <v>1001025546931</v>
       </c>
       <c r="C352" t="s">
-        <v>756</v>
+        <v>485</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>523</v>
+        <v>493</v>
       </c>
       <c r="B353" s="3">
         <v>1001010017539</v>
@@ -6726,7 +6744,7 @@
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>487</v>
+        <v>523</v>
       </c>
       <c r="B354" s="3">
         <v>1001010017539</v>
@@ -6737,7 +6755,7 @@
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>761</v>
+        <v>487</v>
       </c>
       <c r="B355" s="3">
         <v>1001010017539</v>
@@ -6748,18 +6766,18 @@
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>490</v>
+        <v>761</v>
       </c>
       <c r="B356" s="3">
-        <v>1001025766909</v>
+        <v>1001010017539</v>
       </c>
       <c r="C356" t="s">
-        <v>489</v>
+        <v>756</v>
       </c>
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>524</v>
+        <v>490</v>
       </c>
       <c r="B357" s="3">
         <v>1001025766909</v>
@@ -6770,7 +6788,7 @@
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>488</v>
+        <v>524</v>
       </c>
       <c r="B358" s="3">
         <v>1001025766909</v>
@@ -6781,18 +6799,18 @@
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
-        <v>522</v>
+        <v>488</v>
       </c>
       <c r="B359" s="3">
-        <v>1001010014558</v>
+        <v>1001025766909</v>
       </c>
       <c r="C359" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>491</v>
+        <v>522</v>
       </c>
       <c r="B360" s="3">
         <v>1001010014558</v>
@@ -6803,18 +6821,18 @@
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>517</v>
+        <v>491</v>
       </c>
       <c r="B361" s="3">
-        <v>1001012596802</v>
+        <v>1001010014558</v>
       </c>
       <c r="C361" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="B362" s="3">
         <v>1001012596802</v>
@@ -6825,7 +6843,7 @@
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>494</v>
+        <v>526</v>
       </c>
       <c r="B363" s="3">
         <v>1001012596802</v>
@@ -6836,18 +6854,18 @@
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="B364" s="3">
-        <v>1001012596801</v>
+        <v>1001012596802</v>
       </c>
       <c r="C364" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="B365" s="3">
         <v>1001012596801</v>
@@ -6858,7 +6876,7 @@
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>496</v>
+        <v>525</v>
       </c>
       <c r="B366" s="3">
         <v>1001012596801</v>
@@ -6869,161 +6887,161 @@
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B367" s="3">
-        <v>1001062353684</v>
+        <v>1001012596801</v>
       </c>
       <c r="C367" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B368" s="3">
-        <v>1001010014555</v>
+        <v>1001062353684</v>
       </c>
       <c r="C368" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B369" s="3">
-        <v>1001083424691</v>
+        <v>1001010014555</v>
       </c>
       <c r="C369" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B370" s="3">
-        <v>1001190765679</v>
+        <v>1001083424691</v>
       </c>
       <c r="C370" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B371" s="3">
-        <v>1001085636200</v>
+        <v>1001190765679</v>
       </c>
       <c r="C371" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B372" s="3">
-        <v>1001020836253</v>
+        <v>1001085636200</v>
       </c>
       <c r="C372" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B373" s="3">
-        <v>1001084226492</v>
+        <v>1001020836253</v>
       </c>
       <c r="C373" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B374" s="3">
-        <v>1001223296921</v>
+        <v>1001084226492</v>
       </c>
       <c r="C374" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B375" s="3">
-        <v>1001053944786</v>
+        <v>1001223296921</v>
       </c>
       <c r="C375" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="B376" s="3">
-        <v>1001010016839</v>
+        <v>1001053944786</v>
       </c>
       <c r="C376" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="B377" s="3">
-        <v>1001023857038</v>
+        <v>1001010016839</v>
       </c>
       <c r="C377" t="s">
-        <v>568</v>
+        <v>521</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B378" s="3">
-        <v>1001040434903</v>
+        <v>1001023857038</v>
       </c>
       <c r="C378" t="s">
-        <v>529</v>
+        <v>568</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B379" s="3">
-        <v>1001080216842</v>
+        <v>1001040434903</v>
       </c>
       <c r="C379" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="B380" s="3">
-        <v>1001022466951</v>
+        <v>1001080216842</v>
       </c>
       <c r="C380" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B381" s="3">
         <v>1001022466951</v>
@@ -7034,84 +7052,84 @@
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="B382" s="3">
-        <v>1001035276653</v>
+        <v>1001022466951</v>
       </c>
       <c r="C382" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="B383" s="3">
-        <v>1001062353680</v>
+        <v>1001035276653</v>
       </c>
       <c r="C383" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B384" s="3">
-        <v>1001061971146</v>
+        <v>1001062353680</v>
       </c>
       <c r="C384" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B385" s="3">
-        <v>1001225636201</v>
+        <v>1001061971146</v>
       </c>
       <c r="C385" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B386" s="3">
-        <v>1001095227035</v>
+        <v>1001225636201</v>
       </c>
       <c r="C386" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B387" s="3">
-        <v>1001023857038</v>
+        <v>1001095227035</v>
       </c>
       <c r="C387" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>794</v>
+        <v>567</v>
       </c>
       <c r="B388" s="3">
-        <v>1001025027040</v>
+        <v>1001023857038</v>
       </c>
       <c r="C388" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>569</v>
+        <v>794</v>
       </c>
       <c r="B389" s="3">
         <v>1001025027040</v>
@@ -7122,18 +7140,18 @@
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B390" s="3">
-        <v>1001223297103</v>
+        <v>1001025027040</v>
       </c>
       <c r="C390" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B391" s="3">
         <v>1001223297103</v>
@@ -7144,7 +7162,7 @@
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B392" s="3">
         <v>1001223297103</v>
@@ -7155,18 +7173,18 @@
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
-        <v>593</v>
+        <v>572</v>
       </c>
       <c r="B393" s="3">
-        <v>1001010032675</v>
+        <v>1001223297103</v>
       </c>
       <c r="C393" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
-        <v>574</v>
+        <v>593</v>
       </c>
       <c r="B394" s="3">
         <v>1001010032675</v>
@@ -7177,18 +7195,18 @@
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
-        <v>598</v>
+        <v>574</v>
       </c>
       <c r="B395" s="3">
-        <v>1001035937001</v>
+        <v>1001010032675</v>
       </c>
       <c r="C395" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
-        <v>576</v>
+        <v>598</v>
       </c>
       <c r="B396" s="3">
         <v>1001035937001</v>
@@ -7199,18 +7217,18 @@
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
       <c r="B397" s="3">
-        <v>1001084217090</v>
+        <v>1001035937001</v>
       </c>
       <c r="C397" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="B398" s="3">
         <v>1001084217090</v>
@@ -7221,18 +7239,18 @@
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
-        <v>600</v>
+        <v>578</v>
       </c>
       <c r="B399" s="3">
-        <v>1001022377066</v>
+        <v>1001084217090</v>
       </c>
       <c r="C399" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="B400" s="3">
         <v>1001022377066</v>
@@ -7243,18 +7261,18 @@
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="B401" s="3">
-        <v>1001022467080</v>
+        <v>1001022377066</v>
       </c>
       <c r="C401" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
-        <v>582</v>
+        <v>601</v>
       </c>
       <c r="B402" s="3">
         <v>1001022467080</v>
@@ -7265,18 +7283,18 @@
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
-        <v>602</v>
+        <v>582</v>
       </c>
       <c r="B403" s="3">
-        <v>1001025507255</v>
+        <v>1001022467080</v>
       </c>
       <c r="C403" t="s">
-        <v>735</v>
+        <v>583</v>
       </c>
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
-        <v>584</v>
+        <v>602</v>
       </c>
       <c r="B404" s="3">
         <v>1001025507255</v>
@@ -7287,7 +7305,7 @@
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
-        <v>742</v>
+        <v>584</v>
       </c>
       <c r="B405" s="3">
         <v>1001025507255</v>
@@ -7298,18 +7316,18 @@
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
-        <v>605</v>
+        <v>742</v>
       </c>
       <c r="B406" s="3">
-        <v>1001022657075</v>
+        <v>1001025507255</v>
       </c>
       <c r="C406" t="s">
-        <v>586</v>
+        <v>735</v>
       </c>
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
-        <v>585</v>
+        <v>605</v>
       </c>
       <c r="B407" s="3">
         <v>1001022657075</v>
@@ -7320,18 +7338,18 @@
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
-        <v>603</v>
+        <v>585</v>
       </c>
       <c r="B408" s="3">
-        <v>1001022467082</v>
+        <v>1001022657075</v>
       </c>
       <c r="C408" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>587</v>
+        <v>603</v>
       </c>
       <c r="B409" s="3">
         <v>1001022467082</v>
@@ -7342,18 +7360,18 @@
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
-        <v>604</v>
+        <v>587</v>
       </c>
       <c r="B410" s="3">
-        <v>1001022377070</v>
+        <v>1001022467082</v>
       </c>
       <c r="C410" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
-        <v>589</v>
+        <v>604</v>
       </c>
       <c r="B411" s="3">
         <v>1001022377070</v>
@@ -7364,18 +7382,18 @@
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
-        <v>606</v>
+        <v>589</v>
       </c>
       <c r="B412" s="3">
-        <v>1001022657073</v>
+        <v>1001022377070</v>
       </c>
       <c r="C412" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="B413" s="3">
         <v>1001022657073</v>
@@ -7386,18 +7404,18 @@
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
-        <v>617</v>
+        <v>591</v>
       </c>
       <c r="B414" s="3">
-        <v>1001010027126</v>
+        <v>1001022657073</v>
       </c>
       <c r="C414" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>594</v>
+        <v>617</v>
       </c>
       <c r="B415" s="3">
         <v>1001010027126</v>
@@ -7408,18 +7426,18 @@
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B416" s="3">
-        <v>1001010027125</v>
+        <v>1001010027126</v>
       </c>
       <c r="C416" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
-        <v>618</v>
+        <v>596</v>
       </c>
       <c r="B417" s="3">
         <v>1001010027125</v>
@@ -7430,18 +7448,18 @@
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
-        <v>640</v>
+        <v>618</v>
       </c>
       <c r="B418" s="3">
-        <v>1001016366888</v>
+        <v>1001010027125</v>
       </c>
       <c r="C418" t="s">
-        <v>620</v>
+        <v>597</v>
       </c>
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
-        <v>619</v>
+        <v>640</v>
       </c>
       <c r="B419" s="3">
         <v>1001016366888</v>
@@ -7452,18 +7470,18 @@
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
-        <v>641</v>
+        <v>619</v>
       </c>
       <c r="B420" s="3">
-        <v>1001300367133</v>
+        <v>1001016366888</v>
       </c>
       <c r="C420" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="B421" s="3">
         <v>1001300367133</v>
@@ -7474,18 +7492,18 @@
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>639</v>
+        <v>621</v>
       </c>
       <c r="B422" s="3">
-        <v>1001303637564</v>
+        <v>1001300367133</v>
       </c>
       <c r="C422" t="s">
-        <v>754</v>
+        <v>622</v>
       </c>
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
-        <v>623</v>
+        <v>639</v>
       </c>
       <c r="B423" s="3">
         <v>1001303637564</v>
@@ -7496,18 +7514,18 @@
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
-        <v>642</v>
+        <v>623</v>
       </c>
       <c r="B424" s="3">
-        <v>1001304527146</v>
+        <v>1001303637564</v>
       </c>
       <c r="C424" t="s">
-        <v>625</v>
+        <v>754</v>
       </c>
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>624</v>
+        <v>642</v>
       </c>
       <c r="B425" s="3">
         <v>1001304527146</v>
@@ -7518,18 +7536,18 @@
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="B426" s="3">
-        <v>1001300517134</v>
+        <v>1001304527146</v>
       </c>
       <c r="C426" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>626</v>
+        <v>637</v>
       </c>
       <c r="B427" s="3">
         <v>1001300517134</v>
@@ -7540,29 +7558,29 @@
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B428" s="3">
-        <v>1001300457135</v>
+        <v>1001300517134</v>
       </c>
       <c r="C428" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B429" s="3">
-        <v>1001304527144</v>
+        <v>1001300457135</v>
       </c>
       <c r="C429" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="B430" s="3">
         <v>1001304527144</v>
@@ -7573,18 +7591,18 @@
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
-        <v>662</v>
+        <v>638</v>
       </c>
       <c r="B431" s="3">
-        <v>1001081596620</v>
+        <v>1001304527144</v>
       </c>
       <c r="C431" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>645</v>
+        <v>662</v>
       </c>
       <c r="B432" s="3">
         <v>1001081596620</v>
@@ -7595,18 +7613,18 @@
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
-        <v>667</v>
+        <v>645</v>
       </c>
       <c r="B433" s="3">
-        <v>1001085637187</v>
+        <v>1001081596620</v>
       </c>
       <c r="C433" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
-        <v>647</v>
+        <v>667</v>
       </c>
       <c r="B434" s="3">
         <v>1001085637187</v>
@@ -7617,18 +7635,18 @@
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
-        <v>666</v>
+        <v>647</v>
       </c>
       <c r="B435" s="3">
-        <v>1001015676877</v>
+        <v>1001085637187</v>
       </c>
       <c r="C435" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
-        <v>649</v>
+        <v>666</v>
       </c>
       <c r="B436" s="3">
         <v>1001015676877</v>
@@ -7639,18 +7657,18 @@
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
-        <v>669</v>
+        <v>649</v>
       </c>
       <c r="B437" s="3">
-        <v>1001015686878</v>
+        <v>1001015676877</v>
       </c>
       <c r="C437" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
-        <v>651</v>
+        <v>669</v>
       </c>
       <c r="B438" s="3">
         <v>1001015686878</v>
@@ -7661,51 +7679,51 @@
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B439" s="3">
-        <v>1001302277232</v>
+        <v>1001015686878</v>
       </c>
       <c r="C439" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B440" s="3">
-        <v>1001304497237</v>
+        <v>1001302277232</v>
       </c>
       <c r="C440" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B441" s="3">
-        <v>1001303107241</v>
+        <v>1001304497237</v>
       </c>
       <c r="C441" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="B442" s="3">
-        <v>1002162216872</v>
+        <v>1001303107241</v>
       </c>
       <c r="C442" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="B443" s="3">
         <v>1002162216872</v>
@@ -7716,18 +7734,18 @@
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
-        <v>683</v>
+        <v>668</v>
       </c>
       <c r="B444" s="3">
-        <v>1001063237147</v>
+        <v>1002162216872</v>
       </c>
       <c r="C444" t="s">
-        <v>675</v>
+        <v>661</v>
       </c>
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
-        <v>670</v>
+        <v>683</v>
       </c>
       <c r="B445" s="3">
         <v>1001063237147</v>
@@ -7738,18 +7756,18 @@
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="B446" s="3">
-        <v>1001063097227</v>
+        <v>1001063237147</v>
       </c>
       <c r="C446" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="B447" s="3">
         <v>1001063097227</v>
@@ -7760,18 +7778,18 @@
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="B448" s="3">
-        <v>1001066537225</v>
+        <v>1001063097227</v>
       </c>
       <c r="C448" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="B449" s="3">
         <v>1001066537225</v>
@@ -7782,18 +7800,18 @@
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="B450" s="3">
-        <v>1001066527226</v>
+        <v>1001066537225</v>
       </c>
       <c r="C450" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="B451" s="3">
         <v>1001066527226</v>
@@ -7804,29 +7822,29 @@
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B452" s="3">
-        <v>1001066547228</v>
+        <v>1001066527226</v>
       </c>
       <c r="C452" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>690</v>
+        <v>674</v>
       </c>
       <c r="B453" s="3">
-        <v>1001063237229</v>
+        <v>1001066547228</v>
       </c>
       <c r="C453" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="B454" s="3">
         <v>1001063237229</v>
@@ -7837,18 +7855,18 @@
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="B455" s="3">
-        <v>1001063237150</v>
+        <v>1001063237229</v>
       </c>
       <c r="C455" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="B456" s="3">
         <v>1001063237150</v>
@@ -7859,18 +7877,18 @@
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B457" s="3">
-        <v>1001022467276</v>
+        <v>1001063237150</v>
       </c>
       <c r="C457" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="B458" s="3">
         <v>1001022467276</v>
@@ -7881,18 +7899,18 @@
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
-        <v>470</v>
+        <v>691</v>
       </c>
       <c r="B459" s="3">
-        <v>1001022556837</v>
+        <v>1001022467276</v>
       </c>
       <c r="C459" t="s">
-        <v>471</v>
+        <v>689</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
-        <v>713</v>
+        <v>470</v>
       </c>
       <c r="B460" s="3">
         <v>1001022556837</v>
@@ -7903,29 +7921,29 @@
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="B461" s="5">
+        <v>713</v>
+      </c>
+      <c r="B461" s="3">
         <v>1001022556837</v>
       </c>
-      <c r="C461" s="6" t="s">
+      <c r="C461" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B462" s="3">
-        <v>1001205376221</v>
-      </c>
-      <c r="C462" t="s">
-        <v>172</v>
+        <v>694</v>
+      </c>
+      <c r="B462" s="5">
+        <v>1001022556837</v>
+      </c>
+      <c r="C462" s="6" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
-        <v>711</v>
+        <v>174</v>
       </c>
       <c r="B463" s="3">
         <v>1001205376221</v>
@@ -7936,29 +7954,29 @@
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="B464" s="5">
+        <v>711</v>
+      </c>
+      <c r="B464" s="3">
         <v>1001205376221</v>
       </c>
-      <c r="C464" s="6" t="s">
+      <c r="C464" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="B465" s="3">
-        <v>1001304197608</v>
-      </c>
-      <c r="C465" t="s">
-        <v>779</v>
+        <v>695</v>
+      </c>
+      <c r="B465" s="5">
+        <v>1001205376221</v>
+      </c>
+      <c r="C465" s="6" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
-        <v>708</v>
+        <v>479</v>
       </c>
       <c r="B466" s="3">
         <v>1001304197608</v>
@@ -7969,7 +7987,7 @@
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
-        <v>697</v>
+        <v>708</v>
       </c>
       <c r="B467" s="3">
         <v>1001304197608</v>
@@ -7980,7 +7998,7 @@
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
-        <v>797</v>
+        <v>697</v>
       </c>
       <c r="B468" s="3">
         <v>1001304197608</v>
@@ -7991,29 +8009,29 @@
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="B469" s="5">
-        <v>1001010106325</v>
-      </c>
-      <c r="C469" s="6" t="s">
-        <v>49</v>
+        <v>797</v>
+      </c>
+      <c r="B469" s="3">
+        <v>1001304197608</v>
+      </c>
+      <c r="C469" t="s">
+        <v>779</v>
       </c>
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="B470" s="5">
-        <v>1001013957231</v>
+        <v>1001010106325</v>
       </c>
       <c r="C470" s="6" t="s">
-        <v>705</v>
+        <v>49</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
       <c r="B471" s="5">
         <v>1001013957231</v>
@@ -8024,18 +8042,18 @@
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B472" s="3">
-        <v>1001220286279</v>
-      </c>
-      <c r="C472" t="s">
-        <v>45</v>
+        <v>699</v>
+      </c>
+      <c r="B472" s="5">
+        <v>1001013957231</v>
+      </c>
+      <c r="C472" s="6" t="s">
+        <v>705</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
-        <v>715</v>
+        <v>44</v>
       </c>
       <c r="B473" s="3">
         <v>1001220286279</v>
@@ -8046,29 +8064,29 @@
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="B474" s="5">
+        <v>715</v>
+      </c>
+      <c r="B474" s="3">
         <v>1001220286279</v>
       </c>
-      <c r="C474" s="6" t="s">
+      <c r="C474" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="B475" s="5">
-        <v>1001223297092</v>
+        <v>1001220286279</v>
       </c>
       <c r="C475" s="6" t="s">
-        <v>706</v>
+        <v>45</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
-        <v>701</v>
+        <v>710</v>
       </c>
       <c r="B476" s="5">
         <v>1001223297092</v>
@@ -8079,18 +8097,18 @@
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="B477" s="3">
-        <v>1001020836724</v>
-      </c>
-      <c r="C477" t="s">
-        <v>564</v>
+        <v>701</v>
+      </c>
+      <c r="B477" s="5">
+        <v>1001223297092</v>
+      </c>
+      <c r="C477" s="6" t="s">
+        <v>706</v>
       </c>
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
-        <v>712</v>
+        <v>563</v>
       </c>
       <c r="B478" s="3">
         <v>1001020836724</v>
@@ -8101,29 +8119,29 @@
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
-        <v>702</v>
-      </c>
-      <c r="B479" s="5">
+        <v>712</v>
+      </c>
+      <c r="B479" s="3">
         <v>1001020836724</v>
       </c>
-      <c r="C479" s="6" t="s">
+      <c r="C479" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="B480" s="5">
-        <v>1001062475707</v>
+        <v>1001020836724</v>
       </c>
       <c r="C480" s="6" t="s">
-        <v>707</v>
+        <v>564</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="B481" s="5">
         <v>1001062475707</v>
@@ -8134,40 +8152,40 @@
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B482" s="5">
-        <v>1001033856609</v>
+        <v>1001062475707</v>
       </c>
       <c r="C482" s="6" t="s">
-        <v>222</v>
+        <v>707</v>
       </c>
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B483" s="5">
+        <v>1001033856609</v>
+      </c>
+      <c r="C483" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A484" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="B483" s="3">
+      <c r="B484" s="3">
         <v>1001025767284</v>
       </c>
-      <c r="C483" s="6" t="s">
+      <c r="C484" s="6" t="s">
         <v>489</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A484" s="7" t="s">
-        <v>717</v>
-      </c>
-      <c r="B484" s="5">
-        <v>1001301777332</v>
-      </c>
-      <c r="C484" s="6" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="485" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A485" s="7" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
       <c r="B485" s="5">
         <v>1001301777332</v>
@@ -8178,18 +8196,18 @@
     </row>
     <row r="486" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A486" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B486" s="5">
-        <v>1001303987333</v>
+        <v>1001301777332</v>
       </c>
       <c r="C486" s="6" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="487" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A487" s="7" t="s">
-        <v>718</v>
+        <v>732</v>
       </c>
       <c r="B487" s="5">
         <v>1001303987333</v>
@@ -8200,29 +8218,29 @@
     </row>
     <row r="488" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A488" s="7" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B488" s="5">
-        <v>1001012426220</v>
+        <v>1001303987333</v>
       </c>
       <c r="C488" s="6" t="s">
-        <v>186</v>
+        <v>724</v>
       </c>
     </row>
     <row r="489" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A489" s="7" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="B489" s="5">
-        <v>1001300387157</v>
+        <v>1001012426220</v>
       </c>
       <c r="C489" s="6" t="s">
-        <v>725</v>
+        <v>186</v>
       </c>
     </row>
     <row r="490" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A490" s="7" t="s">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="B490" s="5">
         <v>1001300387157</v>
@@ -8233,18 +8251,18 @@
     </row>
     <row r="491" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A491" s="7" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B491" s="5">
-        <v>1001220226208</v>
+        <v>1001300387157</v>
       </c>
       <c r="C491" s="6" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="492" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A492" s="7" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="B492" s="5">
         <v>1001220226208</v>
@@ -8255,18 +8273,18 @@
     </row>
     <row r="493" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A493" s="7" t="s">
+        <v>728</v>
+      </c>
+      <c r="B493" s="5">
+        <v>1001220226208</v>
+      </c>
+      <c r="C493" s="6" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A494" s="7" t="s">
         <v>722</v>
-      </c>
-      <c r="B493" s="5">
-        <v>1001063656967</v>
-      </c>
-      <c r="C493" s="6" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A494" s="2" t="s">
-        <v>729</v>
       </c>
       <c r="B494" s="5">
         <v>1001063656967</v>
@@ -8277,40 +8295,40 @@
     </row>
     <row r="495" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="B495" s="3">
-        <v>1001065616832</v>
-      </c>
-      <c r="C495" t="s">
-        <v>739</v>
+        <v>729</v>
+      </c>
+      <c r="B495" s="5">
+        <v>1001063656967</v>
+      </c>
+      <c r="C495" s="6" t="s">
+        <v>727</v>
       </c>
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B496" s="3">
-        <v>1001060677299</v>
+        <v>1001065616832</v>
       </c>
       <c r="C496" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="B497" s="3">
-        <v>1001453907612</v>
+        <v>1001060677299</v>
       </c>
       <c r="C497" t="s">
-        <v>781</v>
+        <v>741</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
-        <v>793</v>
+        <v>745</v>
       </c>
       <c r="B498" s="3">
         <v>1001453907612</v>
@@ -8321,7 +8339,7 @@
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
-        <v>746</v>
+        <v>793</v>
       </c>
       <c r="B499" s="3">
         <v>1001453907612</v>
@@ -8332,248 +8350,314 @@
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B500" s="3">
-        <v>1001015026797</v>
+        <v>1001453907612</v>
       </c>
       <c r="C500" t="s">
-        <v>748</v>
+        <v>781</v>
       </c>
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B501" s="3">
-        <v>1001095226925</v>
+        <v>1001015026797</v>
       </c>
       <c r="C501" t="s">
-        <v>788</v>
+        <v>748</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B502" s="3">
-        <v>1001035277059</v>
+        <v>1001095226925</v>
       </c>
       <c r="C502" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B503" s="3">
-        <v>1001025767461</v>
+        <v>1001035277059</v>
       </c>
       <c r="C503" t="s">
-        <v>792</v>
+        <v>751</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B504" s="3">
-        <v>1001303637564</v>
+        <v>1001025767461</v>
       </c>
       <c r="C504" t="s">
-        <v>754</v>
+        <v>792</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B505" s="3">
-        <v>1001026947371</v>
+        <v>1001303637564</v>
       </c>
       <c r="C505" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B506" s="3">
-        <v>1001012427523</v>
+        <v>1001026947371</v>
       </c>
       <c r="C506" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="B507" s="3">
-        <v>1001022467083</v>
+        <v>1001012427523</v>
       </c>
       <c r="C507" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="B508" s="3">
-        <v>1001307357489</v>
+        <v>1001022467083</v>
       </c>
       <c r="C508" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B509" s="3">
-        <v>1001025507271</v>
+        <v>1001307357489</v>
       </c>
       <c r="C509" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B510" s="3">
-        <v>1001084856008</v>
+        <v>1001025507271</v>
       </c>
       <c r="C510" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B511" s="3">
-        <v>1001200677442</v>
+        <v>1001084856008</v>
       </c>
       <c r="C511" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B512" s="3">
-        <v>1001300456946</v>
+        <v>1001200677442</v>
       </c>
       <c r="C512" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
-        <v>795</v>
+        <v>776</v>
       </c>
       <c r="B513" s="3">
-        <v>1001093316411</v>
+        <v>1001300456946</v>
       </c>
       <c r="C513" t="s">
-        <v>796</v>
+        <v>777</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
-        <v>798</v>
+        <v>818</v>
       </c>
       <c r="B514" s="3">
-        <v>1001097747647</v>
+        <v>1001093316411</v>
       </c>
       <c r="C514" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
-        <v>811</v>
+        <v>795</v>
       </c>
       <c r="B515" s="3">
-        <v>1001097747647</v>
+        <v>1001093316411</v>
       </c>
       <c r="C515" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B516" s="3">
-        <v>1001097767651</v>
+        <v>1001097747647</v>
       </c>
       <c r="C516" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B517" s="3">
-        <v>1001097767651</v>
+        <v>1001097747647</v>
       </c>
       <c r="C517" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
-        <v>807</v>
+        <v>800</v>
       </c>
       <c r="B518" s="3">
-        <v>1001307077513</v>
+        <v>1001097767651</v>
       </c>
       <c r="C518" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="B519" s="3">
-        <v>1001307587562</v>
+        <v>1001097767651</v>
       </c>
       <c r="C519" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
       <c r="B520" s="3">
-        <v>1001307107516</v>
+        <v>1001307077513</v>
       </c>
       <c r="C520" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
+        <v>807</v>
+      </c>
+      <c r="B521" s="3">
+        <v>1001307077513</v>
+      </c>
+      <c r="C521" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A522" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="B522" s="3">
+        <v>1001307587562</v>
+      </c>
+      <c r="C522" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A523" s="2" t="s">
+        <v>808</v>
+      </c>
+      <c r="B523" s="3">
+        <v>1001307587562</v>
+      </c>
+      <c r="C523" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A524" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="B524" s="3">
+        <v>1001307107516</v>
+      </c>
+      <c r="C524" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A525" s="2" t="s">
+        <v>809</v>
+      </c>
+      <c r="B525" s="3">
+        <v>1001307107516</v>
+      </c>
+      <c r="C525" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A526" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="B526" s="3">
+        <v>1001107397485</v>
+      </c>
+      <c r="C526" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A527" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="B521" s="3">
+      <c r="B527" s="3">
         <v>1001107397485</v>
       </c>
-      <c r="C521" t="s">
+      <c r="C527" t="s">
         <v>806</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C521" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
+  <autoFilter ref="A1:C527" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8A741CE-41D3-49D3-9CFD-B875F606173D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919C9A28-5D9F-4D83-A7F9-645E6EA01EC6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$527</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$532</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="819">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="836">
   <si>
     <t>1С</t>
   </si>
@@ -2491,6 +2491,57 @@
   </si>
   <si>
     <t>6411 ВЕТЧ.РУБЛЕНАЯ ПМ в/у срез 0.3кг 6шт.  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>6602 БАВАРСКИЕ ПМ сос ц/о мгс 0.35кг 8шт.</t>
+  </si>
+  <si>
+    <t>7156 СЕРВЕЛАТ КОПЧ.НА БУКЕ в/к в/у 0.35кг_50с</t>
+  </si>
+  <si>
+    <t>СЕРВЕЛАТ КОПЧ.НА БУКЕ в/к в/у 0.35кг_50с</t>
+  </si>
+  <si>
+    <t>8014 ДОКТОРСКАЯ ПРЕМИУМ вар п/о(п)</t>
+  </si>
+  <si>
+    <t>ДОКТОРСКАЯ ПРЕМИУМ п/о(п)</t>
+  </si>
+  <si>
+    <t>7536 ДОКТОРСКАЯ ГОСТ Останкино вар п/о</t>
+  </si>
+  <si>
+    <t>ДОКТОРСКАЯ ГОСТ Останкино вар п/о</t>
+  </si>
+  <si>
+    <t>7514 ЛЮБИТЕЛЬСКАЯ ОСТАНКИНСКАЯ вар ц/о в/у</t>
+  </si>
+  <si>
+    <t>ЛЮБИТЕЛЬСКАЯ ОСТАНКИНСКАЯ вар ц/о в/у</t>
+  </si>
+  <si>
+    <t>7518 ТЕЛЯЧЬЯ ГОСТ Останкино вар н/о в/у</t>
+  </si>
+  <si>
+    <t>ТЕЛЯЧЬЯ ГОСТ Останкино вар н/о в/у</t>
+  </si>
+  <si>
+    <t>6929 КАРБОНAД ДОМАШНИЙ ПМ к/в кр/к в/у</t>
+  </si>
+  <si>
+    <t>КАРБОНAД ДОМАШНИЙ ПМ к/в кр/к в/у</t>
+  </si>
+  <si>
+    <t>7626 БРАУНШВЕЙГСКАЯ с/к с/н мгс 1/100_Л10</t>
+  </si>
+  <si>
+    <t>БРАУНШВЕЙГСКАЯ с/к с/н мгс 1/100_Л10</t>
+  </si>
+  <si>
+    <t>0614 ПРАЗДНИЧНАЯ с/к в/с дек.спец.мгс</t>
+  </si>
+  <si>
+    <t>ПРАЗДНИЧНАЯ с/к в/с дек.спец.мгс</t>
   </si>
 </sst>
 </file>
@@ -2847,7 +2898,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F527"/>
+  <dimension ref="A1:F536"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" style="2" customWidth="1"/>
@@ -4423,7 +4474,7 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="B143" s="3">
         <v>1001021966602</v>
@@ -4434,40 +4485,40 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>162</v>
+        <v>819</v>
       </c>
       <c r="B144" s="3">
-        <v>6233</v>
+        <v>1001021966602</v>
       </c>
       <c r="C144" t="s">
-        <v>161</v>
+        <v>791</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>248</v>
+        <v>160</v>
       </c>
       <c r="B145" s="3">
-        <v>1001012816341</v>
+        <v>1001021966602</v>
       </c>
       <c r="C145" t="s">
-        <v>423</v>
+        <v>791</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>469</v>
+        <v>162</v>
       </c>
       <c r="B146" s="3">
-        <v>1001012816341</v>
+        <v>6233</v>
       </c>
       <c r="C146" t="s">
-        <v>423</v>
+        <v>161</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>472</v>
+        <v>248</v>
       </c>
       <c r="B147" s="3">
         <v>1001012816341</v>
@@ -4478,7 +4529,7 @@
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>163</v>
+        <v>469</v>
       </c>
       <c r="B148" s="3">
         <v>1001012816341</v>
@@ -4489,62 +4540,62 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>164</v>
+        <v>472</v>
       </c>
       <c r="B149" s="3">
-        <v>6750</v>
+        <v>1001012816341</v>
       </c>
       <c r="C149" t="s">
-        <v>76</v>
+        <v>423</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B150" s="3">
-        <v>6751</v>
+        <v>1001012816341</v>
       </c>
       <c r="C150" t="s">
-        <v>78</v>
+        <v>423</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B151" s="3">
-        <v>5982</v>
+        <v>6750</v>
       </c>
       <c r="C151" t="s">
-        <v>167</v>
+        <v>76</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>518</v>
+        <v>165</v>
       </c>
       <c r="B152" s="3">
-        <v>1001022656854</v>
+        <v>6751</v>
       </c>
       <c r="C152" t="s">
-        <v>412</v>
+        <v>78</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>535</v>
+        <v>166</v>
       </c>
       <c r="B153" s="3">
-        <v>1001022656854</v>
+        <v>5982</v>
       </c>
       <c r="C153" t="s">
-        <v>412</v>
+        <v>167</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>436</v>
+        <v>518</v>
       </c>
       <c r="B154" s="3">
         <v>1001022656854</v>
@@ -4555,7 +4606,7 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>168</v>
+        <v>535</v>
       </c>
       <c r="B155" s="3">
         <v>1001022656854</v>
@@ -4566,392 +4617,392 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>173</v>
+        <v>436</v>
       </c>
       <c r="B156" s="3">
-        <v>1001094966025</v>
+        <v>1001022656854</v>
       </c>
       <c r="C156" t="s">
-        <v>170</v>
+        <v>412</v>
       </c>
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B157" s="3">
-        <v>6025</v>
+        <v>1001022656854</v>
       </c>
       <c r="C157" t="s">
-        <v>170</v>
+        <v>412</v>
       </c>
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B158" s="3">
-        <v>1001022373812</v>
+        <v>1001094966025</v>
       </c>
       <c r="C158" t="s">
-        <v>3</v>
+        <v>170</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B159" s="3">
-        <v>1001100606827</v>
+        <v>6025</v>
       </c>
       <c r="C159" t="s">
-        <v>312</v>
+        <v>170</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>324</v>
+        <v>176</v>
       </c>
       <c r="B160" s="3">
-        <v>1001100606827</v>
+        <v>1001022373812</v>
       </c>
       <c r="C160" t="s">
-        <v>312</v>
+        <v>3</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B161" s="3">
-        <v>1001100616826</v>
+        <v>1001100606827</v>
       </c>
       <c r="C161" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B162" s="3">
-        <v>1001100616826</v>
+        <v>1001100606827</v>
       </c>
       <c r="C162" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B163" s="3">
-        <v>1001100626828</v>
+        <v>1001100616826</v>
       </c>
       <c r="C163" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B164" s="3">
-        <v>1001100626828</v>
+        <v>1001100616826</v>
       </c>
       <c r="C164" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B165" s="3">
-        <v>1001035026308</v>
+        <v>1001100626828</v>
       </c>
       <c r="C165" t="s">
-        <v>181</v>
+        <v>314</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>539</v>
+        <v>326</v>
       </c>
       <c r="B166" s="3">
-        <v>1001014486159</v>
+        <v>1001100626828</v>
       </c>
       <c r="C166" t="s">
-        <v>540</v>
+        <v>314</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B167" s="3">
-        <v>1001014486159</v>
+        <v>1001035026308</v>
       </c>
       <c r="C167" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>184</v>
+        <v>539</v>
       </c>
       <c r="B168" s="3">
-        <v>1001035326217</v>
+        <v>1001014486159</v>
       </c>
       <c r="C168" t="s">
-        <v>271</v>
+        <v>540</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>486</v>
+        <v>182</v>
       </c>
       <c r="B169" s="3">
-        <v>1001012426220</v>
+        <v>1001014486159</v>
       </c>
       <c r="C169" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B170" s="3">
-        <v>1001012426220</v>
+        <v>1001035326217</v>
       </c>
       <c r="C170" t="s">
-        <v>186</v>
+        <v>271</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>187</v>
+        <v>486</v>
       </c>
       <c r="B171" s="3">
-        <v>1001022466236</v>
+        <v>1001012426220</v>
       </c>
       <c r="C171" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B172" s="3">
-        <v>1001021966602</v>
+        <v>1001012426220</v>
       </c>
       <c r="C172" t="s">
-        <v>791</v>
+        <v>186</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B173" s="3">
-        <v>1001022296656</v>
+        <v>1001022466236</v>
       </c>
       <c r="C173" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="B174" s="3">
-        <v>1001301876697</v>
+        <v>1001022296656</v>
       </c>
       <c r="C174" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="B175" s="3">
-        <v>1001022246713</v>
+        <v>1001301876697</v>
       </c>
       <c r="C175" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="B176" s="3">
-        <v>1001022376722</v>
+        <v>1001022246713</v>
       </c>
       <c r="C176" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B177" s="3">
-        <v>1001020846751</v>
+        <v>1001022376722</v>
       </c>
       <c r="C177" t="s">
-        <v>78</v>
+        <v>199</v>
       </c>
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B178" s="3">
-        <v>1001022725819</v>
+        <v>1001020846751</v>
       </c>
       <c r="C178" t="s">
-        <v>202</v>
+        <v>78</v>
       </c>
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B179" s="3">
-        <v>1001012825337</v>
+        <v>1001022725819</v>
       </c>
       <c r="C179" t="s">
-        <v>26</v>
+        <v>202</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B180" s="3">
-        <v>1001012815336</v>
+        <v>1001012825337</v>
       </c>
       <c r="C180" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B181" s="3">
-        <v>1001234146448</v>
+        <v>1001012815336</v>
       </c>
       <c r="C181" t="s">
-        <v>59</v>
+        <v>24</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B182" s="3">
-        <v>1001022725819</v>
+        <v>1001234146448</v>
       </c>
       <c r="C182" t="s">
-        <v>202</v>
+        <v>59</v>
       </c>
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B183" s="3">
-        <v>1001092676027</v>
+        <v>1001022725819</v>
       </c>
       <c r="C183" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="B184" s="3">
-        <v>1001301876213</v>
+        <v>1001092676027</v>
       </c>
       <c r="C184" t="s">
-        <v>69</v>
+        <v>208</v>
       </c>
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B185" s="3">
-        <v>1001035026308</v>
+        <v>1001301876213</v>
       </c>
       <c r="C185" t="s">
-        <v>388</v>
+        <v>69</v>
       </c>
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B186" s="3">
-        <v>1001234146448</v>
+        <v>1001035026308</v>
       </c>
       <c r="C186" t="s">
-        <v>59</v>
+        <v>388</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="B187" s="3">
-        <v>1001025176475</v>
+        <v>1001234146448</v>
       </c>
       <c r="C187" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B188" s="3">
-        <v>1001012456498</v>
+        <v>1001025176475</v>
       </c>
       <c r="C188" t="s">
-        <v>218</v>
+        <v>64</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B189" s="3">
-        <v>1001010036596</v>
+        <v>1001012456498</v>
       </c>
       <c r="C189" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>550</v>
+        <v>219</v>
       </c>
       <c r="B190" s="3">
-        <v>1001033856608</v>
+        <v>1001010036596</v>
       </c>
       <c r="C190" t="s">
-        <v>541</v>
+        <v>220</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>543</v>
+        <v>550</v>
       </c>
       <c r="B191" s="3">
         <v>1001033856608</v>
@@ -4962,18 +5013,18 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="B192" s="3">
-        <v>1001033856609</v>
+        <v>1001033856608</v>
       </c>
       <c r="C192" t="s">
-        <v>222</v>
+        <v>541</v>
       </c>
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>221</v>
+        <v>551</v>
       </c>
       <c r="B193" s="3">
         <v>1001033856609</v>
@@ -4984,315 +5035,315 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="B194" s="3">
-        <v>1001093345495</v>
+        <v>1001033856609</v>
       </c>
       <c r="C194" t="s">
-        <v>424</v>
+        <v>222</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B195" s="3">
-        <v>6550</v>
+        <v>1001093345495</v>
       </c>
       <c r="C195" t="s">
-        <v>227</v>
+        <v>424</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B196" s="3">
-        <v>1001304506684</v>
+        <v>6550</v>
       </c>
       <c r="C196" t="s">
-        <v>53</v>
+        <v>227</v>
       </c>
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B197" s="3">
-        <v>1001010113248</v>
+        <v>1001304506684</v>
       </c>
       <c r="C197" t="s">
-        <v>230</v>
+        <v>53</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>396</v>
+        <v>229</v>
       </c>
       <c r="B198" s="3">
-        <v>1001063926780</v>
+        <v>1001010113248</v>
       </c>
       <c r="C198" t="s">
-        <v>397</v>
+        <v>230</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>231</v>
+        <v>396</v>
       </c>
       <c r="B199" s="3">
-        <v>6586</v>
+        <v>1001063926780</v>
       </c>
       <c r="C199" t="s">
-        <v>232</v>
+        <v>397</v>
       </c>
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="B200" s="3">
-        <v>1001303636467</v>
+        <v>6586</v>
       </c>
       <c r="C200" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="B201" s="3">
-        <v>1001304496701</v>
+        <v>1001303636467</v>
       </c>
       <c r="C201" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B202" s="3">
-        <v>6144</v>
+        <v>1001304496701</v>
       </c>
       <c r="C202" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="B203" s="3">
-        <v>1001022725819</v>
+        <v>6144</v>
       </c>
       <c r="C203" t="s">
-        <v>202</v>
+        <v>239</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="B204" s="3">
-        <v>1001022373812</v>
+        <v>1001022725819</v>
       </c>
       <c r="C204" t="s">
-        <v>3</v>
+        <v>202</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B205" s="3">
-        <v>1001024906062</v>
+        <v>1001022373812</v>
       </c>
       <c r="C205" t="s">
-        <v>244</v>
+        <v>3</v>
       </c>
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="B206" s="3">
-        <v>1001303056692</v>
+        <v>1001024906062</v>
       </c>
       <c r="C206" t="s">
-        <v>54</v>
+        <v>244</v>
       </c>
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B207" s="3">
-        <v>1001301876697</v>
+        <v>1001303056692</v>
       </c>
       <c r="C207" t="s">
-        <v>194</v>
+        <v>54</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B208" s="3">
-        <v>1001012634574</v>
+        <v>1001301876697</v>
       </c>
       <c r="C208" t="s">
-        <v>11</v>
+        <v>194</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B209" s="3">
-        <v>1001092485452</v>
+        <v>1001012634574</v>
       </c>
       <c r="C209" t="s">
-        <v>250</v>
+        <v>11</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B210" s="3">
-        <v>1001020966144</v>
+        <v>1001092485452</v>
       </c>
       <c r="C210" t="s">
-        <v>135</v>
+        <v>250</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B211" s="3">
-        <v>6586</v>
+        <v>1001020966144</v>
       </c>
       <c r="C211" t="s">
-        <v>232</v>
+        <v>135</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B212" s="3">
-        <v>1001304496701</v>
+        <v>6586</v>
       </c>
       <c r="C212" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B213" s="3">
-        <v>1001063655015</v>
+        <v>1001304496701</v>
       </c>
       <c r="C213" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B214" s="3">
-        <v>1001060763287</v>
+        <v>1001063655015</v>
       </c>
       <c r="C214" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B215" s="3">
-        <v>1001225416228</v>
+        <v>1001060763287</v>
       </c>
       <c r="C215" t="s">
-        <v>151</v>
+        <v>259</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B216" s="3">
-        <v>1001032736550</v>
+        <v>1001225416228</v>
       </c>
       <c r="C216" t="s">
-        <v>786</v>
+        <v>151</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B217" s="3">
-        <v>6758</v>
+        <v>1001032736550</v>
       </c>
       <c r="C217" t="s">
-        <v>263</v>
+        <v>786</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B218" s="3">
-        <v>1001020965976</v>
+        <v>6758</v>
       </c>
       <c r="C218" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B219" s="3">
-        <v>1001215576586</v>
+        <v>1001020965976</v>
       </c>
       <c r="C219" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="B220" s="3">
-        <v>1001094896026</v>
+        <v>1001215576586</v>
       </c>
       <c r="C220" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
-        <v>477</v>
+        <v>268</v>
       </c>
       <c r="B221" s="3">
-        <v>1001215576586</v>
+        <v>1001094896026</v>
       </c>
       <c r="C221" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
-        <v>270</v>
+        <v>477</v>
       </c>
       <c r="B222" s="3">
         <v>1001215576586</v>
@@ -5303,18 +5354,18 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
-        <v>763</v>
+        <v>270</v>
       </c>
       <c r="B223" s="3">
-        <v>1001092436470</v>
+        <v>1001215576586</v>
       </c>
       <c r="C223" t="s">
-        <v>764</v>
+        <v>267</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
-        <v>272</v>
+        <v>763</v>
       </c>
       <c r="B224" s="3">
         <v>1001092436470</v>
@@ -5325,29 +5376,29 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B225" s="3">
-        <v>1001203146555</v>
+        <v>1001092436470</v>
       </c>
       <c r="C225" t="s">
-        <v>277</v>
+        <v>764</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="B226" s="3">
-        <v>1001016747343</v>
+        <v>1001203146555</v>
       </c>
       <c r="C226" t="s">
-        <v>734</v>
+        <v>277</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
-        <v>696</v>
+        <v>288</v>
       </c>
       <c r="B227" s="3">
         <v>1001016747343</v>
@@ -5358,7 +5409,7 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
-        <v>279</v>
+        <v>696</v>
       </c>
       <c r="B228" s="3">
         <v>1001016747343</v>
@@ -5369,7 +5420,7 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
-        <v>736</v>
+        <v>279</v>
       </c>
       <c r="B229" s="3">
         <v>1001016747343</v>
@@ -5380,51 +5431,51 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
-        <v>281</v>
+        <v>736</v>
       </c>
       <c r="B230" s="3">
-        <v>1001014765993</v>
+        <v>1001016747343</v>
       </c>
       <c r="C230" t="s">
-        <v>280</v>
+        <v>734</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B231" s="3">
-        <v>1001025166776</v>
+        <v>1001014765993</v>
       </c>
       <c r="C231" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B232" s="3">
-        <v>1001025506777</v>
+        <v>1001025166776</v>
       </c>
       <c r="C232" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="B233" s="3">
-        <v>1001025546822</v>
+        <v>1001025506777</v>
       </c>
       <c r="C233" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B234" s="3">
         <v>1001025546822</v>
@@ -5435,40 +5486,40 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="B235" s="3">
         <v>1001025546822</v>
       </c>
       <c r="C235" t="s">
-        <v>533</v>
+        <v>287</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
-        <v>286</v>
+        <v>319</v>
       </c>
       <c r="B236" s="3">
         <v>1001025546822</v>
       </c>
       <c r="C236" t="s">
-        <v>287</v>
+        <v>533</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
-        <v>643</v>
+        <v>286</v>
       </c>
       <c r="B237" s="3">
-        <v>1001024976616</v>
+        <v>1001025546822</v>
       </c>
       <c r="C237" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
-        <v>290</v>
+        <v>643</v>
       </c>
       <c r="B238" s="3">
         <v>1001024976616</v>
@@ -5479,29 +5530,29 @@
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B239" s="3">
-        <v>1001010855247</v>
+        <v>1001024976616</v>
       </c>
       <c r="C239" t="s">
-        <v>22</v>
+        <v>289</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
-        <v>368</v>
+        <v>291</v>
       </c>
       <c r="B240" s="3">
-        <v>1001223296919</v>
+        <v>1001010855247</v>
       </c>
       <c r="C240" t="s">
-        <v>371</v>
+        <v>22</v>
       </c>
     </row>
     <row r="241" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
-        <v>60</v>
+        <v>368</v>
       </c>
       <c r="B241" s="3">
         <v>1001223296919</v>
@@ -5512,7 +5563,7 @@
     </row>
     <row r="242" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
-        <v>214</v>
+        <v>60</v>
       </c>
       <c r="B242" s="3">
         <v>1001223296919</v>
@@ -5523,29 +5574,29 @@
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
-        <v>440</v>
+        <v>214</v>
       </c>
       <c r="B243" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C243" t="s">
-        <v>456</v>
+        <v>371</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="B244" s="3">
         <v>1001223296919</v>
       </c>
       <c r="C244" t="s">
-        <v>371</v>
+        <v>456</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
-        <v>292</v>
+        <v>462</v>
       </c>
       <c r="B245" s="3">
         <v>1001223296919</v>
@@ -5556,73 +5607,73 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B246" s="3">
-        <v>1001014765993</v>
+        <v>1001223296919</v>
       </c>
       <c r="C246" t="s">
-        <v>280</v>
+        <v>371</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B247" s="3">
-        <v>1001025166776</v>
+        <v>1001014765993</v>
       </c>
       <c r="C247" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="248" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B248" s="3">
-        <v>1001025506777</v>
+        <v>1001025166776</v>
       </c>
       <c r="C248" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="249" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B249" s="3">
-        <v>1001025526778</v>
+        <v>1001025506777</v>
       </c>
       <c r="C249" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B250" s="3">
-        <v>1001304236685</v>
+        <v>1001025526778</v>
       </c>
       <c r="C250" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
-        <v>327</v>
+        <v>302</v>
       </c>
       <c r="B251" s="3">
-        <v>1001015496769</v>
+        <v>1001304236685</v>
       </c>
       <c r="C251" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="B252" s="3">
         <v>1001015496769</v>
@@ -5633,84 +5684,84 @@
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B253" s="3">
-        <v>1001014766798</v>
+        <v>1001015496769</v>
       </c>
       <c r="C253" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="B254" s="3">
-        <v>1001015026797</v>
+        <v>1001014766798</v>
       </c>
       <c r="C254" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B255" s="3">
-        <v>1001205386222</v>
+        <v>1001015026797</v>
       </c>
       <c r="C255" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B256" s="3">
-        <v>1001092675224</v>
+        <v>1001205386222</v>
       </c>
       <c r="C256" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B257" s="3">
-        <v>1001225406223</v>
+        <v>1001092675224</v>
       </c>
       <c r="C257" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="B258" s="3">
-        <v>1001300366790</v>
+        <v>1001225406223</v>
       </c>
       <c r="C258" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
-        <v>458</v>
+        <v>331</v>
       </c>
       <c r="B259" s="3">
-        <v>1001304096792</v>
+        <v>1001300366790</v>
       </c>
       <c r="C259" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="260" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
-        <v>333</v>
+        <v>458</v>
       </c>
       <c r="B260" s="3">
         <v>1001304096792</v>
@@ -5721,18 +5772,18 @@
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
-        <v>358</v>
+        <v>333</v>
       </c>
       <c r="B261" s="3">
-        <v>1001303637603</v>
+        <v>1001304096792</v>
       </c>
       <c r="C261" t="s">
-        <v>755</v>
+        <v>344</v>
       </c>
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="B262" s="3">
         <v>1001303637603</v>
@@ -5743,7 +5794,7 @@
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
-        <v>334</v>
+        <v>378</v>
       </c>
       <c r="B263" s="3">
         <v>1001303637603</v>
@@ -5754,7 +5805,7 @@
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
-        <v>767</v>
+        <v>334</v>
       </c>
       <c r="B264" s="3">
         <v>1001303637603</v>
@@ -5765,18 +5816,18 @@
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
-        <v>379</v>
+        <v>767</v>
       </c>
       <c r="B265" s="3">
-        <v>1001303636794</v>
+        <v>1001303637603</v>
       </c>
       <c r="C265" t="s">
-        <v>345</v>
+        <v>755</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
-        <v>478</v>
+        <v>379</v>
       </c>
       <c r="B266" s="3">
         <v>1001303636794</v>
@@ -5787,7 +5838,7 @@
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
-        <v>335</v>
+        <v>478</v>
       </c>
       <c r="B267" s="3">
         <v>1001303636794</v>
@@ -5798,51 +5849,51 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B268" s="3">
-        <v>1001302596795</v>
+        <v>1001303636794</v>
       </c>
       <c r="C268" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B269" s="3">
-        <v>1001302596796</v>
+        <v>1001302596795</v>
       </c>
       <c r="C269" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="270" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B270" s="3">
-        <v>1001300456804</v>
+        <v>1001302596796</v>
       </c>
       <c r="C270" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>427</v>
+        <v>338</v>
       </c>
       <c r="B271" s="3">
-        <v>1001300366806</v>
+        <v>1001300456804</v>
       </c>
       <c r="C271" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>339</v>
+        <v>427</v>
       </c>
       <c r="B272" s="3">
         <v>1001300366806</v>
@@ -5853,62 +5904,62 @@
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B273" s="3">
-        <v>1001300516803</v>
+        <v>1001300366806</v>
       </c>
       <c r="C273" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B274" s="3">
-        <v>1001300366807</v>
+        <v>1001300516803</v>
       </c>
       <c r="C274" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="B275" s="3">
         <v>1001300366807</v>
       </c>
       <c r="C275" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B276" s="3">
-        <v>1001300516785</v>
+        <v>1001300366807</v>
       </c>
       <c r="C276" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="277" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
-        <v>519</v>
+        <v>354</v>
       </c>
       <c r="B277" s="3">
-        <v>1001300456787</v>
+        <v>1001300516785</v>
       </c>
       <c r="C277" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>534</v>
+        <v>519</v>
       </c>
       <c r="B278" s="3">
         <v>1001300456787</v>
@@ -5919,7 +5970,7 @@
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>356</v>
+        <v>534</v>
       </c>
       <c r="B279" s="3">
         <v>1001300456787</v>
@@ -5930,62 +5981,62 @@
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B280" s="3">
-        <v>1001302596795</v>
+        <v>1001300456787</v>
       </c>
       <c r="C280" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
     </row>
     <row r="281" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B281" s="3">
-        <v>1001012486332</v>
+        <v>1001302596795</v>
       </c>
       <c r="C281" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B282" s="3">
-        <v>1001012566345</v>
+        <v>1001012486332</v>
       </c>
       <c r="C282" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B283" s="3">
-        <v>1001031076528</v>
+        <v>1001012566345</v>
       </c>
       <c r="C283" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="284" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="B284" s="3">
-        <v>1001020836761</v>
+        <v>1001031076528</v>
       </c>
       <c r="C284" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B285" s="3">
         <v>1001020836761</v>
@@ -5996,7 +6047,7 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>372</v>
+        <v>400</v>
       </c>
       <c r="B286" s="3">
         <v>1001020836761</v>
@@ -6007,18 +6058,18 @@
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>391</v>
+        <v>372</v>
       </c>
       <c r="B287" s="3">
-        <v>1001020846764</v>
+        <v>1001020836761</v>
       </c>
       <c r="C287" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
     </row>
     <row r="288" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="B288" s="3">
         <v>1001020846764</v>
@@ -6029,7 +6080,7 @@
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="B289" s="3">
         <v>1001020846764</v>
@@ -6040,18 +6091,18 @@
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>474</v>
+        <v>374</v>
       </c>
       <c r="B290" s="3">
-        <v>1001300366790</v>
+        <v>1001020846764</v>
       </c>
       <c r="C290" t="s">
-        <v>342</v>
+        <v>375</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>376</v>
+        <v>474</v>
       </c>
       <c r="B291" s="3">
         <v>1001300366790</v>
@@ -6062,18 +6113,18 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>332</v>
+        <v>376</v>
       </c>
       <c r="B292" s="3">
-        <v>1001304096791</v>
+        <v>1001300366790</v>
       </c>
       <c r="C292" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>449</v>
+        <v>332</v>
       </c>
       <c r="B293" s="3">
         <v>1001304096791</v>
@@ -6084,7 +6135,7 @@
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>377</v>
+        <v>449</v>
       </c>
       <c r="B294" s="3">
         <v>1001304096791</v>
@@ -6095,73 +6146,73 @@
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B295" s="3">
-        <v>1001302596795</v>
+        <v>1001304096791</v>
       </c>
       <c r="C295" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B296" s="3">
-        <v>1001300516803</v>
+        <v>1001302596795</v>
       </c>
       <c r="C296" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B297" s="3">
-        <v>1001300456804</v>
+        <v>1001300516803</v>
       </c>
       <c r="C297" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B298" s="3">
-        <v>1001300366807</v>
+        <v>1001300456804</v>
       </c>
       <c r="C298" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B299" s="3">
-        <v>1001302596796</v>
+        <v>1001300366807</v>
       </c>
       <c r="C299" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>433</v>
+        <v>384</v>
       </c>
       <c r="B300" s="3">
-        <v>1001023696765</v>
+        <v>1001302596796</v>
       </c>
       <c r="C300" t="s">
-        <v>386</v>
+        <v>347</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>452</v>
+        <v>433</v>
       </c>
       <c r="B301" s="3">
         <v>1001023696765</v>
@@ -6172,7 +6223,7 @@
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>385</v>
+        <v>452</v>
       </c>
       <c r="B302" s="3">
         <v>1001023696765</v>
@@ -6183,18 +6234,18 @@
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B303" s="3">
-        <v>1001023696767</v>
+        <v>1001023696765</v>
       </c>
       <c r="C303" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="304" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="B304" s="3">
         <v>1001023696767</v>
@@ -6205,7 +6256,7 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>389</v>
+        <v>402</v>
       </c>
       <c r="B305" s="3">
         <v>1001023696767</v>
@@ -6216,18 +6267,18 @@
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B306" s="3">
-        <v>1001024976829</v>
+        <v>1001023696767</v>
       </c>
       <c r="C306" t="s">
-        <v>787</v>
+        <v>390</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B307" s="3">
         <v>1001024976829</v>
@@ -6238,29 +6289,29 @@
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="B308" s="3">
-        <v>1001022376722</v>
+        <v>1001024976829</v>
       </c>
       <c r="C308" t="s">
-        <v>110</v>
+        <v>787</v>
       </c>
     </row>
     <row r="309" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>432</v>
+        <v>405</v>
       </c>
       <c r="B309" s="3">
-        <v>1001020846762</v>
+        <v>1001022376722</v>
       </c>
       <c r="C309" t="s">
-        <v>407</v>
+        <v>110</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>451</v>
+        <v>432</v>
       </c>
       <c r="B310" s="3">
         <v>1001020846762</v>
@@ -6271,7 +6322,7 @@
     </row>
     <row r="311" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>406</v>
+        <v>451</v>
       </c>
       <c r="B311" s="3">
         <v>1001020846762</v>
@@ -6282,18 +6333,18 @@
     </row>
     <row r="312" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>115</v>
+        <v>406</v>
       </c>
       <c r="B312" s="3">
-        <v>1001022656853</v>
+        <v>1001020846762</v>
       </c>
       <c r="C312" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>473</v>
+        <v>115</v>
       </c>
       <c r="B313" s="3">
         <v>1001022656853</v>
@@ -6304,18 +6355,18 @@
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>555</v>
+        <v>473</v>
       </c>
       <c r="B314" s="3">
-        <v>1001022656948</v>
+        <v>1001022656853</v>
       </c>
       <c r="C314" t="s">
-        <v>546</v>
+        <v>410</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="B315" s="3">
         <v>1001022656948</v>
@@ -6326,7 +6377,7 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>409</v>
+        <v>549</v>
       </c>
       <c r="B316" s="3">
         <v>1001022656948</v>
@@ -6337,29 +6388,29 @@
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="B317" s="3">
-        <v>1001022656852</v>
+        <v>1001022656948</v>
       </c>
       <c r="C317" t="s">
-        <v>416</v>
+        <v>546</v>
       </c>
     </row>
     <row r="318" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>434</v>
+        <v>415</v>
       </c>
       <c r="B318" s="3">
-        <v>1001020836759</v>
+        <v>1001022656852</v>
       </c>
       <c r="C318" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>450</v>
+        <v>434</v>
       </c>
       <c r="B319" s="3">
         <v>1001020836759</v>
@@ -6370,7 +6421,7 @@
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
-        <v>417</v>
+        <v>450</v>
       </c>
       <c r="B320" s="3">
         <v>1001020836759</v>
@@ -6381,51 +6432,51 @@
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B321" s="3">
-        <v>1001023856870</v>
+        <v>1001020836759</v>
       </c>
       <c r="C321" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>435</v>
+        <v>419</v>
       </c>
       <c r="B322" s="3">
-        <v>1001013956426</v>
+        <v>1001023856870</v>
       </c>
       <c r="C322" t="s">
-        <v>413</v>
+        <v>420</v>
       </c>
     </row>
     <row r="323" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B323" s="3">
-        <v>1001093345495</v>
+        <v>1001013956426</v>
       </c>
       <c r="C323" t="s">
-        <v>424</v>
+        <v>413</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>466</v>
+        <v>437</v>
       </c>
       <c r="B324" s="3">
-        <v>1001022656868</v>
+        <v>1001093345495</v>
       </c>
       <c r="C324" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
     </row>
     <row r="325" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>438</v>
+        <v>466</v>
       </c>
       <c r="B325" s="3">
         <v>1001022656868</v>
@@ -6436,18 +6487,18 @@
     </row>
     <row r="326" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>157</v>
+        <v>438</v>
       </c>
       <c r="B326" s="3">
-        <v>1001034065698</v>
+        <v>1001022656868</v>
       </c>
       <c r="C326" t="s">
-        <v>411</v>
+        <v>439</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="B327" s="3">
         <v>1001034065698</v>
@@ -6458,7 +6509,7 @@
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>464</v>
+        <v>175</v>
       </c>
       <c r="B328" s="3">
         <v>1001034065698</v>
@@ -6469,7 +6520,7 @@
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
       <c r="B329" s="3">
         <v>1001034065698</v>
@@ -6480,29 +6531,29 @@
     </row>
     <row r="330" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B330" s="3">
-        <v>1001084216206</v>
+        <v>1001034065698</v>
       </c>
       <c r="C330" t="s">
-        <v>370</v>
+        <v>411</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="B331" s="3">
-        <v>1001015646861</v>
+        <v>1001084216206</v>
       </c>
       <c r="C331" t="s">
-        <v>408</v>
+        <v>370</v>
       </c>
     </row>
     <row r="332" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="B332" s="3">
         <v>1001015646861</v>
@@ -6513,18 +6564,18 @@
     </row>
     <row r="333" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="B333" s="3">
-        <v>1001025176768</v>
+        <v>1001015646861</v>
       </c>
       <c r="C333" t="s">
-        <v>431</v>
+        <v>408</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="B334" s="3">
         <v>1001025176768</v>
@@ -6535,7 +6586,7 @@
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B335" s="3">
         <v>1001025176768</v>
@@ -6546,18 +6597,18 @@
     </row>
     <row r="336" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="B336" s="3">
-        <v>1001025486770</v>
+        <v>1001025176768</v>
       </c>
       <c r="C336" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>454</v>
+        <v>429</v>
       </c>
       <c r="B337" s="3">
         <v>1001025486770</v>
@@ -6568,7 +6619,7 @@
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="B338" s="3">
         <v>1001025486770</v>
@@ -6579,18 +6630,18 @@
     </row>
     <row r="339" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>197</v>
+        <v>446</v>
       </c>
       <c r="B339" s="3">
-        <v>1001012816340</v>
+        <v>1001025486770</v>
       </c>
       <c r="C339" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
     </row>
     <row r="340" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>468</v>
+        <v>197</v>
       </c>
       <c r="B340" s="3">
         <v>1001012816340</v>
@@ -6601,7 +6652,7 @@
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="B341" s="3">
         <v>1001012816340</v>
@@ -6612,18 +6663,18 @@
     </row>
     <row r="342" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
-        <v>293</v>
+        <v>447</v>
       </c>
       <c r="B342" s="3">
-        <v>1001203146834</v>
+        <v>1001012816340</v>
       </c>
       <c r="C342" t="s">
-        <v>414</v>
+        <v>422</v>
       </c>
     </row>
     <row r="343" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>441</v>
+        <v>293</v>
       </c>
       <c r="B343" s="3">
         <v>1001203146834</v>
@@ -6634,7 +6685,7 @@
     </row>
     <row r="344" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="B344" s="3">
         <v>1001203146834</v>
@@ -6645,7 +6696,7 @@
     </row>
     <row r="345" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>448</v>
+        <v>465</v>
       </c>
       <c r="B345" s="3">
         <v>1001203146834</v>
@@ -6656,40 +6707,40 @@
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="B346" s="3">
-        <v>1001300456788</v>
+        <v>1001203146834</v>
       </c>
       <c r="C346" t="s">
-        <v>461</v>
+        <v>414</v>
       </c>
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="B347" s="3">
-        <v>1001300516786</v>
+        <v>1001300456788</v>
       </c>
       <c r="C347" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>530</v>
+        <v>475</v>
       </c>
       <c r="B348" s="3">
-        <v>1001092436495</v>
+        <v>1001300516786</v>
       </c>
       <c r="C348" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="B349" s="3">
         <v>1001092436495</v>
@@ -6700,7 +6751,7 @@
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>480</v>
+        <v>537</v>
       </c>
       <c r="B350" s="3">
         <v>1001092436495</v>
@@ -6711,40 +6762,40 @@
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="B351" s="3">
-        <v>1001025526901</v>
+        <v>1001092436495</v>
       </c>
       <c r="C351" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="352" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B352" s="3">
-        <v>1001025546931</v>
+        <v>1001025526901</v>
       </c>
       <c r="C352" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
     </row>
     <row r="353" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="B353" s="3">
-        <v>1001010017539</v>
+        <v>1001025546931</v>
       </c>
       <c r="C353" t="s">
-        <v>756</v>
+        <v>485</v>
       </c>
     </row>
     <row r="354" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>523</v>
+        <v>493</v>
       </c>
       <c r="B354" s="3">
         <v>1001010017539</v>
@@ -6755,7 +6806,7 @@
     </row>
     <row r="355" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>487</v>
+        <v>523</v>
       </c>
       <c r="B355" s="3">
         <v>1001010017539</v>
@@ -6766,7 +6817,7 @@
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>761</v>
+        <v>487</v>
       </c>
       <c r="B356" s="3">
         <v>1001010017539</v>
@@ -6777,18 +6828,18 @@
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>490</v>
+        <v>761</v>
       </c>
       <c r="B357" s="3">
-        <v>1001025766909</v>
+        <v>1001010017539</v>
       </c>
       <c r="C357" t="s">
-        <v>489</v>
+        <v>756</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>524</v>
+        <v>490</v>
       </c>
       <c r="B358" s="3">
         <v>1001025766909</v>
@@ -6799,7 +6850,7 @@
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
-        <v>488</v>
+        <v>524</v>
       </c>
       <c r="B359" s="3">
         <v>1001025766909</v>
@@ -6810,18 +6861,18 @@
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>522</v>
+        <v>488</v>
       </c>
       <c r="B360" s="3">
-        <v>1001010014558</v>
+        <v>1001025766909</v>
       </c>
       <c r="C360" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
     </row>
     <row r="361" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>491</v>
+        <v>522</v>
       </c>
       <c r="B361" s="3">
         <v>1001010014558</v>
@@ -6832,18 +6883,18 @@
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>517</v>
+        <v>491</v>
       </c>
       <c r="B362" s="3">
-        <v>1001012596802</v>
+        <v>1001010014558</v>
       </c>
       <c r="C362" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="B363" s="3">
         <v>1001012596802</v>
@@ -6854,7 +6905,7 @@
     </row>
     <row r="364" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>494</v>
+        <v>526</v>
       </c>
       <c r="B364" s="3">
         <v>1001012596802</v>
@@ -6865,18 +6916,18 @@
     </row>
     <row r="365" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>512</v>
+        <v>494</v>
       </c>
       <c r="B365" s="3">
-        <v>1001012596801</v>
+        <v>1001012596802</v>
       </c>
       <c r="C365" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="366" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="B366" s="3">
         <v>1001012596801</v>
@@ -6887,7 +6938,7 @@
     </row>
     <row r="367" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>496</v>
+        <v>525</v>
       </c>
       <c r="B367" s="3">
         <v>1001012596801</v>
@@ -6898,161 +6949,161 @@
     </row>
     <row r="368" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="B368" s="3">
-        <v>1001062353684</v>
+        <v>1001012596801</v>
       </c>
       <c r="C368" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
     <row r="369" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B369" s="3">
-        <v>1001010014555</v>
+        <v>1001062353684</v>
       </c>
       <c r="C369" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
     </row>
     <row r="370" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B370" s="3">
-        <v>1001083424691</v>
+        <v>1001010014555</v>
       </c>
       <c r="C370" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B371" s="3">
-        <v>1001190765679</v>
+        <v>1001083424691</v>
       </c>
       <c r="C371" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="B372" s="3">
-        <v>1001085636200</v>
+        <v>1001190765679</v>
       </c>
       <c r="C372" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="B373" s="3">
-        <v>1001020836253</v>
+        <v>1001085636200</v>
       </c>
       <c r="C373" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="B374" s="3">
-        <v>1001084226492</v>
+        <v>1001020836253</v>
       </c>
       <c r="C374" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="B375" s="3">
-        <v>1001223296921</v>
+        <v>1001084226492</v>
       </c>
       <c r="C375" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
     </row>
     <row r="376" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="B376" s="3">
-        <v>1001053944786</v>
+        <v>1001223296921</v>
       </c>
       <c r="C376" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="B377" s="3">
-        <v>1001010016839</v>
+        <v>1001053944786</v>
       </c>
       <c r="C377" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>527</v>
+        <v>520</v>
       </c>
       <c r="B378" s="3">
-        <v>1001023857038</v>
+        <v>1001010016839</v>
       </c>
       <c r="C378" t="s">
-        <v>568</v>
+        <v>521</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B379" s="3">
-        <v>1001040434903</v>
+        <v>1001023857038</v>
       </c>
       <c r="C379" t="s">
-        <v>529</v>
+        <v>568</v>
       </c>
     </row>
     <row r="380" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B380" s="3">
-        <v>1001080216842</v>
+        <v>1001040434903</v>
       </c>
       <c r="C380" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
     </row>
     <row r="381" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="B381" s="3">
-        <v>1001022466951</v>
+        <v>1001080216842</v>
       </c>
       <c r="C381" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
     </row>
     <row r="382" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B382" s="3">
         <v>1001022466951</v>
@@ -7063,84 +7114,84 @@
     </row>
     <row r="383" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="B383" s="3">
-        <v>1001035276653</v>
+        <v>1001022466951</v>
       </c>
       <c r="C383" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
     </row>
     <row r="384" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="B384" s="3">
-        <v>1001062353680</v>
+        <v>1001035276653</v>
       </c>
       <c r="C384" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
     </row>
     <row r="385" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B385" s="3">
-        <v>1001061971146</v>
+        <v>1001062353680</v>
       </c>
       <c r="C385" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B386" s="3">
-        <v>1001225636201</v>
+        <v>1001061971146</v>
       </c>
       <c r="C386" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B387" s="3">
-        <v>1001095227035</v>
+        <v>1001225636201</v>
       </c>
       <c r="C387" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
     </row>
     <row r="388" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="B388" s="3">
-        <v>1001023857038</v>
+        <v>1001095227035</v>
       </c>
       <c r="C388" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="389" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>794</v>
+        <v>567</v>
       </c>
       <c r="B389" s="3">
-        <v>1001025027040</v>
+        <v>1001023857038</v>
       </c>
       <c r="C389" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
-        <v>569</v>
+        <v>794</v>
       </c>
       <c r="B390" s="3">
         <v>1001025027040</v>
@@ -7151,18 +7202,18 @@
     </row>
     <row r="391" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="B391" s="3">
-        <v>1001223297103</v>
+        <v>1001025027040</v>
       </c>
       <c r="C391" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="392" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B392" s="3">
         <v>1001223297103</v>
@@ -7173,7 +7224,7 @@
     </row>
     <row r="393" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B393" s="3">
         <v>1001223297103</v>
@@ -7184,18 +7235,18 @@
     </row>
     <row r="394" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
-        <v>593</v>
+        <v>572</v>
       </c>
       <c r="B394" s="3">
-        <v>1001010032675</v>
+        <v>1001223297103</v>
       </c>
       <c r="C394" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
-        <v>574</v>
+        <v>593</v>
       </c>
       <c r="B395" s="3">
         <v>1001010032675</v>
@@ -7206,18 +7257,18 @@
     </row>
     <row r="396" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
-        <v>598</v>
+        <v>574</v>
       </c>
       <c r="B396" s="3">
-        <v>1001035937001</v>
+        <v>1001010032675</v>
       </c>
       <c r="C396" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="397" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
-        <v>576</v>
+        <v>598</v>
       </c>
       <c r="B397" s="3">
         <v>1001035937001</v>
@@ -7228,18 +7279,18 @@
     </row>
     <row r="398" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
-        <v>599</v>
+        <v>576</v>
       </c>
       <c r="B398" s="3">
-        <v>1001084217090</v>
+        <v>1001035937001</v>
       </c>
       <c r="C398" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
     </row>
     <row r="399" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
-        <v>578</v>
+        <v>599</v>
       </c>
       <c r="B399" s="3">
         <v>1001084217090</v>
@@ -7250,18 +7301,18 @@
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
-        <v>600</v>
+        <v>578</v>
       </c>
       <c r="B400" s="3">
-        <v>1001022377066</v>
+        <v>1001084217090</v>
       </c>
       <c r="C400" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="401" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="B401" s="3">
         <v>1001022377066</v>
@@ -7272,18 +7323,18 @@
     </row>
     <row r="402" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="B402" s="3">
-        <v>1001022467080</v>
+        <v>1001022377066</v>
       </c>
       <c r="C402" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
     </row>
     <row r="403" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
-        <v>582</v>
+        <v>601</v>
       </c>
       <c r="B403" s="3">
         <v>1001022467080</v>
@@ -7294,18 +7345,18 @@
     </row>
     <row r="404" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
-        <v>602</v>
+        <v>582</v>
       </c>
       <c r="B404" s="3">
-        <v>1001025507255</v>
+        <v>1001022467080</v>
       </c>
       <c r="C404" t="s">
-        <v>735</v>
+        <v>583</v>
       </c>
     </row>
     <row r="405" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
-        <v>584</v>
+        <v>602</v>
       </c>
       <c r="B405" s="3">
         <v>1001025507255</v>
@@ -7316,7 +7367,7 @@
     </row>
     <row r="406" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
-        <v>742</v>
+        <v>584</v>
       </c>
       <c r="B406" s="3">
         <v>1001025507255</v>
@@ -7327,18 +7378,18 @@
     </row>
     <row r="407" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
-        <v>605</v>
+        <v>742</v>
       </c>
       <c r="B407" s="3">
-        <v>1001022657075</v>
+        <v>1001025507255</v>
       </c>
       <c r="C407" t="s">
-        <v>586</v>
+        <v>735</v>
       </c>
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
-        <v>585</v>
+        <v>605</v>
       </c>
       <c r="B408" s="3">
         <v>1001022657075</v>
@@ -7349,18 +7400,18 @@
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
-        <v>603</v>
+        <v>585</v>
       </c>
       <c r="B409" s="3">
-        <v>1001022467082</v>
+        <v>1001022657075</v>
       </c>
       <c r="C409" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
-        <v>587</v>
+        <v>603</v>
       </c>
       <c r="B410" s="3">
         <v>1001022467082</v>
@@ -7371,18 +7422,18 @@
     </row>
     <row r="411" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
-        <v>604</v>
+        <v>587</v>
       </c>
       <c r="B411" s="3">
-        <v>1001022377070</v>
+        <v>1001022467082</v>
       </c>
       <c r="C411" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="412" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
-        <v>589</v>
+        <v>604</v>
       </c>
       <c r="B412" s="3">
         <v>1001022377070</v>
@@ -7393,18 +7444,18 @@
     </row>
     <row r="413" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
-        <v>606</v>
+        <v>589</v>
       </c>
       <c r="B413" s="3">
-        <v>1001022657073</v>
+        <v>1001022377070</v>
       </c>
       <c r="C413" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="414" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
-        <v>591</v>
+        <v>606</v>
       </c>
       <c r="B414" s="3">
         <v>1001022657073</v>
@@ -7415,18 +7466,18 @@
     </row>
     <row r="415" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
-        <v>617</v>
+        <v>591</v>
       </c>
       <c r="B415" s="3">
-        <v>1001010027126</v>
+        <v>1001022657073</v>
       </c>
       <c r="C415" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
     </row>
     <row r="416" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
-        <v>594</v>
+        <v>617</v>
       </c>
       <c r="B416" s="3">
         <v>1001010027126</v>
@@ -7437,18 +7488,18 @@
     </row>
     <row r="417" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="B417" s="3">
-        <v>1001010027125</v>
+        <v>1001010027126</v>
       </c>
       <c r="C417" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="418" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
-        <v>618</v>
+        <v>596</v>
       </c>
       <c r="B418" s="3">
         <v>1001010027125</v>
@@ -7459,18 +7510,18 @@
     </row>
     <row r="419" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
-        <v>640</v>
+        <v>618</v>
       </c>
       <c r="B419" s="3">
-        <v>1001016366888</v>
+        <v>1001010027125</v>
       </c>
       <c r="C419" t="s">
-        <v>620</v>
+        <v>597</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
-        <v>619</v>
+        <v>640</v>
       </c>
       <c r="B420" s="3">
         <v>1001016366888</v>
@@ -7481,18 +7532,18 @@
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
-        <v>641</v>
+        <v>619</v>
       </c>
       <c r="B421" s="3">
-        <v>1001300367133</v>
+        <v>1001016366888</v>
       </c>
       <c r="C421" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
-        <v>621</v>
+        <v>641</v>
       </c>
       <c r="B422" s="3">
         <v>1001300367133</v>
@@ -7503,18 +7554,18 @@
     </row>
     <row r="423" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
-        <v>639</v>
+        <v>621</v>
       </c>
       <c r="B423" s="3">
-        <v>1001303637564</v>
+        <v>1001300367133</v>
       </c>
       <c r="C423" t="s">
-        <v>754</v>
+        <v>622</v>
       </c>
     </row>
     <row r="424" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
-        <v>623</v>
+        <v>639</v>
       </c>
       <c r="B424" s="3">
         <v>1001303637564</v>
@@ -7525,18 +7576,18 @@
     </row>
     <row r="425" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
-        <v>642</v>
+        <v>623</v>
       </c>
       <c r="B425" s="3">
-        <v>1001304527146</v>
+        <v>1001303637564</v>
       </c>
       <c r="C425" t="s">
-        <v>625</v>
+        <v>754</v>
       </c>
     </row>
     <row r="426" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
-        <v>624</v>
+        <v>642</v>
       </c>
       <c r="B426" s="3">
         <v>1001304527146</v>
@@ -7547,18 +7598,18 @@
     </row>
     <row r="427" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
-        <v>637</v>
+        <v>624</v>
       </c>
       <c r="B427" s="3">
-        <v>1001300517134</v>
+        <v>1001304527146</v>
       </c>
       <c r="C427" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
     </row>
     <row r="428" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
-        <v>626</v>
+        <v>637</v>
       </c>
       <c r="B428" s="3">
         <v>1001300517134</v>
@@ -7569,29 +7620,29 @@
     </row>
     <row r="429" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="B429" s="3">
-        <v>1001300457135</v>
+        <v>1001300517134</v>
       </c>
       <c r="C429" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B430" s="3">
-        <v>1001304527144</v>
+        <v>1001300457135</v>
       </c>
       <c r="C430" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="B431" s="3">
         <v>1001304527144</v>
@@ -7602,18 +7653,18 @@
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
-        <v>662</v>
+        <v>638</v>
       </c>
       <c r="B432" s="3">
-        <v>1001081596620</v>
+        <v>1001304527144</v>
       </c>
       <c r="C432" t="s">
-        <v>644</v>
+        <v>631</v>
       </c>
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
-        <v>645</v>
+        <v>662</v>
       </c>
       <c r="B433" s="3">
         <v>1001081596620</v>
@@ -7624,18 +7675,18 @@
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
-        <v>667</v>
+        <v>645</v>
       </c>
       <c r="B434" s="3">
-        <v>1001085637187</v>
+        <v>1001081596620</v>
       </c>
       <c r="C434" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
-        <v>647</v>
+        <v>667</v>
       </c>
       <c r="B435" s="3">
         <v>1001085637187</v>
@@ -7646,18 +7697,18 @@
     </row>
     <row r="436" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
-        <v>666</v>
+        <v>647</v>
       </c>
       <c r="B436" s="3">
-        <v>1001015676877</v>
+        <v>1001085637187</v>
       </c>
       <c r="C436" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
-        <v>649</v>
+        <v>666</v>
       </c>
       <c r="B437" s="3">
         <v>1001015676877</v>
@@ -7668,18 +7719,18 @@
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
-        <v>669</v>
+        <v>649</v>
       </c>
       <c r="B438" s="3">
-        <v>1001015686878</v>
+        <v>1001015676877</v>
       </c>
       <c r="C438" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="439" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
-        <v>651</v>
+        <v>669</v>
       </c>
       <c r="B439" s="3">
         <v>1001015686878</v>
@@ -7690,51 +7741,51 @@
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B440" s="3">
-        <v>1001302277232</v>
+        <v>1001015686878</v>
       </c>
       <c r="C440" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B441" s="3">
-        <v>1001304497237</v>
+        <v>1001302277232</v>
       </c>
       <c r="C441" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B442" s="3">
-        <v>1001303107241</v>
+        <v>1001304497237</v>
       </c>
       <c r="C442" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="B443" s="3">
-        <v>1002162216872</v>
+        <v>1001303107241</v>
       </c>
       <c r="C443" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
     </row>
     <row r="444" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
-        <v>668</v>
+        <v>660</v>
       </c>
       <c r="B444" s="3">
         <v>1002162216872</v>
@@ -7745,18 +7796,18 @@
     </row>
     <row r="445" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
-        <v>683</v>
+        <v>668</v>
       </c>
       <c r="B445" s="3">
-        <v>1001063237147</v>
+        <v>1002162216872</v>
       </c>
       <c r="C445" t="s">
-        <v>675</v>
+        <v>661</v>
       </c>
     </row>
     <row r="446" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
-        <v>670</v>
+        <v>683</v>
       </c>
       <c r="B446" s="3">
         <v>1001063237147</v>
@@ -7767,18 +7818,18 @@
     </row>
     <row r="447" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
-        <v>682</v>
+        <v>670</v>
       </c>
       <c r="B447" s="3">
-        <v>1001063097227</v>
+        <v>1001063237147</v>
       </c>
       <c r="C447" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="448" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="B448" s="3">
         <v>1001063097227</v>
@@ -7789,18 +7840,18 @@
     </row>
     <row r="449" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="B449" s="3">
-        <v>1001066537225</v>
+        <v>1001063097227</v>
       </c>
       <c r="C449" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
     </row>
     <row r="450" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
       <c r="B450" s="3">
         <v>1001066537225</v>
@@ -7811,18 +7862,18 @@
     </row>
     <row r="451" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="B451" s="3">
-        <v>1001066527226</v>
+        <v>1001066537225</v>
       </c>
       <c r="C451" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="452" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="B452" s="3">
         <v>1001066527226</v>
@@ -7833,29 +7884,29 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B453" s="3">
-        <v>1001066547228</v>
+        <v>1001066527226</v>
       </c>
       <c r="C453" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="454" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
-        <v>690</v>
+        <v>674</v>
       </c>
       <c r="B454" s="3">
-        <v>1001063237229</v>
+        <v>1001066547228</v>
       </c>
       <c r="C454" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
     </row>
     <row r="455" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
-        <v>684</v>
+        <v>690</v>
       </c>
       <c r="B455" s="3">
         <v>1001063237229</v>
@@ -7866,18 +7917,18 @@
     </row>
     <row r="456" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
-        <v>692</v>
+        <v>684</v>
       </c>
       <c r="B456" s="3">
-        <v>1001063237150</v>
+        <v>1001063237229</v>
       </c>
       <c r="C456" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="B457" s="3">
         <v>1001063237150</v>
@@ -7888,18 +7939,18 @@
     </row>
     <row r="458" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B458" s="3">
-        <v>1001022467276</v>
+        <v>1001063237150</v>
       </c>
       <c r="C458" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="B459" s="3">
         <v>1001022467276</v>
@@ -7910,18 +7961,18 @@
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
-        <v>470</v>
+        <v>691</v>
       </c>
       <c r="B460" s="3">
-        <v>1001022556837</v>
+        <v>1001022467276</v>
       </c>
       <c r="C460" t="s">
-        <v>471</v>
+        <v>689</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
-        <v>713</v>
+        <v>470</v>
       </c>
       <c r="B461" s="3">
         <v>1001022556837</v>
@@ -7932,29 +7983,29 @@
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="B462" s="5">
+        <v>713</v>
+      </c>
+      <c r="B462" s="3">
         <v>1001022556837</v>
       </c>
-      <c r="C462" s="6" t="s">
+      <c r="C462" t="s">
         <v>471</v>
       </c>
     </row>
     <row r="463" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="B463" s="3">
-        <v>1001205376221</v>
-      </c>
-      <c r="C463" t="s">
-        <v>172</v>
+        <v>694</v>
+      </c>
+      <c r="B463" s="5">
+        <v>1001022556837</v>
+      </c>
+      <c r="C463" s="6" t="s">
+        <v>471</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
-        <v>711</v>
+        <v>174</v>
       </c>
       <c r="B464" s="3">
         <v>1001205376221</v>
@@ -7965,29 +8016,29 @@
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
-        <v>695</v>
-      </c>
-      <c r="B465" s="5">
+        <v>711</v>
+      </c>
+      <c r="B465" s="3">
         <v>1001205376221</v>
       </c>
-      <c r="C465" s="6" t="s">
+      <c r="C465" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="B466" s="3">
-        <v>1001304197608</v>
-      </c>
-      <c r="C466" t="s">
-        <v>779</v>
+        <v>695</v>
+      </c>
+      <c r="B466" s="5">
+        <v>1001205376221</v>
+      </c>
+      <c r="C466" s="6" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
-        <v>708</v>
+        <v>479</v>
       </c>
       <c r="B467" s="3">
         <v>1001304197608</v>
@@ -7998,7 +8049,7 @@
     </row>
     <row r="468" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
-        <v>697</v>
+        <v>708</v>
       </c>
       <c r="B468" s="3">
         <v>1001304197608</v>
@@ -8009,7 +8060,7 @@
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
-        <v>797</v>
+        <v>697</v>
       </c>
       <c r="B469" s="3">
         <v>1001304197608</v>
@@ -8020,29 +8071,29 @@
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
-        <v>698</v>
-      </c>
-      <c r="B470" s="5">
-        <v>1001010106325</v>
-      </c>
-      <c r="C470" s="6" t="s">
-        <v>49</v>
+        <v>797</v>
+      </c>
+      <c r="B470" s="3">
+        <v>1001304197608</v>
+      </c>
+      <c r="C470" t="s">
+        <v>779</v>
       </c>
     </row>
     <row r="471" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="B471" s="5">
-        <v>1001013957231</v>
+        <v>1001010106325</v>
       </c>
       <c r="C471" s="6" t="s">
-        <v>705</v>
+        <v>49</v>
       </c>
     </row>
     <row r="472" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
-        <v>699</v>
+        <v>709</v>
       </c>
       <c r="B472" s="5">
         <v>1001013957231</v>
@@ -8053,18 +8104,18 @@
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B473" s="3">
-        <v>1001220286279</v>
-      </c>
-      <c r="C473" t="s">
-        <v>45</v>
+        <v>699</v>
+      </c>
+      <c r="B473" s="5">
+        <v>1001013957231</v>
+      </c>
+      <c r="C473" s="6" t="s">
+        <v>705</v>
       </c>
     </row>
     <row r="474" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
-        <v>715</v>
+        <v>44</v>
       </c>
       <c r="B474" s="3">
         <v>1001220286279</v>
@@ -8075,29 +8126,29 @@
     </row>
     <row r="475" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="B475" s="5">
+        <v>715</v>
+      </c>
+      <c r="B475" s="3">
         <v>1001220286279</v>
       </c>
-      <c r="C475" s="6" t="s">
+      <c r="C475" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
-        <v>710</v>
+        <v>700</v>
       </c>
       <c r="B476" s="5">
-        <v>1001223297092</v>
+        <v>1001220286279</v>
       </c>
       <c r="C476" s="6" t="s">
-        <v>706</v>
+        <v>45</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
-        <v>701</v>
+        <v>710</v>
       </c>
       <c r="B477" s="5">
         <v>1001223297092</v>
@@ -8108,18 +8159,18 @@
     </row>
     <row r="478" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="B478" s="3">
-        <v>1001020836724</v>
-      </c>
-      <c r="C478" t="s">
-        <v>564</v>
+        <v>701</v>
+      </c>
+      <c r="B478" s="5">
+        <v>1001223297092</v>
+      </c>
+      <c r="C478" s="6" t="s">
+        <v>706</v>
       </c>
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
-        <v>712</v>
+        <v>563</v>
       </c>
       <c r="B479" s="3">
         <v>1001020836724</v>
@@ -8130,29 +8181,29 @@
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
-        <v>702</v>
-      </c>
-      <c r="B480" s="5">
+        <v>712</v>
+      </c>
+      <c r="B480" s="3">
         <v>1001020836724</v>
       </c>
-      <c r="C480" s="6" t="s">
+      <c r="C480" t="s">
         <v>564</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
-        <v>714</v>
+        <v>702</v>
       </c>
       <c r="B481" s="5">
-        <v>1001062475707</v>
+        <v>1001020836724</v>
       </c>
       <c r="C481" s="6" t="s">
-        <v>707</v>
+        <v>564</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="B482" s="5">
         <v>1001062475707</v>
@@ -8163,40 +8214,40 @@
     </row>
     <row r="483" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B483" s="5">
-        <v>1001033856609</v>
+        <v>1001062475707</v>
       </c>
       <c r="C483" s="6" t="s">
-        <v>222</v>
+        <v>707</v>
       </c>
     </row>
     <row r="484" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B484" s="5">
+        <v>1001033856609</v>
+      </c>
+      <c r="C484" s="6" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A485" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="B484" s="3">
+      <c r="B485" s="3">
         <v>1001025767284</v>
       </c>
-      <c r="C484" s="6" t="s">
+      <c r="C485" s="6" t="s">
         <v>489</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A485" s="7" t="s">
-        <v>717</v>
-      </c>
-      <c r="B485" s="5">
-        <v>1001301777332</v>
-      </c>
-      <c r="C485" s="6" t="s">
-        <v>723</v>
       </c>
     </row>
     <row r="486" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A486" s="7" t="s">
-        <v>731</v>
+        <v>717</v>
       </c>
       <c r="B486" s="5">
         <v>1001301777332</v>
@@ -8207,18 +8258,18 @@
     </row>
     <row r="487" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A487" s="7" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B487" s="5">
-        <v>1001303987333</v>
+        <v>1001301777332</v>
       </c>
       <c r="C487" s="6" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="488" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A488" s="7" t="s">
-        <v>718</v>
+        <v>732</v>
       </c>
       <c r="B488" s="5">
         <v>1001303987333</v>
@@ -8229,29 +8280,29 @@
     </row>
     <row r="489" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A489" s="7" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B489" s="5">
-        <v>1001012426220</v>
+        <v>1001303987333</v>
       </c>
       <c r="C489" s="6" t="s">
-        <v>186</v>
+        <v>724</v>
       </c>
     </row>
     <row r="490" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A490" s="7" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="B490" s="5">
-        <v>1001300387157</v>
+        <v>1001012426220</v>
       </c>
       <c r="C490" s="6" t="s">
-        <v>725</v>
+        <v>186</v>
       </c>
     </row>
     <row r="491" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A491" s="7" t="s">
-        <v>720</v>
+        <v>730</v>
       </c>
       <c r="B491" s="5">
         <v>1001300387157</v>
@@ -8262,18 +8313,18 @@
     </row>
     <row r="492" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A492" s="7" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B492" s="5">
-        <v>1001220226208</v>
+        <v>1001300387157</v>
       </c>
       <c r="C492" s="6" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
     </row>
     <row r="493" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A493" s="7" t="s">
-        <v>728</v>
+        <v>721</v>
       </c>
       <c r="B493" s="5">
         <v>1001220226208</v>
@@ -8284,18 +8335,18 @@
     </row>
     <row r="494" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A494" s="7" t="s">
+        <v>728</v>
+      </c>
+      <c r="B494" s="5">
+        <v>1001220226208</v>
+      </c>
+      <c r="C494" s="6" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A495" s="7" t="s">
         <v>722</v>
-      </c>
-      <c r="B494" s="5">
-        <v>1001063656967</v>
-      </c>
-      <c r="C494" s="6" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A495" s="2" t="s">
-        <v>729</v>
       </c>
       <c r="B495" s="5">
         <v>1001063656967</v>
@@ -8306,40 +8357,40 @@
     </row>
     <row r="496" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
-        <v>738</v>
-      </c>
-      <c r="B496" s="3">
-        <v>1001065616832</v>
-      </c>
-      <c r="C496" t="s">
-        <v>739</v>
+        <v>729</v>
+      </c>
+      <c r="B496" s="5">
+        <v>1001063656967</v>
+      </c>
+      <c r="C496" s="6" t="s">
+        <v>727</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="B497" s="3">
-        <v>1001060677299</v>
+        <v>1001065616832</v>
       </c>
       <c r="C497" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="B498" s="3">
-        <v>1001453907612</v>
+        <v>1001060677299</v>
       </c>
       <c r="C498" t="s">
-        <v>781</v>
+        <v>741</v>
       </c>
     </row>
     <row r="499" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
-        <v>793</v>
+        <v>745</v>
       </c>
       <c r="B499" s="3">
         <v>1001453907612</v>
@@ -8350,7 +8401,7 @@
     </row>
     <row r="500" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
-        <v>746</v>
+        <v>793</v>
       </c>
       <c r="B500" s="3">
         <v>1001453907612</v>
@@ -8361,161 +8412,161 @@
     </row>
     <row r="501" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B501" s="3">
-        <v>1001015026797</v>
+        <v>1001453907612</v>
       </c>
       <c r="C501" t="s">
-        <v>748</v>
+        <v>781</v>
       </c>
     </row>
     <row r="502" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B502" s="3">
-        <v>1001095226925</v>
+        <v>1001015026797</v>
       </c>
       <c r="C502" t="s">
-        <v>788</v>
+        <v>748</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B503" s="3">
-        <v>1001035277059</v>
+        <v>1001095226925</v>
       </c>
       <c r="C503" t="s">
-        <v>751</v>
+        <v>788</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="B504" s="3">
-        <v>1001025767461</v>
+        <v>1001035277059</v>
       </c>
       <c r="C504" t="s">
-        <v>792</v>
+        <v>751</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B505" s="3">
-        <v>1001303637564</v>
+        <v>1001025767461</v>
       </c>
       <c r="C505" t="s">
-        <v>754</v>
+        <v>792</v>
       </c>
     </row>
     <row r="506" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="B506" s="3">
-        <v>1001026947371</v>
+        <v>1001303637564</v>
       </c>
       <c r="C506" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="B507" s="3">
-        <v>1001012427523</v>
+        <v>1001026947371</v>
       </c>
       <c r="C507" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="B508" s="3">
-        <v>1001022467083</v>
+        <v>1001012427523</v>
       </c>
       <c r="C508" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
     </row>
     <row r="509" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="B509" s="3">
-        <v>1001307357489</v>
+        <v>1001022467083</v>
       </c>
       <c r="C509" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
     </row>
     <row r="510" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="B510" s="3">
-        <v>1001025507271</v>
+        <v>1001307357489</v>
       </c>
       <c r="C510" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
     </row>
     <row r="511" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="B511" s="3">
-        <v>1001084856008</v>
+        <v>1001025507271</v>
       </c>
       <c r="C511" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
     </row>
     <row r="512" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="B512" s="3">
-        <v>1001200677442</v>
+        <v>1001084856008</v>
       </c>
       <c r="C512" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
     </row>
     <row r="513" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="B513" s="3">
-        <v>1001300456946</v>
+        <v>1001200677442</v>
       </c>
       <c r="C513" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="514" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
-        <v>818</v>
+        <v>776</v>
       </c>
       <c r="B514" s="3">
-        <v>1001093316411</v>
+        <v>1001300456946</v>
       </c>
       <c r="C514" t="s">
-        <v>796</v>
+        <v>777</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
-        <v>795</v>
+        <v>818</v>
       </c>
       <c r="B515" s="3">
         <v>1001093316411</v>
@@ -8526,18 +8577,18 @@
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="B516" s="3">
-        <v>1001097747647</v>
+        <v>1001093316411</v>
       </c>
       <c r="C516" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
-        <v>811</v>
+        <v>798</v>
       </c>
       <c r="B517" s="3">
         <v>1001097747647</v>
@@ -8548,18 +8599,18 @@
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
-        <v>800</v>
+        <v>811</v>
       </c>
       <c r="B518" s="3">
-        <v>1001097767651</v>
+        <v>1001097747647</v>
       </c>
       <c r="C518" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
     </row>
     <row r="519" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
-        <v>812</v>
+        <v>800</v>
       </c>
       <c r="B519" s="3">
         <v>1001097767651</v>
@@ -8570,18 +8621,18 @@
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B520" s="3">
-        <v>1001307077513</v>
+        <v>1001097767651</v>
       </c>
       <c r="C520" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
     </row>
     <row r="521" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="B521" s="3">
         <v>1001307077513</v>
@@ -8592,18 +8643,18 @@
     </row>
     <row r="522" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
       <c r="B522" s="3">
-        <v>1001307587562</v>
+        <v>1001307077513</v>
       </c>
       <c r="C522" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="523" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
-        <v>808</v>
+        <v>816</v>
       </c>
       <c r="B523" s="3">
         <v>1001307587562</v>
@@ -8614,18 +8665,18 @@
     </row>
     <row r="524" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
-        <v>815</v>
+        <v>808</v>
       </c>
       <c r="B524" s="3">
-        <v>1001307107516</v>
+        <v>1001307587562</v>
       </c>
       <c r="C524" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
-        <v>809</v>
+        <v>815</v>
       </c>
       <c r="B525" s="3">
         <v>1001307107516</v>
@@ -8636,18 +8687,18 @@
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="B526" s="3">
-        <v>1001107397485</v>
+        <v>1001307107516</v>
       </c>
       <c r="C526" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="527" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="B527" s="3">
         <v>1001107397485</v>
@@ -8656,8 +8707,107 @@
         <v>806</v>
       </c>
     </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A528" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="B528" s="3">
+        <v>1001107397485</v>
+      </c>
+      <c r="C528" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A529" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="B529" s="3">
+        <v>1001304237156</v>
+      </c>
+      <c r="C529" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A530" s="2" t="s">
+        <v>822</v>
+      </c>
+      <c r="B530" s="3">
+        <v>1001010108014</v>
+      </c>
+      <c r="C530" t="s">
+        <v>823</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A531" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="B531" s="3">
+        <v>1001010017536</v>
+      </c>
+      <c r="C531" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A532" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B532" s="3">
+        <v>1001017557514</v>
+      </c>
+      <c r="C532" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A533" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="B533" s="3">
+        <v>1001017567518</v>
+      </c>
+      <c r="C533" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A534" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B534" s="3">
+        <v>1001085476929</v>
+      </c>
+      <c r="C534" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A535" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="B535" s="3">
+        <v>1001066607626</v>
+      </c>
+      <c r="C535" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A536" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="B536" s="3">
+        <v>1001060720614</v>
+      </c>
+      <c r="C536" t="s">
+        <v>835</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C527" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
+  <autoFilter ref="A1:C532" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919C9A28-5D9F-4D83-A7F9-645E6EA01EC6}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA610BE-4E97-4118-9DFB-D249BF1F2160}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$532</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$547</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="836">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="853">
   <si>
     <t>1С</t>
   </si>
@@ -2542,6 +2542,57 @@
   </si>
   <si>
     <t>ПРАЗДНИЧНАЯ с/к в/с дек.спец.мгс</t>
+  </si>
+  <si>
+    <t>0614 ПРАЗДНИЧНАЯ с/к в/с дек.спец.мгс  Останкино</t>
+  </si>
+  <si>
+    <t>6929 КАРБОНАД ДОМАШНИЙ ПМ к/в кр/к в/у  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7156 СЕРВЕЛАТ КОПЧ.НА БУКЕ в/к в/у 0.35кг_50с  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7514 ЛЮБИТЕЛЬСКАЯ ОСТАНКИНСКАЯ вар п/о в/у  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7518 ТЕЛЯЧЬЯ ГОСТ Останкино вар п/о в/у  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>7143 БРАУНШВЕЙГСКАЯ ГОСТ с/к в/у 1/220 8шт.</t>
+  </si>
+  <si>
+    <t>БРАУНШВЕЙГСКАЯ ГОСТ с/к в/у 1/220 8шт.</t>
+  </si>
+  <si>
+    <t>САЛЯМИ ФИНСКАЯ Папа может с/к в/у 1/150</t>
+  </si>
+  <si>
+    <t>7456 САЛЯМИ ФИНСКАЯ Папа может с/к в/у 1/150</t>
+  </si>
+  <si>
+    <t>7386 БАРСЕЛОНА ПМ с/к в/у 1/150  ОСТАНКИНО</t>
+  </si>
+  <si>
+    <t>БАРСЕЛОНА ПМ с/к в/у 1/150</t>
+  </si>
+  <si>
+    <t>7710 КРАКОВСКАЯ ГОСТ п/к н/о мгс 0.3кг</t>
+  </si>
+  <si>
+    <t>КРАКОВСКАЯ ГОСТ п/к н/о мгс 0.3кг</t>
+  </si>
+  <si>
+    <t>7344 КОНСЕРВЫ МЯС.ГОВЯДИНА ТУШ. В/С 338г_ЧЗ</t>
+  </si>
+  <si>
+    <t>КОНСЕРВЫ МЯС.ГОВЯДИНА ТУШ. В/С 338г_ЧЗ</t>
+  </si>
+  <si>
+    <t>7345 КОНСЕРВЫ МЯС.СВИНИНА ТУШ. В/С 325г_ЧЗ</t>
+  </si>
+  <si>
+    <t>КОНСЕРВЫ МЯС.СВИНИНА ТУШ. В/С 325г_ЧЗ</t>
   </si>
 </sst>
 </file>
@@ -2898,7 +2949,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F536"/>
+  <dimension ref="A1:F547"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" style="2" customWidth="1"/>
@@ -8720,7 +8771,7 @@
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
-        <v>820</v>
+        <v>838</v>
       </c>
       <c r="B529" s="3">
         <v>1001304237156</v>
@@ -8731,83 +8782,204 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B530" s="3">
-        <v>1001010108014</v>
+        <v>1001304237156</v>
       </c>
       <c r="C530" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B531" s="3">
-        <v>1001010017536</v>
+        <v>1001010108014</v>
       </c>
       <c r="C531" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B532" s="3">
-        <v>1001017557514</v>
+        <v>1001010017536</v>
       </c>
       <c r="C532" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
-        <v>828</v>
+        <v>839</v>
       </c>
       <c r="B533" s="3">
-        <v>1001017567518</v>
+        <v>1001017557514</v>
       </c>
       <c r="C533" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
       <c r="B534" s="3">
-        <v>1001085476929</v>
+        <v>1001017557514</v>
       </c>
       <c r="C534" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
-        <v>832</v>
+        <v>840</v>
       </c>
       <c r="B535" s="3">
-        <v>1001066607626</v>
+        <v>1001017567518</v>
       </c>
       <c r="C535" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="B536" s="3">
+        <v>1001017567518</v>
+      </c>
+      <c r="C536" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A537" s="2" t="s">
+        <v>837</v>
+      </c>
+      <c r="B537" s="3">
+        <v>1001085476929</v>
+      </c>
+      <c r="C537" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A538" s="2" t="s">
+        <v>830</v>
+      </c>
+      <c r="B538" s="3">
+        <v>1001085476929</v>
+      </c>
+      <c r="C538" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A539" s="2" t="s">
+        <v>832</v>
+      </c>
+      <c r="B539" s="3">
+        <v>1001066607626</v>
+      </c>
+      <c r="C539" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A540" s="2" t="s">
         <v>834</v>
       </c>
-      <c r="B536" s="3">
+      <c r="B540" s="3">
         <v>1001060720614</v>
       </c>
-      <c r="C536" t="s">
+      <c r="C540" t="s">
         <v>835</v>
       </c>
     </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A541" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="B541" s="3">
+        <v>1001060720614</v>
+      </c>
+      <c r="C541" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A542" s="2" t="s">
+        <v>841</v>
+      </c>
+      <c r="B542" s="3">
+        <v>1001060717143</v>
+      </c>
+      <c r="C542" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A543" s="2" t="s">
+        <v>844</v>
+      </c>
+      <c r="B543" s="3">
+        <v>1001063097456</v>
+      </c>
+      <c r="C543" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A544" s="2" t="s">
+        <v>845</v>
+      </c>
+      <c r="B544" s="3">
+        <v>1001067017386</v>
+      </c>
+      <c r="C544" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A545" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="B545" s="3">
+        <v>1001307587710</v>
+      </c>
+      <c r="C545" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A546" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="B546" s="3">
+        <v>1001122287344</v>
+      </c>
+      <c r="C546" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A547" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="B547" s="3">
+        <v>1001123677345</v>
+      </c>
+      <c r="C547" t="s">
+        <v>852</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C532" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
+  <autoFilter ref="A1:C547" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
+++ b/в бланки заводов/Останкино КИ/ostankino_ki/NV/moduls/1С.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино КИ\ostankino_ki\NV\moduls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA610BE-4E97-4118-9DFB-D249BF1F2160}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3A6E37-333F-4714-A509-591E6D40E294}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$547</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Лист1!$A$1:$C$548</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1093" uniqueCount="853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="854">
   <si>
     <t>1С</t>
   </si>
@@ -2593,6 +2593,9 @@
   </si>
   <si>
     <t>КОНСЕРВЫ МЯС.СВИНИНА ТУШ. В/С 325г_ЧЗ</t>
+  </si>
+  <si>
+    <t>8014 ДОКТОРСКАЯ ПРЕМИУМ вар п/о(п)    ОСТАНКИНО</t>
   </si>
 </sst>
 </file>
@@ -2949,7 +2952,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F547"/>
+  <dimension ref="A1:F548"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.7109375" style="2" customWidth="1"/>
@@ -8793,7 +8796,7 @@
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
-        <v>822</v>
+        <v>853</v>
       </c>
       <c r="B531" s="3">
         <v>1001010108014</v>
@@ -8804,29 +8807,29 @@
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B532" s="3">
-        <v>1001010017536</v>
+        <v>1001010108014</v>
       </c>
       <c r="C532" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
-        <v>839</v>
+        <v>824</v>
       </c>
       <c r="B533" s="3">
-        <v>1001017557514</v>
+        <v>1001010017536</v>
       </c>
       <c r="C533" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
-        <v>826</v>
+        <v>839</v>
       </c>
       <c r="B534" s="3">
         <v>1001017557514</v>
@@ -8837,18 +8840,18 @@
     </row>
     <row r="535" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
-        <v>840</v>
+        <v>826</v>
       </c>
       <c r="B535" s="3">
-        <v>1001017567518</v>
+        <v>1001017557514</v>
       </c>
       <c r="C535" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
-        <v>828</v>
+        <v>840</v>
       </c>
       <c r="B536" s="3">
         <v>1001017567518</v>
@@ -8859,18 +8862,18 @@
     </row>
     <row r="537" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
-        <v>837</v>
+        <v>828</v>
       </c>
       <c r="B537" s="3">
-        <v>1001085476929</v>
+        <v>1001017567518</v>
       </c>
       <c r="C537" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
     </row>
     <row r="538" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="B538" s="3">
         <v>1001085476929</v>
@@ -8881,29 +8884,29 @@
     </row>
     <row r="539" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B539" s="3">
-        <v>1001066607626</v>
+        <v>1001085476929</v>
       </c>
       <c r="C539" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
     </row>
     <row r="540" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B540" s="3">
-        <v>1001060720614</v>
+        <v>1001066607626</v>
       </c>
       <c r="C540" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="B541" s="3">
         <v>1001060720614</v>
@@ -8914,72 +8917,83 @@
     </row>
     <row r="542" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="B542" s="3">
-        <v>1001060717143</v>
+        <v>1001060720614</v>
       </c>
       <c r="C542" t="s">
-        <v>842</v>
+        <v>835</v>
       </c>
     </row>
     <row r="543" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="B543" s="3">
-        <v>1001063097456</v>
+        <v>1001060717143</v>
       </c>
       <c r="C543" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="544" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="B544" s="3">
-        <v>1001067017386</v>
+        <v>1001063097456</v>
       </c>
       <c r="C544" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
     </row>
     <row r="545" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="B545" s="3">
-        <v>1001307587710</v>
+        <v>1001067017386</v>
       </c>
       <c r="C545" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
     </row>
     <row r="546" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="B546" s="3">
-        <v>1001122287344</v>
+        <v>1001307587710</v>
       </c>
       <c r="C546" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
     </row>
     <row r="547" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
+        <v>849</v>
+      </c>
+      <c r="B547" s="3">
+        <v>1001122287344</v>
+      </c>
+      <c r="C547" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A548" s="2" t="s">
         <v>851</v>
       </c>
-      <c r="B547" s="3">
+      <c r="B548" s="3">
         <v>1001123677345</v>
       </c>
-      <c r="C547" t="s">
+      <c r="C548" t="s">
         <v>852</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C547" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
+  <autoFilter ref="A1:C548" xr:uid="{B07A98A7-8665-46F4-A02B-642D1147C8E7}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
